--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R102096dbf4034fae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rd08ade5eb2bb44a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rb8bd387d19dc4bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R466326ef6cd641bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R63c855fc0e854bf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R6f1f9c5811ce4b99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rdc30ba2eccd740d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R2836c1088b7f4dc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R3bb806f3b70e40e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Re18e91d39acd42d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rfe39097f30554548"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Ref27145c00344ad6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R9995bf2f71ca4ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R20a421363e694269"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R541b79c78de344e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R0da0d5089e2f431e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -348,7 +348,7 @@
         <x:color rgb="FF17365D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAF7"/>
         </x:patternFill>
       </x:fill>
@@ -358,7 +358,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -368,7 +368,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -379,7 +379,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -436,8 +436,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DataModelSlices" displayName="DataModelSlices" ref="A4:H17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="DataModelSlices" displayName="DataModelSlices" ref="A4:H16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="App"/>
     <x:tableColumn id="2" name="Slice"/>
@@ -453,8 +452,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D345" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:D345"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D323" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="App"/>
     <x:tableColumn id="2" name="Slice"/>
@@ -713,7 +711,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Technical companion to AppSheet_Data_Model_Overview.docx</x:v>
+        <x:v>Technical companion to AppSheet_Data_Model_Overview.md</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -729,28 +727,29 @@
         <x:v>Value</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="15" hidden="0" customHeight="1">
+    <x:row r="5" ht="32" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>Conversion status</x:v>
+        <x:v>Reconciliation status</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Converted from the Word baseline; not reconciled with the live AppSheet configuration.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+        <x:v>Reconciled with OLTP production v2.200079 for charge and repayment validation rules on 2026-08-31. The OLAP structure and all 81 shared VCs remain at the reconciled 2026-08-30 baseline.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34" hidden="0" customHeight="1">
       <x:c r="A6" s="12" t="str">
-        <x:v>Source baseline</x:v>
+        <x:v>Live baselines</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>AppSheet_Data_Model_Reference.docx (2026-08-29)</x:v>
+        <x:v>OLTP v2.200079 — Loan Manager ผู้จัดการสินเชื่อ — 93844270-6aa5-420b-a960-bcdf08abd357
+OLAP v1.000151 — Loan Business Insights — e74dd368-654f-44d7-bccf-83cf361d1cdb</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="12" t="str">
-        <x:v>Conversion date</x:v>
+        <x:v>Reconciliation date</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31 (Asia/Singapore)</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -785,8 +784,7 @@
         <x:v>Slices</x:v>
       </x:c>
       <x:c r="B11" s="14" t="n">
-        <x:f>COUNTA('Slices'!A5:A100)</x:f>
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -810,7 +808,7 @@
         <x:v>Columns</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>One row per unioned column definition. This is the authoritative column-level inventory for the reference pair.</x:v>
+        <x:v>One row per unioned column definition. Shared rows follow the OLAP order; OLTP-only columns are appended where necessary.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -850,7 +848,7 @@
         <x:v>Change Log</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>Append-only record of accepted reference changes and reconciliation status.</x:v>
+        <x:v>Reserved historical worksheet. Authoritative change history is maintained in Change Logs/*.md.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -858,12 +856,12 @@
         <x:v>Maintenance rule</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>Update the technical rows first, append a Change Log entry, then revise Word only when narrative meaning or governance changes.</x:v>
+        <x:v>For every model change, update this workbook, AppSheet_Data_Model_Overview.md, and a dated Markdown file in Change Logs/.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="35" t="str">
-        <x:v>Important: this workbook was created by splitting the existing Word reference. It was not reconciled with the live AppSheet database, OLTP app, or OLAP app during conversion. Update the Change Log after reconciliation.</x:v>
+        <x:v>Shared VC baseline: 81 VCs are now used by both apps. OLAP includes the complete Last Interest Charge Date → Accrued Interest Days → Accrued Interest dependency chain; no compared shared-VC differences remain.</x:v>
       </x:c>
       <x:c r="B24" s="36"/>
       <x:c r="C24" s="36"/>
@@ -872,7 +870,9 @@
       <x:c r="F24" s="37"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="38"/>
+      <x:c r="A25" s="38" t="str">
+        <x:v>Shared VC baseline: 81 VCs are used by both apps and no compared shared-VC differences remain. OLTP financial-entry validation baseline: production v2.200079 blocks zero-value charge/repayment rows and negative principal while retaining negative-interest default adjustments.</x:v>
+      </x:c>
       <x:c r="B25" s="39"/>
       <x:c r="C25" s="39"/>
       <x:c r="D25" s="39"/>
@@ -1109,8 +1109,8 @@
       <x:c r="E11" s="57" t="str">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F11" s="57" t="str">
-        <x:v>25</x:v>
+      <x:c r="F11" s="57" t="n">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G11" s="59" t="str">
         <x:v>Loan contracts, commercial terms, lifecycle state, balances, and loan-level risk metrics.</x:v>
@@ -1215,7 +1215,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff9d2273b5c94263"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91af3f4cadd64505"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1248,7 +1248,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Union of OLTP and OLAP physical columns and virtual columns. Expressions are stored as text for auditability.</x:v>
+        <x:v>Reconciled union of OLTP and OLAP physical and virtual columns. All 81 shared VCs matched the OLTP baseline after the OLAP dependency repair on 2026-08-30. OLTP charge and repayment validation rules were reconciled to production version 2.200079 on 2026-08-31.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -1327,7 +1327,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F6" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G6" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -1353,7 +1353,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F7" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G7" s="59" t="str">
         <x:v>Stores the authoritative source value for Borrower Name.</x:v>
@@ -1379,7 +1379,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F8" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>PII</x:v>
       </x:c>
       <x:c r="G8" s="59" t="str">
         <x:v>Stores the authoritative source value for Telephone.</x:v>
@@ -1431,7 +1431,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F10" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G10" s="59" t="str">
         <x:v>Stores the source date for Creation Date.</x:v>
@@ -1645,7 +1645,7 @@
         <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
       </x:c>
       <x:c r="H18" s="59" t="str">
-        <x:v>IF( SUM( SELECT( Loans[Outstanding Principal], AND([Ref Borrowers] = [_THISROW].[Row ID], [Loan Status] = "ยังไม่ปิดยอด") ) ) &gt; 0, SUM( SELECT( Loans[Total Interest Received], AND([Ref Borrowers] = [_THISROW].[Row ID], [Loan Status] = "ยังไม่ปิดยอด") ) ) / SUM( SELECT( Loans[Outstanding Principal], AND([Ref Borrowers] = [_THISROW].[Row ID], [Loan Status] = "ยังไม่ปิดยอด") ) ), 0)</x:v>
+        <x:v>IF([Total Outstanding Principal] &gt; 0, [Active Loan Interest Earned] / [Total Outstanding Principal], 0)</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -2087,7 +2087,7 @@
         <x:v>Derived business-state or risk indicator.</x:v>
       </x:c>
       <x:c r="H35" s="59" t="str">
-        <x:v>IFS( COUNT([Todays Collection Charges]) = 0, "", COUNT( SELECT( Charges[Row ID], AND( IN([Row ID], [_THISROW].[Todays Collection Charges]), [Charge Date] &lt; TODAY(), [Payment Status] &lt;&gt; "ชำระแล้ว" ) ) ) &gt; 0, "Overdue", COUNT( SELECT( Charges[Row ID], AND( IN([Row ID], [_THISROW].[Todays Collection Charges]), [Payment Status] &lt;&gt; "ชำระแล้ว" ) ) ) = 0, "Fully Paid", OR( COUNT( SELECT( Charges[Row ID], AND( IN([Row ID], [_THISROW].[Todays Collection Charges]), [Payment Status] = "ชำระบางส่วน" ) ) ) &gt; 0, AND( COUNT( SELECT( Charges[Row ID], AND( IN([Row ID], [_THISROW].[Todays Collection Charges]), [Payment Status] = "ชำระแล้ว" ) ) ) &gt; 0, COUNT( SELECT( Charges[Row ID], AND( IN([Row ID], [_THISROW].[Todays Collection Charges]), [Payment Status] &lt;&gt; "ชำระแล้ว" ) ) ) &gt; 0 ) ), "Partially Paid", TRUE, "Not Paid")</x:v>
+        <x:v>IFS( COUNT([Todays Collection Charges]) = 0, "", COUNT( SELECT( Charges[Row ID], AND( IN([Row ID], [_THISROW].[Todays Collection Charges]), [Charge Date] &lt; TODAY(), [Payment Status] &lt;&gt; "ชำระแล้ว" ) ) ) &gt; 0, "Overdue", AND( NOT(IN("รอชำระ", [Todays Collection Charges][Payment Status])), NOT(IN("ชำระบางส่วน", [Todays Collection Charges][Payment Status])) ), "Fully Paid", OR( IN("ชำระบางส่วน", [Todays Collection Charges][Payment Status]), AND( IN("ชำระแล้ว", [Todays Collection Charges][Payment Status]), IN("รอชำระ", [Todays Collection Charges][Payment Status]) ) ), "Partially Paid", TRUE, "Not Paid")</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -2835,7 +2835,7 @@
         <x:v>OLAP only</x:v>
       </x:c>
       <x:c r="F64" s="57" t="str">
-        <x:v>Key, Label</x:v>
+        <x:v>Key, Label, Required</x:v>
       </x:c>
       <x:c r="G64" s="59" t="str">
         <x:v>Stores the source date for Date.</x:v>
@@ -3459,7 +3459,7 @@
         <x:v>OLAP only</x:v>
       </x:c>
       <x:c r="F88" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G88" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -3485,7 +3485,7 @@
         <x:v>OLAP only</x:v>
       </x:c>
       <x:c r="F89" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G89" s="59" t="str">
         <x:v>Reference key that links this row to the configured parent table.</x:v>
@@ -3511,7 +3511,7 @@
         <x:v>OLAP only</x:v>
       </x:c>
       <x:c r="F90" s="57" t="str">
-        <x:v>Label</x:v>
+        <x:v>Label, Required</x:v>
       </x:c>
       <x:c r="G90" s="59" t="str">
         <x:v>Stores the source date for Contribution Date.</x:v>
@@ -3537,7 +3537,7 @@
         <x:v>OLAP only</x:v>
       </x:c>
       <x:c r="F91" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G91" s="59" t="str">
         <x:v>Stores the authoritative source value for Transaction Type.</x:v>
@@ -3563,7 +3563,7 @@
         <x:v>OLAP only</x:v>
       </x:c>
       <x:c r="F92" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G92" s="59" t="str">
         <x:v>Stores the financially material source value for Amount.</x:v>
@@ -3693,7 +3693,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F97" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G97" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -3745,7 +3745,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F99" s="57" t="str">
-        <x:v>Label</x:v>
+        <x:v>Label, Required</x:v>
       </x:c>
       <x:c r="G99" s="59" t="str">
         <x:v>Stores the source date for Charge Date.</x:v>
@@ -3771,13 +3771,13 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F100" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G100" s="59" t="str">
         <x:v>Stores the financially material source value for Interest Due.</x:v>
       </x:c>
       <x:c r="H100" s="59" t="str">
-        <x:v>Stored source column; initial value: 0</x:v>
+        <x:v>Stored source column; initial value: 0; OLTP Valid_If: OR([Principal Due] &lt;&gt; 0, [_THIS] &lt;&gt; 0)</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -3797,13 +3797,13 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F101" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G101" s="59" t="str">
         <x:v>Stores the financially material source value for Principal Due.</x:v>
       </x:c>
       <x:c r="H101" s="59" t="str">
-        <x:v>Stored source column; initial value: 0</x:v>
+        <x:v>Stored source column; initial value: 0; OLTP Valid_If: [_THIS] &gt;= 0</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -3956,7 +3956,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G107" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Date on which the charge became fully paid. Display name in both apps: วันที่ชำระครบ / Paid in Full Date.</x:v>
       </x:c>
       <x:c r="H107" s="59" t="str">
         <x:v>IF([Payment Status] = "ชำระแล้ว", MAX([Related Repayments][Payment Date]), "")</x:v>
@@ -4395,7 +4395,7 @@
         <x:v>OLAP only</x:v>
       </x:c>
       <x:c r="F124" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G124" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -4993,7 +4993,7 @@
         <x:v>OLAP only</x:v>
       </x:c>
       <x:c r="F147" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G147" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -5565,7 +5565,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F169" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G169" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -5591,7 +5591,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F170" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>OLTP: Required; OLAP: -</x:v>
       </x:c>
       <x:c r="G170" s="59" t="str">
         <x:v>Stores the source date for Loan Date.</x:v>
@@ -5643,7 +5643,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F172" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>OLTP: Required; OLAP: -</x:v>
       </x:c>
       <x:c r="G172" s="59" t="str">
         <x:v>Stores the financially material source value for Principal Amount.</x:v>
@@ -5747,7 +5747,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F176" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>OLTP: Required; OLAP: -</x:v>
       </x:c>
       <x:c r="G176" s="59" t="str">
         <x:v>Stores the controlled workflow state for Loan Status.</x:v>
@@ -5799,7 +5799,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F178" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>OLTP: Required; OLAP: -</x:v>
       </x:c>
       <x:c r="G178" s="59" t="str">
         <x:v>Stores the authoritative source value for Loan Type.</x:v>
@@ -6530,11 +6530,10 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G206" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Closed-loan duration in calendar days, based on Close Date and inclusive of the Loan Date.</x:v>
       </x:c>
       <x:c r="H206" s="59" t="str">
-        <x:v>OLTP: IF( ISNOTBLANK([Close Date]), FLOOR(TOTALHOURS([Close Date] - [Loan Date]) / 24) + 1, "")
-OLAP: IF(ISNOTBLANK([Loan End Date]), TOTALHOURS([Loan End Date] - [Loan Date]) / 24 + 1, "")</x:v>
+        <x:v>IF( ISNOTBLANK([Close Date]), FLOOR(TOTALHOURS([Close Date] - [Loan Date]) / 24) + 1, "")</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -6681,13 +6680,13 @@
         <x:v>VC / Date</x:v>
       </x:c>
       <x:c r="E212" s="57" t="str">
-        <x:v>OLTP only</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F212" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Searchable</x:v>
       </x:c>
       <x:c r="G212" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Latest related Charge Date; the lower boundary for calculating uncharged daily-interest accrual.</x:v>
       </x:c>
       <x:c r="H212" s="59" t="str">
         <x:v>MAX([Related Charges][Charge Date])</x:v>
@@ -6707,13 +6706,13 @@
         <x:v>VC / Number</x:v>
       </x:c>
       <x:c r="E213" s="57" t="str">
-        <x:v>OLTP only</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F213" s="57" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="G213" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Elapsed accrual days since Last Interest Charge Date, or since Loan Date when no interest charge exists.</x:v>
       </x:c>
       <x:c r="H213" s="59" t="str">
         <x:v>IF( ISBLANK([Last Interest Charge Date]), TOTALHOURS(TODAY() - [Loan Date])/24, TOTALHOURS(TODAY() - [Last Interest Charge Date])/24)</x:v>
@@ -6733,13 +6732,13 @@
         <x:v>VC / Price</x:v>
       </x:c>
       <x:c r="E214" s="57" t="str">
-        <x:v>OLTP only</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F214" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Show_If: [Loan Type] = "ดอกเบี้ยรายวัน"</x:v>
       </x:c>
       <x:c r="G214" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
+        <x:v>Uncharged interest for a daily-interest loan, calculated from Current Daily Interest and Accrued Interest Days.</x:v>
       </x:c>
       <x:c r="H214" s="59" t="str">
         <x:v>IF( [Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest] * [Accrued Interest Days], 0)</x:v>
@@ -6788,7 +6787,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F216" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G216" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -6814,7 +6813,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F217" s="57" t="str">
-        <x:v>Label</x:v>
+        <x:v>OLTP: Label; OLAP: Label, Required</x:v>
       </x:c>
       <x:c r="G217" s="59" t="str">
         <x:v>Stores the authoritative source value for Partner Name.</x:v>
@@ -6840,7 +6839,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F218" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>OLTP: -; OLAP: Required</x:v>
       </x:c>
       <x:c r="G218" s="59" t="str">
         <x:v>Stores the authoritative source value for Partner Role.</x:v>
@@ -6866,7 +6865,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F219" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>OLTP: PII; OLAP: Required</x:v>
       </x:c>
       <x:c r="G219" s="59" t="str">
         <x:v>Stores the authoritative source value for Email.</x:v>
@@ -7230,7 +7229,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F233" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G233" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -7256,7 +7255,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F234" s="57" t="str">
-        <x:v>Label</x:v>
+        <x:v>Label, Required</x:v>
       </x:c>
       <x:c r="G234" s="59" t="str">
         <x:v>Stores the source date for Payment Date.</x:v>
@@ -7265,7 +7264,7 @@
         <x:v>Stored source column; initial value: TODAY()</x:v>
       </x:c>
     </x:row>
-    <x:row r="235" ht="15" hidden="0" customHeight="1">
+    <x:row r="235" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A235" s="57" t="str">
         <x:v>Repayments</x:v>
       </x:c>
@@ -7282,16 +7281,16 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F235" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G235" s="59" t="str">
         <x:v>Stores the financially material source value for Principal Paid.</x:v>
       </x:c>
       <x:c r="H235" s="59" t="str">
-        <x:v>Stored source column; initial value: 0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="236" ht="15" hidden="0" customHeight="1">
+        <x:v>Stored source column; initial value: 0; OLTP Valid_If: AND( [_THIS] &gt;= 0, [_THIS] &lt;= ( [Ref Charges].[Principal Due] - SUM( SELECT( Repayments[Principal Paid], AND( [Ref Charges] = [_THISROW].[Ref Charges], [Row ID] &lt;&gt; [_THISROW].[Row ID] ) ) ) ))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A236" s="57" t="str">
         <x:v>Repayments</x:v>
       </x:c>
@@ -7308,13 +7307,13 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F236" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G236" s="59" t="str">
         <x:v>Stores the financially material source value for Interest Paid.</x:v>
       </x:c>
       <x:c r="H236" s="59" t="str">
-        <x:v>Stored source column; initial value: 0</x:v>
+        <x:v>Stored source column; initial value: 0; OLTP Valid_If: AND( [_THIS] &lt;= ( [Ref Charges].[Interest Due] - SUM( SELECT( Repayments[Interest Paid], AND( [Ref Charges] = [_THISROW].[Ref Charges], [Row ID] &lt;&gt; [_THISROW].[Row ID] ) ) ) ), OR([Principal Paid] &lt;&gt; 0, [_THIS] &lt;&gt; 0) )</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="15" hidden="0" customHeight="1">
@@ -7386,7 +7385,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F239" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="G239" s="59" t="str">
         <x:v>Reference key that links this row to the configured parent table.</x:v>
@@ -7412,7 +7411,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F240" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>PII</x:v>
       </x:c>
       <x:c r="G240" s="59" t="str">
         <x:v>Stores the authoritative source value for Created By.</x:v>
@@ -7802,7 +7801,7 @@
         <x:v>OLAP only</x:v>
       </x:c>
       <x:c r="F255" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G255" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -8010,7 +8009,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F263" s="57" t="str">
-        <x:v>Key</x:v>
+        <x:v>Key, Required</x:v>
       </x:c>
       <x:c r="G263" s="59" t="str">
         <x:v>Immutable row key generated by the source database.</x:v>
@@ -8322,7 +8321,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F275" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Show: FALSE</x:v>
       </x:c>
       <x:c r="G275" s="59" t="str">
         <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
@@ -8348,7 +8347,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F276" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Show: FALSE</x:v>
       </x:c>
       <x:c r="G276" s="59" t="str">
         <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
@@ -8374,7 +8373,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F277" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Show: FALSE</x:v>
       </x:c>
       <x:c r="G277" s="59" t="str">
         <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
@@ -8536,7 +8535,7 @@
         <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
       </x:c>
       <x:c r="H283" s="59" t="str">
-        <x:v>[Total Profit of Outstanding Loans] / [Outstanding Principal]</x:v>
+        <x:v>IF([Outstanding Principal] &gt; 0, [Total Profit of Outstanding Loans] / [Outstanding Principal], 0)</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="15" hidden="0" customHeight="1">
@@ -8764,7 +8763,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F292" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Show_If: COUNT( SELECT( Borrowers[Row ID], [Daily Collection Status] = "Fully Paid" )) &gt; 0; Searchable</x:v>
       </x:c>
       <x:c r="G292" s="59" t="str">
         <x:v>Derived AppSheet value used by the app workflow, presentation, or reporting model.</x:v>
@@ -8790,7 +8789,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F293" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Show_If: COUNT( SELECT( Borrowers[Row ID], [Daily Collection Status] = "Partially Paid" )) &gt; 0; Searchable</x:v>
       </x:c>
       <x:c r="G293" s="59" t="str">
         <x:v>Derived AppSheet value used by the app workflow, presentation, or reporting model.</x:v>
@@ -8816,7 +8815,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F294" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Show_If: COUNT( SELECT( Borrowers[Row ID], [Daily Collection Status] = "Overdue" )) &gt; 0; Searchable</x:v>
       </x:c>
       <x:c r="G294" s="59" t="str">
         <x:v>Derived AppSheet value used by the app workflow, presentation, or reporting model.</x:v>
@@ -8842,7 +8841,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F295" s="57" t="str">
-        <x:v>-</x:v>
+        <x:v>Show_If: COUNT( SELECT( Borrowers[Row ID], [Daily Collection Status] = "Not Paid" )) &gt; 0; Searchable</x:v>
       </x:c>
       <x:c r="G295" s="59" t="str">
         <x:v>Derived AppSheet value used by the app workflow, presentation, or reporting model.</x:v>
@@ -8992,7 +8991,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98574bc939ae407f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R957e96f52c0e43f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9019,7 +9018,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Direct Ref relationships converted from the Word baseline; confirm against AppSheet during reconciliation.</x:v>
+        <x:v>Direct Ref targets and Is a part of? settings reconciled with both live AppSheet editors on 2026-08-30.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -9186,7 +9185,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R950db783859f4a11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13f99eda3db64f3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9219,7 +9218,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Slice filters, update permissions, purposes, and included-column counts.</x:v>
+        <x:v>Live slice filters, update permissions, purposes, and included-column counts reconciled on 2026-08-30.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -9277,44 +9276,44 @@
       <x:c r="G5" s="58" t="str">
         <x:v>Read-only borrower workboard restricted to borrowers with a current collection status.</x:v>
       </x:c>
-      <x:c r="H5" s="58" t="str"/>
+      <x:c r="H5" s="58"/>
     </x:row>
     <x:row r="6" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A6" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B6" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C6" s="57" t="str">
-        <x:v>Charges</x:v>
+        <x:v>Borrowers</x:v>
       </x:c>
       <x:c r="D6" s="59" t="str">
-        <x:v>OR(  [Payment Status] = "รอชำระ",  [Payment Status] = "ชำระบางส่วน",  AND(    [Payment Status] = "ชำระแล้ว",    [Payment Date] = TODAY()  ))</x:v>
+        <x:v>[Total Outstanding Principal] &gt; 0</x:v>
       </x:c>
       <x:c r="E6" s="57" t="str">
-        <x:v>Updates, Adds, Deletes</x:v>
+        <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F6" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="59" t="str">
-        <x:v>Operational charge queue containing pending or partially paid items plus items completed today.</x:v>
-      </x:c>
-      <x:c r="H6" s="59" t="str"/>
+        <x:v>Read-only OLAP subset of borrowers whose outstanding principal is greater than zero.</x:v>
+      </x:c>
+      <x:c r="H6" s="59"/>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B7" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C7" s="57" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
       <x:c r="D7" s="59" t="str">
-        <x:v>[Total Outstanding Principal] &gt; 0</x:v>
+        <x:v>[Profit Last 30 Days] &gt; 0</x:v>
       </x:c>
       <x:c r="E7" s="57" t="str">
         <x:v>Read-only</x:v>
@@ -9323,43 +9322,43 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="G7" s="59" t="str">
-        <x:v>Read-only OLAP subset of borrowers whose outstanding principal is greater than zero.</x:v>
-      </x:c>
-      <x:c r="H7" s="59" t="str"/>
+        <x:v>Read-only OLAP subset of borrowers contributing positive interest profit in the last 30 days.</x:v>
+      </x:c>
+      <x:c r="H7" s="59"/>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B8" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C8" s="57" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
       <x:c r="D8" s="59" t="str">
-        <x:v>[Profit Last 30 Days] &gt; 0</x:v>
+        <x:v>TRUE</x:v>
       </x:c>
       <x:c r="E8" s="57" t="str">
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F8" s="57" t="n">
-        <x:v>56</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G8" s="59" t="str">
-        <x:v>Read-only OLAP subset of borrowers contributing positive interest profit in the last 30 days.</x:v>
-      </x:c>
-      <x:c r="H8" s="59" t="str"/>
+        <x:v>Curated, read-only borrower feed for downstream reporting and dashboard reconciliation.</x:v>
+      </x:c>
+      <x:c r="H8" s="59"/>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B9" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C9" s="57" t="str">
-        <x:v>Borrowers</x:v>
+        <x:v>Charges</x:v>
       </x:c>
       <x:c r="D9" s="59" t="str">
         <x:v>TRUE</x:v>
@@ -9368,49 +9367,49 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F9" s="57" t="n">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="59" t="str">
-        <x:v>Curated, read-only borrower feed for downstream reporting and dashboard reconciliation.</x:v>
-      </x:c>
-      <x:c r="H9" s="59" t="str"/>
+        <x:v>Curated, read-only charge feed with due, paid, remaining, lateness, and borrower fields.</x:v>
+      </x:c>
+      <x:c r="H9" s="59"/>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B10" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C10" s="57" t="str">
-        <x:v>Charges</x:v>
+        <x:v>Daily Analytics</x:v>
       </x:c>
       <x:c r="D10" s="59" t="str">
-        <x:v>TRUE</x:v>
+        <x:v>[Snapshot Date] &gt;= NOW() - 7</x:v>
       </x:c>
       <x:c r="E10" s="57" t="str">
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F10" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G10" s="59" t="str">
-        <x:v>Curated, read-only charge feed with due, paid, remaining, lateness, and borrower fields.</x:v>
-      </x:c>
-      <x:c r="H10" s="59" t="str"/>
+        <x:v>Rolling seven-day daily-analytics window for recent trend analysis.</x:v>
+      </x:c>
+      <x:c r="H10" s="59"/>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B11" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C11" s="57" t="str">
         <x:v>Daily Analytics</x:v>
       </x:c>
       <x:c r="D11" s="59" t="str">
-        <x:v>[Snapshot Date] &gt;= NOW() - 7</x:v>
+        <x:v>[Snapshot Date] &gt;= NOW() - 30</x:v>
       </x:c>
       <x:c r="E11" s="57" t="str">
         <x:v>Read-only</x:v>
@@ -9419,22 +9418,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G11" s="59" t="str">
-        <x:v>Rolling seven-day daily-analytics window for recent trend analysis.</x:v>
-      </x:c>
-      <x:c r="H11" s="59" t="str"/>
+        <x:v>Rolling 30-day daily-analytics window for monthly and near-term trend analysis.</x:v>
+      </x:c>
+      <x:c r="H11" s="59"/>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B12" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C12" s="57" t="str">
         <x:v>Daily Analytics</x:v>
       </x:c>
       <x:c r="D12" s="59" t="str">
-        <x:v>[Snapshot Date] &gt;= NOW() - 30</x:v>
+        <x:v>[Snapshot Date] &gt;= NOW() - 90</x:v>
       </x:c>
       <x:c r="E12" s="57" t="str">
         <x:v>Read-only</x:v>
@@ -9443,43 +9442,43 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="G12" s="59" t="str">
-        <x:v>Rolling 30-day daily-analytics window for monthly and near-term trend analysis.</x:v>
-      </x:c>
-      <x:c r="H12" s="59" t="str"/>
+        <x:v>Rolling 90-day daily-analytics window for medium-term portfolio trends.</x:v>
+      </x:c>
+      <x:c r="H12" s="59"/>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B13" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C13" s="57" t="str">
         <x:v>Daily Analytics</x:v>
       </x:c>
       <x:c r="D13" s="59" t="str">
-        <x:v>[Snapshot Date] &gt;= NOW() - 90</x:v>
+        <x:v>TRUE</x:v>
       </x:c>
       <x:c r="E13" s="57" t="str">
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F13" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G13" s="59" t="str">
-        <x:v>Rolling 90-day daily-analytics window for medium-term portfolio trends.</x:v>
-      </x:c>
-      <x:c r="H13" s="59" t="str"/>
+        <x:v>Curated, read-only daily snapshot feed for governed downstream reporting.</x:v>
+      </x:c>
+      <x:c r="H13" s="59"/>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B14" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C14" s="57" t="str">
-        <x:v>Daily Analytics</x:v>
+        <x:v>Loans</x:v>
       </x:c>
       <x:c r="D14" s="59" t="str">
         <x:v>TRUE</x:v>
@@ -9488,22 +9487,22 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F14" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G14" s="59" t="str">
-        <x:v>Curated, read-only daily snapshot feed for governed downstream reporting.</x:v>
-      </x:c>
-      <x:c r="H14" s="59" t="str"/>
+        <x:v>Curated, read-only loan feed containing contract, balance, rate, age, and default fields.</x:v>
+      </x:c>
+      <x:c r="H14" s="59"/>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B15" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Repayments</x:v>
       </x:c>
       <x:c r="C15" s="57" t="str">
-        <x:v>Loans</x:v>
+        <x:v>Repayments</x:v>
       </x:c>
       <x:c r="D15" s="59" t="str">
         <x:v>TRUE</x:v>
@@ -9512,22 +9511,22 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F15" s="57" t="n">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G15" s="59" t="str">
-        <x:v>Curated, read-only loan feed containing contract, balance, rate, age, and default fields.</x:v>
-      </x:c>
-      <x:c r="H15" s="59" t="str"/>
+        <x:v>Curated, read-only posted-payment feed with loan and charge references.</x:v>
+      </x:c>
+      <x:c r="H15" s="59"/>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B16" s="59" t="str">
-        <x:v>Reporting Repayments</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C16" s="57" t="str">
-        <x:v>Repayments</x:v>
+        <x:v>Statistics</x:v>
       </x:c>
       <x:c r="D16" s="59" t="str">
         <x:v>TRUE</x:v>
@@ -9536,36 +9535,22 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F16" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G16" s="59" t="str">
-        <x:v>Curated, read-only posted-payment feed with loan and charge references.</x:v>
-      </x:c>
-      <x:c r="H16" s="59" t="str"/>
+        <x:v>Curated, read-only KPI feed for governed dashboard totals.</x:v>
+      </x:c>
+      <x:c r="H16" s="59"/>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B17" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C17" s="57" t="str">
-        <x:v>Statistics</x:v>
-      </x:c>
-      <x:c r="D17" s="59" t="str">
-        <x:v>TRUE</x:v>
-      </x:c>
-      <x:c r="E17" s="57" t="str">
-        <x:v>Read-only</x:v>
-      </x:c>
-      <x:c r="F17" s="57" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G17" s="59" t="str">
-        <x:v>Curated, read-only KPI feed for governed dashboard totals.</x:v>
-      </x:c>
-      <x:c r="H17" s="59" t="str"/>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -9574,7 +9559,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc016faf1829b4386"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cf256f1f5a1412d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9599,7 +9584,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>One row per included slice column. Sort by App, Slice, and Column Order to restore display order.</x:v>
+        <x:v>One row per live included slice column, preserving display order; reconciled on 2026-08-30.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -9761,10 +9746,10 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B15" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C15" s="57" t="n">
         <x:v>1</x:v>
@@ -9775,10 +9760,10 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B16" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C16" s="57" t="n">
         <x:v>2</x:v>
@@ -9789,282 +9774,282 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B17" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C17" s="57" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D17" s="59" t="str">
-        <x:v>Ref Loans</x:v>
+        <x:v>Borrower Name</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B18" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C18" s="57" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D18" s="59" t="str">
-        <x:v>Charge Date</x:v>
+        <x:v>Telephone</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B19" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C19" s="57" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D19" s="59" t="str">
-        <x:v>Interest Due</x:v>
+        <x:v>Description</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B20" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C20" s="57" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D20" s="59" t="str">
-        <x:v>Amount Due</x:v>
+        <x:v>Creation Date</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B21" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C21" s="57" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="59" t="str">
-        <x:v>Borrower Name</x:v>
+        <x:v>Related Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B22" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C22" s="57" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D22" s="59" t="str">
-        <x:v>Related Repayments</x:v>
+        <x:v>Total Interest Earned</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B23" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C23" s="57" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D23" s="59" t="str">
-        <x:v>Payment Status</x:v>
+        <x:v>Total Amount Loaned</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B24" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C24" s="57" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D24" s="59" t="str">
-        <x:v>Payment Date</x:v>
+        <x:v>Total Number of Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B25" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C25" s="57" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D25" s="59" t="str">
-        <x:v>Borrower Name TE</x:v>
+        <x:v>Total Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B26" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C26" s="57" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D26" s="59" t="str">
-        <x:v>Payment Status TE</x:v>
+        <x:v>Header - Active Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B27" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C27" s="57" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D27" s="59" t="str">
-        <x:v>Principal Paid</x:v>
+        <x:v>Borrower Name TE</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B28" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C28" s="57" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D28" s="59" t="str">
-        <x:v>Interest Paid</x:v>
+        <x:v>Return on Active Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B29" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C29" s="57" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D29" s="59" t="str">
-        <x:v>Total Paid</x:v>
+        <x:v>Profit Last 30 Days</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B30" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C30" s="57" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D30" s="59" t="str">
-        <x:v>Principal Remaining</x:v>
+        <x:v>Projected Interest Coverage Date</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B31" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C31" s="57" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D31" s="59" t="str">
-        <x:v>Interest Remaining</x:v>
+        <x:v>Active Loan Interest Earned</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B32" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C32" s="57" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D32" s="59" t="str">
-        <x:v>Amount Remaining</x:v>
+        <x:v>Active Daily Interest</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B33" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C33" s="57" t="n">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D33" s="59" t="str">
-        <x:v>Notes</x:v>
+        <x:v>Related Loan Assessments</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B34" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C34" s="57" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D34" s="59" t="str">
-        <x:v>Payment Count</x:v>
+        <x:v>Related Calendars</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B35" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C35" s="57" t="n">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D35" s="59" t="str">
-        <x:v>Days Outstanding</x:v>
+        <x:v>Closed Loan Interest Earned</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B36" s="59" t="str">
-        <x:v>Payment Collection</x:v>
+        <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C36" s="57" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D36" s="59" t="str">
-        <x:v>Principal Due</x:v>
+        <x:v>Closed Loan Principle</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
@@ -10075,10 +10060,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C37" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D37" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Has Closed Loan</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -10089,10 +10074,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C38" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D38" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>Return on Closed Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
@@ -10103,10 +10088,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C39" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D39" s="59" t="str">
-        <x:v>Borrower Name</x:v>
+        <x:v>Header - Closed Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -10117,10 +10102,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C40" s="57" t="n">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D40" s="59" t="str">
-        <x:v>Telephone</x:v>
+        <x:v>Has Active Loan</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
@@ -10131,10 +10116,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C41" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D41" s="59" t="str">
-        <x:v>Description</x:v>
+        <x:v>30D Gross Principal Days</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -10145,10 +10130,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C42" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D42" s="59" t="str">
-        <x:v>Creation Date</x:v>
+        <x:v>30D Principal Reduction Days</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
@@ -10159,10 +10144,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C43" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D43" s="59" t="str">
-        <x:v>Related Loans</x:v>
+        <x:v>30D Average Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -10173,10 +10158,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C44" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D44" s="59" t="str">
-        <x:v>Total Interest Earned</x:v>
+        <x:v>30D Return on Average Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
@@ -10187,10 +10172,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C45" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D45" s="59" t="str">
-        <x:v>Total Amount Loaned</x:v>
+        <x:v>Daily Collection Status</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -10201,10 +10186,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C46" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="59" t="str">
-        <x:v>Total Number of Loans</x:v>
+        <x:v>Todays Collection Charges</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -10215,10 +10200,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C47" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D47" s="59" t="str">
-        <x:v>Total Outstanding Principal</x:v>
+        <x:v>Todays Amount Due</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -10229,10 +10214,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C48" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D48" s="59" t="str">
-        <x:v>Header - Active Loans</x:v>
+        <x:v>Todays Amount Collected</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -10243,10 +10228,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C49" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D49" s="59" t="str">
-        <x:v>Borrower Name TE</x:v>
+        <x:v>Todays Amount Remaining</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -10257,10 +10242,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C50" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D50" s="59" t="str">
-        <x:v>Return on Active Principal</x:v>
+        <x:v>Portfolio Exposure %</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -10271,10 +10256,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C51" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D51" s="59" t="str">
-        <x:v>Profit Last 30 Days</x:v>
+        <x:v>Active Loan Count</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -10285,10 +10270,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C52" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D52" s="59" t="str">
-        <x:v>Projected Interest Coverage Date</x:v>
+        <x:v>Oldest Active Loan Age</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -10299,10 +10284,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C53" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D53" s="59" t="str">
-        <x:v>Active Loan Interest Earned</x:v>
+        <x:v>Overdue Amount</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -10313,10 +10298,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C54" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D54" s="59" t="str">
-        <x:v>Active Daily Interest</x:v>
+        <x:v>Overdue Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
@@ -10327,10 +10312,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C55" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D55" s="59" t="str">
-        <x:v>Related Loan Assessments</x:v>
+        <x:v>Historical Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
@@ -10341,10 +10326,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C56" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D56" s="59" t="str">
-        <x:v>Related Calendars</x:v>
+        <x:v>On Time Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
@@ -10355,10 +10340,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C57" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D57" s="59" t="str">
-        <x:v>Closed Loan Interest Earned</x:v>
+        <x:v>Lifetime On Time Rate</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -10369,10 +10354,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C58" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D58" s="59" t="str">
-        <x:v>Closed Loan Principle</x:v>
+        <x:v>Recent 30D Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -10383,10 +10368,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C59" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D59" s="59" t="str">
-        <x:v>Has Closed Loan</x:v>
+        <x:v>Recent 30D On Time Count</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -10397,10 +10382,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C60" s="57" t="n">
-        <x:v>24</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D60" s="59" t="str">
-        <x:v>Return on Closed Loans</x:v>
+        <x:v>Recent 30D On Time Rate</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -10411,10 +10396,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C61" s="57" t="n">
-        <x:v>25</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D61" s="59" t="str">
-        <x:v>Header - Closed Loans</x:v>
+        <x:v>Lifetime Late Payment Count</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -10425,10 +10410,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C62" s="57" t="n">
-        <x:v>26</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D62" s="59" t="str">
-        <x:v>Has Active Loan</x:v>
+        <x:v>Recent 30D Late Payment Count</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
@@ -10439,10 +10424,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C63" s="57" t="n">
-        <x:v>27</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D63" s="59" t="str">
-        <x:v>30D Gross Principal Days</x:v>
+        <x:v>Maximum Days Late</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
@@ -10453,10 +10438,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C64" s="57" t="n">
-        <x:v>28</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D64" s="59" t="str">
-        <x:v>30D Principal Reduction Days</x:v>
+        <x:v>Last Late Payment Date</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
@@ -10467,10 +10452,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C65" s="57" t="n">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D65" s="59" t="str">
-        <x:v>30D Average Outstanding Principal</x:v>
+        <x:v>Largest Successful Loan</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -10481,10 +10466,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C66" s="57" t="n">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D66" s="59" t="str">
-        <x:v>30D Return on Average Principal</x:v>
+        <x:v>Average Successful Loan Size</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -10495,10 +10480,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C67" s="57" t="n">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D67" s="59" t="str">
-        <x:v>Daily Collection Status</x:v>
+        <x:v>Default Count</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -10509,10 +10494,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C68" s="57" t="n">
-        <x:v>32</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D68" s="59" t="str">
-        <x:v>Todays Collection Charges</x:v>
+        <x:v>Lifetime Default Loss</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -10523,10 +10508,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C69" s="57" t="n">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D69" s="59" t="str">
-        <x:v>Todays Amount Due</x:v>
+        <x:v>Portfolio Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -10537,10 +10522,10 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C70" s="57" t="n">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D70" s="59" t="str">
-        <x:v>Todays Amount Collected</x:v>
+        <x:v>Portfolio Share Join Key</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -10548,13 +10533,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B71" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C71" s="57" t="n">
-        <x:v>35</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D71" s="59" t="str">
-        <x:v>Todays Amount Remaining</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -10562,13 +10547,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B72" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C72" s="57" t="n">
-        <x:v>36</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D72" s="59" t="str">
-        <x:v>Portfolio Exposure %</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -10576,13 +10561,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B73" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C73" s="57" t="n">
-        <x:v>37</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D73" s="59" t="str">
-        <x:v>Active Loan Count</x:v>
+        <x:v>Borrower Name</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -10590,13 +10575,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B74" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C74" s="57" t="n">
-        <x:v>38</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D74" s="59" t="str">
-        <x:v>Oldest Active Loan Age</x:v>
+        <x:v>Telephone</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -10604,13 +10589,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B75" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C75" s="57" t="n">
-        <x:v>39</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D75" s="59" t="str">
-        <x:v>Overdue Amount</x:v>
+        <x:v>Description</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -10618,13 +10603,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B76" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C76" s="57" t="n">
-        <x:v>40</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D76" s="59" t="str">
-        <x:v>Overdue Charge Count</x:v>
+        <x:v>Creation Date</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -10632,13 +10617,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B77" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C77" s="57" t="n">
-        <x:v>41</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D77" s="59" t="str">
-        <x:v>Historical Charge Count</x:v>
+        <x:v>Related Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
@@ -10646,13 +10631,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B78" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C78" s="57" t="n">
-        <x:v>42</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D78" s="59" t="str">
-        <x:v>On Time Charge Count</x:v>
+        <x:v>Total Interest Earned</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
@@ -10660,13 +10645,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B79" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C79" s="57" t="n">
-        <x:v>43</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D79" s="59" t="str">
-        <x:v>Lifetime On Time Rate</x:v>
+        <x:v>Total Amount Loaned</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
@@ -10674,13 +10659,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B80" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C80" s="57" t="n">
-        <x:v>44</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D80" s="59" t="str">
-        <x:v>Recent 30D Charge Count</x:v>
+        <x:v>Total Number of Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
@@ -10688,13 +10673,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B81" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C81" s="57" t="n">
-        <x:v>45</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D81" s="59" t="str">
-        <x:v>Recent 30D On Time Count</x:v>
+        <x:v>Total Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
@@ -10702,13 +10687,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B82" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C82" s="57" t="n">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D82" s="59" t="str">
-        <x:v>Recent 30D On Time Rate</x:v>
+        <x:v>Header - Active Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
@@ -10716,13 +10701,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B83" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C83" s="57" t="n">
-        <x:v>47</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D83" s="59" t="str">
-        <x:v>Lifetime Late Payment Count</x:v>
+        <x:v>Borrower Name TE</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
@@ -10730,13 +10715,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B84" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C84" s="57" t="n">
-        <x:v>48</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D84" s="59" t="str">
-        <x:v>Recent 30D Late Payment Count</x:v>
+        <x:v>Return on Active Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
@@ -10744,13 +10729,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B85" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C85" s="57" t="n">
-        <x:v>49</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D85" s="59" t="str">
-        <x:v>Maximum Days Late</x:v>
+        <x:v>Profit Last 30 Days</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
@@ -10758,13 +10743,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B86" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C86" s="57" t="n">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D86" s="59" t="str">
-        <x:v>Last Late Payment Date</x:v>
+        <x:v>Projected Interest Coverage Date</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
@@ -10772,13 +10757,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B87" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C87" s="57" t="n">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D87" s="59" t="str">
-        <x:v>Largest Successful Loan</x:v>
+        <x:v>Active Loan Interest Earned</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="15" hidden="0" customHeight="1">
@@ -10786,13 +10771,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B88" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C88" s="57" t="n">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D88" s="59" t="str">
-        <x:v>Average Successful Loan Size</x:v>
+        <x:v>Active Daily Interest</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="15" hidden="0" customHeight="1">
@@ -10800,13 +10785,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B89" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C89" s="57" t="n">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D89" s="59" t="str">
-        <x:v>Default Count</x:v>
+        <x:v>Related Loan Assessments</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="15" hidden="0" customHeight="1">
@@ -10814,13 +10799,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B90" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C90" s="57" t="n">
-        <x:v>54</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D90" s="59" t="str">
-        <x:v>Lifetime Default Loss</x:v>
+        <x:v>Related Calendars</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="15" hidden="0" customHeight="1">
@@ -10828,13 +10813,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B91" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C91" s="57" t="n">
-        <x:v>55</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D91" s="59" t="str">
-        <x:v>Portfolio Outstanding Principal</x:v>
+        <x:v>Closed Loan Interest Earned</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="15" hidden="0" customHeight="1">
@@ -10842,13 +10827,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B92" s="59" t="str">
-        <x:v>Borrowers with Outstanding Loans</x:v>
+        <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C92" s="57" t="n">
-        <x:v>56</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D92" s="59" t="str">
-        <x:v>Portfolio Share Join Key</x:v>
+        <x:v>Closed Loan Principle</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="15" hidden="0" customHeight="1">
@@ -10859,10 +10844,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C93" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D93" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Has Closed Loan</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
@@ -10873,10 +10858,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C94" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D94" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>Return on Closed Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
@@ -10887,10 +10872,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C95" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D95" s="59" t="str">
-        <x:v>Borrower Name</x:v>
+        <x:v>Header - Closed Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
@@ -10901,10 +10886,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C96" s="57" t="n">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D96" s="59" t="str">
-        <x:v>Telephone</x:v>
+        <x:v>Has Active Loan</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
@@ -10915,10 +10900,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C97" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D97" s="59" t="str">
-        <x:v>Description</x:v>
+        <x:v>30D Gross Principal Days</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
@@ -10929,10 +10914,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C98" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D98" s="59" t="str">
-        <x:v>Creation Date</x:v>
+        <x:v>30D Principal Reduction Days</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
@@ -10943,10 +10928,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C99" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D99" s="59" t="str">
-        <x:v>Related Loans</x:v>
+        <x:v>30D Average Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
@@ -10957,10 +10942,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C100" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D100" s="59" t="str">
-        <x:v>Total Interest Earned</x:v>
+        <x:v>30D Return on Average Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
@@ -10971,10 +10956,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C101" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D101" s="59" t="str">
-        <x:v>Total Amount Loaned</x:v>
+        <x:v>Daily Collection Status</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
@@ -10985,10 +10970,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C102" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D102" s="59" t="str">
-        <x:v>Total Number of Loans</x:v>
+        <x:v>Todays Collection Charges</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
@@ -10999,10 +10984,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C103" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D103" s="59" t="str">
-        <x:v>Total Outstanding Principal</x:v>
+        <x:v>Todays Amount Due</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
@@ -11013,10 +10998,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C104" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D104" s="59" t="str">
-        <x:v>Header - Active Loans</x:v>
+        <x:v>Todays Amount Collected</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
@@ -11027,10 +11012,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C105" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D105" s="59" t="str">
-        <x:v>Borrower Name TE</x:v>
+        <x:v>Todays Amount Remaining</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
@@ -11041,10 +11026,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C106" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D106" s="59" t="str">
-        <x:v>Return on Active Principal</x:v>
+        <x:v>Portfolio Exposure %</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
@@ -11055,10 +11040,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C107" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D107" s="59" t="str">
-        <x:v>Profit Last 30 Days</x:v>
+        <x:v>Active Loan Count</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
@@ -11069,10 +11054,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C108" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D108" s="59" t="str">
-        <x:v>Projected Interest Coverage Date</x:v>
+        <x:v>Oldest Active Loan Age</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
@@ -11083,10 +11068,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C109" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D109" s="59" t="str">
-        <x:v>Active Loan Interest Earned</x:v>
+        <x:v>Overdue Amount</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="15" hidden="0" customHeight="1">
@@ -11097,10 +11082,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C110" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D110" s="59" t="str">
-        <x:v>Active Daily Interest</x:v>
+        <x:v>Overdue Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="15" hidden="0" customHeight="1">
@@ -11111,10 +11096,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C111" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D111" s="59" t="str">
-        <x:v>Related Loan Assessments</x:v>
+        <x:v>Historical Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="15" hidden="0" customHeight="1">
@@ -11125,10 +11110,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C112" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D112" s="59" t="str">
-        <x:v>Related Calendars</x:v>
+        <x:v>On Time Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
@@ -11139,10 +11124,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C113" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D113" s="59" t="str">
-        <x:v>Closed Loan Interest Earned</x:v>
+        <x:v>Lifetime On Time Rate</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
@@ -11153,10 +11138,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C114" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D114" s="59" t="str">
-        <x:v>Closed Loan Principle</x:v>
+        <x:v>Recent 30D Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
@@ -11167,10 +11152,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C115" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D115" s="59" t="str">
-        <x:v>Has Closed Loan</x:v>
+        <x:v>Recent 30D On Time Count</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
@@ -11181,10 +11166,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C116" s="57" t="n">
-        <x:v>24</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D116" s="59" t="str">
-        <x:v>Return on Closed Loans</x:v>
+        <x:v>Recent 30D On Time Rate</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -11195,10 +11180,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C117" s="57" t="n">
-        <x:v>25</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D117" s="59" t="str">
-        <x:v>Header - Closed Loans</x:v>
+        <x:v>Lifetime Late Payment Count</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -11209,10 +11194,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C118" s="57" t="n">
-        <x:v>26</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D118" s="59" t="str">
-        <x:v>Has Active Loan</x:v>
+        <x:v>Recent 30D Late Payment Count</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -11223,10 +11208,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C119" s="57" t="n">
-        <x:v>27</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D119" s="59" t="str">
-        <x:v>30D Gross Principal Days</x:v>
+        <x:v>Maximum Days Late</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -11237,10 +11222,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C120" s="57" t="n">
-        <x:v>28</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D120" s="59" t="str">
-        <x:v>30D Principal Reduction Days</x:v>
+        <x:v>Last Late Payment Date</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -11251,10 +11236,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C121" s="57" t="n">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D121" s="59" t="str">
-        <x:v>30D Average Outstanding Principal</x:v>
+        <x:v>Largest Successful Loan</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -11265,10 +11250,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C122" s="57" t="n">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D122" s="59" t="str">
-        <x:v>30D Return on Average Principal</x:v>
+        <x:v>Average Successful Loan Size</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -11279,10 +11264,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C123" s="57" t="n">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D123" s="59" t="str">
-        <x:v>Daily Collection Status</x:v>
+        <x:v>Default Count</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -11293,10 +11278,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C124" s="57" t="n">
-        <x:v>32</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D124" s="59" t="str">
-        <x:v>Todays Collection Charges</x:v>
+        <x:v>Lifetime Default Loss</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -11307,10 +11292,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C125" s="57" t="n">
-        <x:v>33</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D125" s="59" t="str">
-        <x:v>Todays Amount Due</x:v>
+        <x:v>Portfolio Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -11321,10 +11306,10 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C126" s="57" t="n">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D126" s="59" t="str">
-        <x:v>Todays Amount Collected</x:v>
+        <x:v>Portfolio Share Join Key</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -11332,13 +11317,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B127" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C127" s="57" t="n">
-        <x:v>35</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D127" s="59" t="str">
-        <x:v>Todays Amount Remaining</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -11346,13 +11331,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B128" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C128" s="57" t="n">
-        <x:v>36</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D128" s="59" t="str">
-        <x:v>Portfolio Exposure %</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -11360,13 +11345,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B129" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C129" s="57" t="n">
-        <x:v>37</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D129" s="59" t="str">
-        <x:v>Active Loan Count</x:v>
+        <x:v>Borrower Name</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
@@ -11374,13 +11359,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B130" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C130" s="57" t="n">
-        <x:v>38</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D130" s="59" t="str">
-        <x:v>Oldest Active Loan Age</x:v>
+        <x:v>Borrower Name TE</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -11388,13 +11373,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B131" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C131" s="57" t="n">
-        <x:v>39</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D131" s="59" t="str">
-        <x:v>Overdue Amount</x:v>
+        <x:v>Description</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -11402,13 +11387,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B132" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C132" s="57" t="n">
-        <x:v>40</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D132" s="59" t="str">
-        <x:v>Overdue Charge Count</x:v>
+        <x:v>Total Interest Earned</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -11416,13 +11401,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B133" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C133" s="57" t="n">
-        <x:v>41</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D133" s="59" t="str">
-        <x:v>Historical Charge Count</x:v>
+        <x:v>Total Amount Loaned</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -11430,13 +11415,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B134" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C134" s="57" t="n">
-        <x:v>42</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D134" s="59" t="str">
-        <x:v>On Time Charge Count</x:v>
+        <x:v>Total Number of Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -11444,13 +11429,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B135" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C135" s="57" t="n">
-        <x:v>43</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D135" s="59" t="str">
-        <x:v>Lifetime On Time Rate</x:v>
+        <x:v>Total Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -11458,13 +11443,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B136" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C136" s="57" t="n">
-        <x:v>44</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D136" s="59" t="str">
-        <x:v>Recent 30D Charge Count</x:v>
+        <x:v>Daily Collection Status</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
@@ -11472,13 +11457,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B137" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C137" s="57" t="n">
-        <x:v>45</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D137" s="59" t="str">
-        <x:v>Recent 30D On Time Count</x:v>
+        <x:v>Todays Amount Due</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -11486,13 +11471,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B138" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C138" s="57" t="n">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D138" s="59" t="str">
-        <x:v>Recent 30D On Time Rate</x:v>
+        <x:v>Todays Amount Collected</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
@@ -11500,13 +11485,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B139" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C139" s="57" t="n">
-        <x:v>47</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D139" s="59" t="str">
-        <x:v>Lifetime Late Payment Count</x:v>
+        <x:v>Todays Amount Remaining</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -11514,13 +11499,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B140" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C140" s="57" t="n">
-        <x:v>48</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D140" s="59" t="str">
-        <x:v>Recent 30D Late Payment Count</x:v>
+        <x:v>30D Return on Average Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -11528,13 +11513,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B141" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C141" s="57" t="n">
-        <x:v>49</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D141" s="59" t="str">
-        <x:v>Maximum Days Late</x:v>
+        <x:v>Return on Active Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -11542,13 +11527,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B142" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C142" s="57" t="n">
-        <x:v>50</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D142" s="59" t="str">
-        <x:v>Last Late Payment Date</x:v>
+        <x:v>30D Average Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -11556,13 +11541,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B143" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C143" s="57" t="n">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D143" s="59" t="str">
-        <x:v>Largest Successful Loan</x:v>
+        <x:v>Profit Last 30 Days</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -11570,13 +11555,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B144" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C144" s="57" t="n">
-        <x:v>52</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D144" s="59" t="str">
-        <x:v>Average Successful Loan Size</x:v>
+        <x:v>Has Active Loan</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -11584,13 +11569,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B145" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C145" s="57" t="n">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D145" s="59" t="str">
-        <x:v>Default Count</x:v>
+        <x:v>Has Closed Loan</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -11598,13 +11583,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B146" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C146" s="57" t="n">
-        <x:v>54</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D146" s="59" t="str">
-        <x:v>Lifetime Default Loss</x:v>
+        <x:v>Overdue Amount</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -11612,13 +11597,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B147" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C147" s="57" t="n">
-        <x:v>55</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D147" s="59" t="str">
-        <x:v>Portfolio Outstanding Principal</x:v>
+        <x:v>Overdue Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -11626,13 +11611,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B148" s="59" t="str">
-        <x:v>Profit Contribution 30D</x:v>
+        <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C148" s="57" t="n">
-        <x:v>56</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D148" s="59" t="str">
-        <x:v>Portfolio Share Join Key</x:v>
+        <x:v>Oldest Active Loan Age</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -11643,10 +11628,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C149" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D149" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Active Loan Count</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -11657,10 +11642,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C150" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D150" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>Portfolio Exposure %</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -11671,10 +11656,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C151" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D151" s="59" t="str">
-        <x:v>Borrower Name</x:v>
+        <x:v>Historical Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -11685,10 +11670,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C152" s="57" t="n">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D152" s="59" t="str">
-        <x:v>Borrower Name TE</x:v>
+        <x:v>On Time Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -11699,10 +11684,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C153" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D153" s="59" t="str">
-        <x:v>Description</x:v>
+        <x:v>Lifetime On Time Rate</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -11713,10 +11698,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C154" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D154" s="59" t="str">
-        <x:v>Total Interest Earned</x:v>
+        <x:v>Recent 30D Charge Count</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -11727,10 +11712,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C155" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D155" s="59" t="str">
-        <x:v>Total Amount Loaned</x:v>
+        <x:v>Recent 30D On Time Count</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -11741,10 +11726,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C156" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D156" s="59" t="str">
-        <x:v>Total Number of Loans</x:v>
+        <x:v>Recent 30D On Time Rate</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -11755,10 +11740,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C157" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D157" s="59" t="str">
-        <x:v>Total Outstanding Principal</x:v>
+        <x:v>Lifetime Late Payment Count</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -11769,10 +11754,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C158" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D158" s="59" t="str">
-        <x:v>Daily Collection Status</x:v>
+        <x:v>Recent 30D Late Payment Count</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -11783,10 +11768,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C159" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D159" s="59" t="str">
-        <x:v>Todays Amount Due</x:v>
+        <x:v>Maximum Days Late</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -11797,10 +11782,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C160" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D160" s="59" t="str">
-        <x:v>Todays Amount Collected</x:v>
+        <x:v>Last Late Payment Date</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -11811,10 +11796,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C161" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D161" s="59" t="str">
-        <x:v>Todays Amount Remaining</x:v>
+        <x:v>Largest Successful Loan</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -11825,10 +11810,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C162" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D162" s="59" t="str">
-        <x:v>30D Return on Average Principal</x:v>
+        <x:v>Average Successful Loan Size</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -11839,10 +11824,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C163" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D163" s="59" t="str">
-        <x:v>Return on Active Principal</x:v>
+        <x:v>Default Count</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -11853,10 +11838,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C164" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D164" s="59" t="str">
-        <x:v>30D Average Outstanding Principal</x:v>
+        <x:v>Lifetime Default Loss</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -11867,10 +11852,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C165" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D165" s="59" t="str">
-        <x:v>Profit Last 30 Days</x:v>
+        <x:v>Portfolio Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -11881,10 +11866,10 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C166" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D166" s="59" t="str">
-        <x:v>Has Active Loan</x:v>
+        <x:v>Portfolio Share Join Key</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -11892,13 +11877,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B167" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C167" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D167" s="59" t="str">
-        <x:v>Has Closed Loan</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
@@ -11906,13 +11891,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B168" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C168" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D168" s="59" t="str">
-        <x:v>Overdue Amount</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -11920,13 +11905,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B169" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C169" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D169" s="59" t="str">
-        <x:v>Overdue Charge Count</x:v>
+        <x:v>Ref Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -11934,13 +11919,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B170" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C170" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D170" s="59" t="str">
-        <x:v>Oldest Active Loan Age</x:v>
+        <x:v>Charge Date</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -11948,13 +11933,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B171" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C171" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D171" s="59" t="str">
-        <x:v>Active Loan Count</x:v>
+        <x:v>Interest Due</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -11962,13 +11947,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B172" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C172" s="57" t="n">
-        <x:v>24</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D172" s="59" t="str">
-        <x:v>Portfolio Exposure %</x:v>
+        <x:v>Principal Due</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -11976,13 +11961,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B173" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C173" s="57" t="n">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D173" s="59" t="str">
-        <x:v>Historical Charge Count</x:v>
+        <x:v>Amount Due</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -11990,13 +11975,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B174" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C174" s="57" t="n">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D174" s="59" t="str">
-        <x:v>On Time Charge Count</x:v>
+        <x:v>Payment Date</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -12004,13 +11989,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B175" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C175" s="57" t="n">
-        <x:v>27</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D175" s="59" t="str">
-        <x:v>Lifetime On Time Rate</x:v>
+        <x:v>Payment Status TE</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -12018,13 +12003,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B176" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C176" s="57" t="n">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D176" s="59" t="str">
-        <x:v>Recent 30D Charge Count</x:v>
+        <x:v>Principal Paid</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -12032,13 +12017,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B177" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C177" s="57" t="n">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D177" s="59" t="str">
-        <x:v>Recent 30D On Time Count</x:v>
+        <x:v>Interest Paid</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
@@ -12046,13 +12031,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B178" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C178" s="57" t="n">
-        <x:v>30</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D178" s="59" t="str">
-        <x:v>Recent 30D On Time Rate</x:v>
+        <x:v>Total Paid</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -12060,13 +12045,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B179" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C179" s="57" t="n">
-        <x:v>31</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D179" s="59" t="str">
-        <x:v>Lifetime Late Payment Count</x:v>
+        <x:v>Principal Remaining</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
@@ -12074,13 +12059,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B180" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C180" s="57" t="n">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D180" s="59" t="str">
-        <x:v>Recent 30D Late Payment Count</x:v>
+        <x:v>Interest Remaining</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -12088,13 +12073,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B181" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C181" s="57" t="n">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D181" s="59" t="str">
-        <x:v>Maximum Days Late</x:v>
+        <x:v>Amount Remaining</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -12102,13 +12087,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B182" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C182" s="57" t="n">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D182" s="59" t="str">
-        <x:v>Last Late Payment Date</x:v>
+        <x:v>Payment Status</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
@@ -12116,13 +12101,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B183" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C183" s="57" t="n">
-        <x:v>35</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D183" s="59" t="str">
-        <x:v>Largest Successful Loan</x:v>
+        <x:v>Days Late</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
@@ -12130,13 +12115,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B184" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C184" s="57" t="n">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D184" s="59" t="str">
-        <x:v>Average Successful Loan Size</x:v>
+        <x:v>Historical On Time</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="15" hidden="0" customHeight="1">
@@ -12144,13 +12129,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B185" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C185" s="57" t="n">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D185" s="59" t="str">
-        <x:v>Default Count</x:v>
+        <x:v>Historical Late</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" hidden="0" customHeight="1">
@@ -12158,13 +12143,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B186" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Reporting Charges</x:v>
       </x:c>
       <x:c r="C186" s="57" t="n">
-        <x:v>38</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D186" s="59" t="str">
-        <x:v>Lifetime Default Loss</x:v>
+        <x:v>Borrower Name</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="15" hidden="0" customHeight="1">
@@ -12172,13 +12157,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B187" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C187" s="57" t="n">
-        <x:v>39</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D187" s="59" t="str">
-        <x:v>Portfolio Outstanding Principal</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
@@ -12186,13 +12171,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B188" s="59" t="str">
-        <x:v>Reporting Borrowers</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C188" s="57" t="n">
-        <x:v>40</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D188" s="59" t="str">
-        <x:v>Portfolio Share Join Key</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
@@ -12200,13 +12185,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B189" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C189" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D189" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Snapshot Date</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="15" hidden="0" customHeight="1">
@@ -12214,13 +12199,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B190" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C190" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D190" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>Generated At</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
@@ -12228,13 +12213,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B191" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C191" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D191" s="59" t="str">
-        <x:v>Ref Loans</x:v>
+        <x:v>Model Version</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -12242,13 +12227,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B192" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C192" s="57" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D192" s="59" t="str">
-        <x:v>Charge Date</x:v>
+        <x:v>Principal Issued</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -12256,13 +12241,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B193" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C193" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D193" s="59" t="str">
-        <x:v>Interest Due</x:v>
+        <x:v>Loans Issued</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -12270,13 +12255,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B194" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C194" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D194" s="59" t="str">
-        <x:v>Principal Due</x:v>
+        <x:v>Principal Returned</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -12284,13 +12269,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B195" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C195" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D195" s="59" t="str">
-        <x:v>Amount Due</x:v>
+        <x:v>Interest Received</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -12298,13 +12283,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B196" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C196" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D196" s="59" t="str">
-        <x:v>Payment Date</x:v>
+        <x:v>Repayments Count</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -12312,13 +12297,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B197" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C197" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D197" s="59" t="str">
-        <x:v>Payment Status TE</x:v>
+        <x:v>Outstanding Principal EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -12326,13 +12311,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B198" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C198" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D198" s="59" t="str">
-        <x:v>Principal Paid</x:v>
+        <x:v>Active Loans EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -12340,13 +12325,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B199" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C199" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D199" s="59" t="str">
-        <x:v>Interest Paid</x:v>
+        <x:v>Active Borrowers EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -12354,13 +12339,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B200" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C200" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D200" s="59" t="str">
-        <x:v>Total Paid</x:v>
+        <x:v>Pending Charges EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -12368,13 +12353,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B201" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C201" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D201" s="59" t="str">
-        <x:v>Principal Remaining</x:v>
+        <x:v>Total Cash Pool EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -12382,13 +12367,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B202" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C202" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D202" s="59" t="str">
-        <x:v>Interest Remaining</x:v>
+        <x:v>Available Cash EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -12396,13 +12381,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B203" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C203" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D203" s="59" t="str">
-        <x:v>Amount Remaining</x:v>
+        <x:v>Unsettled Profit EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -12410,13 +12395,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B204" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C204" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D204" s="59" t="str">
-        <x:v>Payment Status</x:v>
+        <x:v>Week</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -12424,13 +12409,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B205" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C205" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D205" s="59" t="str">
-        <x:v>Days Late</x:v>
+        <x:v>Month</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -12438,13 +12423,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B206" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C206" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D206" s="59" t="str">
-        <x:v>Historical On Time</x:v>
+        <x:v>Daily Capital Employed</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -12452,13 +12437,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B207" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C207" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D207" s="59" t="str">
-        <x:v>Historical Late</x:v>
+        <x:v>Daily Capital Yield</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -12466,13 +12451,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B208" s="59" t="str">
-        <x:v>Reporting Charges</x:v>
+        <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C208" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D208" s="59" t="str">
-        <x:v>Borrower Name</x:v>
+        <x:v>Portfolio Share Join Key</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -12483,10 +12468,10 @@
         <x:v>Daily Analytics 7 Days</x:v>
       </x:c>
       <x:c r="C209" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D209" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Portfolio Slice</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -12494,13 +12479,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B210" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C210" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D210" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="15" hidden="0" customHeight="1">
@@ -12508,13 +12493,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B211" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C211" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D211" s="59" t="str">
-        <x:v>Snapshot Date</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
@@ -12522,13 +12507,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B212" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C212" s="57" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D212" s="59" t="str">
-        <x:v>Generated At</x:v>
+        <x:v>Snapshot Date</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="15" hidden="0" customHeight="1">
@@ -12536,13 +12521,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B213" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C213" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D213" s="59" t="str">
-        <x:v>Model Version</x:v>
+        <x:v>Generated At</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
@@ -12550,13 +12535,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B214" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C214" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D214" s="59" t="str">
-        <x:v>Principal Issued</x:v>
+        <x:v>Model Version</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="15" hidden="0" customHeight="1">
@@ -12564,13 +12549,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B215" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C215" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D215" s="59" t="str">
-        <x:v>Loans Issued</x:v>
+        <x:v>Principal Issued</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
@@ -12578,13 +12563,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B216" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C216" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D216" s="59" t="str">
-        <x:v>Principal Returned</x:v>
+        <x:v>Loans Issued</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="15" hidden="0" customHeight="1">
@@ -12592,13 +12577,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B217" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C217" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D217" s="59" t="str">
-        <x:v>Interest Received</x:v>
+        <x:v>Principal Returned</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="15" hidden="0" customHeight="1">
@@ -12606,13 +12591,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B218" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C218" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D218" s="59" t="str">
-        <x:v>Repayments Count</x:v>
+        <x:v>Interest Received</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="15" hidden="0" customHeight="1">
@@ -12620,13 +12605,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B219" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C219" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D219" s="59" t="str">
-        <x:v>Outstanding Principal EOD</x:v>
+        <x:v>Repayments Count</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="15" hidden="0" customHeight="1">
@@ -12634,13 +12619,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B220" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C220" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D220" s="59" t="str">
-        <x:v>Active Loans EOD</x:v>
+        <x:v>Outstanding Principal EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="15" hidden="0" customHeight="1">
@@ -12648,13 +12633,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B221" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C221" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D221" s="59" t="str">
-        <x:v>Active Borrowers EOD</x:v>
+        <x:v>Active Loans EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="15" hidden="0" customHeight="1">
@@ -12662,13 +12647,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B222" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C222" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D222" s="59" t="str">
-        <x:v>Pending Charges EOD</x:v>
+        <x:v>Active Borrowers EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="15" hidden="0" customHeight="1">
@@ -12676,13 +12661,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B223" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C223" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D223" s="59" t="str">
-        <x:v>Total Cash Pool EOD</x:v>
+        <x:v>Pending Charges EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="15" hidden="0" customHeight="1">
@@ -12690,13 +12675,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B224" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C224" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D224" s="59" t="str">
-        <x:v>Available Cash EOD</x:v>
+        <x:v>Total Cash Pool EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="15" hidden="0" customHeight="1">
@@ -12704,13 +12689,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B225" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C225" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D225" s="59" t="str">
-        <x:v>Unsettled Profit EOD</x:v>
+        <x:v>Available Cash EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="15" hidden="0" customHeight="1">
@@ -12718,13 +12703,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B226" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C226" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D226" s="59" t="str">
-        <x:v>Week</x:v>
+        <x:v>Unsettled Profit EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="15" hidden="0" customHeight="1">
@@ -12732,13 +12717,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B227" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C227" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D227" s="59" t="str">
-        <x:v>Month</x:v>
+        <x:v>Week</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="15" hidden="0" customHeight="1">
@@ -12746,13 +12731,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B228" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C228" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D228" s="59" t="str">
-        <x:v>Daily Capital Employed</x:v>
+        <x:v>Month</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="15" hidden="0" customHeight="1">
@@ -12760,13 +12745,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B229" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C229" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D229" s="59" t="str">
-        <x:v>Daily Capital Yield</x:v>
+        <x:v>Daily Capital Employed</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="15" hidden="0" customHeight="1">
@@ -12774,13 +12759,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B230" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C230" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D230" s="59" t="str">
-        <x:v>Portfolio Share Join Key</x:v>
+        <x:v>Daily Capital Yield</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="15" hidden="0" customHeight="1">
@@ -12788,13 +12773,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B231" s="59" t="str">
-        <x:v>Daily Analytics 7 Days</x:v>
+        <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C231" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D231" s="59" t="str">
-        <x:v>Portfolio Slice</x:v>
+        <x:v>Portfolio Share Join Key</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="15" hidden="0" customHeight="1">
@@ -12805,10 +12790,10 @@
         <x:v>Daily Analytics 30 Days</x:v>
       </x:c>
       <x:c r="C232" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D232" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Portfolio Slice</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="15" hidden="0" customHeight="1">
@@ -12816,13 +12801,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B233" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C233" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D233" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="15" hidden="0" customHeight="1">
@@ -12830,13 +12815,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B234" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C234" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D234" s="59" t="str">
-        <x:v>Snapshot Date</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="15" hidden="0" customHeight="1">
@@ -12844,13 +12829,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B235" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C235" s="57" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D235" s="59" t="str">
-        <x:v>Generated At</x:v>
+        <x:v>Snapshot Date</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="15" hidden="0" customHeight="1">
@@ -12858,13 +12843,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B236" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C236" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D236" s="59" t="str">
-        <x:v>Model Version</x:v>
+        <x:v>Generated At</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="15" hidden="0" customHeight="1">
@@ -12872,13 +12857,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B237" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C237" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D237" s="59" t="str">
-        <x:v>Principal Issued</x:v>
+        <x:v>Model Version</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="15" hidden="0" customHeight="1">
@@ -12886,13 +12871,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B238" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C238" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D238" s="59" t="str">
-        <x:v>Loans Issued</x:v>
+        <x:v>Principal Issued</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="15" hidden="0" customHeight="1">
@@ -12900,13 +12885,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B239" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C239" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D239" s="59" t="str">
-        <x:v>Principal Returned</x:v>
+        <x:v>Loans Issued</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="15" hidden="0" customHeight="1">
@@ -12914,13 +12899,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B240" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C240" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D240" s="59" t="str">
-        <x:v>Interest Received</x:v>
+        <x:v>Principal Returned</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="15" hidden="0" customHeight="1">
@@ -12928,13 +12913,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B241" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C241" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D241" s="59" t="str">
-        <x:v>Repayments Count</x:v>
+        <x:v>Interest Received</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="15" hidden="0" customHeight="1">
@@ -12942,13 +12927,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B242" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C242" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D242" s="59" t="str">
-        <x:v>Outstanding Principal EOD</x:v>
+        <x:v>Repayments Count</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="15" hidden="0" customHeight="1">
@@ -12956,13 +12941,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B243" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C243" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D243" s="59" t="str">
-        <x:v>Active Loans EOD</x:v>
+        <x:v>Outstanding Principal EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="15" hidden="0" customHeight="1">
@@ -12970,13 +12955,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B244" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C244" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D244" s="59" t="str">
-        <x:v>Active Borrowers EOD</x:v>
+        <x:v>Active Loans EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="15" hidden="0" customHeight="1">
@@ -12984,13 +12969,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B245" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C245" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D245" s="59" t="str">
-        <x:v>Pending Charges EOD</x:v>
+        <x:v>Active Borrowers EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="246" ht="15" hidden="0" customHeight="1">
@@ -12998,13 +12983,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B246" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C246" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D246" s="59" t="str">
-        <x:v>Total Cash Pool EOD</x:v>
+        <x:v>Pending Charges EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="247" ht="15" hidden="0" customHeight="1">
@@ -13012,13 +12997,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B247" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C247" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D247" s="59" t="str">
-        <x:v>Available Cash EOD</x:v>
+        <x:v>Total Cash Pool EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="248" ht="15" hidden="0" customHeight="1">
@@ -13026,13 +13011,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B248" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C248" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D248" s="59" t="str">
-        <x:v>Unsettled Profit EOD</x:v>
+        <x:v>Available Cash EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="249" ht="15" hidden="0" customHeight="1">
@@ -13040,13 +13025,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B249" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C249" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D249" s="59" t="str">
-        <x:v>Week</x:v>
+        <x:v>Unsettled Profit EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="250" ht="15" hidden="0" customHeight="1">
@@ -13054,13 +13039,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B250" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C250" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D250" s="59" t="str">
-        <x:v>Month</x:v>
+        <x:v>Week</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="15" hidden="0" customHeight="1">
@@ -13068,13 +13053,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B251" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C251" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D251" s="59" t="str">
-        <x:v>Daily Capital Employed</x:v>
+        <x:v>Month</x:v>
       </x:c>
     </x:row>
     <x:row r="252" ht="15" hidden="0" customHeight="1">
@@ -13082,13 +13067,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B252" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C252" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D252" s="59" t="str">
-        <x:v>Daily Capital Yield</x:v>
+        <x:v>Daily Capital Employed</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="15" hidden="0" customHeight="1">
@@ -13096,13 +13081,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B253" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C253" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D253" s="59" t="str">
-        <x:v>Portfolio Share Join Key</x:v>
+        <x:v>Daily Capital Yield</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="15" hidden="0" customHeight="1">
@@ -13110,13 +13095,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B254" s="59" t="str">
-        <x:v>Daily Analytics 30 Days</x:v>
+        <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C254" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D254" s="59" t="str">
-        <x:v>Portfolio Slice</x:v>
+        <x:v>Portfolio Share Join Key</x:v>
       </x:c>
     </x:row>
     <x:row r="255" ht="15" hidden="0" customHeight="1">
@@ -13127,10 +13112,10 @@
         <x:v>Daily Analytics 90 Days</x:v>
       </x:c>
       <x:c r="C255" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D255" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Portfolio Slice</x:v>
       </x:c>
     </x:row>
     <x:row r="256" ht="15" hidden="0" customHeight="1">
@@ -13138,13 +13123,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B256" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C256" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D256" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="257" ht="15" hidden="0" customHeight="1">
@@ -13152,13 +13137,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B257" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C257" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D257" s="59" t="str">
-        <x:v>Snapshot Date</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="258" ht="15" hidden="0" customHeight="1">
@@ -13166,13 +13151,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B258" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C258" s="57" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D258" s="59" t="str">
-        <x:v>Generated At</x:v>
+        <x:v>Snapshot Date</x:v>
       </x:c>
     </x:row>
     <x:row r="259" ht="15" hidden="0" customHeight="1">
@@ -13180,13 +13165,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B259" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C259" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D259" s="59" t="str">
-        <x:v>Model Version</x:v>
+        <x:v>Principal Issued</x:v>
       </x:c>
     </x:row>
     <x:row r="260" ht="15" hidden="0" customHeight="1">
@@ -13194,13 +13179,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B260" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C260" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D260" s="59" t="str">
-        <x:v>Principal Issued</x:v>
+        <x:v>Principal Returned</x:v>
       </x:c>
     </x:row>
     <x:row r="261" ht="15" hidden="0" customHeight="1">
@@ -13208,13 +13193,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B261" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C261" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D261" s="59" t="str">
-        <x:v>Loans Issued</x:v>
+        <x:v>Interest Received</x:v>
       </x:c>
     </x:row>
     <x:row r="262" ht="15" hidden="0" customHeight="1">
@@ -13222,13 +13207,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B262" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C262" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D262" s="59" t="str">
-        <x:v>Principal Returned</x:v>
+        <x:v>Outstanding Principal EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="263" ht="15" hidden="0" customHeight="1">
@@ -13236,13 +13221,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B263" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C263" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D263" s="59" t="str">
-        <x:v>Interest Received</x:v>
+        <x:v>Active Loans EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="264" ht="15" hidden="0" customHeight="1">
@@ -13250,13 +13235,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B264" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C264" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D264" s="59" t="str">
-        <x:v>Repayments Count</x:v>
+        <x:v>Active Borrowers EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="265" ht="15" hidden="0" customHeight="1">
@@ -13264,13 +13249,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B265" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C265" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D265" s="59" t="str">
-        <x:v>Outstanding Principal EOD</x:v>
+        <x:v>Pending Charges EOD</x:v>
       </x:c>
     </x:row>
     <x:row r="266" ht="15" hidden="0" customHeight="1">
@@ -13278,13 +13263,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B266" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C266" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D266" s="59" t="str">
-        <x:v>Active Loans EOD</x:v>
+        <x:v>Daily Capital Yield</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="15" hidden="0" customHeight="1">
@@ -13292,13 +13277,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B267" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C267" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D267" s="59" t="str">
-        <x:v>Active Borrowers EOD</x:v>
+        <x:v>Portfolio Share Join Key</x:v>
       </x:c>
     </x:row>
     <x:row r="268" ht="15" hidden="0" customHeight="1">
@@ -13306,13 +13291,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B268" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Daily Analytics</x:v>
       </x:c>
       <x:c r="C268" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D268" s="59" t="str">
-        <x:v>Pending Charges EOD</x:v>
+        <x:v>Portfolio Slice</x:v>
       </x:c>
     </x:row>
     <x:row r="269" ht="15" hidden="0" customHeight="1">
@@ -13320,13 +13305,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B269" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C269" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D269" s="59" t="str">
-        <x:v>Total Cash Pool EOD</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="270" ht="15" hidden="0" customHeight="1">
@@ -13334,13 +13319,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B270" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C270" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D270" s="59" t="str">
-        <x:v>Available Cash EOD</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="271" ht="15" hidden="0" customHeight="1">
@@ -13348,13 +13333,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B271" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C271" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D271" s="59" t="str">
-        <x:v>Unsettled Profit EOD</x:v>
+        <x:v>Loan Date</x:v>
       </x:c>
     </x:row>
     <x:row r="272" ht="15" hidden="0" customHeight="1">
@@ -13362,13 +13347,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B272" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C272" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D272" s="59" t="str">
-        <x:v>Week</x:v>
+        <x:v>Close Date</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="15" hidden="0" customHeight="1">
@@ -13376,13 +13361,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B273" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C273" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D273" s="59" t="str">
-        <x:v>Month</x:v>
+        <x:v>Principal Amount</x:v>
       </x:c>
     </x:row>
     <x:row r="274" ht="15" hidden="0" customHeight="1">
@@ -13390,13 +13375,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B274" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C274" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D274" s="59" t="str">
-        <x:v>Daily Capital Employed</x:v>
+        <x:v>Due Date</x:v>
       </x:c>
     </x:row>
     <x:row r="275" ht="15" hidden="0" customHeight="1">
@@ -13404,13 +13389,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B275" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C275" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D275" s="59" t="str">
-        <x:v>Daily Capital Yield</x:v>
+        <x:v>Ref Borrowers</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="15" hidden="0" customHeight="1">
@@ -13418,13 +13403,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B276" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C276" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D276" s="59" t="str">
-        <x:v>Portfolio Share Join Key</x:v>
+        <x:v>Total Interest Received</x:v>
       </x:c>
     </x:row>
     <x:row r="277" ht="15" hidden="0" customHeight="1">
@@ -13432,13 +13417,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B277" s="59" t="str">
-        <x:v>Daily Analytics 90 Days</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C277" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D277" s="59" t="str">
-        <x:v>Portfolio Slice</x:v>
+        <x:v>Total Principal Received</x:v>
       </x:c>
     </x:row>
     <x:row r="278" ht="15" hidden="0" customHeight="1">
@@ -13446,13 +13431,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B278" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C278" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D278" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="15" hidden="0" customHeight="1">
@@ -13460,13 +13445,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B279" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C279" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D279" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>Total Amount Received</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="15" hidden="0" customHeight="1">
@@ -13474,13 +13459,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B280" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C280" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D280" s="59" t="str">
-        <x:v>Snapshot Date</x:v>
+        <x:v>Loan Status TE</x:v>
       </x:c>
     </x:row>
     <x:row r="281" ht="15" hidden="0" customHeight="1">
@@ -13488,13 +13473,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B281" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C281" s="57" t="n">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D281" s="59" t="str">
-        <x:v>Principal Issued</x:v>
+        <x:v>Loan Age Bucket</x:v>
       </x:c>
     </x:row>
     <x:row r="282" ht="15" hidden="0" customHeight="1">
@@ -13502,13 +13487,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B282" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C282" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D282" s="59" t="str">
-        <x:v>Principal Returned</x:v>
+        <x:v>Loan Type TE</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="15" hidden="0" customHeight="1">
@@ -13516,13 +13501,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B283" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C283" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D283" s="59" t="str">
-        <x:v>Interest Received</x:v>
+        <x:v>Loan Status</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="15" hidden="0" customHeight="1">
@@ -13530,13 +13515,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B284" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C284" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D284" s="59" t="str">
-        <x:v>Outstanding Principal EOD</x:v>
+        <x:v>Loan Type</x:v>
       </x:c>
     </x:row>
     <x:row r="285" ht="15" hidden="0" customHeight="1">
@@ -13544,13 +13529,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B285" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C285" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D285" s="59" t="str">
-        <x:v>Active Loans EOD</x:v>
+        <x:v>Current Daily Interest</x:v>
       </x:c>
     </x:row>
     <x:row r="286" ht="15" hidden="0" customHeight="1">
@@ -13558,13 +13543,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B286" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C286" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D286" s="59" t="str">
-        <x:v>Active Borrowers EOD</x:v>
+        <x:v>Fixed Interest</x:v>
       </x:c>
     </x:row>
     <x:row r="287" ht="15" hidden="0" customHeight="1">
@@ -13572,13 +13557,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B287" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C287" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D287" s="59" t="str">
-        <x:v>Pending Charges EOD</x:v>
+        <x:v>Transfer Fee</x:v>
       </x:c>
     </x:row>
     <x:row r="288" ht="15" hidden="0" customHeight="1">
@@ -13586,13 +13571,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B288" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C288" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D288" s="59" t="str">
-        <x:v>Daily Capital Yield</x:v>
+        <x:v>Interest Payment Interval</x:v>
       </x:c>
     </x:row>
     <x:row r="289" ht="15" hidden="0" customHeight="1">
@@ -13600,13 +13585,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B289" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C289" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D289" s="59" t="str">
-        <x:v>Portfolio Share Join Key</x:v>
+        <x:v>Principal Recovered by Interest %</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="15" hidden="0" customHeight="1">
@@ -13614,13 +13599,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B290" s="59" t="str">
-        <x:v>Reporting Daily Analytics</x:v>
+        <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C290" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D290" s="59" t="str">
-        <x:v>Portfolio Slice</x:v>
+        <x:v>Expected Interest This Month</x:v>
       </x:c>
     </x:row>
     <x:row r="291" ht="15" hidden="0" customHeight="1">
@@ -13631,10 +13616,10 @@
         <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C291" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D291" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Effective Daily Interest Rate</x:v>
       </x:c>
     </x:row>
     <x:row r="292" ht="15" hidden="0" customHeight="1">
@@ -13645,10 +13630,10 @@
         <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C292" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D292" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>Default Loss Amount</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="15" hidden="0" customHeight="1">
@@ -13659,10 +13644,10 @@
         <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C293" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D293" s="59" t="str">
-        <x:v>Loan Date</x:v>
+        <x:v>Defaulted Flag</x:v>
       </x:c>
     </x:row>
     <x:row r="294" ht="15" hidden="0" customHeight="1">
@@ -13673,10 +13658,10 @@
         <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C294" s="57" t="n">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D294" s="59" t="str">
-        <x:v>Close Date</x:v>
+        <x:v>Borrower Name</x:v>
       </x:c>
     </x:row>
     <x:row r="295" ht="15" hidden="0" customHeight="1">
@@ -13687,10 +13672,10 @@
         <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C295" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D295" s="59" t="str">
-        <x:v>Principal Amount</x:v>
+        <x:v>Borrower Name TE</x:v>
       </x:c>
     </x:row>
     <x:row r="296" ht="15" hidden="0" customHeight="1">
@@ -13701,10 +13686,10 @@
         <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C296" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D296" s="59" t="str">
-        <x:v>Due Date</x:v>
+        <x:v>Loan Duration</x:v>
       </x:c>
     </x:row>
     <x:row r="297" ht="15" hidden="0" customHeight="1">
@@ -13715,10 +13700,10 @@
         <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C297" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D297" s="59" t="str">
-        <x:v>Ref Borrowers</x:v>
+        <x:v>Defaulted</x:v>
       </x:c>
     </x:row>
     <x:row r="298" ht="15" hidden="0" customHeight="1">
@@ -13729,10 +13714,10 @@
         <x:v>Reporting Loans</x:v>
       </x:c>
       <x:c r="C298" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D298" s="59" t="str">
-        <x:v>Total Interest Received</x:v>
+        <x:v>Maximum Days Late</x:v>
       </x:c>
     </x:row>
     <x:row r="299" ht="15" hidden="0" customHeight="1">
@@ -13740,13 +13725,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B299" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Repayments</x:v>
       </x:c>
       <x:c r="C299" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D299" s="59" t="str">
-        <x:v>Total Principal Received</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="300" ht="15" hidden="0" customHeight="1">
@@ -13754,13 +13739,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B300" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Repayments</x:v>
       </x:c>
       <x:c r="C300" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D300" s="59" t="str">
-        <x:v>Outstanding Principal</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="301" ht="15" hidden="0" customHeight="1">
@@ -13768,13 +13753,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B301" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Repayments</x:v>
       </x:c>
       <x:c r="C301" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D301" s="59" t="str">
-        <x:v>Total Amount Received</x:v>
+        <x:v>Payment Date</x:v>
       </x:c>
     </x:row>
     <x:row r="302" ht="15" hidden="0" customHeight="1">
@@ -13782,13 +13767,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B302" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Repayments</x:v>
       </x:c>
       <x:c r="C302" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D302" s="59" t="str">
-        <x:v>Loan Status TE</x:v>
+        <x:v>Amount Received</x:v>
       </x:c>
     </x:row>
     <x:row r="303" ht="15" hidden="0" customHeight="1">
@@ -13796,13 +13781,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B303" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Repayments</x:v>
       </x:c>
       <x:c r="C303" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D303" s="59" t="str">
-        <x:v>Loan Age Bucket</x:v>
+        <x:v>Principal Paid</x:v>
       </x:c>
     </x:row>
     <x:row r="304" ht="15" hidden="0" customHeight="1">
@@ -13810,13 +13795,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B304" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Repayments</x:v>
       </x:c>
       <x:c r="C304" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D304" s="59" t="str">
-        <x:v>Loan Type TE</x:v>
+        <x:v>Interest Paid</x:v>
       </x:c>
     </x:row>
     <x:row r="305" ht="15" hidden="0" customHeight="1">
@@ -13824,13 +13809,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B305" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Repayments</x:v>
       </x:c>
       <x:c r="C305" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D305" s="59" t="str">
-        <x:v>Loan Status</x:v>
+        <x:v>Ref Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="306" ht="15" hidden="0" customHeight="1">
@@ -13838,13 +13823,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B306" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Repayments</x:v>
       </x:c>
       <x:c r="C306" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D306" s="59" t="str">
-        <x:v>Loan Type</x:v>
+        <x:v>Ref Charges</x:v>
       </x:c>
     </x:row>
     <x:row r="307" ht="15" hidden="0" customHeight="1">
@@ -13852,13 +13837,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B307" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C307" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D307" s="59" t="str">
-        <x:v>Current Daily Interest</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
     </x:row>
     <x:row r="308" ht="15" hidden="0" customHeight="1">
@@ -13866,13 +13851,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B308" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C308" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D308" s="59" t="str">
-        <x:v>Fixed Interest</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
     </x:row>
     <x:row r="309" ht="15" hidden="0" customHeight="1">
@@ -13880,13 +13865,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B309" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C309" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D309" s="59" t="str">
-        <x:v>Transfer Fee</x:v>
+        <x:v>Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="310" ht="15" hidden="0" customHeight="1">
@@ -13894,13 +13879,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B310" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C310" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D310" s="59" t="str">
-        <x:v>Interest Payment Interval</x:v>
+        <x:v>Active Loans</x:v>
       </x:c>
     </x:row>
     <x:row r="311" ht="15" hidden="0" customHeight="1">
@@ -13908,13 +13893,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B311" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C311" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D311" s="59" t="str">
-        <x:v>Principal Recovered by Interest %</x:v>
+        <x:v>Realized Profit MTD</x:v>
       </x:c>
     </x:row>
     <x:row r="312" ht="15" hidden="0" customHeight="1">
@@ -13922,13 +13907,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B312" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C312" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D312" s="59" t="str">
-        <x:v>Expected Interest This Month</x:v>
+        <x:v>Projected Monthly Profit</x:v>
       </x:c>
     </x:row>
     <x:row r="313" ht="15" hidden="0" customHeight="1">
@@ -13936,13 +13921,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B313" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C313" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D313" s="59" t="str">
-        <x:v>Effective Daily Interest Rate</x:v>
+        <x:v>Peak Cash Pool Date 30D</x:v>
       </x:c>
     </x:row>
     <x:row r="314" ht="15" hidden="0" customHeight="1">
@@ -13950,13 +13935,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B314" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C314" s="57" t="n">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D314" s="59" t="str">
-        <x:v>Default Loss Amount</x:v>
+        <x:v>Expected Daily Interest</x:v>
       </x:c>
     </x:row>
     <x:row r="315" ht="15" hidden="0" customHeight="1">
@@ -13964,13 +13949,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B315" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C315" s="57" t="n">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D315" s="59" t="str">
-        <x:v>Defaulted Flag</x:v>
+        <x:v>Total Cash Pool</x:v>
       </x:c>
     </x:row>
     <x:row r="316" ht="15" hidden="0" customHeight="1">
@@ -13978,13 +13963,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B316" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C316" s="57" t="n">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D316" s="59" t="str">
-        <x:v>Borrower Name</x:v>
+        <x:v>Total Unsettled Profit</x:v>
       </x:c>
     </x:row>
     <x:row r="317" ht="15" hidden="0" customHeight="1">
@@ -13992,13 +13977,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B317" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C317" s="57" t="n">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D317" s="59" t="str">
-        <x:v>Borrower Name TE</x:v>
+        <x:v>Expected Loan Account Balance</x:v>
       </x:c>
     </x:row>
     <x:row r="318" ht="15" hidden="0" customHeight="1">
@@ -14006,13 +13991,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B318" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C318" s="57" t="n">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D318" s="59" t="str">
-        <x:v>Loan Duration</x:v>
+        <x:v>Top 3 Borrower Concentration</x:v>
       </x:c>
     </x:row>
     <x:row r="319" ht="15" hidden="0" customHeight="1">
@@ -14020,13 +14005,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B319" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C319" s="57" t="n">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D319" s="59" t="str">
-        <x:v>Defaulted</x:v>
+        <x:v>Amount Due Today</x:v>
       </x:c>
     </x:row>
     <x:row r="320" ht="15" hidden="0" customHeight="1">
@@ -14034,13 +14019,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B320" s="59" t="str">
-        <x:v>Reporting Loans</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C320" s="57" t="n">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D320" s="59" t="str">
-        <x:v>Maximum Days Late</x:v>
+        <x:v>Amount Collected Today</x:v>
       </x:c>
     </x:row>
     <x:row r="321" ht="15" hidden="0" customHeight="1">
@@ -14048,13 +14033,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B321" s="59" t="str">
-        <x:v>Reporting Repayments</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C321" s="57" t="n">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D321" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Amount Outstanding Today</x:v>
       </x:c>
     </x:row>
     <x:row r="322" ht="15" hidden="0" customHeight="1">
@@ -14062,13 +14047,13 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B322" s="59" t="str">
-        <x:v>Reporting Repayments</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C322" s="57" t="n">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D322" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>Amount Collection Rate Today</x:v>
       </x:c>
     </x:row>
     <x:row r="323" ht="15" hidden="0" customHeight="1">
@@ -14076,322 +14061,146 @@
         <x:v>OLAP</x:v>
       </x:c>
       <x:c r="B323" s="59" t="str">
-        <x:v>Reporting Repayments</x:v>
+        <x:v>Reporting Statistics</x:v>
       </x:c>
       <x:c r="C323" s="57" t="n">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D323" s="59" t="str">
-        <x:v>Payment Date</x:v>
+        <x:v>Total Outstanding Principal</x:v>
       </x:c>
     </x:row>
     <x:row r="324" ht="15" hidden="0" customHeight="1">
-      <x:c r="A324" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B324" s="59" t="str">
-        <x:v>Reporting Repayments</x:v>
-      </x:c>
-      <x:c r="C324" s="57" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D324" s="59" t="str">
-        <x:v>Amount Received</x:v>
-      </x:c>
+      <x:c r="A324"/>
+      <x:c r="B324"/>
+      <x:c r="C324"/>
+      <x:c r="D324"/>
     </x:row>
     <x:row r="325" ht="15" hidden="0" customHeight="1">
-      <x:c r="A325" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B325" s="59" t="str">
-        <x:v>Reporting Repayments</x:v>
-      </x:c>
-      <x:c r="C325" s="57" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D325" s="59" t="str">
-        <x:v>Principal Paid</x:v>
-      </x:c>
+      <x:c r="A325"/>
+      <x:c r="B325"/>
+      <x:c r="C325"/>
+      <x:c r="D325"/>
     </x:row>
     <x:row r="326" ht="15" hidden="0" customHeight="1">
-      <x:c r="A326" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B326" s="59" t="str">
-        <x:v>Reporting Repayments</x:v>
-      </x:c>
-      <x:c r="C326" s="57" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D326" s="59" t="str">
-        <x:v>Interest Paid</x:v>
-      </x:c>
+      <x:c r="A326"/>
+      <x:c r="B326"/>
+      <x:c r="C326"/>
+      <x:c r="D326"/>
     </x:row>
     <x:row r="327" ht="15" hidden="0" customHeight="1">
-      <x:c r="A327" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B327" s="59" t="str">
-        <x:v>Reporting Repayments</x:v>
-      </x:c>
-      <x:c r="C327" s="57" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D327" s="59" t="str">
-        <x:v>Ref Loans</x:v>
-      </x:c>
+      <x:c r="A327"/>
+      <x:c r="B327"/>
+      <x:c r="C327"/>
+      <x:c r="D327"/>
     </x:row>
     <x:row r="328" ht="15" hidden="0" customHeight="1">
-      <x:c r="A328" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B328" s="59" t="str">
-        <x:v>Reporting Repayments</x:v>
-      </x:c>
-      <x:c r="C328" s="57" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D328" s="59" t="str">
-        <x:v>Ref Charges</x:v>
-      </x:c>
+      <x:c r="A328"/>
+      <x:c r="B328"/>
+      <x:c r="C328"/>
+      <x:c r="D328"/>
     </x:row>
     <x:row r="329" ht="15" hidden="0" customHeight="1">
-      <x:c r="A329" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B329" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C329" s="57" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D329" s="59" t="str">
-        <x:v>_RowNumber</x:v>
-      </x:c>
+      <x:c r="A329"/>
+      <x:c r="B329"/>
+      <x:c r="C329"/>
+      <x:c r="D329"/>
     </x:row>
     <x:row r="330" ht="15" hidden="0" customHeight="1">
-      <x:c r="A330" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B330" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C330" s="57" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D330" s="59" t="str">
-        <x:v>Row ID</x:v>
-      </x:c>
+      <x:c r="A330"/>
+      <x:c r="B330"/>
+      <x:c r="C330"/>
+      <x:c r="D330"/>
     </x:row>
     <x:row r="331" ht="15" hidden="0" customHeight="1">
-      <x:c r="A331" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B331" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C331" s="57" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D331" s="59" t="str">
-        <x:v>Outstanding Principal</x:v>
-      </x:c>
+      <x:c r="A331"/>
+      <x:c r="B331"/>
+      <x:c r="C331"/>
+      <x:c r="D331"/>
     </x:row>
     <x:row r="332" ht="15" hidden="0" customHeight="1">
-      <x:c r="A332" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B332" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C332" s="57" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D332" s="59" t="str">
-        <x:v>Active Loans</x:v>
-      </x:c>
+      <x:c r="A332"/>
+      <x:c r="B332"/>
+      <x:c r="C332"/>
+      <x:c r="D332"/>
     </x:row>
     <x:row r="333" ht="15" hidden="0" customHeight="1">
-      <x:c r="A333" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B333" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C333" s="57" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D333" s="59" t="str">
-        <x:v>Realized Profit MTD</x:v>
-      </x:c>
+      <x:c r="A333"/>
+      <x:c r="B333"/>
+      <x:c r="C333"/>
+      <x:c r="D333"/>
     </x:row>
     <x:row r="334" ht="15" hidden="0" customHeight="1">
-      <x:c r="A334" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B334" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C334" s="57" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D334" s="59" t="str">
-        <x:v>Projected Monthly Profit</x:v>
-      </x:c>
+      <x:c r="A334"/>
+      <x:c r="B334"/>
+      <x:c r="C334"/>
+      <x:c r="D334"/>
     </x:row>
     <x:row r="335" ht="15" hidden="0" customHeight="1">
-      <x:c r="A335" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B335" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C335" s="57" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D335" s="59" t="str">
-        <x:v>Peak Cash Pool Date 30D</x:v>
-      </x:c>
+      <x:c r="A335"/>
+      <x:c r="B335"/>
+      <x:c r="C335"/>
+      <x:c r="D335"/>
     </x:row>
     <x:row r="336" ht="15" hidden="0" customHeight="1">
-      <x:c r="A336" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B336" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C336" s="57" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D336" s="59" t="str">
-        <x:v>Expected Daily Interest</x:v>
-      </x:c>
+      <x:c r="A336"/>
+      <x:c r="B336"/>
+      <x:c r="C336"/>
+      <x:c r="D336"/>
     </x:row>
     <x:row r="337" ht="15" hidden="0" customHeight="1">
-      <x:c r="A337" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B337" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C337" s="57" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D337" s="59" t="str">
-        <x:v>Total Cash Pool</x:v>
-      </x:c>
+      <x:c r="A337"/>
+      <x:c r="B337"/>
+      <x:c r="C337"/>
+      <x:c r="D337"/>
     </x:row>
     <x:row r="338" ht="15" hidden="0" customHeight="1">
-      <x:c r="A338" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B338" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C338" s="57" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D338" s="59" t="str">
-        <x:v>Total Unsettled Profit</x:v>
-      </x:c>
+      <x:c r="A338"/>
+      <x:c r="B338"/>
+      <x:c r="C338"/>
+      <x:c r="D338"/>
     </x:row>
     <x:row r="339" ht="15" hidden="0" customHeight="1">
-      <x:c r="A339" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B339" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C339" s="57" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D339" s="59" t="str">
-        <x:v>Expected Loan Account Balance</x:v>
-      </x:c>
+      <x:c r="A339"/>
+      <x:c r="B339"/>
+      <x:c r="C339"/>
+      <x:c r="D339"/>
     </x:row>
     <x:row r="340" ht="15" hidden="0" customHeight="1">
-      <x:c r="A340" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B340" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C340" s="57" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D340" s="59" t="str">
-        <x:v>Top 3 Borrower Concentration</x:v>
-      </x:c>
+      <x:c r="A340"/>
+      <x:c r="B340"/>
+      <x:c r="C340"/>
+      <x:c r="D340"/>
     </x:row>
     <x:row r="341" ht="15" hidden="0" customHeight="1">
-      <x:c r="A341" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B341" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C341" s="57" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D341" s="59" t="str">
-        <x:v>Amount Due Today</x:v>
-      </x:c>
+      <x:c r="A341"/>
+      <x:c r="B341"/>
+      <x:c r="C341"/>
+      <x:c r="D341"/>
     </x:row>
     <x:row r="342" ht="15" hidden="0" customHeight="1">
-      <x:c r="A342" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B342" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C342" s="57" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D342" s="59" t="str">
-        <x:v>Amount Collected Today</x:v>
-      </x:c>
+      <x:c r="A342"/>
+      <x:c r="B342"/>
+      <x:c r="C342"/>
+      <x:c r="D342"/>
     </x:row>
     <x:row r="343" ht="15" hidden="0" customHeight="1">
-      <x:c r="A343" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B343" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C343" s="57" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D343" s="59" t="str">
-        <x:v>Amount Outstanding Today</x:v>
-      </x:c>
+      <x:c r="A343"/>
+      <x:c r="B343"/>
+      <x:c r="C343"/>
+      <x:c r="D343"/>
     </x:row>
     <x:row r="344" ht="15" hidden="0" customHeight="1">
-      <x:c r="A344" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B344" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C344" s="57" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D344" s="59" t="str">
-        <x:v>Amount Collection Rate Today</x:v>
-      </x:c>
+      <x:c r="A344"/>
+      <x:c r="B344"/>
+      <x:c r="C344"/>
+      <x:c r="D344"/>
     </x:row>
     <x:row r="345" ht="15" hidden="0" customHeight="1">
-      <x:c r="A345" s="57" t="str">
-        <x:v>OLAP</x:v>
-      </x:c>
-      <x:c r="B345" s="59" t="str">
-        <x:v>Reporting Statistics</x:v>
-      </x:c>
-      <x:c r="C345" s="57" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D345" s="59" t="str">
-        <x:v>Total Outstanding Principal</x:v>
-      </x:c>
+      <x:c r="A345"/>
+      <x:c r="B345"/>
+      <x:c r="C345"/>
+      <x:c r="D345"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -14400,7 +14209,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5312d95db4334e0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5da3d5f9b3474a06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14429,7 +14238,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Tables and columns documented in only one application definition.</x:v>
+        <x:v>Tables and columns present in only one live application definition; reconciled on 2026-08-30.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -17042,19 +16851,19 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B134" s="57" t="str">
-        <x:v>Loans</x:v>
+        <x:v>Partners</x:v>
       </x:c>
       <x:c r="C134" s="59" t="str">
-        <x:v>Last Interest Charge Date</x:v>
+        <x:v>Related Cash Pool Contributions</x:v>
       </x:c>
       <x:c r="D134" s="57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E134" s="57" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E134" s="57" t="str">
-        <x:v>No</x:v>
-      </x:c>
       <x:c r="F134" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Reverse-reference list of child rows that point to this record.</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
@@ -17062,19 +16871,19 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B135" s="57" t="str">
-        <x:v>Loans</x:v>
+        <x:v>Partners</x:v>
       </x:c>
       <x:c r="C135" s="59" t="str">
-        <x:v>Accrued Interest Days</x:v>
+        <x:v>Related Settlements</x:v>
       </x:c>
       <x:c r="D135" s="57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E135" s="57" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E135" s="57" t="str">
-        <x:v>No</x:v>
-      </x:c>
       <x:c r="F135" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Reverse-reference list of child rows that point to this record.</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
@@ -17082,16 +16891,16 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B136" s="57" t="str">
-        <x:v>Loans</x:v>
+        <x:v>Partners</x:v>
       </x:c>
       <x:c r="C136" s="59" t="str">
-        <x:v>Accrued Interest</x:v>
+        <x:v>Current Pool Contribution</x:v>
       </x:c>
       <x:c r="D136" s="57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E136" s="57" t="str">
         <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E136" s="57" t="str">
-        <x:v>No</x:v>
       </x:c>
       <x:c r="F136" s="59" t="str">
         <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
@@ -17105,7 +16914,7 @@
         <x:v>Partners</x:v>
       </x:c>
       <x:c r="C137" s="59" t="str">
-        <x:v>Related Cash Pool Contributions</x:v>
+        <x:v>Current Pool Share</x:v>
       </x:c>
       <x:c r="D137" s="57" t="str">
         <x:v>No</x:v>
@@ -17114,7 +16923,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F137" s="59" t="str">
-        <x:v>Reverse-reference list of child rows that point to this record.</x:v>
+        <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -17125,7 +16934,7 @@
         <x:v>Partners</x:v>
       </x:c>
       <x:c r="C138" s="59" t="str">
-        <x:v>Related Settlements</x:v>
+        <x:v>Total Profit Earned</x:v>
       </x:c>
       <x:c r="D138" s="57" t="str">
         <x:v>No</x:v>
@@ -17134,7 +16943,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F138" s="59" t="str">
-        <x:v>Reverse-reference list of child rows that point to this record.</x:v>
+        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
@@ -17145,7 +16954,7 @@
         <x:v>Partners</x:v>
       </x:c>
       <x:c r="C139" s="59" t="str">
-        <x:v>Current Pool Contribution</x:v>
+        <x:v>Total Settlement Created</x:v>
       </x:c>
       <x:c r="D139" s="57" t="str">
         <x:v>No</x:v>
@@ -17165,7 +16974,7 @@
         <x:v>Partners</x:v>
       </x:c>
       <x:c r="C140" s="59" t="str">
-        <x:v>Current Pool Share</x:v>
+        <x:v>Completed Settlement</x:v>
       </x:c>
       <x:c r="D140" s="57" t="str">
         <x:v>No</x:v>
@@ -17174,7 +16983,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F140" s="59" t="str">
-        <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
+        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -17185,7 +16994,7 @@
         <x:v>Partners</x:v>
       </x:c>
       <x:c r="C141" s="59" t="str">
-        <x:v>Total Profit Earned</x:v>
+        <x:v>Pending Settlement</x:v>
       </x:c>
       <x:c r="D141" s="57" t="str">
         <x:v>No</x:v>
@@ -17205,7 +17014,7 @@
         <x:v>Partners</x:v>
       </x:c>
       <x:c r="C142" s="59" t="str">
-        <x:v>Total Settlement Created</x:v>
+        <x:v>Available to Settle</x:v>
       </x:c>
       <x:c r="D142" s="57" t="str">
         <x:v>No</x:v>
@@ -17214,7 +17023,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F142" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
+        <x:v>Derived AppSheet value used by the app workflow, presentation, or reporting model.</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -17225,7 +17034,7 @@
         <x:v>Partners</x:v>
       </x:c>
       <x:c r="C143" s="59" t="str">
-        <x:v>Completed Settlement</x:v>
+        <x:v>Summary - Available Pending Settlement</x:v>
       </x:c>
       <x:c r="D143" s="57" t="str">
         <x:v>No</x:v>
@@ -17234,7 +17043,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F143" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
+        <x:v>Presentation-oriented label or bilingual display value.</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -17245,7 +17054,7 @@
         <x:v>Partners</x:v>
       </x:c>
       <x:c r="C144" s="59" t="str">
-        <x:v>Pending Settlement</x:v>
+        <x:v>Summary - Completed Settlement</x:v>
       </x:c>
       <x:c r="D144" s="57" t="str">
         <x:v>No</x:v>
@@ -17254,7 +17063,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F144" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
+        <x:v>Presentation-oriented label or bilingual display value.</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -17265,7 +17074,7 @@
         <x:v>Partners</x:v>
       </x:c>
       <x:c r="C145" s="59" t="str">
-        <x:v>Available to Settle</x:v>
+        <x:v>Summary - Total Profit Earned</x:v>
       </x:c>
       <x:c r="D145" s="57" t="str">
         <x:v>No</x:v>
@@ -17274,7 +17083,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F145" s="59" t="str">
-        <x:v>Derived AppSheet value used by the app workflow, presentation, or reporting model.</x:v>
+        <x:v>Presentation-oriented label or bilingual display value.</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -17282,10 +17091,10 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B146" s="57" t="str">
-        <x:v>Partners</x:v>
+        <x:v>Repayments</x:v>
       </x:c>
       <x:c r="C146" s="59" t="str">
-        <x:v>Summary - Available Pending Settlement</x:v>
+        <x:v>Pool Total at Payment Date</x:v>
       </x:c>
       <x:c r="D146" s="57" t="str">
         <x:v>No</x:v>
@@ -17294,7 +17103,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F146" s="59" t="str">
-        <x:v>Presentation-oriented label or bilingual display value.</x:v>
+        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -17302,10 +17111,10 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B147" s="57" t="str">
-        <x:v>Partners</x:v>
+        <x:v>Repayments</x:v>
       </x:c>
       <x:c r="C147" s="59" t="str">
-        <x:v>Summary - Completed Settlement</x:v>
+        <x:v>Partner A Contribution at Payment Date</x:v>
       </x:c>
       <x:c r="D147" s="57" t="str">
         <x:v>No</x:v>
@@ -17314,7 +17123,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F147" s="59" t="str">
-        <x:v>Presentation-oriented label or bilingual display value.</x:v>
+        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -17322,10 +17131,10 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B148" s="57" t="str">
-        <x:v>Partners</x:v>
+        <x:v>Repayments</x:v>
       </x:c>
       <x:c r="C148" s="59" t="str">
-        <x:v>Summary - Total Profit Earned</x:v>
+        <x:v>Partner B Contribution at Payment Date</x:v>
       </x:c>
       <x:c r="D148" s="57" t="str">
         <x:v>No</x:v>
@@ -17334,7 +17143,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F148" s="59" t="str">
-        <x:v>Presentation-oriented label or bilingual display value.</x:v>
+        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -17345,7 +17154,7 @@
         <x:v>Repayments</x:v>
       </x:c>
       <x:c r="C149" s="59" t="str">
-        <x:v>Pool Total at Payment Date</x:v>
+        <x:v>Partner A Profit Share</x:v>
       </x:c>
       <x:c r="D149" s="57" t="str">
         <x:v>No</x:v>
@@ -17354,7 +17163,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F149" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
@@ -17365,7 +17174,7 @@
         <x:v>Repayments</x:v>
       </x:c>
       <x:c r="C150" s="59" t="str">
-        <x:v>Partner A Contribution at Payment Date</x:v>
+        <x:v>Partner B Profit Share</x:v>
       </x:c>
       <x:c r="D150" s="57" t="str">
         <x:v>No</x:v>
@@ -17374,7 +17183,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F150" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
@@ -17385,7 +17194,7 @@
         <x:v>Repayments</x:v>
       </x:c>
       <x:c r="C151" s="59" t="str">
-        <x:v>Partner B Contribution at Payment Date</x:v>
+        <x:v>Partner A Profit</x:v>
       </x:c>
       <x:c r="D151" s="57" t="str">
         <x:v>No</x:v>
@@ -17394,7 +17203,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F151" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
@@ -17405,7 +17214,7 @@
         <x:v>Repayments</x:v>
       </x:c>
       <x:c r="C152" s="59" t="str">
-        <x:v>Partner A Profit Share</x:v>
+        <x:v>Partner B Profit</x:v>
       </x:c>
       <x:c r="D152" s="57" t="str">
         <x:v>No</x:v>
@@ -17414,7 +17223,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F152" s="59" t="str">
-        <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
+        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
@@ -17425,7 +17234,7 @@
         <x:v>Repayments</x:v>
       </x:c>
       <x:c r="C153" s="59" t="str">
-        <x:v>Partner B Profit Share</x:v>
+        <x:v>Header - Profit</x:v>
       </x:c>
       <x:c r="D153" s="57" t="str">
         <x:v>No</x:v>
@@ -17434,7 +17243,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F153" s="59" t="str">
-        <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
+        <x:v>Presentation-oriented label or bilingual display value.</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
@@ -17445,7 +17254,7 @@
         <x:v>Repayments</x:v>
       </x:c>
       <x:c r="C154" s="59" t="str">
-        <x:v>Partner A Profit</x:v>
+        <x:v>30D Principal Reduction Days</x:v>
       </x:c>
       <x:c r="D154" s="57" t="str">
         <x:v>No</x:v>
@@ -17454,7 +17263,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F154" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
+        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
@@ -17462,10 +17271,10 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B155" s="57" t="str">
-        <x:v>Repayments</x:v>
+        <x:v>Settlements</x:v>
       </x:c>
       <x:c r="C155" s="59" t="str">
-        <x:v>Partner B Profit</x:v>
+        <x:v>_RowNumber</x:v>
       </x:c>
       <x:c r="D155" s="57" t="str">
         <x:v>No</x:v>
@@ -17474,7 +17283,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F155" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
+        <x:v>System-generated source-row ordinal; not a stable business key.</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
@@ -17482,10 +17291,10 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B156" s="57" t="str">
-        <x:v>Repayments</x:v>
+        <x:v>Settlements</x:v>
       </x:c>
       <x:c r="C156" s="59" t="str">
-        <x:v>Header - Profit</x:v>
+        <x:v>Row ID</x:v>
       </x:c>
       <x:c r="D156" s="57" t="str">
         <x:v>No</x:v>
@@ -17494,7 +17303,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F156" s="59" t="str">
-        <x:v>Presentation-oriented label or bilingual display value.</x:v>
+        <x:v>Immutable row key generated by the source database.</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
@@ -17502,10 +17311,10 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B157" s="57" t="str">
-        <x:v>Repayments</x:v>
+        <x:v>Settlements</x:v>
       </x:c>
       <x:c r="C157" s="59" t="str">
-        <x:v>30D Principal Reduction Days</x:v>
+        <x:v>Settlement Date</x:v>
       </x:c>
       <x:c r="D157" s="57" t="str">
         <x:v>No</x:v>
@@ -17514,7 +17323,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F157" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Stores the source date for Settlement Date.</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="15" hidden="0" customHeight="1">
@@ -17525,7 +17334,7 @@
         <x:v>Settlements</x:v>
       </x:c>
       <x:c r="C158" s="59" t="str">
-        <x:v>_RowNumber</x:v>
+        <x:v>Ref Partner</x:v>
       </x:c>
       <x:c r="D158" s="57" t="str">
         <x:v>No</x:v>
@@ -17534,7 +17343,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F158" s="59" t="str">
-        <x:v>System-generated source-row ordinal; not a stable business key.</x:v>
+        <x:v>Reference key that links this row to the configured parent table.</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="15" hidden="0" customHeight="1">
@@ -17545,7 +17354,7 @@
         <x:v>Settlements</x:v>
       </x:c>
       <x:c r="C159" s="59" t="str">
-        <x:v>Row ID</x:v>
+        <x:v>Amount</x:v>
       </x:c>
       <x:c r="D159" s="57" t="str">
         <x:v>No</x:v>
@@ -17554,7 +17363,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F159" s="59" t="str">
-        <x:v>Immutable row key generated by the source database.</x:v>
+        <x:v>Stores the financially material source value for Amount.</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="15" hidden="0" customHeight="1">
@@ -17565,7 +17374,7 @@
         <x:v>Settlements</x:v>
       </x:c>
       <x:c r="C160" s="59" t="str">
-        <x:v>Settlement Date</x:v>
+        <x:v>Status</x:v>
       </x:c>
       <x:c r="D160" s="57" t="str">
         <x:v>No</x:v>
@@ -17574,7 +17383,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F160" s="59" t="str">
-        <x:v>Stores the source date for Settlement Date.</x:v>
+        <x:v>Stores the controlled workflow state for Status.</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="15" hidden="0" customHeight="1">
@@ -17585,7 +17394,7 @@
         <x:v>Settlements</x:v>
       </x:c>
       <x:c r="C161" s="59" t="str">
-        <x:v>Ref Partner</x:v>
+        <x:v>Transfer Date</x:v>
       </x:c>
       <x:c r="D161" s="57" t="str">
         <x:v>No</x:v>
@@ -17594,7 +17403,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F161" s="59" t="str">
-        <x:v>Reference key that links this row to the configured parent table.</x:v>
+        <x:v>Stores the source date for Transfer Date.</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="15" hidden="0" customHeight="1">
@@ -17605,7 +17414,7 @@
         <x:v>Settlements</x:v>
       </x:c>
       <x:c r="C162" s="59" t="str">
-        <x:v>Amount</x:v>
+        <x:v>Notes</x:v>
       </x:c>
       <x:c r="D162" s="57" t="str">
         <x:v>No</x:v>
@@ -17614,7 +17423,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F162" s="59" t="str">
-        <x:v>Stores the financially material source value for Amount.</x:v>
+        <x:v>Stores the authoritative source value for Notes.</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="15" hidden="0" customHeight="1">
@@ -17622,10 +17431,10 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B163" s="57" t="str">
-        <x:v>Settlements</x:v>
+        <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C163" s="59" t="str">
-        <x:v>Status</x:v>
+        <x:v>Active Loans</x:v>
       </x:c>
       <x:c r="D163" s="57" t="str">
         <x:v>No</x:v>
@@ -17634,7 +17443,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F163" s="59" t="str">
-        <x:v>Stores the controlled workflow state for Status.</x:v>
+        <x:v>Derived count used for workload, portfolio, or risk analysis.</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
@@ -17642,10 +17451,10 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B164" s="57" t="str">
-        <x:v>Settlements</x:v>
+        <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C164" s="59" t="str">
-        <x:v>Transfer Date</x:v>
+        <x:v>Peak Cash Pool 30D</x:v>
       </x:c>
       <x:c r="D164" s="57" t="str">
         <x:v>No</x:v>
@@ -17654,7 +17463,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F164" s="59" t="str">
-        <x:v>Stores the source date for Transfer Date.</x:v>
+        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="15" hidden="0" customHeight="1">
@@ -17662,10 +17471,10 @@
         <x:v>Column</x:v>
       </x:c>
       <x:c r="B165" s="57" t="str">
-        <x:v>Settlements</x:v>
+        <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C165" s="59" t="str">
-        <x:v>Notes</x:v>
+        <x:v>Peak Cash Pool Date 30D</x:v>
       </x:c>
       <x:c r="D165" s="57" t="str">
         <x:v>No</x:v>
@@ -17674,7 +17483,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F165" s="59" t="str">
-        <x:v>Stores the authoritative source value for Notes.</x:v>
+        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
@@ -17685,7 +17494,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C166" s="59" t="str">
-        <x:v>Active Loans</x:v>
+        <x:v>Total Cash Pool</x:v>
       </x:c>
       <x:c r="D166" s="57" t="str">
         <x:v>No</x:v>
@@ -17694,7 +17503,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F166" s="59" t="str">
-        <x:v>Derived count used for workload, portfolio, or risk analysis.</x:v>
+        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
@@ -17705,7 +17514,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C167" s="59" t="str">
-        <x:v>Peak Cash Pool 30D</x:v>
+        <x:v>Total Unsettled Profit</x:v>
       </x:c>
       <x:c r="D167" s="57" t="str">
         <x:v>No</x:v>
@@ -17725,7 +17534,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C168" s="59" t="str">
-        <x:v>Peak Cash Pool Date 30D</x:v>
+        <x:v>Expected Loan Account Balance</x:v>
       </x:c>
       <x:c r="D168" s="57" t="str">
         <x:v>No</x:v>
@@ -17734,7 +17543,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F168" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
+        <x:v>Derived count used for workload, portfolio, or risk analysis.</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
@@ -17745,7 +17554,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C169" s="59" t="str">
-        <x:v>Total Cash Pool</x:v>
+        <x:v>Header - Cash Pool</x:v>
       </x:c>
       <x:c r="D169" s="57" t="str">
         <x:v>No</x:v>
@@ -17754,7 +17563,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F169" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
+        <x:v>Presentation-oriented label or bilingual display value.</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -17765,7 +17574,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C170" s="59" t="str">
-        <x:v>Total Unsettled Profit</x:v>
+        <x:v>Total Outstanding Principal</x:v>
       </x:c>
       <x:c r="D170" s="57" t="str">
         <x:v>No</x:v>
@@ -17785,7 +17594,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C171" s="59" t="str">
-        <x:v>Expected Loan Account Balance</x:v>
+        <x:v>Top 3 Borrower Concentration</x:v>
       </x:c>
       <x:c r="D171" s="57" t="str">
         <x:v>No</x:v>
@@ -17794,7 +17603,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F171" s="59" t="str">
-        <x:v>Derived count used for workload, portfolio, or risk analysis.</x:v>
+        <x:v>Derived AppSheet value used by the app workflow, presentation, or reporting model.</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -17805,7 +17614,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C172" s="59" t="str">
-        <x:v>Header - Cash Pool</x:v>
+        <x:v>Amount Due Today</x:v>
       </x:c>
       <x:c r="D172" s="57" t="str">
         <x:v>No</x:v>
@@ -17814,7 +17623,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F172" s="59" t="str">
-        <x:v>Presentation-oriented label or bilingual display value.</x:v>
+        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -17825,7 +17634,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C173" s="59" t="str">
-        <x:v>Total Outstanding Principal</x:v>
+        <x:v>Amount Collected Today</x:v>
       </x:c>
       <x:c r="D173" s="57" t="str">
         <x:v>No</x:v>
@@ -17845,7 +17654,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C174" s="59" t="str">
-        <x:v>Top 3 Borrower Concentration</x:v>
+        <x:v>Amount Outstanding Today</x:v>
       </x:c>
       <x:c r="D174" s="57" t="str">
         <x:v>No</x:v>
@@ -17854,7 +17663,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F174" s="59" t="str">
-        <x:v>Derived AppSheet value used by the app workflow, presentation, or reporting model.</x:v>
+        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -17865,7 +17674,7 @@
         <x:v>Statistics</x:v>
       </x:c>
       <x:c r="C175" s="59" t="str">
-        <x:v>Amount Due Today</x:v>
+        <x:v>Amount Collection Rate Today</x:v>
       </x:c>
       <x:c r="D175" s="57" t="str">
         <x:v>No</x:v>
@@ -17874,68 +17683,32 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F175" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
+        <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
-      <x:c r="A176" s="57" t="str">
-        <x:v>Column</x:v>
-      </x:c>
-      <x:c r="B176" s="57" t="str">
-        <x:v>Statistics</x:v>
-      </x:c>
-      <x:c r="C176" s="59" t="str">
-        <x:v>Amount Collected Today</x:v>
-      </x:c>
-      <x:c r="D176" s="57" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E176" s="57" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F176" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
-      </x:c>
+      <x:c r="A176" s="57"/>
+      <x:c r="B176" s="57"/>
+      <x:c r="C176" s="59"/>
+      <x:c r="D176" s="57"/>
+      <x:c r="E176" s="57"/>
+      <x:c r="F176" s="59"/>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
-      <x:c r="A177" s="57" t="str">
-        <x:v>Column</x:v>
-      </x:c>
-      <x:c r="B177" s="57" t="str">
-        <x:v>Statistics</x:v>
-      </x:c>
-      <x:c r="C177" s="59" t="str">
-        <x:v>Amount Outstanding Today</x:v>
-      </x:c>
-      <x:c r="D177" s="57" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E177" s="57" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F177" s="59" t="str">
-        <x:v>Derived financial aggregate or balance for operational or analytical use.</x:v>
-      </x:c>
+      <x:c r="A177" s="57"/>
+      <x:c r="B177" s="57"/>
+      <x:c r="C177" s="59"/>
+      <x:c r="D177" s="57"/>
+      <x:c r="E177" s="57"/>
+      <x:c r="F177" s="59"/>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
-      <x:c r="A178" s="57" t="str">
-        <x:v>Column</x:v>
-      </x:c>
-      <x:c r="B178" s="57" t="str">
-        <x:v>Statistics</x:v>
-      </x:c>
-      <x:c r="C178" s="59" t="str">
-        <x:v>Amount Collection Rate Today</x:v>
-      </x:c>
-      <x:c r="D178" s="57" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E178" s="57" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F178" s="59" t="str">
-        <x:v>Derived ratio or performance measure calculated from governed source values.</x:v>
-      </x:c>
+      <x:c r="A178" s="57"/>
+      <x:c r="B178" s="57"/>
+      <x:c r="C178" s="59"/>
+      <x:c r="D178" s="57"/>
+      <x:c r="E178" s="57"/>
+      <x:c r="F178" s="59"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -17947,7 +17720,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf43a1b1b71f24bb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7568ae46f6349ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17982,7 +17755,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Append one row for every accepted reference update. Do not overwrite prior entries.</x:v>
+        <x:v>Reserved historical worksheet. Authoritative change history is maintained as Markdown in Change Logs/.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -18052,289 +17825,289 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="61"/>
+      <x:c r="A6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="61"/>
+      <x:c r="A7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="61"/>
+      <x:c r="A8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="61"/>
+      <x:c r="A9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="61"/>
+      <x:c r="A10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="61"/>
+      <x:c r="A11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="61"/>
+      <x:c r="A12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="61"/>
+      <x:c r="A13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="61"/>
+      <x:c r="A14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="61"/>
+      <x:c r="A15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="61"/>
+      <x:c r="A16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="61"/>
+      <x:c r="A17"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="61"/>
+      <x:c r="A18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="61"/>
+      <x:c r="A19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="61"/>
+      <x:c r="A20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="61"/>
+      <x:c r="A21"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="61"/>
+      <x:c r="A22"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="61"/>
+      <x:c r="A23"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="61"/>
+      <x:c r="A24"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="61"/>
+      <x:c r="A25"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="61"/>
+      <x:c r="A26"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="61"/>
+      <x:c r="A27"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="61"/>
+      <x:c r="A28"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="61"/>
+      <x:c r="A29"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="61"/>
+      <x:c r="A30"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="61"/>
+      <x:c r="A31"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="61"/>
+      <x:c r="A32"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="61"/>
+      <x:c r="A33"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="61"/>
+      <x:c r="A34"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="61"/>
+      <x:c r="A35"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="61"/>
+      <x:c r="A36"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="61"/>
+      <x:c r="A37"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="61"/>
+      <x:c r="A38"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="61"/>
+      <x:c r="A39"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="61"/>
+      <x:c r="A40"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="61"/>
+      <x:c r="A41"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="61"/>
+      <x:c r="A42"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="61"/>
+      <x:c r="A43"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="61"/>
+      <x:c r="A44"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="61"/>
+      <x:c r="A45"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="61"/>
+      <x:c r="A46"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="61"/>
+      <x:c r="A47"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="61"/>
+      <x:c r="A48"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="61"/>
+      <x:c r="A49"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="61"/>
+      <x:c r="A50"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="61"/>
+      <x:c r="A51"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="61"/>
+      <x:c r="A52"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="61"/>
+      <x:c r="A53"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="61"/>
+      <x:c r="A54"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="61"/>
+      <x:c r="A55"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="61"/>
+      <x:c r="A56"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="61"/>
+      <x:c r="A57"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="61"/>
+      <x:c r="A58"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="61"/>
+      <x:c r="A59"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="61"/>
+      <x:c r="A60"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="61"/>
+      <x:c r="A61"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="61"/>
+      <x:c r="A62"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="61"/>
+      <x:c r="A63"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="61"/>
+      <x:c r="A64"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="61"/>
+      <x:c r="A65"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="61"/>
+      <x:c r="A66"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="61"/>
+      <x:c r="A67"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="61"/>
+      <x:c r="A68"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="61"/>
+      <x:c r="A69"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="61"/>
+      <x:c r="A70"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="61"/>
+      <x:c r="A71"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="61"/>
+      <x:c r="A72"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="61"/>
+      <x:c r="A73"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="61"/>
+      <x:c r="A74"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="61"/>
+      <x:c r="A75"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="61"/>
+      <x:c r="A76"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="61"/>
+      <x:c r="A77"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="61"/>
+      <x:c r="A78"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="61"/>
+      <x:c r="A79"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="61"/>
+      <x:c r="A80"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="61"/>
+      <x:c r="A81"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="61"/>
+      <x:c r="A82"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="61"/>
+      <x:c r="A83"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="61"/>
+      <x:c r="A84"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="61"/>
+      <x:c r="A85"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="61"/>
+      <x:c r="A86"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="61"/>
+      <x:c r="A87"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="61"/>
+      <x:c r="A88"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="61"/>
+      <x:c r="A89"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="61"/>
+      <x:c r="A90"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="61"/>
+      <x:c r="A91"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="61"/>
+      <x:c r="A92"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="61"/>
+      <x:c r="A93"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="61"/>
+      <x:c r="A94"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="61"/>
+      <x:c r="A95"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="61"/>
+      <x:c r="A96"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="61"/>
+      <x:c r="A97"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="61"/>
+      <x:c r="A98"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="61"/>
+      <x:c r="A99"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="61"/>
+      <x:c r="A100"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -18351,7 +18124,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c2cab78bbca406e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78736ac099de4f7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R8b2c0df50b144b4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R46311ca96db24160"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rfa7e44234bca496c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R95d0a43b75f04986"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Re157bb1229494759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R11827c90661d44cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Ree5480ed78564379"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R80446185eceb41e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R3c5fd6e88fe449a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R1e8ba34253d34452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Re3bfc4ac406b431e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R87e03c4747354fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Re1527714b54946bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R75b6566451fb4126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R86bb6bdffefe40c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R0545f66847c64d8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rd3af4178374c4d7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Re2ead377192147da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Reb92849621844765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R576eae966e1345c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -258,7 +258,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="87">
+  <x:cellXfs count="89">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -440,6 +440,10 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -559,8 +563,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DataModelTables" displayName="DataModelTables" ref="A4:G17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:G17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="DataModelTables" displayName="DataModelTables" ref="A4:G19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:G19"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Table"/>
     <x:tableColumn id="2" name="Source"/>
@@ -575,11 +579,11 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DataModelColumns" displayName="DataModelColumns" ref="A4:H369" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H369"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DataModelColumns" displayName="DataModelColumns" ref="A4:H392" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H392"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Table"/>
-    <x:tableColumn id="2" name="Column Order"/>
+    <x:tableColumn id="2" name="Inventory order"/>
     <x:tableColumn id="3" name="Column"/>
     <x:tableColumn id="4" name="Kind / type"/>
     <x:tableColumn id="5" name="Availability"/>
@@ -592,8 +596,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DataModelRelationships" displayName="DataModelRelationships" ref="A4:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:E18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="DataModelRelationships" displayName="DataModelRelationships" ref="A4:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:E21"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Child table"/>
     <x:tableColumn id="2" name="Ref column"/>
@@ -606,7 +610,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="DataModelSlices" displayName="DataModelSlices" ref="A4:H17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="DataModelSlices" displayName="DataModelSlices" ref="A4:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="App"/>
     <x:tableColumn id="2" name="Slice"/>
@@ -622,7 +626,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D371" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D440" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="App"/>
     <x:tableColumn id="2" name="Slice"/>
@@ -634,8 +638,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="DataModelAppVariances" displayName="DataModelAppVariances" ref="A4:F203" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:F203"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="DataModelAppVariances" displayName="DataModelAppVariances" ref="A4:F227" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:F227"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Object Type"/>
     <x:tableColumn id="2" name="Table"/>
@@ -928,13 +932,11 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="80" customHeight="1">
-      <x:c r="A5" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reconciliation status</x:t>
-        </x:is>
+      <x:c r="A5" s="84" t="str">
+        <x:v>Reconciliation status</x:v>
       </x:c>
       <x:c r="B5" s="85" t="str">
-        <x:v>OLAP schema warnings repaired at v1.100016 on 7 September 2026; rollback v1.100012. Added read-only payment target tables and two repayment Refs, preserving all existing column properties. Twenty shared numeric KPI formulas and displayed values match after refreshing both apps on the same date.</x:v>
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok). Collection settings reconciled in production Operations app; standalone forms/default/setup-review verified. OLAP standalone app opened successfully; its new-column loading is pending reconciliation. Other inventory retains dated scope.</x:v>
       </x:c>
       <x:c r="C5" s="73"/>
       <x:c r="D5" s="73"/>
@@ -942,13 +944,11 @@
       <x:c r="F5" s="73"/>
     </x:row>
     <x:row r="6" ht="80" customHeight="1">
-      <x:c r="A6" s="84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Live baselines</x:t>
-        </x:is>
+      <x:c r="A6" s="84" t="str">
+        <x:v>Live baselines</x:v>
       </x:c>
       <x:c r="B6" s="85" t="str">
-        <x:v>OLAP v1.100016; OLTP v3.000003 observed during this read-only comparison (previous rollout completed v3.000002). No OLTP configuration changed by this task. Existing full backup pair retained, no additional app/database copy.</x:v>
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); rollback OLTP 3.000014. Native backup Money Collection Backup 20260908 (12 tables, rows copied); local runner/docs rollback retained. OLAP last documented 1.100016; no OLAP configuration changed.</x:v>
       </x:c>
       <x:c r="C6" s="73"/>
       <x:c r="D6" s="73"/>
@@ -956,13 +956,11 @@
       <x:c r="F6" s="73"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
-      <x:c r="A7" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Reconciliation date</x:t>
-        </x:is>
+      <x:c r="A7" s="12" t="str">
+        <x:v>Reconciliation date</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>2026-09-04 (Asia/Singapore)</x:v>
+        <x:v>2026-09-08 (Asia/Bangkok), collection settings scope only</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
@@ -973,7 +971,7 @@
       </x:c>
       <x:c r="B8" s="14" t="n">
         <x:f>COUNTA('Tables'!A5:A100)</x:f>
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
@@ -994,7 +992,7 @@
       </x:c>
       <x:c r="B10" s="14" t="n">
         <x:f>COUNTA('Relationships'!A5:A100)</x:f>
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
@@ -1197,12 +1195,12 @@
       <x:c r="E34" s="73"/>
       <x:c r="F34" s="73"/>
     </x:row>
-    <x:row r="35" ht="66" customHeight="1">
+    <x:row r="35" ht="160" customHeight="1">
       <x:c r="A35" s="86" t="str">
         <x:v>Reporting boundary</x:v>
       </x:c>
       <x:c r="B35" s="73" t="str">
-        <x:v>OLAP payment trace schema reconciled at v1.100016; new payment tables READ_ONLY. Existing live KPIs match OLTP at displayed precision. Collection and historical snapshot definitions have distinct date/partial-payment bases documented in the reconciliation log.</x:v>
+        <x:v>8 September 2026: Puifai plan remains 46,000 across 72 charges; eight nominal rates restored and generation disabled. Oum: six charges due 30 September total 35,000 (interest 27,500 + penalties 7,500), no principal. Six original keys rescheduled and 12 superseded unpaid rows deleted with explicit approval and before-values retained. Oum generation disabled. Reactivation task created for 29 September 23:55 Bangkok. Configuration rollback: OLTP 3.000026 / OLAP 1.100018. Manual workflow acceptance and Looker refresh pending.</x:v>
       </x:c>
       <x:c r="C35" s="73"/>
       <x:c r="D35" s="73"/>
@@ -2351,7 +2349,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raef64db8f7c8477c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93b4f3212ec24d5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2378,7 +2376,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>12 native tables; OLTP loads8, OLAP loads13 business tables including external Calendar. OLAP live totals verified; unrelated older detailed inventory remains dated. System process tables excluded.</x:v>
+        <x:v>14 native tables. OLTP loads10: Borrowers has14 physical +28 VCs; new bank table7+3 and singleton settings4+0. OLAP loading of new fields not reconciled; prior counts retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -2428,17 +2426,17 @@
       <x:c r="C5" s="56" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="D5" s="56" t="str">
-        <x:v>7</x:v>
+      <x:c r="D5" s="56" t="n">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="56" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="G5" s="58" t="str">
-        <x:v>Borrower master records and indicators; includes the OLAP-only projected-monthly-profit contribution and borrower value/stability matrix VCs plus the OLTP-only active principal-coverage VC. Hidden Flag is loaded in both apps but filters only the OLTP primary borrower list.</x:v>
+        <x:v>Borrower master; Row ID remains immutable key. Seven new collection fields and two OLTP helpers. OLAP65 VC count is prior baseline; loading of seven new physical fields not reconciled.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
@@ -2567,7 +2565,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="D11" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="57" t="n">
         <x:v>20</x:v>
@@ -2715,6 +2713,52 @@
       </x:c>
       <x:c r="G17" s="73" t="str">
         <x:v>Stored allocation snapshots owned by OLTP. OLAP loads fourteen physical fields and one reverse-reference VC, READ_ONLY.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" customHeight="1">
+      <x:c r="A18" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B18" s="87" t="str">
+        <x:v>Money database</x:v>
+      </x:c>
+      <x:c r="C18" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="D18" s="87" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E18" s="87" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F18" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="G18" s="87" t="str">
+        <x:v>Receiving-account master; add/update only in OLTP. Deactivate used accounts. Two user-authorized records; no details in this dictionary.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" customHeight="1">
+      <x:c r="A19" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="B19" s="87" t="str">
+        <x:v>Money database</x:v>
+      </x:c>
+      <x:c r="C19" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="D19" s="87" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E19" s="87" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="G19" s="87" t="str">
+        <x:v>One shared default receiving-account selection. Update only; no adds/deletes in OLTP.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2724,7 +2768,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re70afbec66b841c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c975c93679348ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2757,7 +2801,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>OLAP v1.100016, 7 September 2026: 36 payment-trace definitions now loaded. Existing OLTP definitions and unrelated OLAP definitions retained. Older unrelated OLAP inventory remains dated; this is a scoped schema/KPI reconciliation.</x:v>
+        <x:v>8 September 2026: Auto Charge Enabled added to Loans in both apps. Eleven existing model expressions reconciled. Manual workflow acceptance remains pending.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -3635,108 +3679,108 @@
         <x:v>IFS( COUNT([Todays Collection Charges]) = 0, "", COUNT( SELECT( Charges[Row ID], AND( IN([Row ID], [_THISROW].[Todays Collection Charges]), [Charge Date] &lt; TODAY(), [Payment Status] &lt;&gt; "ชำระแล้ว" ) ) ) &gt; 0, "Overdue", AND( NOT(IN("รอชำระ", [Todays Collection Charges][Payment Status])), NOT(IN("ชำระบางส่วน", [Todays Collection Charges][Payment Status])) ), "Fully Paid", OR( IN("ชำระบางส่วน", [Todays Collection Charges][Payment Status]), AND( IN("ชำระแล้ว", [Todays Collection Charges][Payment Status]), IN("รอชำระ", [Todays Collection Charges][Payment Status]) ) ), "Partially Paid", TRUE, "Not Paid")</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="15" customHeight="1">
-      <x:c r="A37" s="57" t="str">
+    <x:row r="37" ht="110" customHeight="1">
+      <x:c r="A37" s="82" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
-      <x:c r="B37" s="57" t="n">
+      <x:c r="B37" s="82" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C37" s="59" t="str">
+      <x:c r="C37" s="82" t="str">
         <x:v>Todays Collection Charges</x:v>
       </x:c>
-      <x:c r="D37" s="59" t="str">
+      <x:c r="D37" s="82" t="str">
         <x:v>VC / List</x:v>
       </x:c>
-      <x:c r="E37" s="57" t="str">
+      <x:c r="E37" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F37" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G37" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
-      </x:c>
-      <x:c r="H37" s="59" t="str">
-        <x:v>SELECT( Charges[Row ID], AND( [Ref Loans].[Ref Borrowers] = [_THISROW].[Row ID], OR( AND( [Payment Status] &lt;&gt; "ชำระแล้ว", [Charge Date] &lt;= TODAY() ), AND( [Payment Status] = "ชำระแล้ว", [Payment Date] = TODAY() ) ) ))</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="15" customHeight="1">
-      <x:c r="A38" s="57" t="str">
+      <x:c r="F37" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G37" s="82" t="str">
+        <x:v>Future-charge scope reconciled on 8 September 2026. Due totals exclude future dates; collection includes actual repayment activity today.</x:v>
+      </x:c>
+      <x:c r="H37" s="82" t="str">
+        <x:v>SELECT(Charges[Row ID], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Row ID], OR(AND([Payment Status] &lt;&gt; "ชำระแล้ว", [Charge Date] &lt;= TODAY()), AND([Payment Status] = "ชำระแล้ว", [Payment Date] = TODAY()), IN(TODAY(), [Related Repayments][Payment Date]))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="110" customHeight="1">
+      <x:c r="A38" s="82" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
-      <x:c r="B38" s="57" t="n">
+      <x:c r="B38" s="82" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C38" s="59" t="str">
+      <x:c r="C38" s="82" t="str">
         <x:v>Todays Amount Due</x:v>
       </x:c>
-      <x:c r="D38" s="59" t="str">
+      <x:c r="D38" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E38" s="57" t="str">
+      <x:c r="E38" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F38" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G38" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
-      </x:c>
-      <x:c r="H38" s="59" t="str">
-        <x:v>SUM([Todays Collection Charges][Amount Due])</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="15" customHeight="1">
-      <x:c r="A39" s="57" t="str">
+      <x:c r="F38" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G38" s="82" t="str">
+        <x:v>Future-charge scope reconciled on 8 September 2026. Due totals exclude future dates; collection includes actual repayment activity today.</x:v>
+      </x:c>
+      <x:c r="H38" s="82" t="str">
+        <x:v>SUM(SELECT([Todays Collection Charges][Amount Due], [Charge Date] &lt;= TODAY()))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="110" customHeight="1">
+      <x:c r="A39" s="82" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
-      <x:c r="B39" s="57" t="n">
+      <x:c r="B39" s="82" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C39" s="59" t="str">
+      <x:c r="C39" s="82" t="str">
         <x:v>Todays Amount Collected</x:v>
       </x:c>
-      <x:c r="D39" s="59" t="str">
+      <x:c r="D39" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E39" s="57" t="str">
+      <x:c r="E39" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F39" s="57" t="str">
-        <x:v>Intentional formula variance</x:v>
-      </x:c>
-      <x:c r="G39" s="59" t="str">
-        <x:v>OLTP uses payments dated today; OLAP retains the cumulative paid amount.</x:v>
-      </x:c>
-      <x:c r="H39" s="59" t="str">
-        <x:v>OLTP: SUM([Todays Collection Charges][Payment Received Today]); OLAP: SUM([Todays Collection Charges][Total Paid])</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="21.600000381469727" customHeight="1">
-      <x:c r="A40" s="57" t="str">
+      <x:c r="F39" s="82" t="str">
+        <x:v>Same date basis; different aggregation path</x:v>
+      </x:c>
+      <x:c r="G39" s="82" t="str">
+        <x:v>Both apps sum actual posted repayments dated today, including future-charge partial prepayments.</x:v>
+      </x:c>
+      <x:c r="H39" s="82" t="str">
+        <x:v>OLTP: SUM([Todays Collection Charges][Payment Received Today]); OLAP: SUM(SELECT(Repayments[Amount Received], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Row ID], [Payment Date] = TODAY())))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="110" customHeight="1">
+      <x:c r="A40" s="82" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
-      <x:c r="B40" s="57" t="n">
+      <x:c r="B40" s="82" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C40" s="59" t="str">
+      <x:c r="C40" s="82" t="str">
         <x:v>Todays Amount Remaining</x:v>
       </x:c>
-      <x:c r="D40" s="59" t="str">
+      <x:c r="D40" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E40" s="57" t="str">
+      <x:c r="E40" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F40" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G40" s="59" t="str">
-        <x:v>Derived date, time-window, age, or delinquency measure.</x:v>
-      </x:c>
-      <x:c r="H40" s="59" t="str">
-        <x:v>SUM([Todays Collection Charges][Amount Remaining])</x:v>
+      <x:c r="F40" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G40" s="82" t="str">
+        <x:v>Future-charge scope reconciled on 8 September 2026. Due totals exclude future dates; collection includes actual repayment activity today.</x:v>
+      </x:c>
+      <x:c r="H40" s="82" t="str">
+        <x:v>SUM(SELECT([Todays Collection Charges][Amount Remaining], [Charge Date] &lt;= TODAY()))</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15" customHeight="1">
@@ -4363,30 +4407,30 @@
         <x:v>[Active Loan Interest Earned] - [Total Outstanding Principal]</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="15" customHeight="1">
-      <x:c r="A65" s="57" t="str">
+    <x:row r="65" ht="110" customHeight="1">
+      <x:c r="A65" s="82" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
-      <x:c r="B65" s="57" t="n">
+      <x:c r="B65" s="82" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C65" s="59" t="str">
+      <x:c r="C65" s="82" t="str">
         <x:v>Projected Monthly Profit Contribution</x:v>
       </x:c>
-      <x:c r="D65" s="59" t="str">
+      <x:c r="D65" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E65" s="57" t="str">
+      <x:c r="E65" s="82" t="str">
         <x:v>OLAP only</x:v>
       </x:c>
-      <x:c r="F65" s="57" t="str">
-        <x:v>Show; 0 decimals; bilingual display name</x:v>
-      </x:c>
-      <x:c r="G65" s="59" t="str">
-        <x:v>Borrower-grain contribution that mirrors Statistics[Projected Monthly Profit] for pie-chart attribution across the full Borrowers population.</x:v>
-      </x:c>
-      <x:c r="H65" s="59" t="str">
-        <x:v>SUM(SELECT(Repayments[Interest Paid], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Row ID], MONTH([Payment Date]) = MONTH(TODAY()), YEAR([Payment Date]) = YEAR(TODAY())))) + SUM(SELECT(Charges[Interest Remaining], [Ref Loans].[Ref Borrowers] = [_THISROW].[Row ID])) + SUM(SELECT(Loans[Expected Interest This Month], [Ref Borrowers] = [_THISROW].[Row ID]))</x:v>
+      <x:c r="F65" s="82" t="str">
+        <x:v>Show; 0 decimals; bilingual display name; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G65" s="82" t="str">
+        <x:v>Realized current-month interest plus due-through-today interest remaining plus expected remaining-month interest, without future-charge double counting.</x:v>
+      </x:c>
+      <x:c r="H65" s="82" t="str">
+        <x:v>SUM(SELECT(Repayments[Interest Paid], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Row ID], MONTH([Payment Date]) = MONTH(TODAY()), YEAR([Payment Date]) = YEAR(TODAY())))) + SUM(SELECT(Charges[Interest Remaining], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Row ID], [Charge Date] &lt;= TODAY()))) + SUM(SELECT(Loans[Expected Interest This Month], [Ref Borrowers] = [_THISROW].[Row ID]))</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" customHeight="1">
@@ -4519,29 +4563,29 @@
         <x:v>LOOKUP("MAIN", "Loan Assessment", "Assessment ID", "Minimum Daily Profit Rate")</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="21.600000381469727" customHeight="1">
-      <x:c r="A71" s="57" t="str">
+    <x:row r="71" ht="150" customHeight="1">
+      <x:c r="A71" s="82" t="str">
         <x:v>Calendar</x:v>
       </x:c>
-      <x:c r="B71" s="57" t="n">
+      <x:c r="B71" s="82" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C71" s="59" t="str">
+      <x:c r="C71" s="82" t="str">
         <x:v>Projected Outstanding Principal</x:v>
       </x:c>
-      <x:c r="D71" s="59" t="str">
+      <x:c r="D71" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E71" s="57" t="str">
+      <x:c r="E71" s="82" t="str">
         <x:v>OLAP only</x:v>
       </x:c>
-      <x:c r="F71" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G71" s="59" t="str">
-        <x:v>Projected selected-borrower principal. Daily-installment balances start from current Outstanding Principal, subtract only contract principal after the latest posted Charge through the candidate date/Due Date, and do not go below zero.</x:v>
-      </x:c>
-      <x:c r="H71" s="59" t="str">
+      <x:c r="F71" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G71" s="82" t="str">
+        <x:v>Disabled loans use explicit schedule charges. Enabled loans retain contractual projection branches.</x:v>
+      </x:c>
+      <x:c r="H71" s="82" t="str">
         <x:v>SUM(
   SELECT(
     Loans[Outstanding Principal],
@@ -4549,8 +4593,8 @@
       [Ref Borrowers] = [_THISROW].[Assessment Borrower],
       [Loan Status] = "ยังไม่ปิดยอด",
       OR(
-        [Loan Type] = "ดอกเบี้ยรายวัน",
-        AND([Loan Type] = "กำหนดวันชำระ", [Due Date] &gt; [_THISROW].[Date])
+        AND([Auto Charge Enabled], [Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest] &lt;&gt; 0),
+        AND([Loan Type] = "กำหนดวันชำระ", [Auto Charge Enabled], [Due Date] &gt; [_THISROW].[Date])
       )
     )
   )
@@ -4564,7 +4608,7 @@
         AND(
           [Ref Borrowers] = [_THISROW].[Assessment Borrower],
           [Loan Status] = "ยังไม่ปิดยอด",
-          [Loan Type] = "ผ่อนชำระรายวัน",
+          OR([Loan Type] = "ผ่อนชำระรายวัน", OR(NOT([Auto Charge Enabled]), AND([Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest] = 0))),
           [Loan Date] &lt;= [_THISROW].[Date]
         )
       )
@@ -4579,29 +4623,29 @@
 )</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="21.600000381469727" customHeight="1">
-      <x:c r="A72" s="57" t="str">
+    <x:row r="72" ht="135" customHeight="1">
+      <x:c r="A72" s="82" t="str">
         <x:v>Calendar</x:v>
       </x:c>
-      <x:c r="B72" s="57" t="n">
+      <x:c r="B72" s="82" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C72" s="59" t="str">
+      <x:c r="C72" s="82" t="str">
         <x:v>Projected Interest</x:v>
       </x:c>
-      <x:c r="D72" s="59" t="str">
+      <x:c r="D72" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E72" s="57" t="str">
+      <x:c r="E72" s="82" t="str">
         <x:v>OLAP only</x:v>
       </x:c>
-      <x:c r="F72" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G72" s="59" t="str">
-        <x:v>Actual selected-borrower interest received plus future daily-interest, fixed-date, and uncharged daily-installment interest. Daily-installment Transfer Fee is not projected again.</x:v>
-      </x:c>
-      <x:c r="H72" s="59" t="str">
+      <x:c r="F72" s="82" t="str">
+        <x:v>-; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G72" s="82" t="str">
+        <x:v>Disabled loans use explicit schedule charges. Enabled loans retain contractual projection branches.</x:v>
+      </x:c>
+      <x:c r="H72" s="82" t="str">
         <x:v>SUM(
   SELECT(
     Loans[Total Interest Received],
@@ -4618,7 +4662,7 @@
       AND(
         [Ref Borrowers] = [_THISROW].[Assessment Borrower],
         [Loan Status] = "ยังไม่ปิดยอด",
-        [Loan Type] = "ดอกเบี้ยรายวัน"
+        AND([Auto Charge Enabled], [Loan Type] = "ดอกเบี้ยรายวัน")
       )
     )
   )
@@ -4630,7 +4674,7 @@
     AND(
       [Ref Borrowers] = [_THISROW].[Assessment Borrower],
       [Loan Status] = "ยังไม่ปิดยอด",
-      [Loan Type] = "กำหนดวันชำระ",
+      [Loan Type] = "กำหนดวันชำระ", [Auto Charge Enabled],
       [Due Date] &gt; TODAY(),
       [Due Date] &lt;= [_THISROW].[Date]
     )
@@ -4670,29 +4714,29 @@
         <x:v>TOTALHOURS( [Date] - DATE("01/01/2000")) / 24</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="15" customHeight="1">
-      <x:c r="A74" s="57" t="str">
+    <x:row r="74" ht="100" customHeight="1">
+      <x:c r="A74" s="82" t="str">
         <x:v>Calendar</x:v>
       </x:c>
-      <x:c r="B74" s="57" t="n">
+      <x:c r="B74" s="82" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C74" s="59" t="str">
+      <x:c r="C74" s="82" t="str">
         <x:v>Assessment Principal Base</x:v>
       </x:c>
-      <x:c r="D74" s="59" t="str">
+      <x:c r="D74" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E74" s="57" t="str">
+      <x:c r="E74" s="82" t="str">
         <x:v>OLAP only</x:v>
       </x:c>
-      <x:c r="F74" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G74" s="59" t="str">
-        <x:v>Principal base used by Minimum Required Profit; daily-installment exposure follows the declining contract balance.</x:v>
-      </x:c>
-      <x:c r="H74" s="59" t="str">
+      <x:c r="F74" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G74" s="82" t="str">
+        <x:v>Disabled loans use explicit schedule charges. Enabled loans retain contractual projection branches.</x:v>
+      </x:c>
+      <x:c r="H74" s="82" t="str">
         <x:v>SUM(
   SELECT(
     Loans[Principal Amount],
@@ -4700,8 +4744,8 @@
       [Ref Borrowers] = [_THISROW].[Assessment Borrower],
       [Loan Status] = "ยังไม่ปิดยอด",
       OR(
-        [Loan Type] = "ดอกเบี้ยรายวัน",
-        AND([Loan Type] = "กำหนดวันชำระ", [Due Date] &gt; [_THISROW].[Date])
+        AND([Auto Charge Enabled], [Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest] &lt;&gt; 0),
+        AND([Loan Type] = "กำหนดวันชำระ", [Auto Charge Enabled], [Due Date] &gt; [_THISROW].[Date])
       )
     )
   )
@@ -4709,29 +4753,29 @@
 + [Assessment Installment Contract Outstanding]</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="15" customHeight="1">
-      <x:c r="A75" s="57" t="str">
+    <x:row r="75" ht="100" customHeight="1">
+      <x:c r="A75" s="82" t="str">
         <x:v>Calendar</x:v>
       </x:c>
-      <x:c r="B75" s="57" t="n">
+      <x:c r="B75" s="82" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C75" s="59" t="str">
+      <x:c r="C75" s="82" t="str">
         <x:v>Assessment Principal Start Weight</x:v>
       </x:c>
-      <x:c r="D75" s="59" t="str">
+      <x:c r="D75" s="82" t="str">
         <x:v>VC / Decimal</x:v>
       </x:c>
-      <x:c r="E75" s="57" t="str">
+      <x:c r="E75" s="82" t="str">
         <x:v>OLAP only</x:v>
       </x:c>
-      <x:c r="F75" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G75" s="59" t="str">
-        <x:v>Principal-day start weight used by Minimum Required Profit; algebraically preserves cumulative declining daily-installment principal-days.</x:v>
-      </x:c>
-      <x:c r="H75" s="59" t="str">
+      <x:c r="F75" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G75" s="82" t="str">
+        <x:v>Disabled loans use explicit schedule charges. Enabled loans retain contractual projection branches.</x:v>
+      </x:c>
+      <x:c r="H75" s="82" t="str">
         <x:v>SUM(
   SELECT(
     Loans[Principal Start Weight],
@@ -4739,8 +4783,8 @@
       [Ref Borrowers] = [_THISROW].[Assessment Borrower],
       [Loan Status] = "ยังไม่ปิดยอด",
       OR(
-        [Loan Type] = "ดอกเบี้ยรายวัน",
-        AND([Loan Type] = "กำหนดวันชำระ", [Due Date] &gt; [_THISROW].[Date])
+        AND([Auto Charge Enabled], [Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest] &lt;&gt; 0),
+        AND([Loan Type] = "กำหนดวันชำระ", [Auto Charge Enabled], [Due Date] &gt; [_THISROW].[Date])
       )
     )
   )
@@ -5118,36 +5162,36 @@
         <x:v>DAY([Date])</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="15" customHeight="1">
-      <x:c r="A90" s="57" t="str">
+    <x:row r="90" ht="180" customHeight="1">
+      <x:c r="A90" s="82" t="str">
         <x:v>Calendar</x:v>
       </x:c>
-      <x:c r="B90" s="57" t="n">
+      <x:c r="B90" s="82" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C90" s="59" t="str">
+      <x:c r="C90" s="82" t="str">
         <x:v>Assessment Installment Contract Principal Due</x:v>
       </x:c>
-      <x:c r="D90" s="59" t="str">
+      <x:c r="D90" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E90" s="57" t="str">
+      <x:c r="E90" s="82" t="str">
         <x:v>OLAP only</x:v>
       </x:c>
-      <x:c r="F90" s="57" t="str">
-        <x:v>Hidden; whole baht</x:v>
-      </x:c>
-      <x:c r="G90" s="59" t="str">
-        <x:v>Whole-baht scheduled principal for the candidate Calendar date; FLOOR base plus one baht on the earliest remainder days.</x:v>
-      </x:c>
-      <x:c r="H90" s="59" t="str">
+      <x:c r="F90" s="82" t="str">
+        <x:v>Hidden; whole baht; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G90" s="82" t="str">
+        <x:v>Disabled loans use explicit schedule charges. Enabled loans retain contractual projection branches.</x:v>
+      </x:c>
+      <x:c r="H90" s="82" t="str">
         <x:v>SUM(
   SELECT(
     Loans[Daily Installment Base Principal],
     AND(
       [Ref Borrowers] = [_THISROW].[Assessment Borrower],
       [Loan Status] = "ยังไม่ปิดยอด",
-      [Loan Type] = "ผ่อนชำระรายวัน",
+      [Loan Type] = "ผ่อนชำระรายวัน", [Auto Charge Enabled],
       [Loan Date] &lt;= [_THISROW].[Date],
       [Due Date] &gt;= [_THISROW].[Date],
       [Due Date] &gt;= [Loan Date],
@@ -5161,7 +5205,7 @@
     AND(
       [Ref Borrowers] = [_THISROW].[Assessment Borrower],
       [Loan Status] = "ยังไม่ปิดยอด",
-      [Loan Type] = "ผ่อนชำระรายวัน",
+      [Loan Type] = "ผ่อนชำระรายวัน", [Auto Charge Enabled],
       [Loan Date] &lt;= [_THISROW].[Date],
       [Due Date] &gt;= [_THISROW].[Date],
       [Due Date] &gt;= [Loan Date],
@@ -5173,39 +5217,39 @@
       )
     )
   )
-)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" ht="15" customHeight="1">
-      <x:c r="A91" s="57" t="str">
+) + SUM(SELECT(Charges[Principal Due], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Assessment Borrower], [Ref Loans].[Loan Status] = "ยังไม่ปิดยอด", OR(NOT([Ref Loans].[Auto Charge Enabled]), AND([Ref Loans].[Loan Type] = "ดอกเบี้ยรายวัน", [Ref Loans].[Current Daily Interest] = 0)), [Charge Date] = [_THISROW].[Date])))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="240" customHeight="1">
+      <x:c r="A91" s="82" t="str">
         <x:v>Calendar</x:v>
       </x:c>
-      <x:c r="B91" s="57" t="n">
+      <x:c r="B91" s="82" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C91" s="59" t="str">
+      <x:c r="C91" s="82" t="str">
         <x:v>Assessment Installment Future Principal Due</x:v>
       </x:c>
-      <x:c r="D91" s="59" t="str">
+      <x:c r="D91" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E91" s="57" t="str">
+      <x:c r="E91" s="82" t="str">
         <x:v>OLAP only</x:v>
       </x:c>
-      <x:c r="F91" s="57" t="str">
-        <x:v>Hidden; whole baht</x:v>
-      </x:c>
-      <x:c r="G91" s="59" t="str">
-        <x:v>Whole-baht scheduled principal after each loan's latest posted Charge through its Due Date.</x:v>
-      </x:c>
-      <x:c r="H91" s="59" t="str">
+      <x:c r="F91" s="82" t="str">
+        <x:v>Hidden; whole baht; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G91" s="82" t="str">
+        <x:v>Disabled loans use explicit schedule charges. Enabled loans retain contractual projection branches.</x:v>
+      </x:c>
+      <x:c r="H91" s="82" t="str">
         <x:v>SUM(
   SELECT(
     Loans[Daily Installment Base Principal],
     AND(
       [Ref Borrowers] = [_THISROW].[Assessment Borrower],
       [Loan Status] = "ยังไม่ปิดยอด",
-      [Loan Type] = "ผ่อนชำระรายวัน",
+      [Loan Type] = "ผ่อนชำระรายวัน", [Auto Charge Enabled],
       [Loan Date] &lt;= [_THISROW].[Date],
       [Due Date] &gt;= [_THISROW].[Date],
       [Due Date] &gt;= [Loan Date],
@@ -5224,7 +5268,7 @@
     AND(
       [Ref Borrowers] = [_THISROW].[Assessment Borrower],
       [Loan Status] = "ยังไม่ปิดยอด",
-      [Loan Type] = "ผ่อนชำระรายวัน",
+      [Loan Type] = "ผ่อนชำระรายวัน", [Auto Charge Enabled],
       [Loan Date] &lt;= [_THISROW].[Date],
       [Due Date] &gt;= [_THISROW].[Date],
       [Due Date] &gt;= [Loan Date],
@@ -5241,39 +5285,39 @@
       )
     )
   )
-)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" ht="15" customHeight="1">
-      <x:c r="A92" s="57" t="str">
+) + SUM(SELECT(Charges[Principal Remaining], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Assessment Borrower], [Ref Loans].[Loan Status] = "ยังไม่ปิดยอด", OR(NOT([Ref Loans].[Auto Charge Enabled]), AND([Ref Loans].[Loan Type] = "ดอกเบี้ยรายวัน", [Ref Loans].[Current Daily Interest] = 0)), [Charge Date] = [_THISROW].[Date], [Charge Date] &gt; TODAY())))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="135" customHeight="1">
+      <x:c r="A92" s="82" t="str">
         <x:v>Calendar</x:v>
       </x:c>
-      <x:c r="B92" s="57" t="n">
+      <x:c r="B92" s="82" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C92" s="59" t="str">
+      <x:c r="C92" s="82" t="str">
         <x:v>Assessment Installment Future Interest Due</x:v>
       </x:c>
-      <x:c r="D92" s="59" t="str">
+      <x:c r="D92" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E92" s="57" t="str">
+      <x:c r="E92" s="82" t="str">
         <x:v>OLAP only</x:v>
       </x:c>
-      <x:c r="F92" s="57" t="str">
-        <x:v>Hidden; whole baht</x:v>
-      </x:c>
-      <x:c r="G92" s="59" t="str">
-        <x:v>Scheduled daily-installment payment after the latest Charge minus future scheduled principal; Transfer Fee excluded.</x:v>
-      </x:c>
-      <x:c r="H92" s="59" t="str">
+      <x:c r="F92" s="82" t="str">
+        <x:v>Hidden; whole baht; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G92" s="82" t="str">
+        <x:v>Disabled loans use explicit schedule charges. Enabled loans retain contractual projection branches.</x:v>
+      </x:c>
+      <x:c r="H92" s="82" t="str">
         <x:v>SUM(
   SELECT(
     Loans[Daily Payment Amount],
     AND(
       [Ref Borrowers] = [_THISROW].[Assessment Borrower],
       [Loan Status] = "ยังไม่ปิดยอด",
-      [Loan Type] = "ผ่อนชำระรายวัน",
+      [Loan Type] = "ผ่อนชำระรายวัน", [Auto Charge Enabled],
       [Loan Date] &lt;= [_THISROW].[Date],
       [Due Date] &gt;= [_THISROW].[Date],
       [Due Date] &gt;= [Loan Date],
@@ -5286,56 +5330,33 @@
     )
   )
 )
-- [Assessment Installment Future Principal Due]</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="15" customHeight="1">
-      <x:c r="A93" s="57" t="str">
+- [Assessment Installment Future Principal Due] + SUM(SELECT(Charges[Amount Remaining], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Assessment Borrower], [Ref Loans].[Loan Status] = "ยังไม่ปิดยอด", OR(NOT([Ref Loans].[Auto Charge Enabled]), AND([Ref Loans].[Loan Type] = "ดอกเบี้ยรายวัน", [Ref Loans].[Current Daily Interest] = 0)), [Charge Date] = [_THISROW].[Date], [Charge Date] &gt; TODAY())))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="100" customHeight="1">
+      <x:c r="A93" s="82" t="str">
         <x:v>Calendar</x:v>
       </x:c>
-      <x:c r="B93" s="57" t="n">
+      <x:c r="B93" s="82" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C93" s="59" t="str">
+      <x:c r="C93" s="82" t="str">
         <x:v>Assessment Installment Contract Outstanding</x:v>
       </x:c>
-      <x:c r="D93" s="59" t="str">
+      <x:c r="D93" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E93" s="57" t="str">
+      <x:c r="E93" s="82" t="str">
         <x:v>OLAP only</x:v>
       </x:c>
-      <x:c r="F93" s="57" t="str">
-        <x:v>Hidden; whole baht</x:v>
-      </x:c>
-      <x:c r="G93" s="59" t="str">
-        <x:v>Nonnegative deterministic daily-installment contract balance after cumulative scheduled principal through the Calendar date.</x:v>
-      </x:c>
-      <x:c r="H93" s="59" t="str">
-        <x:v>MAX(
-  LIST(
-    [Assessment Installment Contract Principal Due] * 0,
-    SUM(
-      SELECT(
-        Loans[Principal Amount],
-        AND(
-          [Ref Borrowers] = [_THISROW].[Assessment Borrower],
-          [Loan Status] = "ยังไม่ปิดยอด",
-          [Loan Type] = "ผ่อนชำระรายวัน",
-          [Loan Date] &lt;= [_THISROW].[Date],
-          [Due Date] &gt;= [Loan Date],
-          [Daily Payment Amount] &gt; 0
-        )
-      )
-    )
-    - SUM(
-      SELECT(
-        Calendar[Assessment Installment Contract Principal Due],
-        [Date] &lt;= [_THISROW].[Date]
-      )
-    )
-  )
-)</x:v>
+      <x:c r="F93" s="82" t="str">
+        <x:v>Hidden; whole baht; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G93" s="82" t="str">
+        <x:v>Disabled loans use explicit schedule charges. Enabled loans retain contractual projection branches.</x:v>
+      </x:c>
+      <x:c r="H93" s="82" t="str">
+        <x:v>MAX(LIST([Assessment Installment Contract Principal Due] * 0, SUM(SELECT(Loans[Principal Amount], AND([Ref Borrowers] = [_THISROW].[Assessment Borrower], [Loan Status] = "ยังไม่ปิดยอด", [Loan Date] &lt;= [_THISROW].[Date], OR(AND([Loan Type] = "ผ่อนชำระรายวัน", [Auto Charge Enabled], [Due Date] &gt;= [Loan Date], [Daily Payment Amount] &gt; 0), OR(NOT([Auto Charge Enabled]), AND([Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest] = 0)))))) - SUM(SELECT(Calendar[Assessment Installment Contract Principal Due], [Date] &lt;= [_THISROW].[Date]))))</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="15" customHeight="1">
@@ -8226,30 +8247,30 @@
         <x:v>CONCATENATE( [Borrower Name], "-", TEXT([Principal Amount]), "-", TEXT([Loan Date], "DD/MM"), "-", TEXT([Effective Daily Interest Rate]))</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="15" customHeight="1">
-      <x:c r="A205" s="57" t="str">
+    <x:row r="205" ht="330" customHeight="1">
+      <x:c r="A205" s="82" t="str">
         <x:v>Loans</x:v>
       </x:c>
-      <x:c r="B205" s="57" t="n">
+      <x:c r="B205" s="82" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C205" s="59" t="str">
+      <x:c r="C205" s="82" t="str">
         <x:v>Expected Interest This Month</x:v>
       </x:c>
-      <x:c r="D205" s="59" t="str">
+      <x:c r="D205" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E205" s="57" t="str">
+      <x:c r="E205" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F205" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G205" s="59" t="str">
-        <x:v>Open-loan current-month interest forecast. Daily-installment interest covers only uncharged contract days after the latest posted Charge through the earlier of Due Date and month-end.</x:v>
-      </x:c>
-      <x:c r="H205" s="59" t="str">
-        <x:v>IF([Loan Status] = "ปิดยอดแล้ว", 0, IFS([Loan Type] = "ดอกเบี้ยรายวัน", MAX(LIST([Current Daily Interest] * 0, [Accrued Interest])) + ([Current Daily Interest] * (DAY(EOMONTH(TODAY(), 0)) - DAY(TODAY()))), [Loan Type] = "กำหนดวันชำระ", IF(AND([Due Date] &gt; TODAY(), MONTH([Due Date]) = MONTH(TODAY()), YEAR([Due Date]) = YEAR(TODAY())), [Fixed Interest], 0), [Loan Type] = "ผ่อนชำระรายวัน", IF(AND(ISNOTBLANK(MAX([Related Charges][Charge Date])), IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) &gt; MAX([Related Charges][Charge Date])), ([Daily Payment Amount] * IF(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) &gt; MAX([Related Charges][Charge Date]), TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - MAX([Related Charges][Charge Date])) / 24, 0)) - (FLOOR([Principal Amount] / (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1)) * IF(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) &gt; MAX([Related Charges][Charge Date]), TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - MAX([Related Charges][Charge Date])) / 24, 0) + IF((IF((TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - [Loan Date]) / 24 + 1) &lt; MOD([Principal Amount], (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1)), (TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - [Loan Date]) / 24 + 1), MOD([Principal Amount], (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1))) - (TOTALHOURS(MAX([Related Charges][Charge Date]) - [Loan Date]) / 24 + 2) + 1) &gt; 0, (IF((TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - [Loan Date]) / 24 + 1) &lt; MOD([Principal Amount], (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1)), (TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - [Loan Date]) / 24 + 1), MOD([Principal Amount], (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1))) - (TOTALHOURS(MAX([Related Charges][Charge Date]) - [Loan Date]) / 24 + 2) + 1), 0)), 0), TRUE, 0))</x:v>
+      <x:c r="F205" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G205" s="82" t="str">
+        <x:v>Disabled loans forecast entered future Interest Remaining through month-end. Nominal rates retained.</x:v>
+      </x:c>
+      <x:c r="H205" s="82" t="str">
+        <x:v>IF([Loan Status] = "ปิดยอดแล้ว", 0, IFS(OR(NOT([Auto Charge Enabled]), AND([Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest] = 0)), SUM(SELECT([Related Charges][Interest Remaining], AND([Charge Date] &gt; TODAY(), [Charge Date] &lt;= EOMONTH(TODAY(), 0)))), [Loan Type] = "ดอกเบี้ยรายวัน", MAX(LIST([Current Daily Interest] * 0, [Accrued Interest])) + ([Current Daily Interest] * (DAY(EOMONTH(TODAY(), 0)) - DAY(TODAY()))), [Loan Type] = "กำหนดวันชำระ", IF(AND([Due Date] &gt; TODAY(), MONTH([Due Date]) = MONTH(TODAY()), YEAR([Due Date]) = YEAR(TODAY())), [Fixed Interest], 0), [Loan Type] = "ผ่อนชำระรายวัน", IF(AND(ISNOTBLANK(MAX([Related Charges][Charge Date])), IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) &gt; MAX([Related Charges][Charge Date])), ([Daily Payment Amount] * IF(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) &gt; MAX([Related Charges][Charge Date]), TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - MAX([Related Charges][Charge Date])) / 24, 0)) - (FLOOR([Principal Amount] / (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1)) * IF(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) &gt; MAX([Related Charges][Charge Date]), TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - MAX([Related Charges][Charge Date])) / 24, 0) + IF((IF((TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - [Loan Date]) / 24 + 1) &lt; MOD([Principal Amount], (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1)), (TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - [Loan Date]) / 24 + 1), MOD([Principal Amount], (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1))) - (TOTALHOURS(MAX([Related Charges][Charge Date]) - [Loan Date]) / 24 + 2) + 1) &gt; 0, (IF((TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - [Loan Date]) / 24 + 1) &lt; MOD([Principal Amount], (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1)), (TOTALHOURS(IF([Due Date] &lt; EOMONTH(TODAY(), 0), [Due Date], EOMONTH(TODAY(), 0)) - [Loan Date]) / 24 + 1), MOD([Principal Amount], (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1))) - (TOTALHOURS(MAX([Related Charges][Charge Date]) - [Loan Date]) / 24 + 2) + 1), 0)), 0), TRUE, 0))</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="21.600000381469727" customHeight="1">
@@ -8642,108 +8663,108 @@
         <x:v>MAX(LIST(0) + SELECT(Charges[Days Late], [Ref Loans] = [_THISROW].[Row ID]))</x:v>
       </x:c>
     </x:row>
-    <x:row r="221" ht="15" customHeight="1">
-      <x:c r="A221" s="57" t="str">
+    <x:row r="221" ht="110" customHeight="1">
+      <x:c r="A221" s="82" t="str">
         <x:v>Loans</x:v>
       </x:c>
-      <x:c r="B221" s="57" t="n">
+      <x:c r="B221" s="82" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C221" s="59" t="str">
+      <x:c r="C221" s="82" t="str">
         <x:v>Last Interest Charge Date</x:v>
       </x:c>
-      <x:c r="D221" s="59" t="str">
+      <x:c r="D221" s="82" t="str">
         <x:v>VC / Date</x:v>
       </x:c>
-      <x:c r="E221" s="57" t="str">
+      <x:c r="E221" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F221" s="57" t="str">
-        <x:v>Searchable</x:v>
-      </x:c>
-      <x:c r="G221" s="59" t="str">
-        <x:v>Latest related Charge Date; the lower boundary for calculating uncharged daily-interest accrual.</x:v>
-      </x:c>
-      <x:c r="H221" s="59" t="str">
-        <x:v>MAX([Related Charges][Charge Date])</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222" ht="15" customHeight="1">
-      <x:c r="A222" s="57" t="str">
+      <x:c r="F221" s="82" t="str">
+        <x:v>Searchable; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G221" s="82" t="str">
+        <x:v>Latest related charge dated through today; ignores future schedule dates.</x:v>
+      </x:c>
+      <x:c r="H221" s="82" t="str">
+        <x:v>MAX(SELECT([Related Charges][Charge Date], [Charge Date] &lt;= TODAY()))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="110" customHeight="1">
+      <x:c r="A222" s="82" t="str">
         <x:v>Loans</x:v>
       </x:c>
-      <x:c r="B222" s="57" t="n">
+      <x:c r="B222" s="82" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C222" s="59" t="str">
+      <x:c r="C222" s="82" t="str">
         <x:v>Accrued Interest Days</x:v>
       </x:c>
-      <x:c r="D222" s="59" t="str">
+      <x:c r="D222" s="82" t="str">
         <x:v>VC / Number</x:v>
       </x:c>
-      <x:c r="E222" s="57" t="str">
+      <x:c r="E222" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F222" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G222" s="59" t="str">
-        <x:v>Elapsed accrual days since Last Interest Charge Date, or since Loan Date when no interest charge exists.</x:v>
-      </x:c>
-      <x:c r="H222" s="59" t="str">
-        <x:v>IF( ISBLANK([Last Interest Charge Date]), TOTALHOURS(TODAY() - [Loan Date])/24, TOTALHOURS(TODAY() - [Last Interest Charge Date])/24)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" ht="21.600000381469727" customHeight="1">
-      <x:c r="A223" s="57" t="str">
+      <x:c r="F222" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G222" s="82" t="str">
+        <x:v>Whole elapsed days since the last past/today charge or Loan Date, clamped to zero.</x:v>
+      </x:c>
+      <x:c r="H222" s="82" t="str">
+        <x:v>MAX(LIST(0, FLOOR(IF(ISBLANK([Last Interest Charge Date]), TOTALHOURS(TODAY() - [Loan Date]) / 24, TOTALHOURS(TODAY() - [Last Interest Charge Date]) / 24))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="100" customHeight="1">
+      <x:c r="A223" s="82" t="str">
         <x:v>Loans</x:v>
       </x:c>
-      <x:c r="B223" s="57" t="n">
+      <x:c r="B223" s="82" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C223" s="59" t="str">
+      <x:c r="C223" s="82" t="str">
         <x:v>Accrued Interest</x:v>
       </x:c>
-      <x:c r="D223" s="59" t="str">
+      <x:c r="D223" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E223" s="57" t="str">
+      <x:c r="E223" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F223" s="57" t="str">
-        <x:v>Show_If: [Loan Type] = "ดอกเบี้ยรายวัน"</x:v>
-      </x:c>
-      <x:c r="G223" s="59" t="str">
-        <x:v>Uncharged interest for a daily-interest loan, calculated from Current Daily Interest and Accrued Interest Days.</x:v>
-      </x:c>
-      <x:c r="H223" s="59" t="str">
-        <x:v>IF( [Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest] * [Accrued Interest Days], 0)</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224" ht="15" customHeight="1">
-      <x:c r="A224" s="57" t="str">
+      <x:c r="F223" s="82" t="str">
+        <x:v>Show_If: [Loan Type] = "ดอกเบี้ยรายวัน"; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G223" s="82" t="str">
+        <x:v>Returns zero when Auto Charge Enabled is off. Nominal interest terms remain stored.</x:v>
+      </x:c>
+      <x:c r="H223" s="82" t="str">
+        <x:v>IF([Auto Charge Enabled], IF( [Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest] * [Accrued Interest Days], 0), 0)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="100" customHeight="1">
+      <x:c r="A224" s="82" t="str">
         <x:v>Loans</x:v>
       </x:c>
-      <x:c r="B224" s="57" t="n">
+      <x:c r="B224" s="82" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C224" s="59" t="str">
+      <x:c r="C224" s="82" t="str">
         <x:v>Expected Daily Interest Amount</x:v>
       </x:c>
-      <x:c r="D224" s="59" t="str">
+      <x:c r="D224" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E224" s="57" t="str">
+      <x:c r="E224" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F224" s="57" t="str">
-        <x:v>Hidden in OLTP + OLAP; OLAP Price with 2 decimal digits</x:v>
-      </x:c>
-      <x:c r="G224" s="59" t="str">
-        <x:v>Open-loan daily-interest amount used by operational forecasts: entered daily interest for daily-interest loans and average contract interest for daily-installment loans; zero otherwise.</x:v>
-      </x:c>
-      <x:c r="H224" s="59" t="str">
-        <x:v>IFS( [Loan Status] &lt;&gt; "ยังไม่ปิดยอด", 0, [Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest], AND( [Loan Type] = "ผ่อนชำระรายวัน", ISNOTBLANK([Loan Date]), ISNOTBLANK([Due Date]), [Due Date] &gt;= [Loan Date], [Daily Payment Amount] &gt; 0 ), ( ([Daily Payment Amount] * (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1)) - [Principal Amount] ) / (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1), TRUE, 0)</x:v>
+      <x:c r="F224" s="82" t="str">
+        <x:v>Hidden in OLTP + OLAP; OLAP Price with 2 decimal digits; flag expressions verified OLTP 3.000028 / OLAP 1.100020 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G224" s="82" t="str">
+        <x:v>Returns zero when Auto Charge Enabled is off. Nominal interest terms remain stored.</x:v>
+      </x:c>
+      <x:c r="H224" s="82" t="str">
+        <x:v>IF([Auto Charge Enabled], IFS( [Loan Status] &lt;&gt; "ยังไม่ปิดยอด", 0, [Loan Type] = "ดอกเบี้ยรายวัน", [Current Daily Interest], AND( [Loan Type] = "ผ่อนชำระรายวัน", ISNOTBLANK([Loan Date]), ISNOTBLANK([Due Date]), [Due Date] &gt;= [Loan Date], [Daily Payment Amount] &gt; 0 ), ( ([Daily Payment Amount] * (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1)) - [Principal Amount] ) / (TOTALHOURS([Due Date] - [Loan Date]) / 24 + 1), TRUE, 0), 0)</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="15" customHeight="1">
@@ -10304,30 +10325,30 @@
         <x:v>[Realized Profit MTD]+[Today's Outstanding Interest]+[Forecast Remaining Interest]</x:v>
       </x:c>
     </x:row>
-    <x:row r="284" ht="15" customHeight="1">
-      <x:c r="A284" s="57" t="str">
+    <x:row r="284" ht="110" customHeight="1">
+      <x:c r="A284" s="82" t="str">
         <x:v>Statistics</x:v>
       </x:c>
-      <x:c r="B284" s="57" t="n">
+      <x:c r="B284" s="82" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C284" s="59" t="str">
+      <x:c r="C284" s="82" t="str">
         <x:v>Pending Payment Amount</x:v>
       </x:c>
-      <x:c r="D284" s="59" t="str">
+      <x:c r="D284" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E284" s="57" t="str">
+      <x:c r="E284" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F284" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G284" s="59" t="str">
-        <x:v>Broad sum of all Charges[Amount Remaining] across dates and references; currently reconciles to Collection only while source referential integrity and population scope remain aligned.</x:v>
-      </x:c>
-      <x:c r="H284" s="59" t="str">
-        <x:v>SUM(Charges[Amount Remaining])</x:v>
+      <x:c r="F284" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G284" s="82" t="str">
+        <x:v>Remaining amount for referenced charges with Charge Date &lt;= TODAY. Future charges excluded.</x:v>
+      </x:c>
+      <x:c r="H284" s="82" t="str">
+        <x:v>SUM(SELECT(Charges[Amount Remaining], AND(ISNOTBLANK([Ref Loans]), [Charge Date] &lt;= TODAY())))</x:v>
       </x:c>
     </x:row>
     <x:row r="285" ht="15" customHeight="1">
@@ -10356,30 +10377,30 @@
         <x:v>SUM(Loans[Expected Interest This Month])</x:v>
       </x:c>
     </x:row>
-    <x:row r="286" ht="15" customHeight="1">
-      <x:c r="A286" s="57" t="str">
+    <x:row r="286" ht="110" customHeight="1">
+      <x:c r="A286" s="82" t="str">
         <x:v>Statistics</x:v>
       </x:c>
-      <x:c r="B286" s="57" t="n">
+      <x:c r="B286" s="82" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C286" s="59" t="str">
+      <x:c r="C286" s="82" t="str">
         <x:v>Today's Outstanding Interest</x:v>
       </x:c>
-      <x:c r="D286" s="59" t="str">
+      <x:c r="D286" s="82" t="str">
         <x:v>VC / Price</x:v>
       </x:c>
-      <x:c r="E286" s="57" t="str">
+      <x:c r="E286" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F286" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G286" s="59" t="str">
-        <x:v>Remaining interest across all open Charges without a Charge Date filter; may include prior-period arrears.</x:v>
-      </x:c>
-      <x:c r="H286" s="59" t="str">
-        <x:v>SUM(Charges[Interest Remaining])</x:v>
+      <x:c r="F286" s="82" t="str">
+        <x:v>-; formula inspected OLTP 3.000026 / OLAP 1.100018 as applicable; manual acceptance pending</x:v>
+      </x:c>
+      <x:c r="G286" s="82" t="str">
+        <x:v>Remaining interest for referenced charges with Charge Date &lt;= TODAY. Future charges excluded.</x:v>
+      </x:c>
+      <x:c r="H286" s="82" t="str">
+        <x:v>SUM(SELECT(Charges[Interest Remaining], AND(ISNOTBLANK([Ref Loans]), [Charge Date] &lt;= TODAY())))</x:v>
       </x:c>
     </x:row>
     <x:row r="287" ht="15" customHeight="1">
@@ -12610,6 +12631,630 @@
       <x:c r="H369" s="76" t="str">
         <x:v>OLTP: REF_ROWS("Payments", "Ref Target Charge")
 OLAP v1.100016: List. Same REF_ROWS expression. Initial value blank. No operational payment actions or processing formulas imported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" ht="15" customHeight="1">
+      <x:c r="A370" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B370" s="87" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C370" s="87" t="str">
+        <x:v>Communication Name</x:v>
+      </x:c>
+      <x:c r="D370" s="87" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E370" s="87" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F370" s="87" t="str">
+        <x:v>Editable</x:v>
+      </x:c>
+      <x:c r="G370" s="87" t="str">
+        <x:v>Explicit message address; no suffix stripping. App physical position 8.</x:v>
+      </x:c>
+      <x:c r="H370" s="87" t="str">
+        <x:v>Stored; blank initial value; display name: "ชื่อที่ใช้เรียก / Communication Name"</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" ht="15" customHeight="1">
+      <x:c r="A371" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B371" s="87" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C371" s="87" t="str">
+        <x:v>Instagram Username</x:v>
+      </x:c>
+      <x:c r="D371" s="87" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E371" s="87" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F371" s="87" t="str">
+        <x:v>Editable</x:v>
+      </x:c>
+      <x:c r="G371" s="87" t="str">
+        <x:v>Borrower Instagram handle without @; app physical position 9.</x:v>
+      </x:c>
+      <x:c r="H371" s="87" t="str">
+        <x:v>Stored; blank initial value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" ht="15" customHeight="1">
+      <x:c r="A372" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B372" s="87" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C372" s="87" t="str">
+        <x:v>Instagram Conversation URL</x:v>
+      </x:c>
+      <x:c r="D372" s="87" t="str">
+        <x:v>Physical / Url</x:v>
+      </x:c>
+      <x:c r="E372" s="87" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F372" s="87" t="str">
+        <x:v>Editable</x:v>
+      </x:c>
+      <x:c r="G372" s="87" t="str">
+        <x:v>Verified conversation link; native Text, app Url; position 10.</x:v>
+      </x:c>
+      <x:c r="H372" s="87" t="str">
+        <x:v>Stored; blank initial value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" ht="15" customHeight="1">
+      <x:c r="A373" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B373" s="87" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C373" s="87" t="str">
+        <x:v>Instagram Verified At</x:v>
+      </x:c>
+      <x:c r="D373" s="87" t="str">
+        <x:v>Physical / DateTime</x:v>
+      </x:c>
+      <x:c r="E373" s="87" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F373" s="87" t="str">
+        <x:v>Editable</x:v>
+      </x:c>
+      <x:c r="G373" s="87" t="str">
+        <x:v>Time mapping was actually checked; position 11.</x:v>
+      </x:c>
+      <x:c r="H373" s="87" t="str">
+        <x:v>Stored; blank initial value (removed inferred NOW())</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" ht="15" customHeight="1">
+      <x:c r="A374" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B374" s="87" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C374" s="87" t="str">
+        <x:v>AI Collection Enabled</x:v>
+      </x:c>
+      <x:c r="D374" s="87" t="str">
+        <x:v>Physical / Yes/No</x:v>
+      </x:c>
+      <x:c r="E374" s="87" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F374" s="87" t="str">
+        <x:v>Editable</x:v>
+      </x:c>
+      <x:c r="G374" s="87" t="str">
+        <x:v>Opt-in for the existing AI collection workflow; position 12.</x:v>
+      </x:c>
+      <x:c r="H374" s="87" t="str">
+        <x:v>Stored; initial value FALSE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" ht="15" customHeight="1">
+      <x:c r="A375" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B375" s="87" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C375" s="87" t="str">
+        <x:v>Late Penalty Enabled</x:v>
+      </x:c>
+      <x:c r="D375" s="87" t="str">
+        <x:v>Physical / Yes/No</x:v>
+      </x:c>
+      <x:c r="E375" s="87" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F375" s="87" t="str">
+        <x:v>Editable</x:v>
+      </x:c>
+      <x:c r="G375" s="87" t="str">
+        <x:v>Independent penalty eligibility; position 13. Existing fees never reversed by this flag.</x:v>
+      </x:c>
+      <x:c r="H375" s="87" t="str">
+        <x:v>Stored; initial value FALSE; daily eligibility held in runner SQLite</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" ht="15" customHeight="1">
+      <x:c r="A376" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B376" s="87" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C376" s="87" t="str">
+        <x:v>Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="D376" s="87" t="str">
+        <x:v>Physical / Ref</x:v>
+      </x:c>
+      <x:c r="E376" s="87" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F376" s="87" t="str">
+        <x:v>Editable, Optional</x:v>
+      </x:c>
+      <x:c r="G376" s="87" t="str">
+        <x:v>Borrower-specific receiving bank; position 14.</x:v>
+      </x:c>
+      <x:c r="H376" s="87" t="str">
+        <x:v>Stored native Reference and app Ref -&gt; Collection Bank Accounts; independent lifecycle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" ht="15" customHeight="1">
+      <x:c r="A377" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B377" s="87" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C377" s="87" t="str">
+        <x:v>Effective Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="D377" s="87" t="str">
+        <x:v>Virtual / Ref</x:v>
+      </x:c>
+      <x:c r="E377" s="87" t="str">
+        <x:v>OLTP only</x:v>
+      </x:c>
+      <x:c r="F377" s="87" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="G377" s="87" t="str">
+        <x:v>Borrower override, otherwise singleton default; Ref -&gt; Collection Bank Accounts.</x:v>
+      </x:c>
+      <x:c r="H377" s="87" t="str">
+        <x:v>IF(ISNOTBLANK([Receiving Bank Account]), [Receiving Bank Account], IF(COUNT(Collection Settings[Row ID]) = 1, ANY(Collection Settings[Default Receiving Bank Account]), ""))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" ht="15" customHeight="1">
+      <x:c r="A378" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B378" s="87" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C378" s="87" t="str">
+        <x:v>Collection Setup Issues</x:v>
+      </x:c>
+      <x:c r="D378" s="87" t="str">
+        <x:v>Virtual / Text</x:v>
+      </x:c>
+      <x:c r="E378" s="87" t="str">
+        <x:v>OLTP only</x:v>
+      </x:c>
+      <x:c r="F378" s="87" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="G378" s="87" t="str">
+        <x:v>Enabled borrower name, Instagram mapping/duplicate and effective-bank checks.</x:v>
+      </x:c>
+      <x:c r="H378" s="87" t="str">
+        <x:v>IF([AI Collection Enabled], CONCATENATE(IF(ISBLANK(TRIM([Communication Name])), "Enter communication name. ", ""), IF(ISBLANK([Instagram Username]), "Enter Instagram username. ", IF(OR(CONTAINS([Instagram Username], "@"), CONTAINS([Instagram Username], " "), CONTAINS([Instagram Username], "/")), "Use username only, without @, spaces or URL. ", "")), IF(AND(ISNOTBLANK([Instagram Username]), COUNT(SELECT(Borrowers[Row ID], AND(LOWER([Instagram Username]) = LOWER([_THISROW].[Instagram Username]), [Row ID] &lt;&gt; [_THISROW].[Row ID]))) &gt; 0), "Instagram username is mapped to another borrower. ", ""), IF(NOT(STARTSWITH([Instagram Conversation URL], "https://www.instagram.com/direct/t/")), "Enter verified Instagram conversation URL. ", ""), IF(ISBLANK([Instagram Verified At]), "Verify Instagram mapping. ", ""), IF(ISBLANK([Effective Receiving Bank Account]), "Select borrower bank or one shared default. ", IF(NOT([Effective Receiving Bank Account].[Active]), "Receiving bank account is inactive. ", IF(OR(ISBLANK([Effective Receiving Bank Account].[Bank Name]), ISBLANK([Effective Receiving Bank Account].[Account Number]), ISBLANK([Effective Receiving Bank Account].[Account Holder Name])), "Complete receiving bank details. ", "")))), "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" ht="15" customHeight="1">
+      <x:c r="A379" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B379" s="87" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C379" s="87" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="D379" s="87" t="str">
+        <x:v>Physical / Number</x:v>
+      </x:c>
+      <x:c r="E379" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F379" s="87" t="str">
+        <x:v>Hidden</x:v>
+      </x:c>
+      <x:c r="G379" s="87" t="str">
+        <x:v>Source ordinal, never identity.</x:v>
+      </x:c>
+      <x:c r="H379" s="87" t="str">
+        <x:v>Stored system column</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" ht="15" customHeight="1">
+      <x:c r="A380" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B380" s="87" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C380" s="87" t="str">
+        <x:v>Row ID</x:v>
+      </x:c>
+      <x:c r="D380" s="87" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E380" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F380" s="87" t="str">
+        <x:v>Key, Required, Hidden</x:v>
+      </x:c>
+      <x:c r="G380" s="87" t="str">
+        <x:v>Immutable native key.</x:v>
+      </x:c>
+      <x:c r="H380" s="87" t="str">
+        <x:v>Stored; initial value UNIQUEID("PackedUUID")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" ht="15" customHeight="1">
+      <x:c r="A381" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B381" s="87" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C381" s="87" t="str">
+        <x:v>Account Label</x:v>
+      </x:c>
+      <x:c r="D381" s="87" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E381" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F381" s="87" t="str">
+        <x:v>Label, Required, Editable</x:v>
+      </x:c>
+      <x:c r="G381" s="87" t="str">
+        <x:v>Recognizable receiving-account label.</x:v>
+      </x:c>
+      <x:c r="H381" s="87" t="str">
+        <x:v>Stored</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" ht="15" customHeight="1">
+      <x:c r="A382" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B382" s="87" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C382" s="87" t="str">
+        <x:v>Bank Name</x:v>
+      </x:c>
+      <x:c r="D382" s="87" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E382" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F382" s="87" t="str">
+        <x:v>Required, Editable</x:v>
+      </x:c>
+      <x:c r="G382" s="87" t="str">
+        <x:v>Bank shown in messages.</x:v>
+      </x:c>
+      <x:c r="H382" s="87" t="str">
+        <x:v>Stored</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" ht="15" customHeight="1">
+      <x:c r="A383" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B383" s="87" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C383" s="87" t="str">
+        <x:v>Account Number</x:v>
+      </x:c>
+      <x:c r="D383" s="87" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E383" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F383" s="87" t="str">
+        <x:v>Required, Editable</x:v>
+      </x:c>
+      <x:c r="G383" s="87" t="str">
+        <x:v>Preserve leading zeros and supplied separators.</x:v>
+      </x:c>
+      <x:c r="H383" s="87" t="str">
+        <x:v>Stored</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" ht="15" customHeight="1">
+      <x:c r="A384" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B384" s="87" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C384" s="87" t="str">
+        <x:v>Account Holder Name</x:v>
+      </x:c>
+      <x:c r="D384" s="87" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E384" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F384" s="87" t="str">
+        <x:v>Required, Editable</x:v>
+      </x:c>
+      <x:c r="G384" s="87" t="str">
+        <x:v>Receiving account holder.</x:v>
+      </x:c>
+      <x:c r="H384" s="87" t="str">
+        <x:v>Stored</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" ht="15" customHeight="1">
+      <x:c r="A385" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B385" s="87" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C385" s="87" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="D385" s="87" t="str">
+        <x:v>Physical / Yes/No</x:v>
+      </x:c>
+      <x:c r="E385" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F385" s="87" t="str">
+        <x:v>Editable</x:v>
+      </x:c>
+      <x:c r="G385" s="87" t="str">
+        <x:v>Deactivate instead of deleting used accounts.</x:v>
+      </x:c>
+      <x:c r="H385" s="87" t="str">
+        <x:v>Stored; initial value TRUE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" ht="15" customHeight="1">
+      <x:c r="A386" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B386" s="87" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C386" s="87" t="str">
+        <x:v>Related Collection Settings</x:v>
+      </x:c>
+      <x:c r="D386" s="87" t="str">
+        <x:v>Virtual / List (Ref)</x:v>
+      </x:c>
+      <x:c r="E386" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F386" s="87" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="G386" s="87" t="str">
+        <x:v>Default-setting reverse reference.</x:v>
+      </x:c>
+      <x:c r="H386" s="87" t="str">
+        <x:v>REF_ROWS("Collection Settings", "Default Receiving Bank Account")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" ht="15" customHeight="1">
+      <x:c r="A387" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B387" s="87" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C387" s="87" t="str">
+        <x:v>Related Borrowers</x:v>
+      </x:c>
+      <x:c r="D387" s="87" t="str">
+        <x:v>Virtual / List (Ref)</x:v>
+      </x:c>
+      <x:c r="E387" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F387" s="87" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="G387" s="87" t="str">
+        <x:v>Borrower override reverse reference.</x:v>
+      </x:c>
+      <x:c r="H387" s="87" t="str">
+        <x:v>REF_ROWS("Borrowers", "Receiving Bank Account")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" ht="30" customHeight="1">
+      <x:c r="A388" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="B388" s="87" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C388" s="88" t="str">
+        <x:v>Related Borrowers By Effective Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="D388" s="87" t="str">
+        <x:v>Virtual / List (Ref)</x:v>
+      </x:c>
+      <x:c r="E388" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F388" s="87" t="str">
+        <x:v>Read-only</x:v>
+      </x:c>
+      <x:c r="G388" s="87" t="str">
+        <x:v>Includes borrowers inheriting the shared default.</x:v>
+      </x:c>
+      <x:c r="H388" s="87" t="str">
+        <x:v>REF_ROWS("Borrowers", "Effective Receiving Bank Account")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" ht="15" customHeight="1">
+      <x:c r="A389" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="B389" s="87" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C389" s="87" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="D389" s="87" t="str">
+        <x:v>Physical / Number</x:v>
+      </x:c>
+      <x:c r="E389" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F389" s="87" t="str">
+        <x:v>Hidden</x:v>
+      </x:c>
+      <x:c r="G389" s="87" t="str">
+        <x:v>Source ordinal, never identity.</x:v>
+      </x:c>
+      <x:c r="H389" s="87" t="str">
+        <x:v>Stored system column</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" ht="15" customHeight="1">
+      <x:c r="A390" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="B390" s="87" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C390" s="87" t="str">
+        <x:v>Row ID</x:v>
+      </x:c>
+      <x:c r="D390" s="87" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E390" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F390" s="87" t="str">
+        <x:v>Key, Required, Hidden</x:v>
+      </x:c>
+      <x:c r="G390" s="87" t="str">
+        <x:v>Immutable native key.</x:v>
+      </x:c>
+      <x:c r="H390" s="87" t="str">
+        <x:v>Stored; initial value UNIQUEID("PackedUUID")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" ht="15" customHeight="1">
+      <x:c r="A391" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="B391" s="87" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C391" s="87" t="str">
+        <x:v>Setting Name</x:v>
+      </x:c>
+      <x:c r="D391" s="87" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E391" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F391" s="87" t="str">
+        <x:v>Label, Not editable</x:v>
+      </x:c>
+      <x:c r="G391" s="87" t="str">
+        <x:v>Singleton setting label; one shared row.</x:v>
+      </x:c>
+      <x:c r="H391" s="87" t="str">
+        <x:v>Stored</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" ht="15" customHeight="1">
+      <x:c r="A392" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="B392" s="87" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C392" s="87" t="str">
+        <x:v>Default Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="D392" s="87" t="str">
+        <x:v>Physical / Ref</x:v>
+      </x:c>
+      <x:c r="E392" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="F392" s="87" t="str">
+        <x:v>Required, Editable</x:v>
+      </x:c>
+      <x:c r="G392" s="87" t="str">
+        <x:v>Shared default for borrowers without override.</x:v>
+      </x:c>
+      <x:c r="H392" s="87" t="str">
+        <x:v>Stored native Reference and app Ref -&gt; Collection Bank Accounts; independent lifecycle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" ht="135" customHeight="1">
+      <x:c r="A393" s="73" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="B393" s="73" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C393" s="73" t="str">
+        <x:v>Auto Charge Enabled</x:v>
+      </x:c>
+      <x:c r="D393" s="73" t="str">
+        <x:v>Physical / Yes/No</x:v>
+      </x:c>
+      <x:c r="E393" s="73" t="str">
+        <x:v>OLTP + OLAP</x:v>
+      </x:c>
+      <x:c r="F393" s="73" t="str">
+        <x:v>OLTP editable; OLAP read-only</x:v>
+      </x:c>
+      <x:c r="G393" s="73" t="str">
+        <x:v>TRUE permits generated charges. FALSE disables direct/bulk/bot generation and accrual; manual Charges entry allowed. Existing rows initialized TRUE, then 14 plan loans FALSE.</x:v>
+      </x:c>
+      <x:c r="H393" s="73" t="str">
+        <x:v>Initial value: TRUE. No app formula. Native key h7VnJR1ERY4o6UUaiANzwe. Restore nominal rates without re-enabling generation.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12623,7 +13268,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R309e64d2cbac41cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82452079846c4a65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12648,7 +13293,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>All six payment trace Refs resolve in both apps. OLTP ownership settings retained. All six OLAP payment Refs are independent; new tables and Repayments are READ_ONLY.</x:v>
+        <x:v>Collection bank Refs use immutable Row IDs and independent lifecycles. Existing loan/payment references remain unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -12992,6 +13637,57 @@
       </x:c>
       <x:c r="E18" s="73" t="str">
         <x:v>OLTP independent; optional historical/default trace; native Reference; OLAP loaded, READ_ONLY, IsPartOf false</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" customHeight="1">
+      <x:c r="A19" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B19" s="87" t="str">
+        <x:v>Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="C19" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="D19" s="87" t="str">
+        <x:v>Bank account 1 -&gt; many borrower overrides</x:v>
+      </x:c>
+      <x:c r="E19" s="87" t="str">
+        <x:v>Independent; optional stored Ref</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" customHeight="1">
+      <x:c r="A20" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B20" s="87" t="str">
+        <x:v>Effective Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="C20" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="D20" s="87" t="str">
+        <x:v>Bank account 1 -&gt; many effective borrower accounts</x:v>
+      </x:c>
+      <x:c r="E20" s="87" t="str">
+        <x:v>Computed Ref; no ownership/cascade</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" customHeight="1">
+      <x:c r="A21" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="B21" s="87" t="str">
+        <x:v>Default Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="C21" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="D21" s="87" t="str">
+        <x:v>Bank account 1 -&gt; shared setting</x:v>
+      </x:c>
+      <x:c r="E21" s="87" t="str">
+        <x:v>Independent; required stored Ref</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13001,7 +13697,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf9d80e7ef944275"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7deb2b9fc0f942a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13034,7 +13730,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>OLTP Visible Borrowers33 and Todays Collection Board12 fields reconciled at production cutover. Existing OLAP slices retained without schema regeneration.</x:v>
+        <x:v>OLTP Visible Borrowers and Collection Setup Review include42 fields. Todays Collection Board contains19 after seven physical collection fields were appended during regeneration. OLAP slices unchanged by this build.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -13097,13 +13793,13 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F5" s="83" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G5" s="83" t="str">
-        <x:v>Read-only borrower workboard restricted to borrowers with a current collection status.</x:v>
+        <x:v>Existing collection-board filter retained; seven physical collection settings appended during regeneration.</x:v>
       </x:c>
       <x:c r="H5" s="83" t="str">
-        <x:v>Production 3.000002; exact ordered membership reconciled to accepted clone. Auto-assigned actions.</x:v>
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); base-row details provide effective bank and setup issues.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="55" customHeight="1">
@@ -13123,13 +13819,13 @@
         <x:v>Adds, Updates, Deletes</x:v>
       </x:c>
       <x:c r="F6" s="83" t="n">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G6" s="83" t="str">
-        <x:v>Editable borrower-list slice excluding hidden rows; includes the principal-coverage metric.</x:v>
+        <x:v>Existing borrower-list filter retained; nine collection fields appended.</x:v>
       </x:c>
       <x:c r="H6" s="83" t="str">
-        <x:v>Production 3.000002; exact ordered membership reconciled to accepted clone. Auto-assigned actions.</x:v>
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); borrower edit/detail views expose the new fields.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -13420,6 +14116,32 @@
       </x:c>
       <x:c r="H18" s="72" t="str">
         <x:v>OLAP read-only mirror of the OLTP Todays Collection Board for daily collection export and message-drafting review. The exact column set is adapted to available OLAP fields.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" customHeight="1">
+      <x:c r="A19" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B19" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C19" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D19" s="87" t="str">
+        <x:v>AND([AI Collection Enabled], ISNOTBLANK([Collection Setup Issues]))</x:v>
+      </x:c>
+      <x:c r="E19" s="87" t="str">
+        <x:v>Updates only</x:v>
+      </x:c>
+      <x:c r="F19" s="87" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G19" s="87" t="str">
+        <x:v>Enabled borrowers needing name, Instagram or receiving-bank setup.</x:v>
+      </x:c>
+      <x:c r="H19" s="87" t="str">
+        <x:v>Auto-assigned actions; menu table view; disabled borrowers excluded intentionally.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13429,7 +14151,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80c610d8cce24a42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R582be9882b104751"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18772,6 +19494,818 @@
         <x:v>Overdue Amount</x:v>
       </x:c>
     </x:row>
+    <x:row r="383" ht="15" customHeight="1">
+      <x:c r="A383" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B383" s="87" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C383" s="87" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D383" s="87" t="str">
+        <x:v>Communication Name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" ht="15" customHeight="1">
+      <x:c r="A384" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B384" s="87" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C384" s="87" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D384" s="87" t="str">
+        <x:v>Instagram Username</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" ht="15" customHeight="1">
+      <x:c r="A385" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B385" s="87" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C385" s="87" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D385" s="87" t="str">
+        <x:v>Instagram Conversation URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" ht="15" customHeight="1">
+      <x:c r="A386" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B386" s="87" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C386" s="87" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D386" s="87" t="str">
+        <x:v>Instagram Verified At</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" ht="15" customHeight="1">
+      <x:c r="A387" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B387" s="87" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C387" s="87" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D387" s="87" t="str">
+        <x:v>AI Collection Enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" ht="15" customHeight="1">
+      <x:c r="A388" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B388" s="87" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C388" s="87" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D388" s="87" t="str">
+        <x:v>Late Penalty Enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" ht="15" customHeight="1">
+      <x:c r="A389" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B389" s="87" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C389" s="87" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D389" s="87" t="str">
+        <x:v>Receiving Bank Account</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" ht="15" customHeight="1">
+      <x:c r="A390" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B390" s="87" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C390" s="87" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D390" s="87" t="str">
+        <x:v>Effective Receiving Bank Account</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" ht="15" customHeight="1">
+      <x:c r="A391" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B391" s="87" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C391" s="87" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D391" s="87" t="str">
+        <x:v>Collection Setup Issues</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" ht="15" customHeight="1">
+      <x:c r="A392" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B392" s="87" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C392" s="87" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D392" s="87" t="str">
+        <x:v>Communication Name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" ht="15" customHeight="1">
+      <x:c r="A393" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B393" s="87" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C393" s="87" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D393" s="87" t="str">
+        <x:v>Instagram Username</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" ht="15" customHeight="1">
+      <x:c r="A394" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B394" s="87" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C394" s="87" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D394" s="87" t="str">
+        <x:v>Instagram Conversation URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" ht="15" customHeight="1">
+      <x:c r="A395" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B395" s="87" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C395" s="87" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D395" s="87" t="str">
+        <x:v>Instagram Verified At</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" ht="15" customHeight="1">
+      <x:c r="A396" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B396" s="87" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C396" s="87" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D396" s="87" t="str">
+        <x:v>AI Collection Enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" ht="15" customHeight="1">
+      <x:c r="A397" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B397" s="87" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C397" s="87" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D397" s="87" t="str">
+        <x:v>Late Penalty Enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="15" customHeight="1">
+      <x:c r="A398" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B398" s="87" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C398" s="87" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D398" s="87" t="str">
+        <x:v>Receiving Bank Account</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" ht="15" customHeight="1">
+      <x:c r="A399" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B399" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C399" s="87" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D399" s="87" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" ht="15" customHeight="1">
+      <x:c r="A400" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B400" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C400" s="87" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D400" s="87" t="str">
+        <x:v>Row ID</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" ht="15" customHeight="1">
+      <x:c r="A401" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B401" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C401" s="87" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D401" s="87" t="str">
+        <x:v>Borrower Name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" ht="15" customHeight="1">
+      <x:c r="A402" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B402" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C402" s="87" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D402" s="87" t="str">
+        <x:v>Telephone</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" ht="15" customHeight="1">
+      <x:c r="A403" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B403" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C403" s="87" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D403" s="87" t="str">
+        <x:v>Description</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" ht="15" customHeight="1">
+      <x:c r="A404" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B404" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C404" s="87" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D404" s="87" t="str">
+        <x:v>Creation Date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" ht="15" customHeight="1">
+      <x:c r="A405" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B405" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C405" s="87" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D405" s="87" t="str">
+        <x:v>Hidden Flag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" ht="15" customHeight="1">
+      <x:c r="A406" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B406" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C406" s="87" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D406" s="87" t="str">
+        <x:v>Communication Name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" ht="15" customHeight="1">
+      <x:c r="A407" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B407" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C407" s="87" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D407" s="87" t="str">
+        <x:v>Instagram Username</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" ht="15" customHeight="1">
+      <x:c r="A408" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B408" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C408" s="87" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D408" s="87" t="str">
+        <x:v>Instagram Conversation URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="15" customHeight="1">
+      <x:c r="A409" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B409" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C409" s="87" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D409" s="87" t="str">
+        <x:v>Instagram Verified At</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="15" customHeight="1">
+      <x:c r="A410" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B410" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C410" s="87" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D410" s="87" t="str">
+        <x:v>AI Collection Enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" ht="15" customHeight="1">
+      <x:c r="A411" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B411" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C411" s="87" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D411" s="87" t="str">
+        <x:v>Late Penalty Enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="15" customHeight="1">
+      <x:c r="A412" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B412" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C412" s="87" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D412" s="87" t="str">
+        <x:v>Receiving Bank Account</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" ht="15" customHeight="1">
+      <x:c r="A413" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B413" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C413" s="87" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D413" s="87" t="str">
+        <x:v>Related Loans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="15" customHeight="1">
+      <x:c r="A414" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B414" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C414" s="87" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D414" s="87" t="str">
+        <x:v>Total Interest Earned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" ht="15" customHeight="1">
+      <x:c r="A415" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B415" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C415" s="87" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D415" s="87" t="str">
+        <x:v>Total Amount Loaned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="15" customHeight="1">
+      <x:c r="A416" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B416" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C416" s="87" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D416" s="87" t="str">
+        <x:v>Total Number of Loans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" ht="15" customHeight="1">
+      <x:c r="A417" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B417" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C417" s="87" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D417" s="87" t="str">
+        <x:v>Total Outstanding Principal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="15" customHeight="1">
+      <x:c r="A418" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B418" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C418" s="87" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D418" s="87" t="str">
+        <x:v>Header - Active Loans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" ht="15" customHeight="1">
+      <x:c r="A419" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B419" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C419" s="87" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D419" s="87" t="str">
+        <x:v>Borrower Name TE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="15" customHeight="1">
+      <x:c r="A420" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B420" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C420" s="87" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D420" s="87" t="str">
+        <x:v>Return on Active Principal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" ht="15" customHeight="1">
+      <x:c r="A421" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B421" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C421" s="87" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D421" s="87" t="str">
+        <x:v>Active Loan Interest Earned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" ht="15" customHeight="1">
+      <x:c r="A422" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B422" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C422" s="87" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D422" s="87" t="str">
+        <x:v>Active Daily Interest</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" ht="15" customHeight="1">
+      <x:c r="A423" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B423" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C423" s="87" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D423" s="87" t="str">
+        <x:v>Projected Interest Coverage Date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="15" customHeight="1">
+      <x:c r="A424" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B424" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C424" s="87" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D424" s="87" t="str">
+        <x:v>Closed Loan Interest Earned</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" ht="15" customHeight="1">
+      <x:c r="A425" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B425" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C425" s="87" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D425" s="87" t="str">
+        <x:v>Closed Loan Principle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" ht="15" customHeight="1">
+      <x:c r="A426" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B426" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C426" s="87" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D426" s="87" t="str">
+        <x:v>Has Closed Loan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" ht="15" customHeight="1">
+      <x:c r="A427" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B427" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C427" s="87" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D427" s="87" t="str">
+        <x:v>Return on Closed Loans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="15" customHeight="1">
+      <x:c r="A428" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B428" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C428" s="87" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D428" s="87" t="str">
+        <x:v>Header - Closed Loans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" ht="15" customHeight="1">
+      <x:c r="A429" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B429" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C429" s="87" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D429" s="87" t="str">
+        <x:v>Has Active Loan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="15" customHeight="1">
+      <x:c r="A430" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B430" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C430" s="87" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D430" s="87" t="str">
+        <x:v>Daily Collection Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" ht="15" customHeight="1">
+      <x:c r="A431" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B431" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C431" s="87" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D431" s="87" t="str">
+        <x:v>Todays Collection Charges</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="15" customHeight="1">
+      <x:c r="A432" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B432" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C432" s="87" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D432" s="87" t="str">
+        <x:v>Todays Amount Due</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="15" customHeight="1">
+      <x:c r="A433" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B433" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C433" s="87" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D433" s="87" t="str">
+        <x:v>Todays Amount Collected</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" ht="15" customHeight="1">
+      <x:c r="A434" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B434" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C434" s="87" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D434" s="87" t="str">
+        <x:v>Todays Amount Remaining</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" ht="15" customHeight="1">
+      <x:c r="A435" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B435" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C435" s="87" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D435" s="87" t="str">
+        <x:v>Daily Collection Status - Order</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" ht="15" customHeight="1">
+      <x:c r="A436" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B436" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C436" s="87" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D436" s="87" t="str">
+        <x:v>Borrower Name - Collection</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" ht="15" customHeight="1">
+      <x:c r="A437" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B437" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C437" s="87" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D437" s="87" t="str">
+        <x:v>Active Profit After Principal Coverage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" ht="15" customHeight="1">
+      <x:c r="A438" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B438" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C438" s="87" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D438" s="87" t="str">
+        <x:v>Related Payments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" ht="15" customHeight="1">
+      <x:c r="A439" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B439" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C439" s="87" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D439" s="87" t="str">
+        <x:v>Effective Receiving Bank Account</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" ht="15" customHeight="1">
+      <x:c r="A440" s="87" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B440" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C440" s="87" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D440" s="87" t="str">
+        <x:v>Collection Setup Issues</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
@@ -18779,7 +20313,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b19210182684cb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1ff55aa7b3f41ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18808,7 +20342,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Payment trace fields and reverse references now shared with OLAP. Processing-only VCs stay OLTP-only. Collection Todays Amount Collected retains its documented date-basis variance.</x:v>
+        <x:v>Payment processing VCs remain OLTP-only. Collection amount now shares the same Payment Date = TODAY basis in both apps, using app-specific aggregation paths. Collection settings OLAP availability remains pending reconciliation.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -22786,6 +24320,486 @@
       </x:c>
       <x:c r="F203" t="str">
         <x:v>OLAP v1.100016 loads read-only trace data. OLTP owns posting and input validation; OLAP has no payment processing engine.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="15" customHeight="1">
+      <x:c r="A204" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B204" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C204" s="87" t="str">
+        <x:v>Communication Name</x:v>
+      </x:c>
+      <x:c r="D204" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E204" s="87" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F204" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="15" customHeight="1">
+      <x:c r="A205" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B205" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C205" s="87" t="str">
+        <x:v>Instagram Username</x:v>
+      </x:c>
+      <x:c r="D205" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E205" s="87" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F205" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="15" customHeight="1">
+      <x:c r="A206" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B206" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C206" s="87" t="str">
+        <x:v>Instagram Conversation URL</x:v>
+      </x:c>
+      <x:c r="D206" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E206" s="87" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F206" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="15" customHeight="1">
+      <x:c r="A207" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B207" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C207" s="87" t="str">
+        <x:v>Instagram Verified At</x:v>
+      </x:c>
+      <x:c r="D207" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E207" s="87" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F207" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="15" customHeight="1">
+      <x:c r="A208" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B208" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C208" s="87" t="str">
+        <x:v>AI Collection Enabled</x:v>
+      </x:c>
+      <x:c r="D208" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E208" s="87" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F208" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="15" customHeight="1">
+      <x:c r="A209" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B209" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C209" s="87" t="str">
+        <x:v>Late Penalty Enabled</x:v>
+      </x:c>
+      <x:c r="D209" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E209" s="87" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F209" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="15" customHeight="1">
+      <x:c r="A210" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B210" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C210" s="87" t="str">
+        <x:v>Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="D210" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E210" s="87" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F210" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="15" customHeight="1">
+      <x:c r="A211" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B211" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C211" s="87" t="str">
+        <x:v>Effective Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="D211" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E211" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F211" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="15" customHeight="1">
+      <x:c r="A212" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B212" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C212" s="87" t="str">
+        <x:v>Collection Setup Issues</x:v>
+      </x:c>
+      <x:c r="D212" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E212" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F212" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="15" customHeight="1">
+      <x:c r="A213" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B213" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C213" s="87" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="D213" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E213" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F213" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="15" customHeight="1">
+      <x:c r="A214" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B214" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C214" s="87" t="str">
+        <x:v>Row ID</x:v>
+      </x:c>
+      <x:c r="D214" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E214" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F214" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" ht="15" customHeight="1">
+      <x:c r="A215" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B215" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C215" s="87" t="str">
+        <x:v>Account Label</x:v>
+      </x:c>
+      <x:c r="D215" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E215" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F215" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" ht="15" customHeight="1">
+      <x:c r="A216" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B216" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C216" s="87" t="str">
+        <x:v>Bank Name</x:v>
+      </x:c>
+      <x:c r="D216" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E216" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F216" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" ht="15" customHeight="1">
+      <x:c r="A217" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B217" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C217" s="87" t="str">
+        <x:v>Account Number</x:v>
+      </x:c>
+      <x:c r="D217" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E217" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F217" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" ht="15" customHeight="1">
+      <x:c r="A218" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B218" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C218" s="87" t="str">
+        <x:v>Account Holder Name</x:v>
+      </x:c>
+      <x:c r="D218" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E218" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F218" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" ht="15" customHeight="1">
+      <x:c r="A219" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B219" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C219" s="87" t="str">
+        <x:v>Active</x:v>
+      </x:c>
+      <x:c r="D219" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E219" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F219" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" ht="15" customHeight="1">
+      <x:c r="A220" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B220" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C220" s="87" t="str">
+        <x:v>Related Collection Settings</x:v>
+      </x:c>
+      <x:c r="D220" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E220" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F220" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" ht="15" customHeight="1">
+      <x:c r="A221" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B221" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C221" s="87" t="str">
+        <x:v>Related Borrowers</x:v>
+      </x:c>
+      <x:c r="D221" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E221" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F221" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" ht="15" customHeight="1">
+      <x:c r="A222" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B222" s="87" t="str">
+        <x:v>Collection Bank Accounts</x:v>
+      </x:c>
+      <x:c r="C222" s="87" t="str">
+        <x:v>Related Borrowers By Effective Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="D222" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E222" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F222" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" ht="15" customHeight="1">
+      <x:c r="A223" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B223" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="C223" s="87" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="D223" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E223" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F223" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" ht="15" customHeight="1">
+      <x:c r="A224" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B224" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="C224" s="87" t="str">
+        <x:v>Row ID</x:v>
+      </x:c>
+      <x:c r="D224" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E224" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F224" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" ht="15" customHeight="1">
+      <x:c r="A225" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B225" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="C225" s="87" t="str">
+        <x:v>Setting Name</x:v>
+      </x:c>
+      <x:c r="D225" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E225" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F225" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" ht="15" customHeight="1">
+      <x:c r="A226" s="87" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B226" s="87" t="str">
+        <x:v>Collection Settings</x:v>
+      </x:c>
+      <x:c r="C226" s="87" t="str">
+        <x:v>Default Receiving Bank Account</x:v>
+      </x:c>
+      <x:c r="D226" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E226" s="87" t="str">
+        <x:v>Not configured by this build</x:v>
+      </x:c>
+      <x:c r="F226" s="87" t="str">
+        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" ht="15" customHeight="1">
+      <x:c r="A227" s="87" t="str">
+        <x:v>Slice</x:v>
+      </x:c>
+      <x:c r="B227" s="87" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C227" s="87" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="D227" s="87" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E227" s="87" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F227" s="87" t="str">
+        <x:v>Enabled borrowers with nonempty setup issues;42 columns; update only.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22798,7 +24812,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76c68eb43fe14908"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re21d7c6b7f49410b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22997,7 +25011,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f60023967db45d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5da0cbd605924f34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24650,7 +26664,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf369b1478b854a5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc58431f867aa40d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Re3bfc4ac406b431e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R87e03c4747354fc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Re1527714b54946bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R75b6566451fb4126"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R86bb6bdffefe40c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R0545f66847c64d8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rd3af4178374c4d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Re2ead377192147da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Reb92849621844765"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R576eae966e1345c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R978a4ba07c8c4260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R75d6a21b95274030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R2a868ad445134b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R4613ddcc51d648f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R67417f7e53dd4691"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rda1957a88dc94402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Re70cec8acec54064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R8d3d6b9820814c70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Re7acea659d5e4ccb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Ra17567394299421b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2349,7 +2349,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93b4f3212ec24d5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70f9e137722642ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2768,7 +2768,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c975c93679348ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65e1100419c94299"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8507,30 +8507,31 @@
         <x:v>[Close Date]</x:v>
       </x:c>
     </x:row>
-    <x:row r="215" ht="15" customHeight="1">
-      <x:c r="A215" s="57" t="str">
+    <x:row r="215" ht="100" customHeight="1">
+      <x:c r="A215" s="82" t="str">
         <x:v>Loans</x:v>
       </x:c>
-      <x:c r="B215" s="57" t="n">
+      <x:c r="B215" s="82" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C215" s="59" t="str">
+      <x:c r="C215" s="82" t="str">
         <x:v>Loan Duration</x:v>
       </x:c>
-      <x:c r="D215" s="59" t="str">
+      <x:c r="D215" s="82" t="str">
         <x:v>VC / Number</x:v>
       </x:c>
-      <x:c r="E215" s="57" t="str">
+      <x:c r="E215" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F215" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G215" s="59" t="str">
-        <x:v>Closed-loan duration in calendar days, based on Close Date and inclusive of the Loan Date.</x:v>
-      </x:c>
-      <x:c r="H215" s="59" t="str">
-        <x:v>IF( ISNOTBLANK([Close Date]), FLOOR(TOTALHOURS([Close Date] - [Loan Date]) / 24) + 1, "")</x:v>
+      <x:c r="F215" s="82" t="str">
+        <x:v>OLTP Show_If: ISNOTBLANK([Close Date]); OLAP unchanged</x:v>
+      </x:c>
+      <x:c r="G215" s="82" t="str">
+        <x:v>Closed-loan inclusive days. OLTP hides this field when Close Date is blank. Verified OLTP 3.000045; client acceptance pending.</x:v>
+      </x:c>
+      <x:c r="H215" s="82" t="str">
+        <x:v>OLTP: IF(ISNOTBLANK([Close Date]), FLOOR(TOTALHOURS([Close Date] - [Loan Date]) / 24) + 1, NUMBER(""))
+OLAP (unchanged documented formula): IF(ISNOTBLANK([Close Date]), FLOOR(TOTALHOURS([Close Date] - [Loan Date]) / 24) + 1, "")</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="15" customHeight="1">
@@ -13268,7 +13269,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82452079846c4a65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57edb54b226b48d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13697,7 +13698,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7deb2b9fc0f942a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cb140f7855042e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14151,7 +14152,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R582be9882b104751"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d246e28a5a84a47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20313,7 +20314,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1ff55aa7b3f41ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23a67f253c664d9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24812,7 +24813,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re21d7c6b7f49410b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7369905d8e254a36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25011,7 +25012,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5da0cbd605924f34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f1088617064b22"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26664,7 +26665,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc58431f867aa40d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e59f3d312674445"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,16 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R978a4ba07c8c4260"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R75d6a21b95274030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R2a868ad445134b0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R4613ddcc51d648f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R67417f7e53dd4691"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rda1957a88dc94402"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Re70cec8acec54064"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R8d3d6b9820814c70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Re7acea659d5e4ccb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Ra17567394299421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R32a5d246172544f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rf0ca5ad63efa4310"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R07da4098017e4194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R1bece01d84ae4db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rd690d0d1f5a94f0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R73343225c5e44584"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rcb916faa39ac4fb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Rda7e58d67ee840a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Raabae55c90ae4d55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R4273b0fd2e364e70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R5a7d7385f1494ed0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,7 +26,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -85,8 +86,18 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -121,6 +132,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -258,7 +289,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="89">
+  <x:cellXfs count="98">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -442,6 +473,27 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2349,8 +2401,493 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70f9e137722642ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra191bf39f8514c51"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="97" t="str">
+        <x:v>Experiment</x:v>
+      </x:c>
+      <x:c r="B1" s="97" t="str">
+        <x:v>App version</x:v>
+      </x:c>
+      <x:c r="C1" s="97" t="str">
+        <x:v>Table</x:v>
+      </x:c>
+      <x:c r="D1" s="97" t="str">
+        <x:v>Column / setting</x:v>
+      </x:c>
+      <x:c r="E1" s="97" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="F1" s="97" t="str">
+        <x:v>Scope / status</x:v>
+      </x:c>
+      <x:c r="G1" s="97" t="str">
+        <x:v>Purpose / dependencies</x:v>
+      </x:c>
+      <x:c r="H1" s="97" t="str">
+        <x:v>Exact definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="150" customHeight="1">
+      <x:c r="A2" s="93" t="str">
+        <x:v>P02a</x:v>
+      </x:c>
+      <x:c r="B2" s="93" t="str">
+        <x:v>1.000012</x:v>
+      </x:c>
+      <x:c r="C2" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D2" s="93" t="str">
+        <x:v>Posted Amount</x:v>
+      </x:c>
+      <x:c r="E2" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F2" s="93" t="str">
+        <x:v>Isolated test in progress; no production change.</x:v>
+      </x:c>
+      <x:c r="G2" s="93" t="str">
+        <x:v>Use existing Related Repayments Ref list instead of full-table SELECT. Posting Difference depends on this value. Existing financial reconciliation action predicates unchanged.</x:v>
+      </x:c>
+      <x:c r="H2" s="93" t="str">
+        <x:v>SUM([Related Repayments][Amount Received])</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="150" customHeight="1">
+      <x:c r="A3" s="93" t="str">
+        <x:v>P03a</x:v>
+      </x:c>
+      <x:c r="B3" s="93" t="str">
+        <x:v>1.000006</x:v>
+      </x:c>
+      <x:c r="C3" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D3" s="93" t="str">
+        <x:v>Security filter</x:v>
+      </x:c>
+      <x:c r="E3" s="93" t="str">
+        <x:v>Table filter</x:v>
+      </x:c>
+      <x:c r="F3" s="93" t="str">
+        <x:v>Clone-only diagnostic. Restored 1.000007.</x:v>
+      </x:c>
+      <x:c r="G3" s="93" t="str">
+        <x:v>FALSE excludes Statistics rows. Does not fully remove reporting definitions or all historical dependencies. No receipt-latency improvement demonstrated.</x:v>
+      </x:c>
+      <x:c r="H3" s="93" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="150" customHeight="1">
+      <x:c r="A4" s="93" t="str">
+        <x:v>P03a rollback</x:v>
+      </x:c>
+      <x:c r="B4" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C4" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D4" s="93" t="str">
+        <x:v>Security filter</x:v>
+      </x:c>
+      <x:c r="E4" s="93" t="str">
+        <x:v>Table filter</x:v>
+      </x:c>
+      <x:c r="F4" s="93" t="str">
+        <x:v>Original empty filter restored and verified.</x:v>
+      </x:c>
+      <x:c r="G4" s="93" t="str">
+        <x:v>Restores original row population. No data rows deleted.</x:v>
+      </x:c>
+      <x:c r="H4" s="93" t="str"/>
+    </x:row>
+    <x:row r="5" ht="150" customHeight="1">
+      <x:c r="A5" s="93" t="str">
+        <x:v>P01a</x:v>
+      </x:c>
+      <x:c r="B5" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C5" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D5" s="93" t="str">
+        <x:v>Eligible Charges</x:v>
+      </x:c>
+      <x:c r="E5" s="93" t="str">
+        <x:v>VC / List Ref Charges</x:v>
+      </x:c>
+      <x:c r="F5" s="93" t="str">
+        <x:v>Test clone only. Restored at 1.000005.</x:v>
+      </x:c>
+      <x:c r="G5" s="93" t="str">
+        <x:v>Skip scans for Posted rows. Processing and Error eligibility unchanged. Eligible Outstanding consequently becomes zero on Posted rows. Freeze, Post and Reconcile checks retained.</x:v>
+      </x:c>
+      <x:c r="H5" s="93" t="str">
+        <x:v>IF([Status] = "Posted", LIST(), SELECT(Charges[Row ID], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Ref Borrower], [Amount Remaining] &gt; 0, IFS(IN([_THISROW].[Allocation Method], LIST("Single Full", "Single Partial", "First-day Auto")), [Row ID] = [_THISROW].[Ref Target Charge], [_THISROW].[Allocation Method] = "Loan Close", [Ref Loans] = [_THISROW].[Ref Target Charge].[Ref Loans], IN([_THISROW].[Allocation Method], LIST("Receive All", "Lump Sum")), [Charge Date] &lt;= [_THISROW].[Payment Date], TRUE, FALSE))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="150" customHeight="1">
+      <x:c r="A6" s="93" t="str">
+        <x:v>P01a rollback</x:v>
+      </x:c>
+      <x:c r="B6" s="93" t="str">
+        <x:v>1.000005</x:v>
+      </x:c>
+      <x:c r="C6" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D6" s="93" t="str">
+        <x:v>Eligible Charges</x:v>
+      </x:c>
+      <x:c r="E6" s="93" t="str">
+        <x:v>VC / List Ref Charges</x:v>
+      </x:c>
+      <x:c r="F6" s="93" t="str">
+        <x:v>Test clone current baseline. Production definition unchanged.</x:v>
+      </x:c>
+      <x:c r="G6" s="93" t="str">
+        <x:v>Original full eligibility expression restored for reversal controls.</x:v>
+      </x:c>
+      <x:c r="H6" s="93" t="str">
+        <x:v>SELECT(Charges[Row ID], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Ref Borrower], [Amount Remaining] &gt; 0, IFS(IN([_THISROW].[Allocation Method], LIST("Single Full", "Single Partial", "First-day Auto")), [Row ID] = [_THISROW].[Ref Target Charge], [_THISROW].[Allocation Method] = "Loan Close", [Ref Loans] = [_THISROW].[Ref Target Charge].[Ref Loans], IN([_THISROW].[Allocation Method], LIST("Receive All", "Lump Sum")), [Charge Date] &lt;= [_THISROW].[Payment Date], TRUE, FALSE)))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="150" customHeight="1">
+      <x:c r="A7" s="93" t="str">
+        <x:v>P01b</x:v>
+      </x:c>
+      <x:c r="B7" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C7" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D7" s="93" t="str">
+        <x:v>Calculated Order</x:v>
+      </x:c>
+      <x:c r="E7" s="93" t="str">
+        <x:v>VC / Number</x:v>
+      </x:c>
+      <x:c r="F7" s="93" t="str">
+        <x:v>Rejected after failed receipt. Restored 1.000009.</x:v>
+      </x:c>
+      <x:c r="G7" s="93" t="str">
+        <x:v>Attempted frozen-value reuse. Allocation Order became 1 while stored components remained zero. Receipt Error, no repayment. Not an improvement despite faster Add response.</x:v>
+      </x:c>
+      <x:c r="H7" s="93" t="str">
+        <x:v>IF([Allocation Order] &gt; 0, [Allocation Order], 1 + COUNT(SELECT(Payment Allocations[Row ID], AND([Ref Payment] = [_THISROW].[Ref Payment], OR([Charge Date Snapshot] &gt; [_THISROW].[Charge Date Snapshot], AND([Charge Date Snapshot] = [_THISROW].[Charge Date Snapshot], [Charge Row Number Snapshot] &gt; [_THISROW].[Charge Row Number Snapshot]))))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="150" customHeight="1">
+      <x:c r="A8" s="93" t="str">
+        <x:v>P01b</x:v>
+      </x:c>
+      <x:c r="B8" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C8" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D8" s="93" t="str">
+        <x:v>Calculated Amount</x:v>
+      </x:c>
+      <x:c r="E8" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F8" s="93" t="str">
+        <x:v>Rejected after failed receipt. Restored 1.000009.</x:v>
+      </x:c>
+      <x:c r="G8" s="93" t="str">
+        <x:v>Attempted frozen-value reuse. Allocation Order became 1 while stored components remained zero. Receipt Error, no repayment. Not an improvement despite faster Add response.</x:v>
+      </x:c>
+      <x:c r="H8" s="93" t="str">
+        <x:v>IF([Allocation Order] &gt; 0, [Allocated Amount], MAX(LIST(DECIMAL(0), MIN(LIST(DECIMAL([Amount Remaining Snapshot]), DECIMAL([Ref Payment].[Amount Received]) - DECIMAL(SUM(SELECT(Payment Allocations[Amount Remaining Snapshot], AND([Ref Payment] = [_THISROW].[Ref Payment], [Calculated Order] &lt; [_THISROW].[Calculated Order])))))))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="150" customHeight="1">
+      <x:c r="A9" s="93" t="str">
+        <x:v>P01b</x:v>
+      </x:c>
+      <x:c r="B9" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C9" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D9" s="93" t="str">
+        <x:v>Calculated Interest</x:v>
+      </x:c>
+      <x:c r="E9" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F9" s="93" t="str">
+        <x:v>Rejected after failed receipt. Restored 1.000009.</x:v>
+      </x:c>
+      <x:c r="G9" s="93" t="str">
+        <x:v>Attempted frozen-value reuse. Allocation Order became 1 while stored components remained zero. Receipt Error, no repayment. Not an improvement despite faster Add response.</x:v>
+      </x:c>
+      <x:c r="H9" s="93" t="str">
+        <x:v>IF([Allocation Order] &gt; 0, [Allocated Interest], MIN(LIST(MAX(LIST(DECIMAL(0), DECIMAL([Interest Remaining Snapshot]))), DECIMAL([Calculated Amount]))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="150" customHeight="1">
+      <x:c r="A10" s="93" t="str">
+        <x:v>P01b</x:v>
+      </x:c>
+      <x:c r="B10" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C10" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D10" s="93" t="str">
+        <x:v>Calculated Principal</x:v>
+      </x:c>
+      <x:c r="E10" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F10" s="93" t="str">
+        <x:v>Rejected after failed receipt. Restored 1.000009.</x:v>
+      </x:c>
+      <x:c r="G10" s="93" t="str">
+        <x:v>Attempted frozen-value reuse. Allocation Order became 1 while stored components remained zero. Receipt Error, no repayment. Not an improvement despite faster Add response.</x:v>
+      </x:c>
+      <x:c r="H10" s="93" t="str">
+        <x:v>IF([Allocation Order] &gt; 0, [Allocated Principal], MIN(LIST(MAX(LIST(DECIMAL(0), DECIMAL([Principal Remaining Snapshot]))), DECIMAL([Calculated Amount]) - DECIMAL([Calculated Interest]))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="150" customHeight="1">
+      <x:c r="A11" s="93" t="str">
+        <x:v>P01b rollback</x:v>
+      </x:c>
+      <x:c r="B11" s="93" t="str">
+        <x:v>1.000009</x:v>
+      </x:c>
+      <x:c r="C11" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D11" s="93" t="str">
+        <x:v>Calculated Order</x:v>
+      </x:c>
+      <x:c r="E11" s="93" t="str">
+        <x:v>VC / Number</x:v>
+      </x:c>
+      <x:c r="F11" s="93" t="str">
+        <x:v>Original formulas restored and version verified.</x:v>
+      </x:c>
+      <x:c r="G11" s="93" t="str">
+        <x:v>Recovery uses original calculation and existing Retry after resetting only the unposted synthetic allocation's order from 1 to 0.</x:v>
+      </x:c>
+      <x:c r="H11" s="93" t="str">
+        <x:v>1 + COUNT(SELECT(Payment Allocations[Row ID], AND([Ref Payment] = [_THISROW].[Ref Payment], OR([Charge Date Snapshot] &gt; [_THISROW].[Charge Date Snapshot], AND([Charge Date Snapshot] = [_THISROW].[Charge Date Snapshot], [Charge Row Number Snapshot] &gt; [_THISROW].[Charge Row Number Snapshot])))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="150" customHeight="1">
+      <x:c r="A12" s="93" t="str">
+        <x:v>P01b rollback</x:v>
+      </x:c>
+      <x:c r="B12" s="93" t="str">
+        <x:v>1.000009</x:v>
+      </x:c>
+      <x:c r="C12" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D12" s="93" t="str">
+        <x:v>Calculated Amount</x:v>
+      </x:c>
+      <x:c r="E12" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F12" s="93" t="str">
+        <x:v>Original formulas restored and version verified.</x:v>
+      </x:c>
+      <x:c r="G12" s="93" t="str">
+        <x:v>Recovery uses original calculation and existing Retry after resetting only the unposted synthetic allocation's order from 1 to 0.</x:v>
+      </x:c>
+      <x:c r="H12" s="93" t="str">
+        <x:v>MAX(LIST(DECIMAL(0), MIN(LIST(DECIMAL([Amount Remaining Snapshot]), DECIMAL([Ref Payment].[Amount Received]) - DECIMAL(SUM(SELECT(Payment Allocations[Amount Remaining Snapshot], AND([Ref Payment] = [_THISROW].[Ref Payment], [Calculated Order] &lt; [_THISROW].[Calculated Order]))))))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="150" customHeight="1">
+      <x:c r="A13" s="93" t="str">
+        <x:v>P01b rollback</x:v>
+      </x:c>
+      <x:c r="B13" s="93" t="str">
+        <x:v>1.000009</x:v>
+      </x:c>
+      <x:c r="C13" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D13" s="93" t="str">
+        <x:v>Calculated Interest</x:v>
+      </x:c>
+      <x:c r="E13" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F13" s="93" t="str">
+        <x:v>Original formulas restored and version verified.</x:v>
+      </x:c>
+      <x:c r="G13" s="93" t="str">
+        <x:v>Recovery uses original calculation and existing Retry after resetting only the unposted synthetic allocation's order from 1 to 0.</x:v>
+      </x:c>
+      <x:c r="H13" s="93" t="str">
+        <x:v>MIN(LIST(MAX(LIST(DECIMAL(0), DECIMAL([Interest Remaining Snapshot]))), DECIMAL([Calculated Amount])))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="150" customHeight="1">
+      <x:c r="A14" s="93" t="str">
+        <x:v>P01b rollback</x:v>
+      </x:c>
+      <x:c r="B14" s="93" t="str">
+        <x:v>1.000009</x:v>
+      </x:c>
+      <x:c r="C14" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D14" s="93" t="str">
+        <x:v>Calculated Principal</x:v>
+      </x:c>
+      <x:c r="E14" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F14" s="93" t="str">
+        <x:v>Original formulas restored and version verified.</x:v>
+      </x:c>
+      <x:c r="G14" s="93" t="str">
+        <x:v>Recovery uses original calculation and existing Retry after resetting only the unposted synthetic allocation's order from 1 to 0.</x:v>
+      </x:c>
+      <x:c r="H14" s="93" t="str">
+        <x:v>MIN(LIST(MAX(LIST(DECIMAL(0), DECIMAL([Principal Remaining Snapshot]))), DECIMAL([Calculated Amount]) - DECIMAL([Calculated Interest])))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="150" customHeight="1">
+      <x:c r="A15" s="93" t="str">
+        <x:v>P01c</x:v>
+      </x:c>
+      <x:c r="B15" s="93" t="str">
+        <x:v>1.000010</x:v>
+      </x:c>
+      <x:c r="C15" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D15" s="93" t="str">
+        <x:v>Calculated Order</x:v>
+      </x:c>
+      <x:c r="E15" s="93" t="str">
+        <x:v>VC / Number</x:v>
+      </x:c>
+      <x:c r="F15" s="93" t="str">
+        <x:v>Three Posted samples. Restored 1.000011; not accepted for production.</x:v>
+      </x:c>
+      <x:c r="G15" s="93" t="str">
+        <x:v>Reuse stored helper values only after parent receipt is Posted. All Processing and Error calculations retain original expressions to avoid the P01b freeze-order failure.</x:v>
+      </x:c>
+      <x:c r="H15" s="93" t="str">
+        <x:v>IF([Ref Payment].[Status] = "Posted", [Allocation Order], 1 + COUNT(SELECT(Payment Allocations[Row ID], AND([Ref Payment] = [_THISROW].[Ref Payment], OR([Charge Date Snapshot] &gt; [_THISROW].[Charge Date Snapshot], AND([Charge Date Snapshot] = [_THISROW].[Charge Date Snapshot], [Charge Row Number Snapshot] &gt; [_THISROW].[Charge Row Number Snapshot]))))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="150" customHeight="1">
+      <x:c r="A16" s="93" t="str">
+        <x:v>P01c</x:v>
+      </x:c>
+      <x:c r="B16" s="93" t="str">
+        <x:v>1.000010</x:v>
+      </x:c>
+      <x:c r="C16" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D16" s="93" t="str">
+        <x:v>Calculated Amount</x:v>
+      </x:c>
+      <x:c r="E16" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F16" s="93" t="str">
+        <x:v>Three Posted samples. Restored 1.000011; not accepted for production.</x:v>
+      </x:c>
+      <x:c r="G16" s="93" t="str">
+        <x:v>Reuse stored helper values only after parent receipt is Posted. All Processing and Error calculations retain original expressions to avoid the P01b freeze-order failure.</x:v>
+      </x:c>
+      <x:c r="H16" s="93" t="str">
+        <x:v>IF([Ref Payment].[Status] = "Posted", [Allocated Amount], MAX(LIST(DECIMAL(0), MIN(LIST(DECIMAL([Amount Remaining Snapshot]), DECIMAL([Ref Payment].[Amount Received]) - DECIMAL(SUM(SELECT(Payment Allocations[Amount Remaining Snapshot], AND([Ref Payment] = [_THISROW].[Ref Payment], [Calculated Order] &lt; [_THISROW].[Calculated Order])))))))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="150" customHeight="1">
+      <x:c r="A17" s="93" t="str">
+        <x:v>P01c</x:v>
+      </x:c>
+      <x:c r="B17" s="93" t="str">
+        <x:v>1.000010</x:v>
+      </x:c>
+      <x:c r="C17" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D17" s="93" t="str">
+        <x:v>Calculated Interest</x:v>
+      </x:c>
+      <x:c r="E17" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F17" s="93" t="str">
+        <x:v>Three Posted samples. Restored 1.000011; not accepted for production.</x:v>
+      </x:c>
+      <x:c r="G17" s="93" t="str">
+        <x:v>Reuse stored helper values only after parent receipt is Posted. All Processing and Error calculations retain original expressions to avoid the P01b freeze-order failure.</x:v>
+      </x:c>
+      <x:c r="H17" s="93" t="str">
+        <x:v>IF([Ref Payment].[Status] = "Posted", [Allocated Interest], MIN(LIST(MAX(LIST(DECIMAL(0), DECIMAL([Interest Remaining Snapshot]))), DECIMAL([Calculated Amount]))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="150" customHeight="1">
+      <x:c r="A18" s="93" t="str">
+        <x:v>P01c</x:v>
+      </x:c>
+      <x:c r="B18" s="93" t="str">
+        <x:v>1.000010</x:v>
+      </x:c>
+      <x:c r="C18" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D18" s="93" t="str">
+        <x:v>Calculated Principal</x:v>
+      </x:c>
+      <x:c r="E18" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F18" s="93" t="str">
+        <x:v>Three Posted samples. Restored 1.000011; not accepted for production.</x:v>
+      </x:c>
+      <x:c r="G18" s="93" t="str">
+        <x:v>Reuse stored helper values only after parent receipt is Posted. All Processing and Error calculations retain original expressions to avoid the P01b freeze-order failure.</x:v>
+      </x:c>
+      <x:c r="H18" s="93" t="str">
+        <x:v>IF([Ref Payment].[Status] = "Posted", [Allocated Principal], MIN(LIST(MAX(LIST(DECIMAL(0), DECIMAL([Principal Remaining Snapshot]))), DECIMAL([Calculated Amount]) - DECIMAL([Calculated Interest]))))</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -2768,7 +3305,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65e1100419c94299"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61a0a56b90bf4c19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13269,7 +13806,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57edb54b226b48d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd21574397ba4b6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13698,7 +14235,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cb140f7855042e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raddd74db07aa40d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14152,7 +14689,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d246e28a5a84a47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46dfcd6435b74222"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20314,7 +20851,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23a67f253c664d9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a3aae16d3f842a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24813,7 +25350,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7369905d8e254a36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e01aa2a35344fc7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25012,7 +25549,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f1088617064b22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0520f58cb3e4219"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26665,7 +27202,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e59f3d312674445"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83875edb16244620"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R32a5d246172544f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rf0ca5ad63efa4310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R07da4098017e4194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R1bece01d84ae4db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rd690d0d1f5a94f0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R73343225c5e44584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rcb916faa39ac4fb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Rda7e58d67ee840a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Raabae55c90ae4d55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R4273b0fd2e364e70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R5a7d7385f1494ed0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R59e42d0eb5594056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R6ac6453d12c6483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rda90031e5a174c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Ra837a5ea449e4b9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R658a96a33d3b49ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rc280eb80e53445b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R8daaa05516ce442b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R48ce2de77c5745d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R8403af4920f14a58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R60ad872993b94151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Refffd5c193504f4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -97,7 +97,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="13">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -132,6 +132,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -289,7 +319,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="98">
+  <x:cellXfs count="104">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -494,6 +524,24 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2401,7 +2449,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra191bf39f8514c51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ea27d42e7534a37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2421,28 +2469,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="97" t="str">
+      <x:c r="A1" s="103" t="str">
         <x:v>Experiment</x:v>
       </x:c>
-      <x:c r="B1" s="97" t="str">
+      <x:c r="B1" s="103" t="str">
         <x:v>App version</x:v>
       </x:c>
-      <x:c r="C1" s="97" t="str">
+      <x:c r="C1" s="103" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="D1" s="97" t="str">
+      <x:c r="D1" s="103" t="str">
         <x:v>Column / setting</x:v>
       </x:c>
-      <x:c r="E1" s="97" t="str">
+      <x:c r="E1" s="103" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F1" s="97" t="str">
+      <x:c r="F1" s="103" t="str">
         <x:v>Scope / status</x:v>
       </x:c>
-      <x:c r="G1" s="97" t="str">
+      <x:c r="G1" s="103" t="str">
         <x:v>Purpose / dependencies</x:v>
       </x:c>
-      <x:c r="H1" s="97" t="str">
+      <x:c r="H1" s="103" t="str">
         <x:v>Exact definition</x:v>
       </x:c>
     </x:row>
@@ -2463,7 +2511,7 @@
         <x:v>VC / Price</x:v>
       </x:c>
       <x:c r="F2" s="93" t="str">
-        <x:v>Isolated test in progress; no production change.</x:v>
+        <x:v>Three Posted samples; restored and verified 1.000013. No production change.</x:v>
       </x:c>
       <x:c r="G2" s="93" t="str">
         <x:v>Use existing Related Repayments Ref list instead of full-table SELECT. Posting Difference depends on this value. Existing financial reconciliation action predicates unchanged.</x:v>
@@ -2884,6 +2932,422 @@
       </x:c>
       <x:c r="H18" s="93" t="str">
         <x:v>IF([Ref Payment].[Status] = "Posted", [Allocated Principal], MIN(LIST(MAX(LIST(DECIMAL(0), DECIMAL([Principal Remaining Snapshot]))), DECIMAL([Calculated Amount]) - DECIMAL([Calculated Interest]))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="150" customHeight="1">
+      <x:c r="A19" s="93" t="str">
+        <x:v>P02a rollback</x:v>
+      </x:c>
+      <x:c r="B19" s="93" t="str">
+        <x:v>1.000013</x:v>
+      </x:c>
+      <x:c r="C19" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D19" s="93" t="str">
+        <x:v>Posted Amount</x:v>
+      </x:c>
+      <x:c r="E19" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F19" s="93" t="str">
+        <x:v>Original formula restored and verified.</x:v>
+      </x:c>
+      <x:c r="G19" s="93" t="str">
+        <x:v>Restores baseline full-table SELECT; Posting Difference dependency unchanged.</x:v>
+      </x:c>
+      <x:c r="H19" s="93" t="str">
+        <x:v>SUM(SELECT(Repayments[Amount Received], [Ref Payment] = [_THISROW].[Row ID]))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="150" customHeight="1">
+      <x:c r="A20" s="93" t="str">
+        <x:v>P04a</x:v>
+      </x:c>
+      <x:c r="B20" s="93" t="str">
+        <x:v>1.000014</x:v>
+      </x:c>
+      <x:c r="C20" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D20" s="93" t="str">
+        <x:v>Calculated Amount</x:v>
+      </x:c>
+      <x:c r="E20" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F20" s="93" t="str">
+        <x:v>Three Posted samples; original restored and verified at 1.000018.</x:v>
+      </x:c>
+      <x:c r="G20" s="93" t="str">
+        <x:v>Compare immutable snapshot date/row number directly instead of nested Calculated Order evaluation. Preserves newest-first and tie ordering, full allocation coverage, zero rows and posting guards.</x:v>
+      </x:c>
+      <x:c r="H20" s="93" t="str">
+        <x:v>MAX(LIST(DECIMAL(0), MIN(LIST(DECIMAL([Amount Remaining Snapshot]), DECIMAL([Ref Payment].[Amount Received]) - DECIMAL(SUM(SELECT(Payment Allocations[Amount Remaining Snapshot], AND([Ref Payment] = [_THISROW].[Ref Payment], OR([Charge Date Snapshot] &gt; [_THISROW].[Charge Date Snapshot], AND([Charge Date Snapshot] = [_THISROW].[Charge Date Snapshot], [Charge Row Number Snapshot] &gt; [_THISROW].[Charge Row Number Snapshot]))))))))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="150" customHeight="1">
+      <x:c r="A21" s="93" t="str">
+        <x:v>P06-cache</x:v>
+      </x:c>
+      <x:c r="B21" s="93" t="str">
+        <x:v>1.000015</x:v>
+      </x:c>
+      <x:c r="C21" s="93" t="str">
+        <x:v>App settings</x:v>
+      </x:c>
+      <x:c r="D21" s="93" t="str">
+        <x:v>Server caching</x:v>
+      </x:c>
+      <x:c r="E21" s="93" t="str">
+        <x:v>Setting</x:v>
+      </x:c>
+      <x:c r="F21" s="93" t="str">
+        <x:v>Verified ON in clone; API remains OFF.</x:v>
+      </x:c>
+      <x:c r="G21" s="93" t="str">
+        <x:v>Only caching changed; P04a retained. Delta OFF, Quick ON; warm explicit sync samples exclude initialization and editor preview.</x:v>
+      </x:c>
+      <x:c r="H21" s="93" t="str">
+        <x:v>ON (prior OFF)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="150" customHeight="1">
+      <x:c r="A22" s="93" t="str">
+        <x:v>P06-delta</x:v>
+      </x:c>
+      <x:c r="B22" s="93" t="str">
+        <x:v>1.000016</x:v>
+      </x:c>
+      <x:c r="C22" s="93" t="str">
+        <x:v>App settings</x:v>
+      </x:c>
+      <x:c r="D22" s="93" t="str">
+        <x:v>Delta sync</x:v>
+      </x:c>
+      <x:c r="E22" s="93" t="str">
+        <x:v>Setting</x:v>
+      </x:c>
+      <x:c r="F22" s="93" t="str">
+        <x:v>Five idle syncs; direct note freshness and restoration passed. Restored OFF at 1.000017.</x:v>
+      </x:c>
+      <x:c r="G22" s="93" t="str">
+        <x:v>Cache ON and Quick ON retained; compare with 1.000015. Date-driven VC rollover and cross-table freshness not certified.</x:v>
+      </x:c>
+      <x:c r="H22" s="93" t="str">
+        <x:v>ON (prior OFF)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="150" customHeight="1">
+      <x:c r="A23" s="93" t="str">
+        <x:v>P06-quick</x:v>
+      </x:c>
+      <x:c r="B23" s="93" t="str">
+        <x:v>1.000017</x:v>
+      </x:c>
+      <x:c r="C23" s="93" t="str">
+        <x:v>App settings</x:v>
+      </x:c>
+      <x:c r="D23" s="93" t="str">
+        <x:v>Quick sync</x:v>
+      </x:c>
+      <x:c r="E23" s="93" t="str">
+        <x:v>Setting</x:v>
+      </x:c>
+      <x:c r="F23" s="93" t="str">
+        <x:v>Five idle syncs; median 1.312s. Restored ON at 1.000018.</x:v>
+      </x:c>
+      <x:c r="G23" s="93" t="str">
+        <x:v>Delta restored OFF and cache remains ON. Compare to 1.000015, differing only in Quick sync.</x:v>
+      </x:c>
+      <x:c r="H23" s="93" t="str">
+        <x:v>OFF (prior ON)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="150" customHeight="1">
+      <x:c r="A24" s="93" t="str">
+        <x:v>P04a rollback</x:v>
+      </x:c>
+      <x:c r="B24" s="93" t="str">
+        <x:v>1.000018</x:v>
+      </x:c>
+      <x:c r="C24" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D24" s="93" t="str">
+        <x:v>Calculated Amount</x:v>
+      </x:c>
+      <x:c r="E24" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F24" s="93" t="str">
+        <x:v>Original verified in saved appdoc.</x:v>
+      </x:c>
+      <x:c r="G24" s="93" t="str">
+        <x:v>Baseline formula restored; all earlier formula variants restored.</x:v>
+      </x:c>
+      <x:c r="H24" s="93" t="str">
+        <x:v>MAX(LIST(DECIMAL(0), MIN(LIST(DECIMAL([Amount Remaining Snapshot]), DECIMAL([Ref Payment].[Amount Received]) - DECIMAL(SUM(SELECT(Payment Allocations[Amount Remaining Snapshot], AND([Ref Payment] = [_THISROW].[Ref Payment], [Calculated Order] &lt; [_THISROW].[Calculated Order]))))))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="150" customHeight="1">
+      <x:c r="A25" s="93" t="str">
+        <x:v>P06 rollback</x:v>
+      </x:c>
+      <x:c r="B25" s="93" t="str">
+        <x:v>1.000018</x:v>
+      </x:c>
+      <x:c r="C25" s="93" t="str">
+        <x:v>App settings</x:v>
+      </x:c>
+      <x:c r="D25" s="93" t="str">
+        <x:v>Sync settings</x:v>
+      </x:c>
+      <x:c r="E25" s="93" t="str">
+        <x:v>Settings</x:v>
+      </x:c>
+      <x:c r="F25" s="93" t="str">
+        <x:v>Isolation baseline restored.</x:v>
+      </x:c>
+      <x:c r="G25" s="93" t="str">
+        <x:v>Server cache OFF; delta OFF; quick ON. Start sync, delayed sync and automatic updates retained ON.</x:v>
+      </x:c>
+      <x:c r="H25" s="93" t="str">
+        <x:v>Cache OFF; Delta OFF; Quick ON</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="150" customHeight="1">
+      <x:c r="A26" s="93" t="str">
+        <x:v>P03b intermediate</x:v>
+      </x:c>
+      <x:c r="B26" s="93" t="str">
+        <x:v>1.000019</x:v>
+      </x:c>
+      <x:c r="C26" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D26" s="93" t="str">
+        <x:v>App table availability</x:v>
+      </x:c>
+      <x:c r="E26" s="93" t="str">
+        <x:v>Table / 26 columns, 23 VC</x:v>
+      </x:c>
+      <x:c r="F26" s="93" t="str">
+        <x:v>Removed from test app; non-runnable until dependent views repaired.</x:v>
+      </x:c>
+      <x:c r="G26" s="93" t="str">
+        <x:v>Database table retained. Missing KPIs and Reporting App Shortcut caused load errors. No receipts submitted in this invalid version.</x:v>
+      </x:c>
+      <x:c r="H26" s="93" t="str">
+        <x:v>ABSENT from clone app; physical database unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="150" customHeight="1">
+      <x:c r="A27" s="93" t="str">
+        <x:v>P03b</x:v>
+      </x:c>
+      <x:c r="B27" s="93" t="str">
+        <x:v>1.000020</x:v>
+      </x:c>
+      <x:c r="C27" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D27" s="93" t="str">
+        <x:v>App table availability</x:v>
+      </x:c>
+      <x:c r="E27" s="93" t="str">
+        <x:v>Table / 26 columns, 23 VC</x:v>
+      </x:c>
+      <x:c r="F27" s="93" t="str">
+        <x:v>Three Posted six-charge samples. Restored complete definition at verified 1.000022.</x:v>
+      </x:c>
+      <x:c r="G27" s="93" t="str">
+        <x:v>Diagnostic only. Associated format rules removed by editor; manual generation and reporting actions need review before any real migration. Full rollback 1.000018.</x:v>
+      </x:c>
+      <x:c r="H27" s="93" t="str">
+        <x:v>ABSENT from clone app; physical database unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="150" customHeight="1">
+      <x:c r="A28" s="93" t="str">
+        <x:v>P03b rollback</x:v>
+      </x:c>
+      <x:c r="B28" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C28" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D28" s="93" t="str">
+        <x:v>App table availability</x:v>
+      </x:c>
+      <x:c r="E28" s="93" t="str">
+        <x:v>Table / 26 columns, 23 VC</x:v>
+      </x:c>
+      <x:c r="F28" s="93" t="str">
+        <x:v>Restored complete 1.000018 using native version history.</x:v>
+      </x:c>
+      <x:c r="G28" s="93" t="str">
+        <x:v>Statistics, KPIs, Reporting App Shortcut verified present; configuration baseline restored before materialization.</x:v>
+      </x:c>
+      <x:c r="H28" s="93" t="str">
+        <x:v>PRESENT; original definitions restored</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="150" customHeight="1">
+      <x:c r="A29" s="93" t="str">
+        <x:v>P09 schema</x:v>
+      </x:c>
+      <x:c r="B29" s="93" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C29" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D29" s="93" t="str">
+        <x:v>Perf Cached Principal Paid</x:v>
+      </x:c>
+      <x:c r="E29" s="93" t="str">
+        <x:v>Physical / Price</x:v>
+      </x:c>
+      <x:c r="F29" s="93" t="str">
+        <x:v>Test-only; hidden and nonsearchable; writable by refresh action.</x:v>
+      </x:c>
+      <x:c r="G29" s="93" t="str">
+        <x:v>Regenerated at 1.000023; all original 25 column key/type/label/formula/qualifier definitions verified unchanged. Initially hidden and readonly at 1.000024, then writable at 1.000025 for data-action assignment. No cache-reader changes yet.</x:v>
+      </x:c>
+      <x:c r="H29" s="93" t="str">
+        <x:v>No app formula; ledger-derived value populated by explicit refresh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="150" customHeight="1">
+      <x:c r="A30" s="93" t="str">
+        <x:v>P09 schema</x:v>
+      </x:c>
+      <x:c r="B30" s="93" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C30" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D30" s="93" t="str">
+        <x:v>Perf Cached Interest Paid</x:v>
+      </x:c>
+      <x:c r="E30" s="93" t="str">
+        <x:v>Physical / Price</x:v>
+      </x:c>
+      <x:c r="F30" s="93" t="str">
+        <x:v>Test-only; hidden and nonsearchable; writable by refresh action.</x:v>
+      </x:c>
+      <x:c r="G30" s="93" t="str">
+        <x:v>Regenerated at 1.000023; all original 25 column key/type/label/formula/qualifier definitions verified unchanged. Initially hidden and readonly at 1.000024, then writable at 1.000025 for data-action assignment. No cache-reader changes yet.</x:v>
+      </x:c>
+      <x:c r="H30" s="93" t="str">
+        <x:v>No app formula; ledger-derived value populated by explicit refresh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="150" customHeight="1">
+      <x:c r="A31" s="93" t="str">
+        <x:v>P09 refresh</x:v>
+      </x:c>
+      <x:c r="B31" s="93" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C31" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D31" s="93" t="str">
+        <x:v>Perf - Refresh Charge Paid Cache</x:v>
+      </x:c>
+      <x:c r="E31" s="93" t="str">
+        <x:v>Action / SET_COLUMN_VALUE</x:v>
+      </x:c>
+      <x:c r="F31" s="93" t="str">
+        <x:v>Verified hidden; only two cache assignments.</x:v>
+      </x:c>
+      <x:c r="G31" s="93" t="str">
+        <x:v>Recomputes both components from authoritative related repayment rows; idempotent.</x:v>
+      </x:c>
+      <x:c r="H31" s="93" t="str">
+        <x:v>Perf Cached Principal Paid = SUM([Related Repayments][Principal Paid]); Perf Cached Interest Paid = SUM([Related Repayments][Interest Paid])</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="150" customHeight="1">
+      <x:c r="A32" s="93" t="str">
+        <x:v>P09 backfill</x:v>
+      </x:c>
+      <x:c r="B32" s="93" t="str">
+        <x:v>1.000026</x:v>
+      </x:c>
+      <x:c r="C32" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D32" s="93" t="str">
+        <x:v>Perf - Backfill All Charge Caches</x:v>
+      </x:c>
+      <x:c r="E32" s="93" t="str">
+        <x:v>Action / REF_ACTION</x:v>
+      </x:c>
+      <x:c r="F32" s="93" t="str">
+        <x:v>Verified target before execution; no cache reads changed.</x:v>
+      </x:c>
+      <x:c r="G32" s="93" t="str">
+        <x:v>One-time initialization over copied database only.</x:v>
+      </x:c>
+      <x:c r="H32" s="93" t="str">
+        <x:v>ReferencedTable Charges; ReferencedRows Charges[Row ID]; ReferencedAction Perf - Refresh Charge Paid Cache</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="150" customHeight="1">
+      <x:c r="A33" s="93" t="str">
+        <x:v>P09 bounded initialization</x:v>
+      </x:c>
+      <x:c r="B33" s="93" t="str">
+        <x:v>1.000027</x:v>
+      </x:c>
+      <x:c r="C33" s="93" t="str">
+        <x:v>Statistics / Charges</x:v>
+      </x:c>
+      <x:c r="D33" s="93" t="str">
+        <x:v>Perf - Initialize Charge Caches</x:v>
+      </x:c>
+      <x:c r="E33" s="93" t="str">
+        <x:v>Bot / REF_ACTION</x:v>
+      </x:c>
+      <x:c r="F33" s="93" t="str">
+        <x:v>UI Test execution in progress; no cache readers changed.</x:v>
+      </x:c>
+      <x:c r="G33" s="93" t="str">
+        <x:v>Replaces failed all-row client backfill. No notification task.</x:v>
+      </x:c>
+      <x:c r="H33" s="93" t="str">
+        <x:v>TOP(SELECT(Charges[Row ID], OR(ISBLANK([Perf Cached Principal Paid]), ISBLANK([Perf Cached Interest Paid]))), 100); action Perf - Refresh Charge Paid Cache</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="150" customHeight="1">
+      <x:c r="A34" s="93" t="str">
+        <x:v>P09 new GUI trigger</x:v>
+      </x:c>
+      <x:c r="B34" s="93" t="str">
+        <x:v>1.000028</x:v>
+      </x:c>
+      <x:c r="C34" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D34" s="93" t="str">
+        <x:v>Perf - Initialize Next Cache Batch</x:v>
+      </x:c>
+      <x:c r="E34" s="93" t="str">
+        <x:v>Action / SET_COLUMN_VALUE</x:v>
+      </x:c>
+      <x:c r="F34" s="93" t="str">
+        <x:v>Replaces all-row client wrapper. First click outcome pending.</x:v>
+      </x:c>
+      <x:c r="G34" s="93" t="str">
+        <x:v>Non-key Statistics ID only; original MAIN must be restored. No references found in baseline inventory. New GUI only from this point.</x:v>
+      </x:c>
+      <x:c r="H34" s="93" t="str">
+        <x:v>Statistics ID = CONCATENATE("PERF-CACHE-INIT-", UNIQUEID())</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3305,7 +3769,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61a0a56b90bf4c19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11e2bb00962f43d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13806,7 +14270,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd21574397ba4b6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R480a90986b924ce4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14235,7 +14699,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raddd74db07aa40d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1bfb898f9754e54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14689,7 +15153,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46dfcd6435b74222"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re282524943c848e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20851,7 +21315,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a3aae16d3f842a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc9aaed3b11b450c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25350,7 +25814,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e01aa2a35344fc7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1093c69855d474b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25549,7 +26013,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0520f58cb3e4219"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd24fffd2968c41c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27202,7 +27666,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83875edb16244620"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b6a59df6ba4693"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R59e42d0eb5594056"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R6ac6453d12c6483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rda90031e5a174c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Ra837a5ea449e4b9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R658a96a33d3b49ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rc280eb80e53445b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R8daaa05516ce442b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R48ce2de77c5745d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R8403af4920f14a58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R60ad872993b94151"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Refffd5c193504f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R79a7c6c8c0da487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R5c9112ad24ec482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rc34619690220467b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R1462e69c86444983"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Re0b2c4e28ca34940"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R76948fb212d745ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rfa94536683874f06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R7adcb098727f467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R36bc897ce824407c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rcaada003fd364f52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R0e18422c473a4c10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -97,7 +97,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="19">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -132,6 +132,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -319,7 +339,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="104">
+  <x:cellXfs count="108">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -542,6 +562,18 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2449,7 +2481,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ea27d42e7534a37"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb70980dd8bbe4447"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2469,28 +2501,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="103" t="str">
+      <x:c r="A1" s="107" t="str">
         <x:v>Experiment</x:v>
       </x:c>
-      <x:c r="B1" s="103" t="str">
+      <x:c r="B1" s="107" t="str">
         <x:v>App version</x:v>
       </x:c>
-      <x:c r="C1" s="103" t="str">
+      <x:c r="C1" s="107" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="D1" s="103" t="str">
+      <x:c r="D1" s="107" t="str">
         <x:v>Column / setting</x:v>
       </x:c>
-      <x:c r="E1" s="103" t="str">
+      <x:c r="E1" s="107" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F1" s="103" t="str">
+      <x:c r="F1" s="107" t="str">
         <x:v>Scope / status</x:v>
       </x:c>
-      <x:c r="G1" s="103" t="str">
+      <x:c r="G1" s="107" t="str">
         <x:v>Purpose / dependencies</x:v>
       </x:c>
-      <x:c r="H1" s="103" t="str">
+      <x:c r="H1" s="107" t="str">
         <x:v>Exact definition</x:v>
       </x:c>
     </x:row>
@@ -3289,7 +3321,7 @@
         <x:v>Action / REF_ACTION</x:v>
       </x:c>
       <x:c r="F32" s="93" t="str">
-        <x:v>Verified target before execution; no cache reads changed.</x:v>
+        <x:v>Client all-row attempt crashed; wrapper replaced. Do not replay.</x:v>
       </x:c>
       <x:c r="G32" s="93" t="str">
         <x:v>One-time initialization over copied database only.</x:v>
@@ -3315,7 +3347,7 @@
         <x:v>Bot / REF_ACTION</x:v>
       </x:c>
       <x:c r="F33" s="93" t="str">
-        <x:v>UI Test execution in progress; no cache readers changed.</x:v>
+        <x:v>Initialization completed; bot disabled at 1.000031. Legacy Test-page use discontinued.</x:v>
       </x:c>
       <x:c r="G33" s="93" t="str">
         <x:v>Replaces failed all-row client backfill. No notification task.</x:v>
@@ -3341,13 +3373,299 @@
         <x:v>Action / SET_COLUMN_VALUE</x:v>
       </x:c>
       <x:c r="F34" s="93" t="str">
-        <x:v>Replaces all-row client wrapper. First click outcome pending.</x:v>
+        <x:v>New-GUI trigger executed; Statistics ID restored MAIN; trigger hidden 1.000038.</x:v>
       </x:c>
       <x:c r="G34" s="93" t="str">
         <x:v>Non-key Statistics ID only; original MAIN must be restored. No references found in baseline inventory. New GUI only from this point.</x:v>
       </x:c>
       <x:c r="H34" s="93" t="str">
         <x:v>Statistics ID = CONCATENATE("PERF-CACHE-INIT-", UNIQUEID())</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="150" customHeight="1">
+      <x:c r="A35" s="93" t="str">
+        <x:v>P09 reconciliation</x:v>
+      </x:c>
+      <x:c r="B35" s="93" t="str">
+        <x:v>1.000030</x:v>
+      </x:c>
+      <x:c r="C35" s="93" t="str">
+        <x:v>Statistics / Charges</x:v>
+      </x:c>
+      <x:c r="D35" s="93" t="str">
+        <x:v>Perf - Initialize Next Cache Batch display name</x:v>
+      </x:c>
+      <x:c r="E35" s="93" t="str">
+        <x:v>Action display expression</x:v>
+      </x:c>
+      <x:c r="F35" s="93" t="str">
+        <x:v>New editor preview: missing 0; mismatched 0.</x:v>
+      </x:c>
+      <x:c r="G35" s="93" t="str">
+        <x:v>Compares cache fields with original paid VCs before changing readers. Synthetic components 0 and 3100 also verified.</x:v>
+      </x:c>
+      <x:c r="H35" s="93" t="str">
+        <x:v>CONCATENATE("Perf initialize | missing ", COUNT(SELECT(Charges[Row ID], OR(ISBLANK([Perf Cached Principal Paid]), ISBLANK([Perf Cached Interest Paid])))), " | mismatched ", COUNT(SELECT(Charges[Row ID], OR([Perf Cached Principal Paid] &lt;&gt; [Principal Paid], [Perf Cached Interest Paid] &lt;&gt; [Interest Paid]))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="150" customHeight="1">
+      <x:c r="A36" s="93" t="str">
+        <x:v>P09 maintenance</x:v>
+      </x:c>
+      <x:c r="B36" s="93" t="str">
+        <x:v>1.000032</x:v>
+      </x:c>
+      <x:c r="C36" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D36" s="93" t="str">
+        <x:v>Perf - Refresh Borrower Charge Caches</x:v>
+      </x:c>
+      <x:c r="E36" s="93" t="str">
+        <x:v>Action / REF_ACTION</x:v>
+      </x:c>
+      <x:c r="F36" s="93" t="str">
+        <x:v>Hidden; now unused after receipt rollback.</x:v>
+      </x:c>
+      <x:c r="G36" s="93" t="str">
+        <x:v>Refreshes both components for all charges of the receipt borrower. Ledger recomputation is idempotent.</x:v>
+      </x:c>
+      <x:c r="H36" s="93" t="str">
+        <x:v>ReferencedTable Charges; ReferencedRows SELECT(Charges[Row ID], [Ref Loans].[Ref Borrowers] = [_THISROW].[Ref Borrower]); ReferencedAction Perf - Refresh Charge Paid Cache</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="150" customHeight="1">
+      <x:c r="A37" s="93" t="str">
+        <x:v>P09 receipt sequence</x:v>
+      </x:c>
+      <x:c r="B37" s="93" t="str">
+        <x:v>1.000033</x:v>
+      </x:c>
+      <x:c r="C37" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D37" s="93" t="str">
+        <x:v>Payment - Process Receipt</x:v>
+      </x:c>
+      <x:c r="E37" s="93" t="str">
+        <x:v>Action / COMPOSITE</x:v>
+      </x:c>
+      <x:c r="F37" s="93" t="str">
+        <x:v>Historical seven-step test sequence; original five steps restored 1.000037.</x:v>
+      </x:c>
+      <x:c r="G37" s="93" t="str">
+        <x:v>Includes refresh cost before snapshots and after posting. Original posting/reconciliation actions and predicates unchanged.</x:v>
+      </x:c>
+      <x:c r="H37" s="93" t="str">
+        <x:v>Perf - Refresh Borrower Charge Caches; Payment - Create Snapshots; Payment - Freeze Plan; Payment - Post Plan; Perf - Refresh Borrower Charge Caches; Payment - Reconcile; Payment - Close Paid Loans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="150" customHeight="1">
+      <x:c r="A38" s="93" t="str">
+        <x:v>P09 cached reader</x:v>
+      </x:c>
+      <x:c r="B38" s="93" t="str">
+        <x:v>1.000034</x:v>
+      </x:c>
+      <x:c r="C38" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D38" s="93" t="str">
+        <x:v>Principal Paid</x:v>
+      </x:c>
+      <x:c r="E38" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F38" s="93" t="str">
+        <x:v>Rejected P09a cache lag; originals restored 1.000037. No production change.</x:v>
+      </x:c>
+      <x:c r="G38" s="93" t="str">
+        <x:v>Blank fallback retains original sum. Original formula SUM([Related Repayments][Principal Paid]); baseline rollback 1.000032.</x:v>
+      </x:c>
+      <x:c r="H38" s="93" t="str">
+        <x:v>IF(ISNOTBLANK([Perf Cached Principal Paid]), [Perf Cached Principal Paid], SUM([Related Repayments][Principal Paid]))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="150" customHeight="1">
+      <x:c r="A39" s="93" t="str">
+        <x:v>P09 cached reader</x:v>
+      </x:c>
+      <x:c r="B39" s="93" t="str">
+        <x:v>1.000034</x:v>
+      </x:c>
+      <x:c r="C39" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D39" s="93" t="str">
+        <x:v>Interest Paid</x:v>
+      </x:c>
+      <x:c r="E39" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F39" s="93" t="str">
+        <x:v>Rejected P09a cache lag; originals restored 1.000037. No production change.</x:v>
+      </x:c>
+      <x:c r="G39" s="93" t="str">
+        <x:v>Blank fallback retains original sum. Original formula SUM([Related Repayments][Interest Paid]); baseline rollback 1.000032.</x:v>
+      </x:c>
+      <x:c r="H39" s="93" t="str">
+        <x:v>IF(ISNOTBLANK([Perf Cached Interest Paid]), [Perf Cached Interest Paid], SUM([Related Repayments][Interest Paid]))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="150" customHeight="1">
+      <x:c r="A40" s="93" t="str">
+        <x:v>P09 independent reconciliation</x:v>
+      </x:c>
+      <x:c r="B40" s="93" t="str">
+        <x:v>1.000034</x:v>
+      </x:c>
+      <x:c r="C40" s="93" t="str">
+        <x:v>Statistics / Charges</x:v>
+      </x:c>
+      <x:c r="D40" s="93" t="str">
+        <x:v>Perf - Initialize Next Cache Batch display name</x:v>
+      </x:c>
+      <x:c r="E40" s="93" t="str">
+        <x:v>Action display expression</x:v>
+      </x:c>
+      <x:c r="F40" s="93" t="str">
+        <x:v>Independent ledger comparison verified; action hidden in final 1.000038.</x:v>
+      </x:c>
+      <x:c r="G40" s="93" t="str">
+        <x:v>Must not compare cached fields with cached-reader VCs; doing so would be tautological. Initialization bot disabled at 1.000031; Statistics ID restored MAIN.</x:v>
+      </x:c>
+      <x:c r="H40" s="93" t="str">
+        <x:v>CONCATENATE("Perf initialize | missing ", COUNT(SELECT(Charges[Row ID], OR(ISBLANK([Perf Cached Principal Paid]), ISBLANK([Perf Cached Interest Paid])))), " | mismatched ", COUNT(SELECT(Charges[Row ID], OR([Perf Cached Principal Paid] &lt;&gt; SUM([Related Repayments][Principal Paid]), [Perf Cached Interest Paid] &lt;&gt; SUM([Related Repayments][Interest Paid])))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="150" customHeight="1">
+      <x:c r="A41" s="93" t="str">
+        <x:v>P09b direct refresh</x:v>
+      </x:c>
+      <x:c r="B41" s="93" t="str">
+        <x:v>1.000035</x:v>
+      </x:c>
+      <x:c r="C41" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D41" s="93" t="str">
+        <x:v>Perf - Refresh Charge Paid Cache</x:v>
+      </x:c>
+      <x:c r="E41" s="93" t="str">
+        <x:v>Action / SET_COLUMN_VALUE</x:v>
+      </x:c>
+      <x:c r="F41" s="93" t="str">
+        <x:v>Tested path reconciled; 14.06%/20.87% slower than before/after controls. Hidden and unused at 1.000038.</x:v>
+      </x:c>
+      <x:c r="G41" s="93" t="str">
+        <x:v>Direct table sum corrects observed same-sequence related-list lag. No concurrent or external-writer certification.</x:v>
+      </x:c>
+      <x:c r="H41" s="93" t="str">
+        <x:v>Perf Cached Principal Paid = SUM(SELECT(Repayments[Principal Paid], [Ref Charges] = [_THISROW].[Row ID])); Perf Cached Interest Paid = SUM(SELECT(Repayments[Interest Paid], [Ref Charges] = [_THISROW].[Row ID]))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="150" customHeight="1">
+      <x:c r="A42" s="93" t="str">
+        <x:v>P09 final rollback</x:v>
+      </x:c>
+      <x:c r="B42" s="93" t="str">
+        <x:v>1.000037</x:v>
+      </x:c>
+      <x:c r="C42" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D42" s="93" t="str">
+        <x:v>Principal Paid</x:v>
+      </x:c>
+      <x:c r="E42" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F42" s="93" t="str">
+        <x:v>Original ledger reader restored and verified.</x:v>
+      </x:c>
+      <x:c r="G42" s="93" t="str">
+        <x:v>Cache column remains unused historical evidence.</x:v>
+      </x:c>
+      <x:c r="H42" s="93" t="str">
+        <x:v>SUM([Related Repayments][Principal Paid])</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="150" customHeight="1">
+      <x:c r="A43" s="93" t="str">
+        <x:v>P09 final rollback</x:v>
+      </x:c>
+      <x:c r="B43" s="93" t="str">
+        <x:v>1.000037</x:v>
+      </x:c>
+      <x:c r="C43" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D43" s="93" t="str">
+        <x:v>Interest Paid</x:v>
+      </x:c>
+      <x:c r="E43" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F43" s="93" t="str">
+        <x:v>Original ledger reader restored and verified.</x:v>
+      </x:c>
+      <x:c r="G43" s="93" t="str">
+        <x:v>Intermediate 1.000036 was incomplete; no receipts submitted there.</x:v>
+      </x:c>
+      <x:c r="H43" s="93" t="str">
+        <x:v>SUM([Related Repayments][Interest Paid])</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="150" customHeight="1">
+      <x:c r="A44" s="93" t="str">
+        <x:v>P09 final rollback</x:v>
+      </x:c>
+      <x:c r="B44" s="93" t="str">
+        <x:v>1.000037</x:v>
+      </x:c>
+      <x:c r="C44" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D44" s="93" t="str">
+        <x:v>Payment - Process Receipt</x:v>
+      </x:c>
+      <x:c r="E44" s="93" t="str">
+        <x:v>Action / COMPOSITE</x:v>
+      </x:c>
+      <x:c r="F44" s="93" t="str">
+        <x:v>Original five-step flow restored; three reversal controls Posted.</x:v>
+      </x:c>
+      <x:c r="G44" s="93" t="str">
+        <x:v>No cache maintenance remains in receipt path.</x:v>
+      </x:c>
+      <x:c r="H44" s="93" t="str">
+        <x:v>Payment - Create Snapshots; Payment - Freeze Plan; Payment - Post Plan; Payment - Reconcile; Payment - Close Paid Loans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="150" customHeight="1">
+      <x:c r="A45" s="93" t="str">
+        <x:v>Final lab cleanup</x:v>
+      </x:c>
+      <x:c r="B45" s="93" t="str">
+        <x:v>1.000038</x:v>
+      </x:c>
+      <x:c r="C45" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D45" s="93" t="str">
+        <x:v>Perf - Initialize Next Cache Batch</x:v>
+      </x:c>
+      <x:c r="E45" s="93" t="str">
+        <x:v>Action visibility</x:v>
+      </x:c>
+      <x:c r="F45" s="93" t="str">
+        <x:v>Hidden; initializer bot disabled; Statistics ID MAIN restored.</x:v>
+      </x:c>
+      <x:c r="G45" s="93" t="str">
+        <x:v>Retained for lab recovery only. Do not treat historical cache values as current balances.</x:v>
+      </x:c>
+      <x:c r="H45" s="93" t="str">
+        <x:v>Prominence Do_Not_Display</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3769,7 +4087,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11e2bb00962f43d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8620a662bba43e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14270,7 +14588,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R480a90986b924ce4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6e837d5874345c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14699,7 +15017,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1bfb898f9754e54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7ba59e715e6475a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15153,7 +15471,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re282524943c848e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc09f573333634c04"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21315,7 +21633,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc9aaed3b11b450c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c185013b6e14191"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25814,7 +26132,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1093c69855d474b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3de0ff88828946af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26013,7 +26331,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd24fffd2968c41c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R529ecd47cea74163"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27666,7 +27984,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b6a59df6ba4693"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53ac300938f14aeb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,17 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R79a7c6c8c0da487a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R5c9112ad24ec482d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rc34619690220467b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R1462e69c86444983"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Re0b2c4e28ca34940"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R76948fb212d745ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rfa94536683874f06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R7adcb098727f467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R36bc897ce824407c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rcaada003fd364f52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R0e18422c473a4c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R40d968f488b94b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rbe56627832684152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R743c9184c04c4c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R579f951143204693"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rbecdea6db3e74270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R6ddbb7d808c34d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rddd8a4cc54c94382"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R46b5baab65624f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R62a32becd5c84be0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R97eeea045c2348ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rdbcc72a35e1b4de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rb3cb830aff454437"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -97,7 +98,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -132,6 +133,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -339,7 +345,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="108">
+  <x:cellXfs count="111">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -574,6 +580,11 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2481,7 +2492,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb70980dd8bbe4447"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcc21160190041a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3666,6 +3677,207 @@
       </x:c>
       <x:c r="H45" s="93" t="str">
         <x:v>Prominence Do_Not_Display</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="110" t="str">
+        <x:v>Experiment</x:v>
+      </x:c>
+      <x:c r="B1" s="110" t="str">
+        <x:v>App version</x:v>
+      </x:c>
+      <x:c r="C1" s="110" t="str">
+        <x:v>Table</x:v>
+      </x:c>
+      <x:c r="D1" s="110" t="str">
+        <x:v>Column / setting</x:v>
+      </x:c>
+      <x:c r="E1" s="110" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="F1" s="110" t="str">
+        <x:v>Scope / status</x:v>
+      </x:c>
+      <x:c r="G1" s="110" t="str">
+        <x:v>Purpose / dependencies</x:v>
+      </x:c>
+      <x:c r="H1" s="110" t="str">
+        <x:v>Exact definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="150" customHeight="1">
+      <x:c r="A2" s="93" t="str">
+        <x:v>P01a</x:v>
+      </x:c>
+      <x:c r="B2" s="93" t="str">
+        <x:v>1.000044</x:v>
+      </x:c>
+      <x:c r="C2" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D2" s="93" t="str">
+        <x:v>Eligible Charges</x:v>
+      </x:c>
+      <x:c r="E2" s="93" t="str">
+        <x:v>List / Ref Charges</x:v>
+      </x:c>
+      <x:c r="F2" s="93" t="str">
+        <x:v>Combined candidate retained in test clone</x:v>
+      </x:c>
+      <x:c r="G2" s="93" t="str">
+        <x:v>Posted returns empty; other statuses retain original selection. Eligible Outstanding and Amount Received description become zero on Posted.</x:v>
+      </x:c>
+      <x:c r="H2" s="93" t="str">
+        <x:v>IF([Status] = "Posted", LIST(), SELECT(Charges[Row ID], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Ref Borrower], [Amount Remaining] &gt; 0, IFS(IN([_THISROW].[Allocation Method], LIST("Single Full", "Single Partial", "First-day Auto")), [Row ID] = [_THISROW].[Ref Target Charge], [_THISROW].[Allocation Method] = "Loan Close", [Ref Loans] = [_THISROW].[Ref Target Charge].[Ref Loans], IN([_THISROW].[Allocation Method], LIST("Receive All", "Lump Sum")), [Charge Date] &lt;= [_THISROW].[Payment Date], TRUE, FALSE))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="150" customHeight="1">
+      <x:c r="A3" s="93" t="str">
+        <x:v>P04a</x:v>
+      </x:c>
+      <x:c r="B3" s="93" t="str">
+        <x:v>1.000044</x:v>
+      </x:c>
+      <x:c r="C3" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D3" s="93" t="str">
+        <x:v>Calculated Amount</x:v>
+      </x:c>
+      <x:c r="E3" s="93" t="str">
+        <x:v>Price</x:v>
+      </x:c>
+      <x:c r="F3" s="93" t="str">
+        <x:v>Combined candidate retained in test clone</x:v>
+      </x:c>
+      <x:c r="G3" s="93" t="str">
+        <x:v>Direct date-descending / row-descending predecessor; snapshots, guards and posting sequence unchanged.</x:v>
+      </x:c>
+      <x:c r="H3" s="93" t="str">
+        <x:v>MAX(LIST(DECIMAL(0), MIN(LIST(DECIMAL([Amount Remaining Snapshot]), DECIMAL([Ref Payment].[Amount Received]) - DECIMAL(SUM(SELECT(Payment Allocations[Amount Remaining Snapshot], AND([Ref Payment] = [_THISROW].[Ref Payment], OR([Charge Date Snapshot] &gt; [_THISROW].[Charge Date Snapshot], AND([Charge Date Snapshot] = [_THISROW].[Charge Date Snapshot], [Charge Row Number Snapshot] &gt; [_THISROW].[Charge Row Number Snapshot]))))))))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="150" customHeight="1">
+      <x:c r="A4" s="93" t="str">
+        <x:v>Rollback</x:v>
+      </x:c>
+      <x:c r="B4" s="93" t="str">
+        <x:v>1.000038</x:v>
+      </x:c>
+      <x:c r="C4" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D4" s="93" t="str">
+        <x:v>Eligible Charges</x:v>
+      </x:c>
+      <x:c r="E4" s="93" t="str">
+        <x:v>List / Ref Charges</x:v>
+      </x:c>
+      <x:c r="F4" s="93" t="str">
+        <x:v>Original definition</x:v>
+      </x:c>
+      <x:c r="G4" s="93" t="str">
+        <x:v>Restore this expression to remove P01a.</x:v>
+      </x:c>
+      <x:c r="H4" s="93" t="str">
+        <x:v>SELECT(Charges[Row ID], AND([Ref Loans].[Ref Borrowers] = [_THISROW].[Ref Borrower], [Amount Remaining] &gt; 0, IFS(IN([_THISROW].[Allocation Method], LIST("Single Full", "Single Partial", "First-day Auto")), [Row ID] = [_THISROW].[Ref Target Charge], [_THISROW].[Allocation Method] = "Loan Close", [Ref Loans] = [_THISROW].[Ref Target Charge].[Ref Loans], IN([_THISROW].[Allocation Method], LIST("Receive All", "Lump Sum")), [Charge Date] &lt;= [_THISROW].[Payment Date], TRUE, FALSE)))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="150" customHeight="1">
+      <x:c r="A5" s="93" t="str">
+        <x:v>Rollback</x:v>
+      </x:c>
+      <x:c r="B5" s="93" t="str">
+        <x:v>1.000038</x:v>
+      </x:c>
+      <x:c r="C5" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D5" s="93" t="str">
+        <x:v>Calculated Amount</x:v>
+      </x:c>
+      <x:c r="E5" s="93" t="str">
+        <x:v>Price</x:v>
+      </x:c>
+      <x:c r="F5" s="93" t="str">
+        <x:v>Original definition</x:v>
+      </x:c>
+      <x:c r="G5" s="93" t="str">
+        <x:v>Restore this expression to remove P04a.</x:v>
+      </x:c>
+      <x:c r="H5" s="93" t="str">
+        <x:v>MAX(LIST(DECIMAL(0), MIN(LIST(DECIMAL([Amount Remaining Snapshot]), DECIMAL([Ref Payment].[Amount Received]) - DECIMAL(SUM(SELECT(Payment Allocations[Amount Remaining Snapshot], AND([Ref Payment] = [_THISROW].[Ref Payment], [Calculated Order] &lt; [_THISROW].[Calculated Order]))))))))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="150" customHeight="1">
+      <x:c r="A6" s="93" t="str">
+        <x:v>Diagnostic</x:v>
+      </x:c>
+      <x:c r="B6" s="93" t="str">
+        <x:v>1.000042 → 1.000044</x:v>
+      </x:c>
+      <x:c r="C6" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D6" s="93" t="str">
+        <x:v>Visible Allocations</x:v>
+      </x:c>
+      <x:c r="E6" s="93" t="str">
+        <x:v>List / Ref Payment Allocations</x:v>
+      </x:c>
+      <x:c r="F6" s="93" t="str">
+        <x:v>Temporary all-row display restored; outside timing runs</x:v>
+      </x:c>
+      <x:c r="G6" s="93" t="str">
+        <x:v>All plan rows including zero allocations inspected, then positive-only original restored.</x:v>
+      </x:c>
+      <x:c r="H6" s="93" t="str">
+        <x:v>SELECT(Payment Allocations[Row ID], AND([Ref Payment] = [_THISROW].[Row ID], [Allocated Amount] &gt; 0))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="150" customHeight="1">
+      <x:c r="A7" s="93" t="str">
+        <x:v>Diagnostic</x:v>
+      </x:c>
+      <x:c r="B7" s="93" t="str">
+        <x:v>1.000043 → 1.000044</x:v>
+      </x:c>
+      <x:c r="C7" s="93" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D7" s="93" t="str">
+        <x:v>Receive All Charges</x:v>
+      </x:c>
+      <x:c r="E7" s="93" t="str">
+        <x:v>Action position</x:v>
+      </x:c>
+      <x:c r="F7" s="93" t="str">
+        <x:v>Temporary Prominent restored to Inline; outside timing runs</x:v>
+      </x:c>
+      <x:c r="G7" s="93" t="str">
+        <x:v>Normal receipt logic unchanged; new desktop UI exercised.</x:v>
+      </x:c>
+      <x:c r="H7" s="93" t="str">
+        <x:v>Inline</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4087,7 +4299,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8620a662bba43e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2371162a0c8e4a85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14588,7 +14800,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6e837d5874345c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58556346a9974dfe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15017,7 +15229,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7ba59e715e6475a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R093ff56894c845fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15471,7 +15683,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc09f573333634c04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf54ba8223f7e4bef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21633,7 +21845,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c185013b6e14191"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bd4ce0df6064818"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26132,7 +26344,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3de0ff88828946af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26ef912329af41c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26331,7 +26543,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R529ecd47cea74163"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb02371891eba49a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27984,7 +28196,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53ac300938f14aeb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4bc6996d5bb44c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R40d968f488b94b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rbe56627832684152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R743c9184c04c4c69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R579f951143204693"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rbecdea6db3e74270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R6ddbb7d808c34d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rddd8a4cc54c94382"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R46b5baab65624f37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R62a32becd5c84be0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R97eeea045c2348ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rdbcc72a35e1b4de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rb3cb830aff454437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rd893d693986c4194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R9008d850b3294414"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R4f0d0bb4bf454887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rfc1bf38aaf9445f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rb950f955cc40458d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R31f9e8394d0d444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R0bf2af24bdc74f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R842a9edd6fe64612"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R921fa5e8f16f4a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R3a4b5860a0404a46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rfa88407996944400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R9eb1450f87104df8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -722,8 +722,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DataModelColumns" displayName="DataModelColumns" ref="A4:H392" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H392"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DataModelColumns" displayName="DataModelColumns" ref="A4:H398" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H398"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Table"/>
     <x:tableColumn id="2" name="Inventory order"/>
@@ -769,7 +769,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D440" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D448" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="App"/>
     <x:tableColumn id="2" name="Slice"/>
@@ -781,8 +781,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="DataModelAppVariances" displayName="DataModelAppVariances" ref="A4:F227" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:F227"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="DataModelAppVariances" displayName="DataModelAppVariances" ref="A4:F232" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:F232"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Object Type"/>
     <x:tableColumn id="2" name="Table"/>
@@ -1079,7 +1079,7 @@
         <x:v>Reconciliation status</x:v>
       </x:c>
       <x:c r="B5" s="85" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok). Collection settings reconciled in production Operations app; standalone forms/default/setup-review verified. OLAP standalone app opened successfully; its new-column loading is pending reconciliation. Other inventory retains dated scope.</x:v>
+        <x:v>OLTP 3.000050; 13 September 2026. Partner controls, borrower locations and affected slice memberships verified. New OLAP field loading remains pending. Earlier unrelated inventory retains dated scope.</x:v>
       </x:c>
       <x:c r="C5" s="73"/>
       <x:c r="D5" s="73"/>
@@ -1091,7 +1091,7 @@
         <x:v>Live baselines</x:v>
       </x:c>
       <x:c r="B6" s="85" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); rollback OLTP 3.000014. Native backup Money Collection Backup 20260908 (12 tables, rows copied); local runner/docs rollback retained. OLAP last documented 1.100016; no OLAP configuration changed.</x:v>
+        <x:v>Setup rollback OLTP 3.000045; final 3.000050. App restore does not restore database schema/data. Private cell before-image retained outside Git. No OLAP configuration changed.</x:v>
       </x:c>
       <x:c r="C6" s="73"/>
       <x:c r="D6" s="73"/>
@@ -2492,7 +2492,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcc21160190041a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a30166ee3ba430b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3907,7 +3907,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>14 native tables. OLTP loads10: Borrowers has14 physical +28 VCs; new bank table7+3 and singleton settings4+0. OLAP loading of new fields not reconciled; prior counts retained.</x:v>
+        <x:v>13 September 2026: OLTP Borrowers 16 physical +29 VCs; Partners 8 physical +0 VCs. Counts include source ordinal. Other tables and OLAP counts retain prior verification scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -3958,16 +3958,16 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="D5" s="56" t="n">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F5" s="56" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="G5" s="58" t="str">
-        <x:v>Borrower master; Row ID remains immutable key. Seven new collection fields and two OLTP helpers. OLAP65 VC count is prior baseline; loading of seven new physical fields not reconciled.</x:v>
+        <x:v>OLTP: 45 columns, including source ordinal/key; City and Working Location added. OLAP loading of new fields pending; prior OLAP VCs retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
@@ -4118,8 +4118,8 @@
       <x:c r="C12" s="57" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="D12" s="57" t="str">
-        <x:v>5</x:v>
+      <x:c r="D12" s="57" t="n">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E12" s="57" t="str">
         <x:v>0</x:v>
@@ -4128,7 +4128,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G12" s="59" t="str">
-        <x:v>Partner master records used for capital participation and settlement reporting.</x:v>
+        <x:v>Partner identity, email, language and integration opt-in; OLTP 8 stored columns including ordinal/key. New OLAP field loading pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="65" customHeight="1">
@@ -4299,7 +4299,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2371162a0c8e4a85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41a7575e92db4f9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4332,7 +4332,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>8 September 2026: Auto Charge Enabled added to Loans in both apps. Eleven existing model expressions reconciled. Manual workflow acceptance remains pending.</x:v>
+        <x:v>13 September 2026: five stored partner/location fields added in OLTP 3.000050. No messaging activation. Earlier unrelated inventory retains dated verification scope.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -4493,7 +4493,7 @@
         <x:v>Description</x:v>
       </x:c>
       <x:c r="D9" s="59" t="str">
-        <x:v>Physical / LongText</x:v>
+        <x:v>Physical / Text (OLTP); LongText (OLAP prior)</x:v>
       </x:c>
       <x:c r="E9" s="57" t="str">
         <x:v>OLTP + OLAP</x:v>
@@ -4502,7 +4502,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="59" t="str">
-        <x:v>Stores the authoritative source value for Description.</x:v>
+        <x:v>OLTP Text confirmed during location setup; earlier OLAP LongText inventory retained pending reconciliation.</x:v>
       </x:c>
       <x:c r="H9" s="59" t="str">
         <x:v>Stored source column</x:v>
@@ -14289,7 +14289,7 @@
         <x:v>Editable</x:v>
       </x:c>
       <x:c r="G374" s="87" t="str">
-        <x:v>Opt-in for the existing AI collection workflow; position 12.</x:v>
+        <x:v>Existing borrower opt-in; also required alongside Collection dashboard eligibility for the proposed partner daily briefing. Existing flag values unchanged.</x:v>
       </x:c>
       <x:c r="H374" s="87" t="str">
         <x:v>Stored; initial value FALSE</x:v>
@@ -14787,6 +14787,136 @@
       </x:c>
       <x:c r="H393" s="73" t="str">
         <x:v>Initial value: TRUE. No app formula. Native key h7VnJR1ERY4o6UUaiANzwe. Restore nominal rates without re-enabling generation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" ht="42" customHeight="1">
+      <x:c r="A394" s="73" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="B394" s="73" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C394" s="73" t="str">
+        <x:v>Instagram Username</x:v>
+      </x:c>
+      <x:c r="D394" s="73" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E394" s="73" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F394" s="73" t="str">
+        <x:v>Shown, editable, optional, searchable</x:v>
+      </x:c>
+      <x:c r="G394" s="73" t="str">
+        <x:v>Partner Instagram handle. App position 6. No separate partner list.</x:v>
+      </x:c>
+      <x:c r="H394" s="73" t="str">
+        <x:v>Stored; no formula, default, key or label. Verification binding belongs to later agent implementation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" ht="42" customHeight="1">
+      <x:c r="A395" s="73" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="B395" s="73" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C395" s="73" t="str">
+        <x:v>Language Preference</x:v>
+      </x:c>
+      <x:c r="D395" s="73" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E395" s="73" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F395" s="73" t="str">
+        <x:v>Shown, editable, optional, searchable</x:v>
+      </x:c>
+      <x:c r="G395" s="73" t="str">
+        <x:v>Language for partner notices, replies and email. App position 7.</x:v>
+      </x:c>
+      <x:c r="H395" s="73" t="str">
+        <x:v>Stored; blank initial value. Preferences not inferred or populated. Borrower drafts retain approved Thai.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" ht="42" customHeight="1">
+      <x:c r="A396" s="73" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="B396" s="73" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C396" s="73" t="str">
+        <x:v>IG Integration Enabled</x:v>
+      </x:c>
+      <x:c r="D396" s="73" t="str">
+        <x:v>Physical / Yes/No</x:v>
+      </x:c>
+      <x:c r="E396" s="73" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F396" s="73" t="str">
+        <x:v>Shown, editable, optional, searchable</x:v>
+      </x:c>
+      <x:c r="G396" s="73" t="str">
+        <x:v>Master opt-in for partner Instagram and email fallback. App position 8.</x:v>
+      </x:c>
+      <x:c r="H396" s="73" t="str">
+        <x:v>Initial value FALSE; no app formula. Existing partners unchecked. Only TRUE permits future agent communication.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" ht="42" customHeight="1">
+      <x:c r="A397" s="73" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B397" s="73" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C397" s="73" t="str">
+        <x:v>City</x:v>
+      </x:c>
+      <x:c r="D397" s="73" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E397" s="73" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F397" s="73" t="str">
+        <x:v>Shown, editable, optional, searchable</x:v>
+      </x:c>
+      <x:c r="G397" s="73" t="str">
+        <x:v>Borrower city from the owner location sheet. App position 15.</x:v>
+      </x:c>
+      <x:c r="H397" s="73" t="str">
+        <x:v>Stored; blank initial value; display name: "เมือง / City". Source blanks preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" ht="42" customHeight="1">
+      <x:c r="A398" s="73" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B398" s="73" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C398" s="73" t="str">
+        <x:v>Working Location</x:v>
+      </x:c>
+      <x:c r="D398" s="73" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E398" s="73" t="str">
+        <x:v>OLTP; OLAP pending</x:v>
+      </x:c>
+      <x:c r="F398" s="73" t="str">
+        <x:v>Shown, editable, optional, searchable</x:v>
+      </x:c>
+      <x:c r="G398" s="73" t="str">
+        <x:v>Workplace/locality from the owner location sheet. App position 16.</x:v>
+      </x:c>
+      <x:c r="H398" s="73" t="str">
+        <x:v>Stored; blank initial value; display name: "สถานที่ทำงาน / Working Location". Uncertainty preserved.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14800,7 +14930,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58556346a9974dfe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82c1edae5ecb4b6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15229,7 +15359,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R093ff56894c845fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6373227e1eb1402d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15325,13 +15455,13 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F5" s="83" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G5" s="83" t="str">
-        <x:v>Existing collection-board filter retained; seven physical collection settings appended during regeneration.</x:v>
+        <x:v>Existing daily collection population. Future agent additionally requires due/overdue and AI Collection Enabled; dashboard filter unchanged.</x:v>
       </x:c>
       <x:c r="H5" s="83" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); base-row details provide effective bank and setup issues.</x:v>
+        <x:v>OLTP 3.000050; location columns included after regeneration. Existing row filter and update mode retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="55" customHeight="1">
@@ -15351,13 +15481,13 @@
         <x:v>Adds, Updates, Deletes</x:v>
       </x:c>
       <x:c r="F6" s="83" t="n">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G6" s="83" t="str">
-        <x:v>Existing borrower-list filter retained; nine collection fields appended.</x:v>
+        <x:v>Primary borrower list; City and Working Location exposed in existing form/detail views.</x:v>
       </x:c>
       <x:c r="H6" s="83" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); borrower edit/detail views expose the new fields.</x:v>
+        <x:v>OLTP 3.000050; location columns included after regeneration. Existing row filter and update mode retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -15667,13 +15797,13 @@
         <x:v>Updates only</x:v>
       </x:c>
       <x:c r="F19" s="87" t="n">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G19" s="87" t="str">
         <x:v>Enabled borrowers needing name, Instagram or receiving-bank setup.</x:v>
       </x:c>
       <x:c r="H19" s="87" t="str">
-        <x:v>Auto-assigned actions; menu table view; disabled borrowers excluded intentionally.</x:v>
+        <x:v>OLTP 3.000050; location columns included after regeneration. Existing row filter and update mode retained.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15683,7 +15813,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf54ba8223f7e4bef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8379e6cd54e749fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21838,6 +21968,118 @@
         <x:v>Collection Setup Issues</x:v>
       </x:c>
     </x:row>
+    <x:row r="441">
+      <x:c r="A441" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B441" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C441" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D441" t="str">
+        <x:v>Collection Account Number</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442">
+      <x:c r="A442" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B442" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C442" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D442" t="str">
+        <x:v>City</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443">
+      <x:c r="A443" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B443" t="str">
+        <x:v>Collection Setup Review</x:v>
+      </x:c>
+      <x:c r="C443" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D443" t="str">
+        <x:v>Working Location</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444">
+      <x:c r="A444" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B444" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C444" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D444" t="str">
+        <x:v>City</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445">
+      <x:c r="A445" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B445" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C445" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D445" t="str">
+        <x:v>Working Location</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446">
+      <x:c r="A446" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B446" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C446" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D446" t="str">
+        <x:v>Collection Account Number</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447">
+      <x:c r="A447" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B447" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C447" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D447" t="str">
+        <x:v>City</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448">
+      <x:c r="A448" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B448" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C448" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D448" t="str">
+        <x:v>Working Location</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
@@ -21845,7 +22087,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bd4ce0df6064818"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd662c409624492a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26331,7 +26573,107 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="F227" s="87" t="str">
-        <x:v>Enabled borrowers with nonempty setup issues;42 columns; update only.</x:v>
+        <x:v>Enabled borrowers with setup issues; 45 columns at OLTP 3.000050; update only.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B228" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="C228" t="str">
+        <x:v>Instagram Username</x:v>
+      </x:c>
+      <x:c r="D228" t="str">
+        <x:v>Yes — 3.000050</x:v>
+      </x:c>
+      <x:c r="E228" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F228" t="str">
+        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B229" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="C229" t="str">
+        <x:v>Language Preference</x:v>
+      </x:c>
+      <x:c r="D229" t="str">
+        <x:v>Yes — 3.000050</x:v>
+      </x:c>
+      <x:c r="E229" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F229" t="str">
+        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B230" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="C230" t="str">
+        <x:v>IG Integration Enabled</x:v>
+      </x:c>
+      <x:c r="D230" t="str">
+        <x:v>Yes — 3.000050</x:v>
+      </x:c>
+      <x:c r="E230" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F230" t="str">
+        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B231" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C231" t="str">
+        <x:v>City</x:v>
+      </x:c>
+      <x:c r="D231" t="str">
+        <x:v>Yes — 3.000050</x:v>
+      </x:c>
+      <x:c r="E231" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F231" t="str">
+        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B232" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C232" t="str">
+        <x:v>Working Location</x:v>
+      </x:c>
+      <x:c r="D232" t="str">
+        <x:v>Yes — 3.000050</x:v>
+      </x:c>
+      <x:c r="E232" t="str">
+        <x:v>Pending reconciliation</x:v>
+      </x:c>
+      <x:c r="F232" t="str">
+        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -26344,7 +26686,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26ef912329af41c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfe8af29d8ae41ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26543,7 +26885,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb02371891eba49a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e5f7a3347484eb0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28196,7 +28538,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4bc6996d5bb44c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf15aefded0a44967"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rd893d693986c4194"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R9008d850b3294414"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R4f0d0bb4bf454887"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rfc1bf38aaf9445f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rb950f955cc40458d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R31f9e8394d0d444a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R0bf2af24bdc74f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R842a9edd6fe64612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R921fa5e8f16f4a65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R3a4b5860a0404a46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rfa88407996944400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R9eb1450f87104df8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R04429f714ad54310"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R6eb4a437eb894a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R62093d1a3d63442f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R37c42161bd4d4552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rbbe168736fc445fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rc7efbb7a1e174594"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R5f2f79c51fcb4170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Rc452e6abf5684e0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R45c8270d30ce4000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rdd80efcc0a714ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R4d73f202be074a83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rccf1c12d05d14804"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -769,7 +769,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D448" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D492" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="App"/>
     <x:tableColumn id="2" name="Slice"/>
@@ -1079,7 +1079,7 @@
         <x:v>Reconciliation status</x:v>
       </x:c>
       <x:c r="B5" s="85" t="str">
-        <x:v>OLTP 3.000050; 13 September 2026. Partner controls, borrower locations and affected slice memberships verified. New OLAP field loading remains pending. Earlier unrelated inventory retains dated scope.</x:v>
+        <x:v>13 September 2026: OLTP 3.000050 and OLAP 1.100031 partner/location fields and affected slices reconciled. OLAP partner forms and borrower read-only detail checked. No agent activation.</x:v>
       </x:c>
       <x:c r="C5" s="73"/>
       <x:c r="D5" s="73"/>
@@ -1091,7 +1091,7 @@
         <x:v>Live baselines</x:v>
       </x:c>
       <x:c r="B6" s="85" t="str">
-        <x:v>Setup rollback OLTP 3.000045; final 3.000050. App restore does not restore database schema/data. Private cell before-image retained outside Git. No OLAP configuration changed.</x:v>
+        <x:v>Rollback: OLTP 3.000045; OLAP 1.100028. App restore does not restore shared database data/schema. Private location before-image remains outside Git. Owner acceptance pending.</x:v>
       </x:c>
       <x:c r="C6" s="73"/>
       <x:c r="D6" s="73"/>
@@ -2492,7 +2492,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a30166ee3ba430b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdcff336c8174e33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3907,7 +3907,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>13 September 2026: OLTP Borrowers 16 physical +29 VCs; Partners 8 physical +0 VCs. Counts include source ordinal. Other tables and OLAP counts retain prior verification scope.</x:v>
+        <x:v>13 September 2026: shared partner/location fields reconciled in both apps. OLTP 3.000050; OLAP 1.100031. Other tables retain dated verification scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -3967,7 +3967,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="G5" s="58" t="str">
-        <x:v>OLTP: 45 columns, including source ordinal/key; City and Working Location added. OLAP loading of new fields pending; prior OLAP VCs retained.</x:v>
+        <x:v>OLTP 45 =16 stored +29 VCs; OLAP 81 =16 stored +65 VCs. OLAP read-only, new location fields loaded. Counts include ordinal/key.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
@@ -4128,7 +4128,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G12" s="59" t="str">
-        <x:v>Partner identity, email, language and integration opt-in; OLTP 8 stored columns including ordinal/key. New OLAP field loading pending.</x:v>
+        <x:v>OLTP 8 stored; OLAP 20 =8 stored +12 VCs. OLAP owns partner management, with existing add/update/delete mode preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="65" customHeight="1">
@@ -4299,7 +4299,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41a7575e92db4f9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R285d3bc61d2041ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4332,7 +4332,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>13 September 2026: five stored partner/location fields added in OLTP 3.000050. No messaging activation. Earlier unrelated inventory retains dated verification scope.</x:v>
+        <x:v>13 September 2026: OLTP 3.000050 and OLAP 1.100031 partner/location setup reconciled. Existing OLAP Borrowers remains read-only; no messaging activation. Other inventory retains dated scope.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -4493,7 +4493,7 @@
         <x:v>Description</x:v>
       </x:c>
       <x:c r="D9" s="59" t="str">
-        <x:v>Physical / Text (OLTP); LongText (OLAP prior)</x:v>
+        <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E9" s="57" t="str">
         <x:v>OLTP + OLAP</x:v>
@@ -4502,7 +4502,7 @@
         <x:v>-</x:v>
       </x:c>
       <x:c r="G9" s="59" t="str">
-        <x:v>OLTP Text confirmed during location setup; earlier OLAP LongText inventory retained pending reconciliation.</x:v>
+        <x:v>Text confirmed in both apps during partner/location setup reconciliation.</x:v>
       </x:c>
       <x:c r="H9" s="59" t="str">
         <x:v>Stored source column</x:v>
@@ -10458,7 +10458,7 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F230" s="57" t="str">
-        <x:v>OLTP: PII; OLAP: Required</x:v>
+        <x:v>OLTP: PII; OLAP: Required, PII</x:v>
       </x:c>
       <x:c r="G230" s="59" t="str">
         <x:v>Stores the authoritative source value for Email.</x:v>
@@ -14165,7 +14165,7 @@
 OLAP v1.100016: List. Same REF_ROWS expression. Initial value blank. No operational payment actions or processing formulas imported.</x:v>
       </x:c>
     </x:row>
-    <x:row r="370" ht="15" customHeight="1">
+    <x:row r="370" ht="78" customHeight="1">
       <x:c r="A370" s="87" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -14179,19 +14179,19 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E370" s="87" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F370" s="87" t="str">
-        <x:v>Editable</x:v>
+        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G370" s="87" t="str">
         <x:v>Explicit message address; no suffix stripping. App physical position 8.</x:v>
       </x:c>
       <x:c r="H370" s="87" t="str">
-        <x:v>Stored; blank initial value; display name: "ชื่อที่ใช้เรียก / Communication Name"</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="371" ht="15" customHeight="1">
+        <x:v>Stored; blank initial value. OLTP display name "ชื่อที่ใช้เรียก / Communication Name"; OLAP default field name.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" ht="78" customHeight="1">
       <x:c r="A371" s="87" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -14205,10 +14205,10 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E371" s="87" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F371" s="87" t="str">
-        <x:v>Editable</x:v>
+        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G371" s="87" t="str">
         <x:v>Borrower Instagram handle without @; app physical position 9.</x:v>
@@ -14217,7 +14217,7 @@
         <x:v>Stored; blank initial value</x:v>
       </x:c>
     </x:row>
-    <x:row r="372" ht="15" customHeight="1">
+    <x:row r="372" ht="78" customHeight="1">
       <x:c r="A372" s="87" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -14228,22 +14228,22 @@
         <x:v>Instagram Conversation URL</x:v>
       </x:c>
       <x:c r="D372" s="87" t="str">
-        <x:v>Physical / Url</x:v>
+        <x:v>Physical / Url (OLTP); Text (OLAP)</x:v>
       </x:c>
       <x:c r="E372" s="87" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F372" s="87" t="str">
-        <x:v>Editable</x:v>
+        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G372" s="87" t="str">
         <x:v>Verified conversation link; native Text, app Url; position 10.</x:v>
       </x:c>
       <x:c r="H372" s="87" t="str">
-        <x:v>Stored; blank initial value</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="373" ht="15" customHeight="1">
+        <x:v>Stored native Text; OLTP Url, OLAP Text. Both initial values blank; existing app type variance preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" ht="78" customHeight="1">
       <x:c r="A373" s="87" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -14257,19 +14257,19 @@
         <x:v>Physical / DateTime</x:v>
       </x:c>
       <x:c r="E373" s="87" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F373" s="87" t="str">
-        <x:v>Editable</x:v>
+        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G373" s="87" t="str">
         <x:v>Time mapping was actually checked; position 11.</x:v>
       </x:c>
       <x:c r="H373" s="87" t="str">
-        <x:v>Stored; blank initial value (removed inferred NOW())</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="374" ht="15" customHeight="1">
+        <x:v>Stored; blank initial value in both apps. OLAP inherited NOW() removed during 13 September reconciliation. Existing values unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" ht="78" customHeight="1">
       <x:c r="A374" s="87" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -14283,19 +14283,19 @@
         <x:v>Physical / Yes/No</x:v>
       </x:c>
       <x:c r="E374" s="87" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F374" s="87" t="str">
-        <x:v>Editable</x:v>
+        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G374" s="87" t="str">
         <x:v>Existing borrower opt-in; also required alongside Collection dashboard eligibility for the proposed partner daily briefing. Existing flag values unchanged.</x:v>
       </x:c>
       <x:c r="H374" s="87" t="str">
-        <x:v>Stored; initial value FALSE</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="375" ht="15" customHeight="1">
+        <x:v>Stored; initial FALSE in both apps. OLAP table remains read-only; existing values unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" ht="78" customHeight="1">
       <x:c r="A375" s="87" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -14309,19 +14309,19 @@
         <x:v>Physical / Yes/No</x:v>
       </x:c>
       <x:c r="E375" s="87" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F375" s="87" t="str">
-        <x:v>Editable</x:v>
+        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G375" s="87" t="str">
         <x:v>Independent penalty eligibility; position 13. Existing fees never reversed by this flag.</x:v>
       </x:c>
       <x:c r="H375" s="87" t="str">
-        <x:v>Stored; initial value FALSE; daily eligibility held in runner SQLite</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="376" ht="15" customHeight="1">
+        <x:v>Stored; initial FALSE in both apps. Existing values and collection runtime unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" ht="78" customHeight="1">
       <x:c r="A376" s="87" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -14335,10 +14335,10 @@
         <x:v>Physical / Ref</x:v>
       </x:c>
       <x:c r="E376" s="87" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F376" s="87" t="str">
-        <x:v>Editable, Optional</x:v>
+        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G376" s="87" t="str">
         <x:v>Borrower-specific receiving bank; position 14.</x:v>
@@ -14789,7 +14789,7 @@
         <x:v>Initial value: TRUE. No app formula. Native key h7VnJR1ERY4o6UUaiANzwe. Restore nominal rates without re-enabling generation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="394" ht="42" customHeight="1">
+    <x:row r="394" ht="78" customHeight="1">
       <x:c r="A394" s="73" t="str">
         <x:v>Partners</x:v>
       </x:c>
@@ -14803,19 +14803,19 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E394" s="73" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F394" s="73" t="str">
         <x:v>Shown, editable, optional, searchable</x:v>
       </x:c>
       <x:c r="G394" s="73" t="str">
-        <x:v>Partner Instagram handle. App position 6. No separate partner list.</x:v>
+        <x:v>Partner Instagram handle. Stored position 6 in both apps; managed through OLAP Partners_Form.</x:v>
       </x:c>
       <x:c r="H394" s="73" t="str">
         <x:v>Stored; no formula, default, key or label. Verification binding belongs to later agent implementation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="395" ht="42" customHeight="1">
+    <x:row r="395" ht="78" customHeight="1">
       <x:c r="A395" s="73" t="str">
         <x:v>Partners</x:v>
       </x:c>
@@ -14829,19 +14829,19 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E395" s="73" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F395" s="73" t="str">
         <x:v>Shown, editable, optional, searchable</x:v>
       </x:c>
       <x:c r="G395" s="73" t="str">
-        <x:v>Language for partner notices, replies and email. App position 7.</x:v>
+        <x:v>Partner notices/replies/email language; stored position 7 in both apps. OLAP owns partner management.</x:v>
       </x:c>
       <x:c r="H395" s="73" t="str">
         <x:v>Stored; blank initial value. Preferences not inferred or populated. Borrower drafts retain approved Thai.</x:v>
       </x:c>
     </x:row>
-    <x:row r="396" ht="42" customHeight="1">
+    <x:row r="396" ht="78" customHeight="1">
       <x:c r="A396" s="73" t="str">
         <x:v>Partners</x:v>
       </x:c>
@@ -14855,19 +14855,19 @@
         <x:v>Physical / Yes/No</x:v>
       </x:c>
       <x:c r="E396" s="73" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F396" s="73" t="str">
         <x:v>Shown, editable, optional, searchable</x:v>
       </x:c>
       <x:c r="G396" s="73" t="str">
-        <x:v>Master opt-in for partner Instagram and email fallback. App position 8.</x:v>
+        <x:v>Master opt-in for partner Instagram and email fallback; stored position 8 in both apps. Defaults FALSE; future agent only.</x:v>
       </x:c>
       <x:c r="H396" s="73" t="str">
         <x:v>Initial value FALSE; no app formula. Existing partners unchecked. Only TRUE permits future agent communication.</x:v>
       </x:c>
     </x:row>
-    <x:row r="397" ht="42" customHeight="1">
+    <x:row r="397" ht="78" customHeight="1">
       <x:c r="A397" s="73" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -14881,10 +14881,10 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E397" s="73" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F397" s="73" t="str">
-        <x:v>Shown, editable, optional, searchable</x:v>
+        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G397" s="73" t="str">
         <x:v>Borrower city from the owner location sheet. App position 15.</x:v>
@@ -14893,7 +14893,7 @@
         <x:v>Stored; blank initial value; display name: "เมือง / City". Source blanks preserved.</x:v>
       </x:c>
     </x:row>
-    <x:row r="398" ht="42" customHeight="1">
+    <x:row r="398" ht="78" customHeight="1">
       <x:c r="A398" s="73" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -14907,10 +14907,10 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E398" s="73" t="str">
-        <x:v>OLTP; OLAP pending</x:v>
+        <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F398" s="73" t="str">
-        <x:v>Shown, editable, optional, searchable</x:v>
+        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G398" s="73" t="str">
         <x:v>Workplace/locality from the owner location sheet. App position 16.</x:v>
@@ -14930,7 +14930,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82c1edae5ecb4b6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R008277dddce642bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15359,7 +15359,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6373227e1eb1402d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra680af7fa9eb4228"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15490,7 +15490,7 @@
         <x:v>OLTP 3.000050; location columns included after regeneration. Existing row filter and update mode retained.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="15" customHeight="1">
+    <x:row r="7" ht="96" customHeight="1">
       <x:c r="A7" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
@@ -15507,14 +15507,16 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F7" s="57" t="n">
-        <x:v>56</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G7" s="59" t="str">
         <x:v>Read-only OLAP subset of borrowers whose outstanding principal is greater than zero.</x:v>
       </x:c>
-      <x:c r="H7" s="59"/>
-    </x:row>
-    <x:row r="8" ht="15" customHeight="1">
+      <x:c r="H7" s="59" t="str">
+        <x:v>OLAP 1.100031: exact membership reconciled; City and Working Location appended. Existing filter, actions and read-only mode retained. Earlier membership gaps corrected in inventory.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="96" customHeight="1">
       <x:c r="A8" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
@@ -15531,14 +15533,16 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F8" s="57" t="n">
-        <x:v>56</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G8" s="59" t="str">
         <x:v>Read-only OLAP subset of borrowers contributing positive interest profit in the last 30 days.</x:v>
       </x:c>
-      <x:c r="H8" s="59"/>
-    </x:row>
-    <x:row r="9" ht="15" customHeight="1">
+      <x:c r="H8" s="59" t="str">
+        <x:v>OLAP 1.100031: exact membership reconciled; City and Working Location appended. Existing filter, actions and read-only mode retained. Earlier membership gaps corrected in inventory.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="96" customHeight="1">
       <x:c r="A9" s="57" t="str">
         <x:v>OLAP</x:v>
       </x:c>
@@ -15549,18 +15553,20 @@
         <x:v>Borrowers</x:v>
       </x:c>
       <x:c r="D9" s="59" t="str">
-        <x:v>TRUE</x:v>
+        <x:v>(blank — no row filter)</x:v>
       </x:c>
       <x:c r="E9" s="57" t="str">
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F9" s="57" t="n">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G9" s="59" t="str">
         <x:v>Curated, read-only borrower feed for downstream reporting and dashboard reconciliation, including the borrower value/stability matrix fields.</x:v>
       </x:c>
-      <x:c r="H9" s="59"/>
+      <x:c r="H9" s="59" t="str">
+        <x:v>OLAP 1.100031: exact membership reconciled; City and Working Location appended. Existing filter, actions and read-only mode retained. Earlier membership gaps corrected in inventory.</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="57" t="str">
@@ -15754,7 +15760,7 @@
       </x:c>
       <x:c r="H17" s="59"/>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="96" customHeight="1">
       <x:c r="A18" s="72" t="str">
         <x:v>OLAP</x:v>
       </x:c>
@@ -15771,13 +15777,13 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F18" s="72" t="n">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G18" s="72" t="str">
         <x:v>Read-only daily collection export and message-review slice using OLAP-native current-status, amount, charge-list, hidden-flag, and overdue fields.</x:v>
       </x:c>
       <x:c r="H18" s="72" t="str">
-        <x:v>OLAP read-only mirror of the OLTP Todays Collection Board for daily collection export and message-drafting review. The exact column set is adapted to available OLAP fields.</x:v>
+        <x:v>OLAP 1.100031: exact membership reconciled; City and Working Location appended. Existing filter, actions and read-only mode retained. Earlier membership gaps corrected in inventory.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" customHeight="1">
@@ -15813,7 +15819,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8379e6cd54e749fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a23d02162ae4d84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20856,7 +20862,7 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C361" t="n">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D361" t="str">
         <x:v>Matrix Active Borrower Count</x:v>
@@ -20870,7 +20876,7 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C362" t="n">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D362" t="str">
         <x:v>Matrix Equal Share Benchmark</x:v>
@@ -20884,7 +20890,7 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C363" t="n">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D363" t="str">
         <x:v>Matrix Economic Contribution</x:v>
@@ -20898,7 +20904,7 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C364" t="n">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D364" t="str">
         <x:v>Matrix Recent Reliability Score</x:v>
@@ -20954,7 +20960,7 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C368" t="n">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D368" t="str">
         <x:v>Matrix History Sufficient</x:v>
@@ -20968,7 +20974,7 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C369" t="n">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D369" t="str">
         <x:v>Matrix Stability Score</x:v>
@@ -20982,7 +20988,7 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C370" t="n">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D370" t="str">
         <x:v>Matrix Quadrant</x:v>
@@ -20996,7 +21002,7 @@
         <x:v>Reporting Borrowers</x:v>
       </x:c>
       <x:c r="C371" t="n">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D371" t="str">
         <x:v>Matrix Bubble Label</x:v>
@@ -22077,6 +22083,622 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="D448" t="str">
+        <x:v>Working Location</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449">
+      <x:c r="A449" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B449" t="str">
+        <x:v>Reporting Borrowers</x:v>
+      </x:c>
+      <x:c r="C449" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D449" t="str">
+        <x:v>Hidden Flag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450">
+      <x:c r="A450" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B450" t="str">
+        <x:v>Reporting Borrowers</x:v>
+      </x:c>
+      <x:c r="C450" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D450" t="str">
+        <x:v>Matrix Scaled Economic Contribution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451">
+      <x:c r="A451" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B451" t="str">
+        <x:v>Reporting Borrowers</x:v>
+      </x:c>
+      <x:c r="C451" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D451" t="str">
+        <x:v>Related Payments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452">
+      <x:c r="A452" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B452" t="str">
+        <x:v>Reporting Borrowers</x:v>
+      </x:c>
+      <x:c r="C452" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D452" t="str">
+        <x:v>City</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453">
+      <x:c r="A453" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B453" t="str">
+        <x:v>Reporting Borrowers</x:v>
+      </x:c>
+      <x:c r="C453" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D453" t="str">
+        <x:v>Working Location</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454">
+      <x:c r="A454" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B454" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C454" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D454" t="str">
+        <x:v>Hidden Flag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455">
+      <x:c r="A455" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B455" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C455" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D455" t="str">
+        <x:v>Projected Monthly Profit Contribution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456">
+      <x:c r="A456" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B456" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C456" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D456" t="str">
+        <x:v>Matrix Active Borrower Count</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457">
+      <x:c r="A457" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B457" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C457" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D457" t="str">
+        <x:v>Matrix Equal Share Benchmark</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458">
+      <x:c r="A458" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B458" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C458" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D458" t="str">
+        <x:v>Matrix Economic Contribution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459">
+      <x:c r="A459" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B459" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C459" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D459" t="str">
+        <x:v>Matrix Recent Reliability Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460">
+      <x:c r="A460" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B460" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C460" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D460" t="str">
+        <x:v>Matrix Historical Reliability Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B461" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C461" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D461" t="str">
+        <x:v>Matrix Delay Severity Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462">
+      <x:c r="A462" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B462" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C462" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D462" t="str">
+        <x:v>Matrix Current Condition Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463">
+      <x:c r="A463" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B463" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C463" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D463" t="str">
+        <x:v>Matrix History Sufficient</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464">
+      <x:c r="A464" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B464" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C464" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D464" t="str">
+        <x:v>Matrix Stability Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465">
+      <x:c r="A465" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B465" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C465" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D465" t="str">
+        <x:v>Matrix Quadrant</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466">
+      <x:c r="A466" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B466" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C466" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D466" t="str">
+        <x:v>Matrix Bubble Label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467">
+      <x:c r="A467" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B467" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C467" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D467" t="str">
+        <x:v>Profit Last 10 Days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468">
+      <x:c r="A468" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B468" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C468" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D468" t="str">
+        <x:v>Matrix Scaled Economic Contribution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469">
+      <x:c r="A469" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B469" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C469" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D469" t="str">
+        <x:v>Related Payments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470">
+      <x:c r="A470" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B470" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C470" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D470" t="str">
+        <x:v>City</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471">
+      <x:c r="A471" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B471" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C471" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D471" t="str">
+        <x:v>Working Location</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472">
+      <x:c r="A472" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B472" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C472" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D472" t="str">
+        <x:v>Hidden Flag</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473">
+      <x:c r="A473" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B473" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C473" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D473" t="str">
+        <x:v>Projected Monthly Profit Contribution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474">
+      <x:c r="A474" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B474" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C474" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D474" t="str">
+        <x:v>Matrix Active Borrower Count</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475">
+      <x:c r="A475" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B475" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C475" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D475" t="str">
+        <x:v>Matrix Equal Share Benchmark</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476">
+      <x:c r="A476" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B476" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C476" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D476" t="str">
+        <x:v>Matrix Economic Contribution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477">
+      <x:c r="A477" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B477" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C477" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D477" t="str">
+        <x:v>Matrix Recent Reliability Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478">
+      <x:c r="A478" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B478" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C478" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D478" t="str">
+        <x:v>Matrix Historical Reliability Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479">
+      <x:c r="A479" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B479" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C479" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D479" t="str">
+        <x:v>Matrix Delay Severity Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480">
+      <x:c r="A480" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B480" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C480" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D480" t="str">
+        <x:v>Matrix Current Condition Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481">
+      <x:c r="A481" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B481" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C481" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D481" t="str">
+        <x:v>Matrix History Sufficient</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482">
+      <x:c r="A482" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B482" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C482" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D482" t="str">
+        <x:v>Matrix Stability Score</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483">
+      <x:c r="A483" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B483" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C483" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D483" t="str">
+        <x:v>Matrix Quadrant</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484">
+      <x:c r="A484" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B484" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C484" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D484" t="str">
+        <x:v>Matrix Bubble Label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485">
+      <x:c r="A485" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B485" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C485" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D485" t="str">
+        <x:v>Profit Last 10 Days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486">
+      <x:c r="A486" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B486" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C486" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D486" t="str">
+        <x:v>Matrix Scaled Economic Contribution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487">
+      <x:c r="A487" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B487" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C487" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D487" t="str">
+        <x:v>Related Payments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488">
+      <x:c r="A488" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B488" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C488" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D488" t="str">
+        <x:v>City</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489">
+      <x:c r="A489" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B489" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C489" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D489" t="str">
+        <x:v>Working Location</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490">
+      <x:c r="A490" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B490" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C490" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D490" t="str">
+        <x:v>Related Payments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491">
+      <x:c r="A491" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B491" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C491" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D491" t="str">
+        <x:v>City</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492">
+      <x:c r="A492" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B492" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C492" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D492" t="str">
         <x:v>Working Location</x:v>
       </x:c>
     </x:row>
@@ -22087,7 +22709,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd662c409624492a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfff62d5c127344a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26110,10 +26732,10 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E204" s="87" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F204" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" customHeight="1">
@@ -26130,10 +26752,10 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E205" s="87" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F205" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" customHeight="1">
@@ -26150,10 +26772,10 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E206" s="87" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F206" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>OLTP Url; OLAP Text; native Text. Existing type variance preserved. Both initial values blank.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" customHeight="1">
@@ -26170,10 +26792,10 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E207" s="87" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F207" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" customHeight="1">
@@ -26190,10 +26812,10 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E208" s="87" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F208" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" customHeight="1">
@@ -26210,10 +26832,10 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E209" s="87" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F209" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" customHeight="1">
@@ -26230,10 +26852,10 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="E210" s="87" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F210" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="15" customHeight="1">
@@ -26590,10 +27212,10 @@
         <x:v>Yes — 3.000050</x:v>
       </x:c>
       <x:c r="E228" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F228" t="str">
-        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
@@ -26610,10 +27232,10 @@
         <x:v>Yes — 3.000050</x:v>
       </x:c>
       <x:c r="E229" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F229" t="str">
-        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -26630,10 +27252,10 @@
         <x:v>Yes — 3.000050</x:v>
       </x:c>
       <x:c r="E230" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F230" t="str">
-        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -26650,10 +27272,10 @@
         <x:v>Yes — 3.000050</x:v>
       </x:c>
       <x:c r="E231" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F231" t="str">
-        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -26670,10 +27292,10 @@
         <x:v>Yes — 3.000050</x:v>
       </x:c>
       <x:c r="E232" t="str">
-        <x:v>Pending reconciliation</x:v>
+        <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F232" t="str">
-        <x:v>Stored in shared database; OLTP configured. OLAP app not regenerated by this task.</x:v>
+        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -26686,7 +27308,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfe8af29d8ae41ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ac7d86e7b3745a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26885,7 +27507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e5f7a3347484eb0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1174ee0ff2f24e7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28538,7 +29160,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf15aefded0a44967"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R116bec59645c48da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R04429f714ad54310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R6eb4a437eb894a35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R62093d1a3d63442f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R37c42161bd4d4552"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rbbe168736fc445fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rc7efbb7a1e174594"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R5f2f79c51fcb4170"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Rc452e6abf5684e0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R45c8270d30ce4000"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rdd80efcc0a714ace"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R4d73f202be074a83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rccf1c12d05d14804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc06f07df53d747a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rd8b57970c9d04d2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R23d84db091ef4245"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R3e9179c3f0944505"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rf7af349bb1fb4388"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rf15c677865284f33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R9b2a36d805394c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R2f2d077a8018482f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rf4f07b18f7ec4605"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R231bb5271c2440fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R159a540e4ddd4f34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R88a15560b3a74227"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1079,7 +1079,7 @@
         <x:v>Reconciliation status</x:v>
       </x:c>
       <x:c r="B5" s="85" t="str">
-        <x:v>13 September 2026: OLTP 3.000050 and OLAP 1.100031 partner/location fields and affected slices reconciled. OLAP partner forms and borrower read-only detail checked. No agent activation.</x:v>
+        <x:v>13 September 2026: language enum verified in OLTP 3.000052 and OLAP 1.100033. OLAP current partner form shows English and ไทย. Earlier partner/location fields and slices retain recorded reconciliation scope.</x:v>
       </x:c>
       <x:c r="C5" s="73"/>
       <x:c r="D5" s="73"/>
@@ -1091,7 +1091,7 @@
         <x:v>Live baselines</x:v>
       </x:c>
       <x:c r="B6" s="85" t="str">
-        <x:v>Rollback: OLTP 3.000045; OLAP 1.100028. App restore does not restore shared database data/schema. Private location before-image remains outside Git. Owner acceptance pending.</x:v>
+        <x:v>Language enum rollback: OLTP 3.000050; OLAP 1.100031. Earlier setup rollback: OLTP 3.000045; OLAP 1.100028. App restoration does not restore database data/schema. Owner acceptance pending.</x:v>
       </x:c>
       <x:c r="C6" s="73"/>
       <x:c r="D6" s="73"/>
@@ -2492,7 +2492,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdcff336c8174e33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb86f79d7430741b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3907,7 +3907,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>13 September 2026: shared partner/location fields reconciled in both apps. OLTP 3.000050; OLAP 1.100031. Other tables retain dated verification scope.</x:v>
+        <x:v>13 September 2026: language enum updated in OLTP 3.000052 and OLAP 1.100033; table counts unchanged. Other tables retain dated verification scope.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -4299,7 +4299,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R285d3bc61d2041ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fecfe5482854df6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4332,7 +4332,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>13 September 2026: OLTP 3.000050 and OLAP 1.100031 partner/location setup reconciled. Existing OLAP Borrowers remains read-only; no messaging activation. Other inventory retains dated scope.</x:v>
+        <x:v>13 September 2026: language enum verified in OLTP 3.000052 and OLAP 1.100033. Earlier partner/location and slice reconciliation retains its recorded scope. No messaging activation.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -14815,7 +14815,7 @@
         <x:v>Stored; no formula, default, key or label. Verification binding belongs to later agent implementation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="395" ht="78" customHeight="1">
+    <x:row r="395" ht="110" customHeight="1">
       <x:c r="A395" s="73" t="str">
         <x:v>Partners</x:v>
       </x:c>
@@ -14826,7 +14826,7 @@
         <x:v>Language Preference</x:v>
       </x:c>
       <x:c r="D395" s="73" t="str">
-        <x:v>Physical / Text</x:v>
+        <x:v>Physical / Enum (base Text)</x:v>
       </x:c>
       <x:c r="E395" s="73" t="str">
         <x:v>OLTP + OLAP</x:v>
@@ -14838,7 +14838,7 @@
         <x:v>Partner notices/replies/email language; stored position 7 in both apps. OLAP owns partner management.</x:v>
       </x:c>
       <x:c r="H395" s="73" t="str">
-        <x:v>Stored; blank initial value. Preferences not inferred or populated. Borrower drafts retain approved Thai.</x:v>
+        <x:v>Native database Text; app Enum in both apps. Dropdown: English, ไทย. Other values and other-value autocomplete disabled. Optional; blank initial value. Partner data unchanged. Borrower drafts retain approved Thai.</x:v>
       </x:c>
     </x:row>
     <x:row r="396" ht="78" customHeight="1">
@@ -14930,7 +14930,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R008277dddce642bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b384d860a054e21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15359,7 +15359,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra680af7fa9eb4228"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5756f82d70bf4226"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15819,7 +15819,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a23d02162ae4d84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c120d9e6da4213"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22709,7 +22709,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfff62d5c127344a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4bbb7c6dfe74f47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27229,13 +27229,13 @@
         <x:v>Language Preference</x:v>
       </x:c>
       <x:c r="D229" t="str">
-        <x:v>Yes — 3.000050</x:v>
+        <x:v>Yes — 3.000052</x:v>
       </x:c>
       <x:c r="E229" t="str">
-        <x:v>Yes — 1.100031</x:v>
+        <x:v>Yes — 1.100033</x:v>
       </x:c>
       <x:c r="F229" t="str">
-        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
+        <x:v>Both apps: Enum, base Text, Dropdown, exactly English and ไทย; custom values disabled. Partner management remains in OLAP.</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -27308,7 +27308,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ac7d86e7b3745a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R663a3c3fbdf44d48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27507,7 +27507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1174ee0ff2f24e7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bcb49d128a34f23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29160,7 +29160,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R116bec59645c48da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb12fc9a145a54bcc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc06f07df53d747a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rd8b57970c9d04d2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R23d84db091ef4245"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R3e9179c3f0944505"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rf7af349bb1fb4388"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rf15c677865284f33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R9b2a36d805394c51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R2f2d077a8018482f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rf4f07b18f7ec4605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R231bb5271c2440fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R159a540e4ddd4f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R88a15560b3a74227"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R9651d12c89b948fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rbf63829385f54798"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rabbefa11283742cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R766e019bb4a74dd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R725af707c5154085"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R6bff1397ce6e46a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Raeaba5653582496c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R5628ca0a872f4855"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rdf6bc609c39d470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R8f2e8b19e06740e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Re2fc66bc4b9045ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rbc75ea26b2d241d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1079,7 +1079,7 @@
         <x:v>Reconciliation status</x:v>
       </x:c>
       <x:c r="B5" s="85" t="str">
-        <x:v>13 September 2026: language enum verified in OLTP 3.000052 and OLAP 1.100033. OLAP current partner form shows English and ไทย. Earlier partner/location fields and slices retain recorded reconciliation scope.</x:v>
+        <x:v>Borrower cleanup PARTIAL: five OLTP settings saved; Chrome control failed before final version/readback. OLAP remains prior configuration. See authoritative borrower cleanup change log.</x:v>
       </x:c>
       <x:c r="C5" s="73"/>
       <x:c r="D5" s="73"/>
@@ -2492,7 +2492,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb86f79d7430741b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf31271142f442b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4299,7 +4299,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fecfe5482854df6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dd9cb54c937408e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4332,7 +4332,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>13 September 2026: language enum verified in OLTP 3.000052 and OLAP 1.100033. Earlier partner/location and slice reconciliation retains its recorded scope. No messaging activation.</x:v>
+        <x:v>13 September 2026: borrower cleanup PARTIAL. Five OLTP settings saved; post-save readback and OLAP reconciliation pending. All other inventory retains prior verification scope.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -4430,7 +4430,7 @@
         <x:v>Stored source column; initial value: UNIQUEID("PackedUUID")</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="15" customHeight="1">
+    <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="57" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -4452,8 +4452,8 @@
       <x:c r="G7" s="59" t="str">
         <x:v>Stores the authoritative source value for Borrower Name.</x:v>
       </x:c>
-      <x:c r="H7" s="59" t="str">
-        <x:v>Stored source column</x:v>
+      <x:c r="H7" s="82" t="str">
+        <x:v>Internal name preserved. OLTP display changed to Borrower Name - Thai. OLAP display reconciliation pending. Final readback/tests pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
@@ -4482,7 +4482,7 @@
         <x:v>Stored source column</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="15" customHeight="1">
+    <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="57" t="str">
         <x:v>Borrowers</x:v>
       </x:c>
@@ -4504,8 +4504,8 @@
       <x:c r="G9" s="59" t="str">
         <x:v>Text confirmed in both apps during partner/location setup reconciliation.</x:v>
       </x:c>
-      <x:c r="H9" s="59" t="str">
-        <x:v>Stored source column</x:v>
+      <x:c r="H9" s="82" t="str">
+        <x:v>Internal Description preserved. OLTP display changed to English Name. OLAP and Partner Operations GUI label reconciliation pending. Final readback/tests pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
@@ -14182,13 +14182,13 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F370" s="87" t="str">
-        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
+        <x:v>OLTP required; OLAP prior optional, table read-only. Pending final reconciliation.</x:v>
       </x:c>
       <x:c r="G370" s="87" t="str">
         <x:v>Explicit message address; no suffix stripping. App physical position 8.</x:v>
       </x:c>
-      <x:c r="H370" s="87" t="str">
-        <x:v>Stored; blank initial value. OLTP display name "ชื่อที่ใช้เรียก / Communication Name"; OLAP default field name.</x:v>
+      <x:c r="H370" s="88" t="str">
+        <x:v>OLTP Require enabled. OLAP reconciliation pending. Blank initial value retained. Final readback/tests pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="371" ht="78" customHeight="1">
@@ -14291,8 +14291,8 @@
       <x:c r="G374" s="87" t="str">
         <x:v>Existing borrower opt-in; also required alongside Collection dashboard eligibility for the proposed partner daily briefing. Existing flag values unchanged.</x:v>
       </x:c>
-      <x:c r="H374" s="87" t="str">
-        <x:v>Stored; initial FALSE in both apps. OLAP table remains read-only; existing values unchanged.</x:v>
+      <x:c r="H374" s="88" t="str">
+        <x:v>OLTP initial changed to TRUE for new rows. Existing row values untouched. OLAP reconciliation pending. Final readback/tests pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="375" ht="78" customHeight="1">
@@ -14884,13 +14884,13 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F397" s="73" t="str">
-        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
+        <x:v>OLTP required; OLAP prior optional, table read-only. Pending final reconciliation.</x:v>
       </x:c>
       <x:c r="G397" s="73" t="str">
         <x:v>Borrower city from the owner location sheet. App position 15.</x:v>
       </x:c>
       <x:c r="H397" s="73" t="str">
-        <x:v>Stored; blank initial value; display name: "เมือง / City". Source blanks preserved.</x:v>
+        <x:v>OLTP Require enabled; display เมือง / City and blank initial retained. OLAP reconciliation pending. Final readback/tests pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="398" ht="78" customHeight="1">
@@ -14930,7 +14930,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b384d860a054e21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbefa88207b7e4147"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15359,7 +15359,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5756f82d70bf4226"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71c01aec0b6d4a7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15819,7 +15819,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c120d9e6da4213"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R742f04d9bb684197"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22709,7 +22709,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4bbb7c6dfe74f47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb899178b9b345b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27308,7 +27308,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R663a3c3fbdf44d48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bf1c2fe6a734552"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27507,7 +27507,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bcb49d128a34f23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbec54b2403354202"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29160,7 +29160,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb12fc9a145a54bcc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a2caa9c6b2f4583"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R9651d12c89b948fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rbf63829385f54798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rabbefa11283742cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R766e019bb4a74dd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R725af707c5154085"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R6bff1397ce6e46a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Raeaba5653582496c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R5628ca0a872f4855"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rdf6bc609c39d470a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R8f2e8b19e06740e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Re2fc66bc4b9045ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rbc75ea26b2d241d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rb9853f0907c541e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rc818e69beb2a4e35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R5e6079b1c2934bbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R4bebfdc085464e4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rfc856e925703480f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R7c83090d20924339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R114839d9779d4251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R98ba3e208b9a45e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R84a3dc1cfc4b409b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R54931ad81cbb4447"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rf9ef1b83482c4b54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rd158215a355f46b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -722,8 +722,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DataModelColumns" displayName="DataModelColumns" ref="A4:H398" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:H398"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="DataModelColumns" displayName="DataModelColumns" ref="A4:H399" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:H399"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Table"/>
     <x:tableColumn id="2" name="Inventory order"/>
@@ -769,7 +769,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D492" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="DataModelSliceColumns" displayName="DataModelSliceColumns" ref="A4:D498" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="App"/>
     <x:tableColumn id="2" name="Slice"/>
@@ -781,8 +781,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="DataModelAppVariances" displayName="DataModelAppVariances" ref="A4:F232" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:F232"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="DataModelAppVariances" displayName="DataModelAppVariances" ref="A4:F233" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:F233"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Object Type"/>
     <x:tableColumn id="2" name="Table"/>
@@ -1079,7 +1079,7 @@
         <x:v>Reconciliation status</x:v>
       </x:c>
       <x:c r="B5" s="85" t="str">
-        <x:v>Borrower cleanup PARTIAL: five OLTP settings saved; Chrome control failed before final version/readback. OLAP remains prior configuration. See authoritative borrower cleanup change log.</x:v>
+        <x:v>Borrower cleanup verified: OLTP 3.000064; OLAP 1.100041. New-GUI form/detail checks passed; owner acceptance pending. Retired inventory is explicitly labeled.</x:v>
       </x:c>
       <x:c r="C5" s="73"/>
       <x:c r="D5" s="73"/>
@@ -1091,7 +1091,7 @@
         <x:v>Live baselines</x:v>
       </x:c>
       <x:c r="B6" s="85" t="str">
-        <x:v>Language enum rollback: OLTP 3.000050; OLAP 1.100031. Earlier setup rollback: OLTP 3.000045; OLAP 1.100028. App restoration does not restore database data/schema. Owner acceptance pending.</x:v>
+        <x:v>Cleanup rollback OLTP 3.000052 / OLAP 1.100033; native database copy Money BACKUP Borrower Cleanup 20260913. Restore schema/data separately and preserve intervening edits.</x:v>
       </x:c>
       <x:c r="C6" s="73"/>
       <x:c r="D6" s="73"/>
@@ -2492,7 +2492,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf31271142f442b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79a4e735b1af4cdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3907,7 +3907,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>13 September 2026: language enum updated in OLTP 3.000052 and OLAP 1.100033; table counts unchanged. Other tables retain dated verification scope.</x:v>
+        <x:v>13 September 2026: Borrowers cleanup complete in both apps; stored counts include ordinal/key. Two collection tables retired.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -3958,16 +3958,16 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="D5" s="56" t="n">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E5" s="56" t="n">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F5" s="56" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="G5" s="58" t="str">
-        <x:v>OLTP 45 =16 stored +29 VCs; OLAP 81 =16 stored +65 VCs. OLAP read-only, new location fields loaded. Counts include ordinal/key.</x:v>
+        <x:v>OLTP 38 =12 stored +26 VCs; OLAP 77 =12 stored +65 VCs. Address loaded; obsolete fields removed. OLAP read-only.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
@@ -4254,19 +4254,19 @@
         <x:v>Money database</x:v>
       </x:c>
       <x:c r="C18" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="D18" s="87" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="87" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F18" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="87" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G18" s="87" t="str">
-        <x:v>Receiving-account master; add/update only in OLTP. Deactivate used accounts. Two user-authorized records; no details in this dictionary.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" customHeight="1">
@@ -4277,19 +4277,19 @@
         <x:v>Money database</x:v>
       </x:c>
       <x:c r="C19" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="D19" s="87" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="87" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+      <x:c r="F19" s="87" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G19" s="87" t="str">
-        <x:v>One shared default receiving-account selection. Update only; no adds/deletes in OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4299,7 +4299,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dd9cb54c937408e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40613c357604443c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4332,7 +4332,7 @@
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>13 September 2026: borrower cleanup PARTIAL. Five OLTP settings saved; post-save readback and OLAP reconciliation pending. All other inventory retains prior verification scope.</x:v>
+        <x:v>13 September 2026: borrower cleanup reconciled in OLTP 3.000064 and OLAP 1.100041. Retired rows are historical, not active schema.</x:v>
       </x:c>
       <x:c r="B2"/>
       <x:c r="C2"/>
@@ -4453,7 +4453,7 @@
         <x:v>Stores the authoritative source value for Borrower Name.</x:v>
       </x:c>
       <x:c r="H7" s="82" t="str">
-        <x:v>Internal name preserved. OLTP display changed to Borrower Name - Thai. OLAP display reconciliation pending. Final readback/tests pending.</x:v>
+        <x:v>Internal Borrower Name retained; display Borrower Name - Thai in both apps.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
@@ -4470,16 +4470,16 @@
         <x:v>Physical / Phone</x:v>
       </x:c>
       <x:c r="E8" s="57" t="str">
-        <x:v>OLTP + OLAP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F8" s="57" t="str">
-        <x:v>PII</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G8" s="59" t="str">
-        <x:v>Stores the authoritative source value for Telephone.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H8" s="59" t="str">
-        <x:v>Stored source column</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
@@ -4505,7 +4505,7 @@
         <x:v>Text confirmed in both apps during partner/location setup reconciliation.</x:v>
       </x:c>
       <x:c r="H9" s="82" t="str">
-        <x:v>Internal Description preserved. OLTP display changed to English Name. OLAP and Partner Operations GUI label reconciliation pending. Final readback/tests pending.</x:v>
+        <x:v>Internal Description retained; display English Name in both apps. Existing formulas/API keys preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
@@ -14182,13 +14182,13 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F370" s="87" t="str">
-        <x:v>OLTP required; OLAP prior optional, table read-only. Pending final reconciliation.</x:v>
+        <x:v>Required; OLTP editable, OLAP table read-only</x:v>
       </x:c>
       <x:c r="G370" s="87" t="str">
-        <x:v>Explicit message address; no suffix stripping. App physical position 8.</x:v>
+        <x:v>Explicit communication name; required. Stored position 7 in both apps.</x:v>
       </x:c>
       <x:c r="H370" s="88" t="str">
-        <x:v>OLTP Require enabled. OLAP reconciliation pending. Blank initial value retained. Final readback/tests pending.</x:v>
+        <x:v>Required in both apps. OLTP editable; OLAP table remains read-only. Blank initial value.</x:v>
       </x:c>
     </x:row>
     <x:row r="371" ht="78" customHeight="1">
@@ -14231,16 +14231,16 @@
         <x:v>Physical / Url (OLTP); Text (OLAP)</x:v>
       </x:c>
       <x:c r="E372" s="87" t="str">
-        <x:v>OLTP + OLAP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F372" s="87" t="str">
-        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G372" s="87" t="str">
-        <x:v>Verified conversation link; native Text, app Url; position 10.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H372" s="87" t="str">
-        <x:v>Stored native Text; OLTP Url, OLAP Text. Both initial values blank; existing app type variance preserved.</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="373" ht="78" customHeight="1">
@@ -14257,16 +14257,16 @@
         <x:v>Physical / DateTime</x:v>
       </x:c>
       <x:c r="E373" s="87" t="str">
-        <x:v>OLTP + OLAP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F373" s="87" t="str">
-        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G373" s="87" t="str">
-        <x:v>Time mapping was actually checked; position 11.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H373" s="87" t="str">
-        <x:v>Stored; blank initial value in both apps. OLAP inherited NOW() removed during 13 September reconciliation. Existing values unchanged.</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="374" ht="78" customHeight="1">
@@ -14292,7 +14292,7 @@
         <x:v>Existing borrower opt-in; also required alongside Collection dashboard eligibility for the proposed partner daily briefing. Existing flag values unchanged.</x:v>
       </x:c>
       <x:c r="H374" s="88" t="str">
-        <x:v>OLTP initial changed to TRUE for new rows. Existing row values untouched. OLAP reconciliation pending. Final readback/tests pending.</x:v>
+        <x:v>Initial TRUE in both apps for new rows only. Existing row values not edited by cleanup.</x:v>
       </x:c>
     </x:row>
     <x:row r="375" ht="78" customHeight="1">
@@ -14309,16 +14309,16 @@
         <x:v>Physical / Yes/No</x:v>
       </x:c>
       <x:c r="E375" s="87" t="str">
-        <x:v>OLTP + OLAP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F375" s="87" t="str">
-        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G375" s="87" t="str">
-        <x:v>Independent penalty eligibility; position 13. Existing fees never reversed by this flag.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H375" s="87" t="str">
-        <x:v>Stored; initial FALSE in both apps. Existing values and collection runtime unchanged.</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="376" ht="78" customHeight="1">
@@ -14335,16 +14335,16 @@
         <x:v>Physical / Ref</x:v>
       </x:c>
       <x:c r="E376" s="87" t="str">
-        <x:v>OLTP + OLAP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F376" s="87" t="str">
-        <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G376" s="87" t="str">
-        <x:v>Borrower-specific receiving bank; position 14.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H376" s="87" t="str">
-        <x:v>Stored native Reference and app Ref -&gt; Collection Bank Accounts; independent lifecycle</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="377" ht="15" customHeight="1">
@@ -14361,16 +14361,16 @@
         <x:v>Virtual / Ref</x:v>
       </x:c>
       <x:c r="E377" s="87" t="str">
-        <x:v>OLTP only</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F377" s="87" t="str">
-        <x:v>Read-only</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G377" s="87" t="str">
-        <x:v>Borrower override, otherwise singleton default; Ref -&gt; Collection Bank Accounts.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H377" s="87" t="str">
-        <x:v>IF(ISNOTBLANK([Receiving Bank Account]), [Receiving Bank Account], IF(COUNT(Collection Settings[Row ID]) = 1, ANY(Collection Settings[Default Receiving Bank Account]), ""))</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="378" ht="15" customHeight="1">
@@ -14387,16 +14387,16 @@
         <x:v>Virtual / Text</x:v>
       </x:c>
       <x:c r="E378" s="87" t="str">
-        <x:v>OLTP only</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F378" s="87" t="str">
-        <x:v>Read-only</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G378" s="87" t="str">
-        <x:v>Enabled borrower name, Instagram mapping/duplicate and effective-bank checks.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H378" s="87" t="str">
-        <x:v>IF([AI Collection Enabled], CONCATENATE(IF(ISBLANK(TRIM([Communication Name])), "Enter communication name. ", ""), IF(ISBLANK([Instagram Username]), "Enter Instagram username. ", IF(OR(CONTAINS([Instagram Username], "@"), CONTAINS([Instagram Username], " "), CONTAINS([Instagram Username], "/")), "Use username only, without @, spaces or URL. ", "")), IF(AND(ISNOTBLANK([Instagram Username]), COUNT(SELECT(Borrowers[Row ID], AND(LOWER([Instagram Username]) = LOWER([_THISROW].[Instagram Username]), [Row ID] &lt;&gt; [_THISROW].[Row ID]))) &gt; 0), "Instagram username is mapped to another borrower. ", ""), IF(NOT(STARTSWITH([Instagram Conversation URL], "https://www.instagram.com/direct/t/")), "Enter verified Instagram conversation URL. ", ""), IF(ISBLANK([Instagram Verified At]), "Verify Instagram mapping. ", ""), IF(ISBLANK([Effective Receiving Bank Account]), "Select borrower bank or one shared default. ", IF(NOT([Effective Receiving Bank Account].[Active]), "Receiving bank account is inactive. ", IF(OR(ISBLANK([Effective Receiving Bank Account].[Bank Name]), ISBLANK([Effective Receiving Bank Account].[Account Number]), ISBLANK([Effective Receiving Bank Account].[Account Holder Name])), "Complete receiving bank details. ", "")))), "")</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="379" ht="15" customHeight="1">
@@ -14413,16 +14413,16 @@
         <x:v>Physical / Number</x:v>
       </x:c>
       <x:c r="E379" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F379" s="87" t="str">
-        <x:v>Hidden</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G379" s="87" t="str">
-        <x:v>Source ordinal, never identity.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H379" s="87" t="str">
-        <x:v>Stored system column</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="380" ht="15" customHeight="1">
@@ -14439,16 +14439,16 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E380" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F380" s="87" t="str">
-        <x:v>Key, Required, Hidden</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G380" s="87" t="str">
-        <x:v>Immutable native key.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H380" s="87" t="str">
-        <x:v>Stored; initial value UNIQUEID("PackedUUID")</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="381" ht="15" customHeight="1">
@@ -14465,16 +14465,16 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E381" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F381" s="87" t="str">
-        <x:v>Label, Required, Editable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G381" s="87" t="str">
-        <x:v>Recognizable receiving-account label.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H381" s="87" t="str">
-        <x:v>Stored</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="382" ht="15" customHeight="1">
@@ -14491,16 +14491,16 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E382" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F382" s="87" t="str">
-        <x:v>Required, Editable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G382" s="87" t="str">
-        <x:v>Bank shown in messages.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H382" s="87" t="str">
-        <x:v>Stored</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="383" ht="15" customHeight="1">
@@ -14517,16 +14517,16 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E383" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F383" s="87" t="str">
-        <x:v>Required, Editable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G383" s="87" t="str">
-        <x:v>Preserve leading zeros and supplied separators.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H383" s="87" t="str">
-        <x:v>Stored</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="384" ht="15" customHeight="1">
@@ -14543,16 +14543,16 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E384" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F384" s="87" t="str">
-        <x:v>Required, Editable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G384" s="87" t="str">
-        <x:v>Receiving account holder.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H384" s="87" t="str">
-        <x:v>Stored</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="385" ht="15" customHeight="1">
@@ -14569,16 +14569,16 @@
         <x:v>Physical / Yes/No</x:v>
       </x:c>
       <x:c r="E385" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F385" s="87" t="str">
-        <x:v>Editable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G385" s="87" t="str">
-        <x:v>Deactivate instead of deleting used accounts.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H385" s="87" t="str">
-        <x:v>Stored; initial value TRUE</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="386" ht="15" customHeight="1">
@@ -14595,16 +14595,16 @@
         <x:v>Virtual / List (Ref)</x:v>
       </x:c>
       <x:c r="E386" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F386" s="87" t="str">
-        <x:v>Read-only</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G386" s="87" t="str">
-        <x:v>Default-setting reverse reference.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H386" s="87" t="str">
-        <x:v>REF_ROWS("Collection Settings", "Default Receiving Bank Account")</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="387" ht="15" customHeight="1">
@@ -14621,16 +14621,16 @@
         <x:v>Virtual / List (Ref)</x:v>
       </x:c>
       <x:c r="E387" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F387" s="87" t="str">
-        <x:v>Read-only</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G387" s="87" t="str">
-        <x:v>Borrower override reverse reference.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H387" s="87" t="str">
-        <x:v>REF_ROWS("Borrowers", "Receiving Bank Account")</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="388" ht="30" customHeight="1">
@@ -14647,16 +14647,16 @@
         <x:v>Virtual / List (Ref)</x:v>
       </x:c>
       <x:c r="E388" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F388" s="87" t="str">
-        <x:v>Read-only</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G388" s="87" t="str">
-        <x:v>Includes borrowers inheriting the shared default.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H388" s="87" t="str">
-        <x:v>REF_ROWS("Borrowers", "Effective Receiving Bank Account")</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="389" ht="15" customHeight="1">
@@ -14673,16 +14673,16 @@
         <x:v>Physical / Number</x:v>
       </x:c>
       <x:c r="E389" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F389" s="87" t="str">
-        <x:v>Hidden</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G389" s="87" t="str">
-        <x:v>Source ordinal, never identity.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H389" s="87" t="str">
-        <x:v>Stored system column</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="390" ht="15" customHeight="1">
@@ -14699,16 +14699,16 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E390" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F390" s="87" t="str">
-        <x:v>Key, Required, Hidden</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G390" s="87" t="str">
-        <x:v>Immutable native key.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H390" s="87" t="str">
-        <x:v>Stored; initial value UNIQUEID("PackedUUID")</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="391" ht="15" customHeight="1">
@@ -14725,16 +14725,16 @@
         <x:v>Physical / Text</x:v>
       </x:c>
       <x:c r="E391" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F391" s="87" t="str">
-        <x:v>Label, Not editable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G391" s="87" t="str">
-        <x:v>Singleton setting label; one shared row.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H391" s="87" t="str">
-        <x:v>Stored</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="392" ht="15" customHeight="1">
@@ -14751,16 +14751,16 @@
         <x:v>Physical / Ref</x:v>
       </x:c>
       <x:c r="E392" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired — neither app</x:v>
       </x:c>
       <x:c r="F392" s="87" t="str">
-        <x:v>Required, Editable</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="G392" s="87" t="str">
-        <x:v>Shared default for borrowers without override.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
       <x:c r="H392" s="87" t="str">
-        <x:v>Stored native Reference and app Ref -&gt; Collection Bank Accounts; independent lifecycle</x:v>
+        <x:v>Historical definition retired; see cleanup change log for rollback.</x:v>
       </x:c>
     </x:row>
     <x:row r="393" ht="135" customHeight="1">
@@ -14884,13 +14884,13 @@
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="F397" s="73" t="str">
-        <x:v>OLTP required; OLAP prior optional, table read-only. Pending final reconciliation.</x:v>
+        <x:v>Required; OLTP editable, OLAP table read-only</x:v>
       </x:c>
       <x:c r="G397" s="73" t="str">
-        <x:v>Borrower city from the owner location sheet. App position 15.</x:v>
+        <x:v>Borrower city from owner location sheet. Stored position 10 in both apps.</x:v>
       </x:c>
       <x:c r="H397" s="73" t="str">
-        <x:v>OLTP Require enabled; display เมือง / City and blank initial retained. OLAP reconciliation pending. Final readback/tests pending.</x:v>
+        <x:v>Required in both apps. Blank initial value; display เมือง / City. Existing values preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="398" ht="78" customHeight="1">
@@ -14913,10 +14913,36 @@
         <x:v>OLTP editable; OLAP table read-only; shown, optional, searchable</x:v>
       </x:c>
       <x:c r="G398" s="73" t="str">
-        <x:v>Workplace/locality from the owner location sheet. App position 16.</x:v>
+        <x:v>Workplace/locality from owner location sheet. Stored position 11 in both apps.</x:v>
       </x:c>
       <x:c r="H398" s="73" t="str">
         <x:v>Stored; blank initial value; display name: "สถานที่ทำงาน / Working Location". Uncertainty preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" ht="78" customHeight="1">
+      <x:c r="A399" s="73" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="B399" s="73" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C399" s="73" t="str">
+        <x:v>Address</x:v>
+      </x:c>
+      <x:c r="D399" s="73" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="E399" s="73" t="str">
+        <x:v>OLTP + OLAP</x:v>
+      </x:c>
+      <x:c r="F399" s="73" t="str">
+        <x:v>Optional; OLTP editable, OLAP table read-only</x:v>
+      </x:c>
+      <x:c r="G399" s="73" t="str">
+        <x:v>Borrower address from owner location sheet; seven exact-name matches imported.</x:v>
+      </x:c>
+      <x:c r="H399" s="73" t="str">
+        <x:v>Blank initial; no formula. Included in both apps borrower views and affected slices.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14930,7 +14956,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbefa88207b7e4147"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb09b089999644e46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15303,7 +15329,7 @@
     </x:row>
     <x:row r="19" ht="15" customHeight="1">
       <x:c r="A19" s="87" t="str">
-        <x:v>Borrowers</x:v>
+        <x:v>Retired — Borrowers</x:v>
       </x:c>
       <x:c r="B19" s="87" t="str">
         <x:v>Receiving Bank Account</x:v>
@@ -15320,7 +15346,7 @@
     </x:row>
     <x:row r="20" ht="15" customHeight="1">
       <x:c r="A20" s="87" t="str">
-        <x:v>Borrowers</x:v>
+        <x:v>Retired — Borrowers</x:v>
       </x:c>
       <x:c r="B20" s="87" t="str">
         <x:v>Effective Receiving Bank Account</x:v>
@@ -15337,7 +15363,7 @@
     </x:row>
     <x:row r="21" ht="15" customHeight="1">
       <x:c r="A21" s="87" t="str">
-        <x:v>Collection Settings</x:v>
+        <x:v>Retired — Collection Settings</x:v>
       </x:c>
       <x:c r="B21" s="87" t="str">
         <x:v>Default Receiving Bank Account</x:v>
@@ -15359,7 +15385,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71c01aec0b6d4a7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c64ae7a7f954995"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15455,13 +15481,13 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F5" s="83" t="n">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G5" s="83" t="str">
         <x:v>Existing daily collection population. Future agent additionally requires due/overdue and AI Collection Enabled; dashboard filter unchanged.</x:v>
       </x:c>
       <x:c r="H5" s="83" t="str">
-        <x:v>OLTP 3.000050; location columns included after regeneration. Existing row filter and update mode retained.</x:v>
+        <x:v>Cleanup reconciled. Address included; filters and permissions preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="55" customHeight="1">
@@ -15481,13 +15507,13 @@
         <x:v>Adds, Updates, Deletes</x:v>
       </x:c>
       <x:c r="F6" s="83" t="n">
-        <x:v>45</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G6" s="83" t="str">
         <x:v>Primary borrower list; City and Working Location exposed in existing form/detail views.</x:v>
       </x:c>
       <x:c r="H6" s="83" t="str">
-        <x:v>OLTP 3.000050; location columns included after regeneration. Existing row filter and update mode retained.</x:v>
+        <x:v>Cleanup reconciled. Address included; filters and permissions preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="96" customHeight="1">
@@ -15513,7 +15539,7 @@
         <x:v>Read-only OLAP subset of borrowers whose outstanding principal is greater than zero.</x:v>
       </x:c>
       <x:c r="H7" s="59" t="str">
-        <x:v>OLAP 1.100031: exact membership reconciled; City and Working Location appended. Existing filter, actions and read-only mode retained. Earlier membership gaps corrected in inventory.</x:v>
+        <x:v>Cleanup reconciled. Address included; filters and permissions preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="96" customHeight="1">
@@ -15539,7 +15565,7 @@
         <x:v>Read-only OLAP subset of borrowers contributing positive interest profit in the last 30 days.</x:v>
       </x:c>
       <x:c r="H8" s="59" t="str">
-        <x:v>OLAP 1.100031: exact membership reconciled; City and Working Location appended. Existing filter, actions and read-only mode retained. Earlier membership gaps corrected in inventory.</x:v>
+        <x:v>Cleanup reconciled. Address included; filters and permissions preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="96" customHeight="1">
@@ -15559,13 +15585,13 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F9" s="57" t="n">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G9" s="59" t="str">
         <x:v>Curated, read-only borrower feed for downstream reporting and dashboard reconciliation, including the borrower value/stability matrix fields.</x:v>
       </x:c>
       <x:c r="H9" s="59" t="str">
-        <x:v>OLAP 1.100031: exact membership reconciled; City and Working Location appended. Existing filter, actions and read-only mode retained. Earlier membership gaps corrected in inventory.</x:v>
+        <x:v>Cleanup reconciled. Address included; filters and permissions preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
@@ -15777,18 +15803,18 @@
         <x:v>Read-only</x:v>
       </x:c>
       <x:c r="F18" s="72" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="72" t="str">
         <x:v>Read-only daily collection export and message-review slice using OLAP-native current-status, amount, charge-list, hidden-flag, and overdue fields.</x:v>
       </x:c>
       <x:c r="H18" s="72" t="str">
-        <x:v>OLAP 1.100031: exact membership reconciled; City and Working Location appended. Existing filter, actions and read-only mode retained. Earlier membership gaps corrected in inventory.</x:v>
+        <x:v>Cleanup reconciled. Address included; filters and permissions preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" customHeight="1">
       <x:c r="A19" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B19" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -15797,19 +15823,19 @@
         <x:v>Borrowers</x:v>
       </x:c>
       <x:c r="D19" s="87" t="str">
-        <x:v>AND([AI Collection Enabled], ISNOTBLANK([Collection Setup Issues]))</x:v>
+        <x:v>Not active</x:v>
       </x:c>
       <x:c r="E19" s="87" t="str">
-        <x:v>Updates only</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="F19" s="87" t="n">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G19" s="87" t="str">
-        <x:v>Enabled borrowers needing name, Instagram or receiving-bank setup.</x:v>
+        <x:v>Historical setup-review slice</x:v>
       </x:c>
       <x:c r="H19" s="87" t="str">
-        <x:v>OLTP 3.000050; location columns included after regeneration. Existing row filter and update mode retained.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15819,7 +15845,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R742f04d9bb684197"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ba644b5b14846d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15914,7 +15940,7 @@
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="57" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B8" s="59" t="str">
         <x:v>Visible Borrowers</x:v>
@@ -15934,7 +15960,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C9" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D9" s="59" t="str">
         <x:v>Description</x:v>
@@ -15948,7 +15974,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C10" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D10" s="59" t="str">
         <x:v>Creation Date</x:v>
@@ -15962,7 +15988,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C11" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D11" s="59" t="str">
         <x:v>Hidden Flag</x:v>
@@ -15976,7 +16002,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C12" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="59" t="str">
         <x:v>Related Loans</x:v>
@@ -15990,7 +16016,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C13" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D13" s="59" t="str">
         <x:v>Total Interest Earned</x:v>
@@ -16004,7 +16030,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C14" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D14" s="59" t="str">
         <x:v>Total Amount Loaned</x:v>
@@ -16018,7 +16044,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C15" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D15" s="59" t="str">
         <x:v>Total Number of Loans</x:v>
@@ -16032,7 +16058,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C16" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="59" t="str">
         <x:v>Total Outstanding Principal</x:v>
@@ -16046,7 +16072,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C17" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D17" s="59" t="str">
         <x:v>Header - Active Loans</x:v>
@@ -16060,7 +16086,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C18" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D18" s="59" t="str">
         <x:v>Borrower Name TE</x:v>
@@ -16074,7 +16100,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C19" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D19" s="59" t="str">
         <x:v>Return on Active Principal</x:v>
@@ -16088,7 +16114,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C20" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="59" t="str">
         <x:v>Active Loan Interest Earned</x:v>
@@ -16102,7 +16128,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C21" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D21" s="59" t="str">
         <x:v>Active Daily Interest</x:v>
@@ -16116,7 +16142,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C22" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D22" s="59" t="str">
         <x:v>Projected Interest Coverage Date</x:v>
@@ -16130,7 +16156,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C23" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D23" s="59" t="str">
         <x:v>Closed Loan Interest Earned</x:v>
@@ -16144,7 +16170,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C24" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D24" s="59" t="str">
         <x:v>Closed Loan Principle</x:v>
@@ -16158,7 +16184,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C25" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D25" s="59" t="str">
         <x:v>Has Closed Loan</x:v>
@@ -16172,7 +16198,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C26" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D26" s="59" t="str">
         <x:v>Return on Closed Loans</x:v>
@@ -16186,7 +16212,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C27" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D27" s="59" t="str">
         <x:v>Header - Closed Loans</x:v>
@@ -16200,7 +16226,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C28" s="57" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D28" s="59" t="str">
         <x:v>Has Active Loan</x:v>
@@ -16214,7 +16240,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C29" s="57" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D29" s="59" t="str">
         <x:v>Daily Collection Status</x:v>
@@ -16228,7 +16254,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C30" s="57" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D30" s="59" t="str">
         <x:v>Todays Collection Charges</x:v>
@@ -16242,7 +16268,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C31" s="57" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D31" s="59" t="str">
         <x:v>Todays Amount Due</x:v>
@@ -16256,7 +16282,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C32" s="57" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D32" s="59" t="str">
         <x:v>Todays Amount Collected</x:v>
@@ -16270,7 +16296,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C33" s="57" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D33" s="59" t="str">
         <x:v>Todays Amount Remaining</x:v>
@@ -16284,7 +16310,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C34" s="57" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D34" s="59" t="str">
         <x:v>Daily Collection Status - Order</x:v>
@@ -16298,7 +16324,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C35" s="57" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D35" s="59" t="str">
         <x:v>Borrower Name - Collection</x:v>
@@ -16312,7 +16338,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C36" s="57" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D36" s="59" t="str">
         <x:v>Active Profit After Principal Coverage</x:v>
@@ -16326,7 +16352,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C37" s="57" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D37" s="59" t="str">
         <x:v>Related Payments</x:v>
@@ -16544,7 +16570,7 @@
     </x:row>
     <x:row r="53" ht="15" customHeight="1">
       <x:c r="A53" s="57" t="str">
-        <x:v>OLAP</x:v>
+        <x:v>Retired OLAP</x:v>
       </x:c>
       <x:c r="B53" s="59" t="str">
         <x:v>Borrowers with Outstanding Loans</x:v>
@@ -16564,7 +16590,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C54" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D54" s="59" t="str">
         <x:v>Description</x:v>
@@ -16578,7 +16604,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C55" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D55" s="59" t="str">
         <x:v>Creation Date</x:v>
@@ -16592,7 +16618,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C56" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D56" s="59" t="str">
         <x:v>Related Loans</x:v>
@@ -16606,7 +16632,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C57" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D57" s="59" t="str">
         <x:v>Total Interest Earned</x:v>
@@ -16620,7 +16646,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C58" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D58" s="59" t="str">
         <x:v>Total Amount Loaned</x:v>
@@ -16634,7 +16660,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C59" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D59" s="59" t="str">
         <x:v>Total Number of Loans</x:v>
@@ -16648,7 +16674,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C60" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D60" s="59" t="str">
         <x:v>Total Outstanding Principal</x:v>
@@ -16662,7 +16688,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C61" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D61" s="59" t="str">
         <x:v>Header - Active Loans</x:v>
@@ -16676,7 +16702,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C62" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D62" s="59" t="str">
         <x:v>Borrower Name TE</x:v>
@@ -16690,7 +16716,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C63" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D63" s="59" t="str">
         <x:v>Return on Active Principal</x:v>
@@ -16704,7 +16730,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C64" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D64" s="59" t="str">
         <x:v>Profit Last 30 Days</x:v>
@@ -16718,7 +16744,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C65" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D65" s="59" t="str">
         <x:v>Projected Interest Coverage Date</x:v>
@@ -16732,7 +16758,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C66" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D66" s="59" t="str">
         <x:v>Active Loan Interest Earned</x:v>
@@ -16746,7 +16772,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C67" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D67" s="59" t="str">
         <x:v>Active Daily Interest</x:v>
@@ -16760,7 +16786,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C68" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D68" s="59" t="str">
         <x:v>Related Loan Assessments</x:v>
@@ -16774,7 +16800,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C69" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D69" s="59" t="str">
         <x:v>Related Calendars</x:v>
@@ -16788,7 +16814,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C70" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D70" s="59" t="str">
         <x:v>Closed Loan Interest Earned</x:v>
@@ -16802,7 +16828,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C71" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D71" s="59" t="str">
         <x:v>Closed Loan Principle</x:v>
@@ -16816,7 +16842,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C72" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D72" s="59" t="str">
         <x:v>Has Closed Loan</x:v>
@@ -16830,7 +16856,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C73" s="57" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D73" s="59" t="str">
         <x:v>Return on Closed Loans</x:v>
@@ -16844,7 +16870,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C74" s="57" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D74" s="59" t="str">
         <x:v>Header - Closed Loans</x:v>
@@ -16858,7 +16884,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C75" s="57" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D75" s="59" t="str">
         <x:v>Has Active Loan</x:v>
@@ -16872,7 +16898,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C76" s="57" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D76" s="59" t="str">
         <x:v>30D Gross Principal Days</x:v>
@@ -16886,7 +16912,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C77" s="57" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D77" s="59" t="str">
         <x:v>30D Principal Reduction Days</x:v>
@@ -16900,7 +16926,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C78" s="57" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D78" s="59" t="str">
         <x:v>30D Average Outstanding Principal</x:v>
@@ -16914,7 +16940,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C79" s="57" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D79" s="59" t="str">
         <x:v>30D Return on Average Principal</x:v>
@@ -16928,7 +16954,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C80" s="57" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D80" s="59" t="str">
         <x:v>Daily Collection Status</x:v>
@@ -16942,7 +16968,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C81" s="57" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D81" s="59" t="str">
         <x:v>Todays Collection Charges</x:v>
@@ -16956,7 +16982,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C82" s="57" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D82" s="59" t="str">
         <x:v>Todays Amount Due</x:v>
@@ -16970,7 +16996,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C83" s="57" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D83" s="59" t="str">
         <x:v>Todays Amount Collected</x:v>
@@ -16984,7 +17010,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C84" s="57" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D84" s="59" t="str">
         <x:v>Todays Amount Remaining</x:v>
@@ -16998,7 +17024,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C85" s="57" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D85" s="59" t="str">
         <x:v>Portfolio Exposure %</x:v>
@@ -17012,7 +17038,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C86" s="57" t="n">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D86" s="59" t="str">
         <x:v>Active Loan Count</x:v>
@@ -17026,7 +17052,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C87" s="57" t="n">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D87" s="59" t="str">
         <x:v>Oldest Active Loan Age</x:v>
@@ -17040,7 +17066,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C88" s="57" t="n">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D88" s="59" t="str">
         <x:v>Overdue Amount</x:v>
@@ -17054,7 +17080,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C89" s="57" t="n">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D89" s="59" t="str">
         <x:v>Overdue Charge Count</x:v>
@@ -17068,7 +17094,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C90" s="57" t="n">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D90" s="59" t="str">
         <x:v>Historical Charge Count</x:v>
@@ -17082,7 +17108,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C91" s="57" t="n">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D91" s="59" t="str">
         <x:v>On Time Charge Count</x:v>
@@ -17096,7 +17122,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C92" s="57" t="n">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D92" s="59" t="str">
         <x:v>Lifetime On Time Rate</x:v>
@@ -17110,7 +17136,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C93" s="57" t="n">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D93" s="59" t="str">
         <x:v>Recent 30D Charge Count</x:v>
@@ -17124,7 +17150,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C94" s="57" t="n">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D94" s="59" t="str">
         <x:v>Recent 30D On Time Count</x:v>
@@ -17138,7 +17164,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C95" s="57" t="n">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D95" s="59" t="str">
         <x:v>Recent 30D On Time Rate</x:v>
@@ -17152,7 +17178,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C96" s="57" t="n">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D96" s="59" t="str">
         <x:v>Lifetime Late Payment Count</x:v>
@@ -17166,7 +17192,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C97" s="57" t="n">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D97" s="59" t="str">
         <x:v>Recent 30D Late Payment Count</x:v>
@@ -17180,7 +17206,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C98" s="57" t="n">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D98" s="59" t="str">
         <x:v>Maximum Days Late</x:v>
@@ -17194,7 +17220,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C99" s="57" t="n">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D99" s="59" t="str">
         <x:v>Last Late Payment Date</x:v>
@@ -17208,7 +17234,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C100" s="57" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D100" s="59" t="str">
         <x:v>Largest Successful Loan</x:v>
@@ -17222,7 +17248,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C101" s="57" t="n">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D101" s="59" t="str">
         <x:v>Average Successful Loan Size</x:v>
@@ -17236,7 +17262,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C102" s="57" t="n">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D102" s="59" t="str">
         <x:v>Default Count</x:v>
@@ -17250,7 +17276,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C103" s="57" t="n">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D103" s="59" t="str">
         <x:v>Lifetime Default Loss</x:v>
@@ -17264,7 +17290,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C104" s="57" t="n">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D104" s="59" t="str">
         <x:v>Portfolio Outstanding Principal</x:v>
@@ -17278,7 +17304,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C105" s="57" t="n">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D105" s="59" t="str">
         <x:v>Portfolio Share Join Key</x:v>
@@ -17328,7 +17354,7 @@
     </x:row>
     <x:row r="109" ht="15" customHeight="1">
       <x:c r="A109" s="57" t="str">
-        <x:v>OLAP</x:v>
+        <x:v>Retired OLAP</x:v>
       </x:c>
       <x:c r="B109" s="59" t="str">
         <x:v>Profit Contribution 30D</x:v>
@@ -17348,7 +17374,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C110" s="57" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D110" s="59" t="str">
         <x:v>Description</x:v>
@@ -17362,7 +17388,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C111" s="57" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D111" s="59" t="str">
         <x:v>Creation Date</x:v>
@@ -17376,7 +17402,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C112" s="57" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D112" s="59" t="str">
         <x:v>Related Loans</x:v>
@@ -17390,7 +17416,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C113" s="57" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D113" s="59" t="str">
         <x:v>Total Interest Earned</x:v>
@@ -17404,7 +17430,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C114" s="57" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D114" s="59" t="str">
         <x:v>Total Amount Loaned</x:v>
@@ -17418,7 +17444,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C115" s="57" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D115" s="59" t="str">
         <x:v>Total Number of Loans</x:v>
@@ -17432,7 +17458,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C116" s="57" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D116" s="59" t="str">
         <x:v>Total Outstanding Principal</x:v>
@@ -17446,7 +17472,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C117" s="57" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D117" s="59" t="str">
         <x:v>Header - Active Loans</x:v>
@@ -17460,7 +17486,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C118" s="57" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D118" s="59" t="str">
         <x:v>Borrower Name TE</x:v>
@@ -17474,7 +17500,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C119" s="57" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D119" s="59" t="str">
         <x:v>Return on Active Principal</x:v>
@@ -17488,7 +17514,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C120" s="57" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D120" s="59" t="str">
         <x:v>Profit Last 30 Days</x:v>
@@ -17502,7 +17528,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C121" s="57" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D121" s="59" t="str">
         <x:v>Projected Interest Coverage Date</x:v>
@@ -17516,7 +17542,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C122" s="57" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D122" s="59" t="str">
         <x:v>Active Loan Interest Earned</x:v>
@@ -17530,7 +17556,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C123" s="57" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D123" s="59" t="str">
         <x:v>Active Daily Interest</x:v>
@@ -17544,7 +17570,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C124" s="57" t="n">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D124" s="59" t="str">
         <x:v>Related Loan Assessments</x:v>
@@ -17558,7 +17584,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C125" s="57" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D125" s="59" t="str">
         <x:v>Related Calendars</x:v>
@@ -17572,7 +17598,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C126" s="57" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D126" s="59" t="str">
         <x:v>Closed Loan Interest Earned</x:v>
@@ -17586,7 +17612,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C127" s="57" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D127" s="59" t="str">
         <x:v>Closed Loan Principle</x:v>
@@ -17600,7 +17626,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C128" s="57" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D128" s="59" t="str">
         <x:v>Has Closed Loan</x:v>
@@ -17614,7 +17640,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C129" s="57" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D129" s="59" t="str">
         <x:v>Return on Closed Loans</x:v>
@@ -17628,7 +17654,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C130" s="57" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D130" s="59" t="str">
         <x:v>Header - Closed Loans</x:v>
@@ -17642,7 +17668,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C131" s="57" t="n">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D131" s="59" t="str">
         <x:v>Has Active Loan</x:v>
@@ -17656,7 +17682,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C132" s="57" t="n">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D132" s="59" t="str">
         <x:v>30D Gross Principal Days</x:v>
@@ -17670,7 +17696,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C133" s="57" t="n">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D133" s="59" t="str">
         <x:v>30D Principal Reduction Days</x:v>
@@ -17684,7 +17710,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C134" s="57" t="n">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D134" s="59" t="str">
         <x:v>30D Average Outstanding Principal</x:v>
@@ -17698,7 +17724,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C135" s="57" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D135" s="59" t="str">
         <x:v>30D Return on Average Principal</x:v>
@@ -17712,7 +17738,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C136" s="57" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D136" s="59" t="str">
         <x:v>Daily Collection Status</x:v>
@@ -17726,7 +17752,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C137" s="57" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D137" s="59" t="str">
         <x:v>Todays Collection Charges</x:v>
@@ -17740,7 +17766,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C138" s="57" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D138" s="59" t="str">
         <x:v>Todays Amount Due</x:v>
@@ -17754,7 +17780,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C139" s="57" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D139" s="59" t="str">
         <x:v>Todays Amount Collected</x:v>
@@ -17768,7 +17794,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C140" s="57" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D140" s="59" t="str">
         <x:v>Todays Amount Remaining</x:v>
@@ -17782,7 +17808,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C141" s="57" t="n">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D141" s="59" t="str">
         <x:v>Portfolio Exposure %</x:v>
@@ -17796,7 +17822,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C142" s="57" t="n">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D142" s="59" t="str">
         <x:v>Active Loan Count</x:v>
@@ -17810,7 +17836,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C143" s="57" t="n">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D143" s="59" t="str">
         <x:v>Oldest Active Loan Age</x:v>
@@ -17824,7 +17850,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C144" s="57" t="n">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D144" s="59" t="str">
         <x:v>Overdue Amount</x:v>
@@ -17838,7 +17864,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C145" s="57" t="n">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D145" s="59" t="str">
         <x:v>Overdue Charge Count</x:v>
@@ -17852,7 +17878,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C146" s="57" t="n">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D146" s="59" t="str">
         <x:v>Historical Charge Count</x:v>
@@ -17866,7 +17892,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C147" s="57" t="n">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D147" s="59" t="str">
         <x:v>On Time Charge Count</x:v>
@@ -17880,7 +17906,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C148" s="57" t="n">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D148" s="59" t="str">
         <x:v>Lifetime On Time Rate</x:v>
@@ -17894,7 +17920,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C149" s="57" t="n">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D149" s="59" t="str">
         <x:v>Recent 30D Charge Count</x:v>
@@ -17908,7 +17934,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C150" s="57" t="n">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D150" s="59" t="str">
         <x:v>Recent 30D On Time Count</x:v>
@@ -17922,7 +17948,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C151" s="57" t="n">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D151" s="59" t="str">
         <x:v>Recent 30D On Time Rate</x:v>
@@ -17936,7 +17962,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C152" s="57" t="n">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D152" s="59" t="str">
         <x:v>Lifetime Late Payment Count</x:v>
@@ -17950,7 +17976,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C153" s="57" t="n">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D153" s="59" t="str">
         <x:v>Recent 30D Late Payment Count</x:v>
@@ -17964,7 +17990,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C154" s="57" t="n">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D154" s="59" t="str">
         <x:v>Maximum Days Late</x:v>
@@ -17978,7 +18004,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C155" s="57" t="n">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D155" s="59" t="str">
         <x:v>Last Late Payment Date</x:v>
@@ -17992,7 +18018,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C156" s="57" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D156" s="59" t="str">
         <x:v>Largest Successful Loan</x:v>
@@ -18006,7 +18032,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C157" s="57" t="n">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D157" s="59" t="str">
         <x:v>Average Successful Loan Size</x:v>
@@ -18020,7 +18046,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C158" s="57" t="n">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D158" s="59" t="str">
         <x:v>Default Count</x:v>
@@ -18034,7 +18060,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C159" s="57" t="n">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D159" s="59" t="str">
         <x:v>Lifetime Default Loss</x:v>
@@ -18048,7 +18074,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C160" s="57" t="n">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D160" s="59" t="str">
         <x:v>Portfolio Outstanding Principal</x:v>
@@ -18062,7 +18088,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C161" s="57" t="n">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D161" s="59" t="str">
         <x:v>Portfolio Share Join Key</x:v>
@@ -21170,7 +21196,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C383" s="87" t="n">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D383" s="87" t="str">
         <x:v>Communication Name</x:v>
@@ -21184,7 +21210,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C384" s="87" t="n">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D384" s="87" t="str">
         <x:v>Instagram Username</x:v>
@@ -21192,7 +21218,7 @@
     </x:row>
     <x:row r="385" ht="15" customHeight="1">
       <x:c r="A385" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B385" s="87" t="str">
         <x:v>Visible Borrowers</x:v>
@@ -21206,7 +21232,7 @@
     </x:row>
     <x:row r="386" ht="15" customHeight="1">
       <x:c r="A386" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B386" s="87" t="str">
         <x:v>Visible Borrowers</x:v>
@@ -21226,7 +21252,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C387" s="87" t="n">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D387" s="87" t="str">
         <x:v>AI Collection Enabled</x:v>
@@ -21234,7 +21260,7 @@
     </x:row>
     <x:row r="388" ht="15" customHeight="1">
       <x:c r="A388" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B388" s="87" t="str">
         <x:v>Visible Borrowers</x:v>
@@ -21248,7 +21274,7 @@
     </x:row>
     <x:row r="389" ht="15" customHeight="1">
       <x:c r="A389" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B389" s="87" t="str">
         <x:v>Visible Borrowers</x:v>
@@ -21262,7 +21288,7 @@
     </x:row>
     <x:row r="390" ht="15" customHeight="1">
       <x:c r="A390" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B390" s="87" t="str">
         <x:v>Visible Borrowers</x:v>
@@ -21276,7 +21302,7 @@
     </x:row>
     <x:row r="391" ht="15" customHeight="1">
       <x:c r="A391" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B391" s="87" t="str">
         <x:v>Visible Borrowers</x:v>
@@ -21318,7 +21344,7 @@
     </x:row>
     <x:row r="394" ht="15" customHeight="1">
       <x:c r="A394" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B394" s="87" t="str">
         <x:v>Todays Collection Board</x:v>
@@ -21332,7 +21358,7 @@
     </x:row>
     <x:row r="395" ht="15" customHeight="1">
       <x:c r="A395" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B395" s="87" t="str">
         <x:v>Todays Collection Board</x:v>
@@ -21352,7 +21378,7 @@
         <x:v>Todays Collection Board</x:v>
       </x:c>
       <x:c r="C396" s="87" t="n">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D396" s="87" t="str">
         <x:v>AI Collection Enabled</x:v>
@@ -21360,7 +21386,7 @@
     </x:row>
     <x:row r="397" ht="15" customHeight="1">
       <x:c r="A397" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B397" s="87" t="str">
         <x:v>Todays Collection Board</x:v>
@@ -21374,7 +21400,7 @@
     </x:row>
     <x:row r="398" ht="15" customHeight="1">
       <x:c r="A398" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B398" s="87" t="str">
         <x:v>Todays Collection Board</x:v>
@@ -21388,7 +21414,7 @@
     </x:row>
     <x:row r="399" ht="15" customHeight="1">
       <x:c r="A399" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B399" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21402,7 +21428,7 @@
     </x:row>
     <x:row r="400" ht="15" customHeight="1">
       <x:c r="A400" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B400" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21416,7 +21442,7 @@
     </x:row>
     <x:row r="401" ht="15" customHeight="1">
       <x:c r="A401" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B401" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21430,7 +21456,7 @@
     </x:row>
     <x:row r="402" ht="15" customHeight="1">
       <x:c r="A402" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B402" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21444,7 +21470,7 @@
     </x:row>
     <x:row r="403" ht="15" customHeight="1">
       <x:c r="A403" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B403" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21458,7 +21484,7 @@
     </x:row>
     <x:row r="404" ht="15" customHeight="1">
       <x:c r="A404" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B404" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21472,7 +21498,7 @@
     </x:row>
     <x:row r="405" ht="15" customHeight="1">
       <x:c r="A405" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B405" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21486,7 +21512,7 @@
     </x:row>
     <x:row r="406" ht="15" customHeight="1">
       <x:c r="A406" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B406" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21500,7 +21526,7 @@
     </x:row>
     <x:row r="407" ht="15" customHeight="1">
       <x:c r="A407" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B407" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21514,7 +21540,7 @@
     </x:row>
     <x:row r="408" ht="15" customHeight="1">
       <x:c r="A408" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B408" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21528,7 +21554,7 @@
     </x:row>
     <x:row r="409" ht="15" customHeight="1">
       <x:c r="A409" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B409" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21542,7 +21568,7 @@
     </x:row>
     <x:row r="410" ht="15" customHeight="1">
       <x:c r="A410" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B410" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21556,7 +21582,7 @@
     </x:row>
     <x:row r="411" ht="15" customHeight="1">
       <x:c r="A411" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B411" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21570,7 +21596,7 @@
     </x:row>
     <x:row r="412" ht="15" customHeight="1">
       <x:c r="A412" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B412" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21584,7 +21610,7 @@
     </x:row>
     <x:row r="413" ht="15" customHeight="1">
       <x:c r="A413" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B413" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21598,7 +21624,7 @@
     </x:row>
     <x:row r="414" ht="15" customHeight="1">
       <x:c r="A414" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B414" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21612,7 +21638,7 @@
     </x:row>
     <x:row r="415" ht="15" customHeight="1">
       <x:c r="A415" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B415" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21626,7 +21652,7 @@
     </x:row>
     <x:row r="416" ht="15" customHeight="1">
       <x:c r="A416" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B416" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21640,7 +21666,7 @@
     </x:row>
     <x:row r="417" ht="15" customHeight="1">
       <x:c r="A417" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B417" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21654,7 +21680,7 @@
     </x:row>
     <x:row r="418" ht="15" customHeight="1">
       <x:c r="A418" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B418" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21668,7 +21694,7 @@
     </x:row>
     <x:row r="419" ht="15" customHeight="1">
       <x:c r="A419" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B419" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21682,7 +21708,7 @@
     </x:row>
     <x:row r="420" ht="15" customHeight="1">
       <x:c r="A420" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B420" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21696,7 +21722,7 @@
     </x:row>
     <x:row r="421" ht="15" customHeight="1">
       <x:c r="A421" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B421" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21710,7 +21736,7 @@
     </x:row>
     <x:row r="422" ht="15" customHeight="1">
       <x:c r="A422" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B422" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21724,7 +21750,7 @@
     </x:row>
     <x:row r="423" ht="15" customHeight="1">
       <x:c r="A423" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B423" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21738,7 +21764,7 @@
     </x:row>
     <x:row r="424" ht="15" customHeight="1">
       <x:c r="A424" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B424" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21752,7 +21778,7 @@
     </x:row>
     <x:row r="425" ht="15" customHeight="1">
       <x:c r="A425" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B425" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21766,7 +21792,7 @@
     </x:row>
     <x:row r="426" ht="15" customHeight="1">
       <x:c r="A426" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B426" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21780,7 +21806,7 @@
     </x:row>
     <x:row r="427" ht="15" customHeight="1">
       <x:c r="A427" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B427" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21794,7 +21820,7 @@
     </x:row>
     <x:row r="428" ht="15" customHeight="1">
       <x:c r="A428" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B428" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21808,7 +21834,7 @@
     </x:row>
     <x:row r="429" ht="15" customHeight="1">
       <x:c r="A429" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B429" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21822,7 +21848,7 @@
     </x:row>
     <x:row r="430" ht="15" customHeight="1">
       <x:c r="A430" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B430" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21836,7 +21862,7 @@
     </x:row>
     <x:row r="431" ht="15" customHeight="1">
       <x:c r="A431" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B431" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21850,7 +21876,7 @@
     </x:row>
     <x:row r="432" ht="15" customHeight="1">
       <x:c r="A432" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B432" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21864,7 +21890,7 @@
     </x:row>
     <x:row r="433" ht="15" customHeight="1">
       <x:c r="A433" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B433" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21878,7 +21904,7 @@
     </x:row>
     <x:row r="434" ht="15" customHeight="1">
       <x:c r="A434" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B434" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21892,7 +21918,7 @@
     </x:row>
     <x:row r="435" ht="15" customHeight="1">
       <x:c r="A435" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B435" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21906,7 +21932,7 @@
     </x:row>
     <x:row r="436" ht="15" customHeight="1">
       <x:c r="A436" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B436" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21920,7 +21946,7 @@
     </x:row>
     <x:row r="437" ht="15" customHeight="1">
       <x:c r="A437" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B437" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21934,7 +21960,7 @@
     </x:row>
     <x:row r="438" ht="15" customHeight="1">
       <x:c r="A438" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B438" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21948,7 +21974,7 @@
     </x:row>
     <x:row r="439" ht="15" customHeight="1">
       <x:c r="A439" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B439" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21962,7 +21988,7 @@
     </x:row>
     <x:row r="440" ht="15" customHeight="1">
       <x:c r="A440" s="87" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B440" s="87" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21976,7 +22002,7 @@
     </x:row>
     <x:row r="441">
       <x:c r="A441" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B441" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -21990,7 +22016,7 @@
     </x:row>
     <x:row r="442">
       <x:c r="A442" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B442" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -22004,7 +22030,7 @@
     </x:row>
     <x:row r="443">
       <x:c r="A443" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B443" t="str">
         <x:v>Collection Setup Review</x:v>
@@ -22024,7 +22050,7 @@
         <x:v>Todays Collection Board</x:v>
       </x:c>
       <x:c r="C444" t="n">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D444" t="str">
         <x:v>City</x:v>
@@ -22038,7 +22064,7 @@
         <x:v>Todays Collection Board</x:v>
       </x:c>
       <x:c r="C445" t="n">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D445" t="str">
         <x:v>Working Location</x:v>
@@ -22046,7 +22072,7 @@
     </x:row>
     <x:row r="446">
       <x:c r="A446" t="str">
-        <x:v>OLTP</x:v>
+        <x:v>Retired OLTP</x:v>
       </x:c>
       <x:c r="B446" t="str">
         <x:v>Visible Borrowers</x:v>
@@ -22066,7 +22092,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C447" t="n">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D447" t="str">
         <x:v>City</x:v>
@@ -22080,7 +22106,7 @@
         <x:v>Visible Borrowers</x:v>
       </x:c>
       <x:c r="C448" t="n">
-        <x:v>45</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D448" t="str">
         <x:v>Working Location</x:v>
@@ -22164,7 +22190,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C454" t="n">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D454" t="str">
         <x:v>Hidden Flag</x:v>
@@ -22178,7 +22204,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C455" t="n">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D455" t="str">
         <x:v>Projected Monthly Profit Contribution</x:v>
@@ -22192,7 +22218,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C456" t="n">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D456" t="str">
         <x:v>Matrix Active Borrower Count</x:v>
@@ -22206,7 +22232,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C457" t="n">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D457" t="str">
         <x:v>Matrix Equal Share Benchmark</x:v>
@@ -22220,7 +22246,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C458" t="n">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D458" t="str">
         <x:v>Matrix Economic Contribution</x:v>
@@ -22234,7 +22260,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C459" t="n">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D459" t="str">
         <x:v>Matrix Recent Reliability Score</x:v>
@@ -22248,7 +22274,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C460" t="n">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D460" t="str">
         <x:v>Matrix Historical Reliability Score</x:v>
@@ -22262,7 +22288,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C461" t="n">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D461" t="str">
         <x:v>Matrix Delay Severity Score</x:v>
@@ -22276,7 +22302,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C462" t="n">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D462" t="str">
         <x:v>Matrix Current Condition Score</x:v>
@@ -22290,7 +22316,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C463" t="n">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D463" t="str">
         <x:v>Matrix History Sufficient</x:v>
@@ -22304,7 +22330,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C464" t="n">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D464" t="str">
         <x:v>Matrix Stability Score</x:v>
@@ -22318,7 +22344,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C465" t="n">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D465" t="str">
         <x:v>Matrix Quadrant</x:v>
@@ -22332,7 +22358,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C466" t="n">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D466" t="str">
         <x:v>Matrix Bubble Label</x:v>
@@ -22346,7 +22372,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C467" t="n">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D467" t="str">
         <x:v>Profit Last 10 Days</x:v>
@@ -22360,7 +22386,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C468" t="n">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D468" t="str">
         <x:v>Matrix Scaled Economic Contribution</x:v>
@@ -22374,7 +22400,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C469" t="n">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D469" t="str">
         <x:v>Related Payments</x:v>
@@ -22388,7 +22414,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C470" t="n">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D470" t="str">
         <x:v>City</x:v>
@@ -22402,7 +22428,7 @@
         <x:v>Borrowers with Outstanding Loans</x:v>
       </x:c>
       <x:c r="C471" t="n">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D471" t="str">
         <x:v>Working Location</x:v>
@@ -22416,7 +22442,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C472" t="n">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D472" t="str">
         <x:v>Hidden Flag</x:v>
@@ -22430,7 +22456,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C473" t="n">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D473" t="str">
         <x:v>Projected Monthly Profit Contribution</x:v>
@@ -22444,7 +22470,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C474" t="n">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D474" t="str">
         <x:v>Matrix Active Borrower Count</x:v>
@@ -22458,7 +22484,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C475" t="n">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D475" t="str">
         <x:v>Matrix Equal Share Benchmark</x:v>
@@ -22472,7 +22498,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C476" t="n">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D476" t="str">
         <x:v>Matrix Economic Contribution</x:v>
@@ -22486,7 +22512,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C477" t="n">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D477" t="str">
         <x:v>Matrix Recent Reliability Score</x:v>
@@ -22500,7 +22526,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C478" t="n">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D478" t="str">
         <x:v>Matrix Historical Reliability Score</x:v>
@@ -22514,7 +22540,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C479" t="n">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D479" t="str">
         <x:v>Matrix Delay Severity Score</x:v>
@@ -22528,7 +22554,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C480" t="n">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D480" t="str">
         <x:v>Matrix Current Condition Score</x:v>
@@ -22542,7 +22568,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C481" t="n">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D481" t="str">
         <x:v>Matrix History Sufficient</x:v>
@@ -22556,7 +22582,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C482" t="n">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D482" t="str">
         <x:v>Matrix Stability Score</x:v>
@@ -22570,7 +22596,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C483" t="n">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D483" t="str">
         <x:v>Matrix Quadrant</x:v>
@@ -22584,7 +22610,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C484" t="n">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D484" t="str">
         <x:v>Matrix Bubble Label</x:v>
@@ -22598,7 +22624,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C485" t="n">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D485" t="str">
         <x:v>Profit Last 10 Days</x:v>
@@ -22612,7 +22638,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C486" t="n">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D486" t="str">
         <x:v>Matrix Scaled Economic Contribution</x:v>
@@ -22626,7 +22652,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C487" t="n">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D487" t="str">
         <x:v>Related Payments</x:v>
@@ -22640,7 +22666,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C488" t="n">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D488" t="str">
         <x:v>City</x:v>
@@ -22654,7 +22680,7 @@
         <x:v>Profit Contribution 30D</x:v>
       </x:c>
       <x:c r="C489" t="n">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D489" t="str">
         <x:v>Working Location</x:v>
@@ -22700,6 +22726,90 @@
       </x:c>
       <x:c r="D492" t="str">
         <x:v>Working Location</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493">
+      <x:c r="A493" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B493" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C493" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D493" t="str">
+        <x:v>Address</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494">
+      <x:c r="A494" t="str">
+        <x:v>OLTP</x:v>
+      </x:c>
+      <x:c r="B494" t="str">
+        <x:v>Visible Borrowers</x:v>
+      </x:c>
+      <x:c r="C494" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D494" t="str">
+        <x:v>Address</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495">
+      <x:c r="A495" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B495" t="str">
+        <x:v>Borrowers with Outstanding Loans</x:v>
+      </x:c>
+      <x:c r="C495" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D495" t="str">
+        <x:v>Address</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496">
+      <x:c r="A496" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B496" t="str">
+        <x:v>Profit Contribution 30D</x:v>
+      </x:c>
+      <x:c r="C496" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D496" t="str">
+        <x:v>Address</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497">
+      <x:c r="A497" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B497" t="str">
+        <x:v>Reporting Borrowers</x:v>
+      </x:c>
+      <x:c r="C497" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D497" t="str">
+        <x:v>Address</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498">
+      <x:c r="A498" t="str">
+        <x:v>OLAP</x:v>
+      </x:c>
+      <x:c r="B498" t="str">
+        <x:v>Todays Collection Board</x:v>
+      </x:c>
+      <x:c r="C498" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D498" t="str">
+        <x:v>Address</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22709,7 +22819,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb899178b9b345b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb2f9462cb394bf4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26735,7 +26845,7 @@
         <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F204" s="87" t="str">
-        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
+        <x:v>Required in both apps. OLTP editable; OLAP table remains read-only. Blank initial value.</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" customHeight="1">
@@ -26769,13 +26879,13 @@
         <x:v>Instagram Conversation URL</x:v>
       </x:c>
       <x:c r="D206" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E206" s="87" t="str">
-        <x:v>Yes — 1.100031</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F206" s="87" t="str">
-        <x:v>OLTP Url; OLAP Text; native Text. Existing type variance preserved. Both initial values blank.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" customHeight="1">
@@ -26789,13 +26899,13 @@
         <x:v>Instagram Verified At</x:v>
       </x:c>
       <x:c r="D207" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E207" s="87" t="str">
-        <x:v>Yes — 1.100031</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F207" s="87" t="str">
-        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" customHeight="1">
@@ -26815,7 +26925,7 @@
         <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F208" s="87" t="str">
-        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
+        <x:v>Initial TRUE in both apps for new rows only. Existing row values not edited by cleanup.</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" customHeight="1">
@@ -26829,13 +26939,13 @@
         <x:v>Late Penalty Enabled</x:v>
       </x:c>
       <x:c r="D209" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E209" s="87" t="str">
-        <x:v>Yes — 1.100031</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F209" s="87" t="str">
-        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" customHeight="1">
@@ -26849,13 +26959,13 @@
         <x:v>Receiving Bank Account</x:v>
       </x:c>
       <x:c r="D210" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E210" s="87" t="str">
-        <x:v>Yes — 1.100031</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F210" s="87" t="str">
-        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="15" customHeight="1">
@@ -26869,13 +26979,13 @@
         <x:v>Effective Receiving Bank Account</x:v>
       </x:c>
       <x:c r="D211" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E211" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F211" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="15" customHeight="1">
@@ -26889,13 +26999,13 @@
         <x:v>Collection Setup Issues</x:v>
       </x:c>
       <x:c r="D212" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E212" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F212" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="15" customHeight="1">
@@ -26909,13 +27019,13 @@
         <x:v>_RowNumber</x:v>
       </x:c>
       <x:c r="D213" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E213" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F213" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="15" customHeight="1">
@@ -26929,13 +27039,13 @@
         <x:v>Row ID</x:v>
       </x:c>
       <x:c r="D214" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E214" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F214" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="15" customHeight="1">
@@ -26949,13 +27059,13 @@
         <x:v>Account Label</x:v>
       </x:c>
       <x:c r="D215" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E215" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F215" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="15" customHeight="1">
@@ -26969,13 +27079,13 @@
         <x:v>Bank Name</x:v>
       </x:c>
       <x:c r="D216" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E216" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F216" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="15" customHeight="1">
@@ -26989,13 +27099,13 @@
         <x:v>Account Number</x:v>
       </x:c>
       <x:c r="D217" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E217" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F217" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="15" customHeight="1">
@@ -27009,13 +27119,13 @@
         <x:v>Account Holder Name</x:v>
       </x:c>
       <x:c r="D218" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E218" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F218" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="15" customHeight="1">
@@ -27029,13 +27139,13 @@
         <x:v>Active</x:v>
       </x:c>
       <x:c r="D219" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E219" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F219" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="15" customHeight="1">
@@ -27049,13 +27159,13 @@
         <x:v>Related Collection Settings</x:v>
       </x:c>
       <x:c r="D220" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E220" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F220" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="15" customHeight="1">
@@ -27069,13 +27179,13 @@
         <x:v>Related Borrowers</x:v>
       </x:c>
       <x:c r="D221" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E221" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F221" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="15" customHeight="1">
@@ -27089,13 +27199,13 @@
         <x:v>Related Borrowers By Effective Receiving Bank Account</x:v>
       </x:c>
       <x:c r="D222" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E222" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F222" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="15" customHeight="1">
@@ -27109,13 +27219,13 @@
         <x:v>_RowNumber</x:v>
       </x:c>
       <x:c r="D223" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E223" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F223" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="15" customHeight="1">
@@ -27129,13 +27239,13 @@
         <x:v>Row ID</x:v>
       </x:c>
       <x:c r="D224" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E224" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F224" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="15" customHeight="1">
@@ -27149,13 +27259,13 @@
         <x:v>Setting Name</x:v>
       </x:c>
       <x:c r="D225" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E225" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F225" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="15" customHeight="1">
@@ -27169,13 +27279,13 @@
         <x:v>Default Receiving Bank Account</x:v>
       </x:c>
       <x:c r="D226" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E226" s="87" t="str">
-        <x:v>Not configured by this build</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F226" s="87" t="str">
-        <x:v>OLTP 3.000024; 8 September 2026 (Asia/Bangkok); collection settings owned by OLTP.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="15" customHeight="1">
@@ -27189,13 +27299,13 @@
         <x:v>Collection Setup Review</x:v>
       </x:c>
       <x:c r="D227" s="87" t="str">
-        <x:v>Yes</x:v>
+        <x:v>Removed</x:v>
       </x:c>
       <x:c r="E227" s="87" t="str">
-        <x:v>No</x:v>
+        <x:v>Removed / absent</x:v>
       </x:c>
       <x:c r="F227" s="87" t="str">
-        <x:v>Enabled borrowers with setup issues; 45 columns at OLTP 3.000050; update only.</x:v>
+        <x:v>Removed 13 September 2026; historical inventory only, not an active dependency.</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
@@ -27275,7 +27385,7 @@
         <x:v>Yes — 1.100031</x:v>
       </x:c>
       <x:c r="F231" t="str">
-        <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
+        <x:v>Required in both apps. Blank initial value; display เมือง / City. Existing values preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -27296,6 +27406,26 @@
       </x:c>
       <x:c r="F232" t="str">
         <x:v>Verified loaded in OLAP. Partner fields managed in OLAP; borrower table remains read-only. Existing financial formulas and row flags unchanged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" t="str">
+        <x:v>Column</x:v>
+      </x:c>
+      <x:c r="B233" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="C233" t="str">
+        <x:v>Address</x:v>
+      </x:c>
+      <x:c r="D233" t="str">
+        <x:v>Yes — 3.000064</x:v>
+      </x:c>
+      <x:c r="E233" t="str">
+        <x:v>Yes — 1.100041</x:v>
+      </x:c>
+      <x:c r="F233" t="str">
+        <x:v>Text, optional; blank initial. Seven source addresses imported and reloaded.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -27308,7 +27438,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bf1c2fe6a734552"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R196b4f6281b84e49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27507,7 +27637,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbec54b2403354202"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc396ec1e9a8432c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29160,7 +29290,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a2caa9c6b2f4583"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref1d43f31d454711"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rb9853f0907c541e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rc818e69beb2a4e35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R5e6079b1c2934bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R4bebfdc085464e4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rfc856e925703480f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R7c83090d20924339"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R114839d9779d4251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R98ba3e208b9a45e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R84a3dc1cfc4b409b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R54931ad81cbb4447"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rf9ef1b83482c4b54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rd158215a355f46b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R16ef4dce4a404f59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R3a3c1dbe9cde4888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R7d7c6d1b0b9b4855"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rf0274cd7b5cf4361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R795c4633819943b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R6a70cd4520b24fbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rad8890efd2ad4c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R4f71724f3ba14f40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R99d46dde0e634099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R3cb019cf2f464b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R37b3e1a8ef934be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rc3e951c7837740e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R1c3d80887d6444f6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -98,7 +99,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="24">
+  <x:fills count="25">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -133,6 +134,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -345,7 +351,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="111">
+  <x:cellXfs count="114">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -585,6 +591,11 @@
     <x:xf numFmtId="0" fontId="11" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2492,7 +2503,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79a4e735b1af4cdc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R392b43b532d44c18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3878,6 +3889,1199 @@
       </x:c>
       <x:c r="H7" s="93" t="str">
         <x:v>Inline</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="113" t="str">
+        <x:v>Experiment</x:v>
+      </x:c>
+      <x:c r="B1" s="113" t="str">
+        <x:v>App version</x:v>
+      </x:c>
+      <x:c r="C1" s="113" t="str">
+        <x:v>Table</x:v>
+      </x:c>
+      <x:c r="D1" s="113" t="str">
+        <x:v>Column / setting</x:v>
+      </x:c>
+      <x:c r="E1" s="113" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="F1" s="113" t="str">
+        <x:v>Scope / status</x:v>
+      </x:c>
+      <x:c r="G1" s="113" t="str">
+        <x:v>Purpose / dependencies</x:v>
+      </x:c>
+      <x:c r="H1" s="113" t="str">
+        <x:v>Exact definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="150" customHeight="1">
+      <x:c r="A2" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B2" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C2" s="93" t="str">
+        <x:v>poc_source</x:v>
+      </x:c>
+      <x:c r="D2" s="93" t="str">
+        <x:v>Table access</x:v>
+      </x:c>
+      <x:c r="E2" s="93" t="str">
+        <x:v>Configuration</x:v>
+      </x:c>
+      <x:c r="F2" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G2" s="93" t="str">
+        <x:v>Source: database-1</x:v>
+      </x:c>
+      <x:c r="H2" s="93" t="str">
+        <x:v>UPDATES_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="150" customHeight="1">
+      <x:c r="A3" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B3" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C3" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D3" s="93" t="str">
+        <x:v>Table access</x:v>
+      </x:c>
+      <x:c r="E3" s="93" t="str">
+        <x:v>Configuration</x:v>
+      </x:c>
+      <x:c r="F3" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G3" s="93" t="str">
+        <x:v>Source: native</x:v>
+      </x:c>
+      <x:c r="H3" s="93" t="str">
+        <x:v>UPDATES_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="150" customHeight="1">
+      <x:c r="A4" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B4" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C4" s="93" t="str">
+        <x:v>poc_projection</x:v>
+      </x:c>
+      <x:c r="D4" s="93" t="str">
+        <x:v>Table access</x:v>
+      </x:c>
+      <x:c r="E4" s="93" t="str">
+        <x:v>Configuration</x:v>
+      </x:c>
+      <x:c r="F4" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G4" s="93" t="str">
+        <x:v>Source: database-1</x:v>
+      </x:c>
+      <x:c r="H4" s="93" t="str">
+        <x:v>READ_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="150" customHeight="1">
+      <x:c r="A5" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B5" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C5" s="93" t="str">
+        <x:v>poc_events</x:v>
+      </x:c>
+      <x:c r="D5" s="93" t="str">
+        <x:v>Table access</x:v>
+      </x:c>
+      <x:c r="E5" s="93" t="str">
+        <x:v>Configuration</x:v>
+      </x:c>
+      <x:c r="F5" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G5" s="93" t="str">
+        <x:v>Source: database-1</x:v>
+      </x:c>
+      <x:c r="H5" s="93" t="str">
+        <x:v>READ_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="150" customHeight="1">
+      <x:c r="A6" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B6" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C6" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D6" s="93" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="E6" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F6" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G6" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H6" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: Yes
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="150" customHeight="1">
+      <x:c r="A7" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B7" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C7" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D7" s="93" t="str">
+        <x:v>_EMAIL</x:v>
+      </x:c>
+      <x:c r="E7" s="93" t="str">
+        <x:v>Email</x:v>
+      </x:c>
+      <x:c r="F7" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G7" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H7" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+App formula: USEREMAIL()
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="150" customHeight="1">
+      <x:c r="A8" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B8" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C8" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D8" s="93" t="str">
+        <x:v>_NAME</x:v>
+      </x:c>
+      <x:c r="E8" s="93" t="str">
+        <x:v>Name</x:v>
+      </x:c>
+      <x:c r="F8" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G8" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H8" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+App formula: USERNAME()
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="150" customHeight="1">
+      <x:c r="A9" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B9" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C9" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D9" s="93" t="str">
+        <x:v>_LOCATION</x:v>
+      </x:c>
+      <x:c r="E9" s="93" t="str">
+        <x:v>LatLong</x:v>
+      </x:c>
+      <x:c r="F9" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G9" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H9" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="150" customHeight="1">
+      <x:c r="A10" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B10" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C10" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D10" s="93" t="str">
+        <x:v>Options Heading</x:v>
+      </x:c>
+      <x:c r="E10" s="93" t="str">
+        <x:v>Show</x:v>
+      </x:c>
+      <x:c r="F10" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G10" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H10" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: Yes
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="150" customHeight="1">
+      <x:c r="A11" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B11" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C11" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D11" s="93" t="str">
+        <x:v>Option 1</x:v>
+      </x:c>
+      <x:c r="E11" s="93" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="F11" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G11" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H11" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="150" customHeight="1">
+      <x:c r="A12" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B12" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C12" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D12" s="93" t="str">
+        <x:v>Option 2</x:v>
+      </x:c>
+      <x:c r="E12" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F12" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G12" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H12" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="150" customHeight="1">
+      <x:c r="A13" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B13" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C13" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D13" s="93" t="str">
+        <x:v>Country Option</x:v>
+      </x:c>
+      <x:c r="E13" s="93" t="str">
+        <x:v>Enum</x:v>
+      </x:c>
+      <x:c r="F13" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G13" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H13" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="150" customHeight="1">
+      <x:c r="A14" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B14" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C14" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D14" s="93" t="str">
+        <x:v>Language Option</x:v>
+      </x:c>
+      <x:c r="E14" s="93" t="str">
+        <x:v>Enum</x:v>
+      </x:c>
+      <x:c r="F14" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G14" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H14" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="150" customHeight="1">
+      <x:c r="A15" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B15" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C15" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D15" s="93" t="str">
+        <x:v>Option 5</x:v>
+      </x:c>
+      <x:c r="E15" s="93" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="F15" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G15" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H15" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="150" customHeight="1">
+      <x:c r="A16" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B16" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C16" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D16" s="93" t="str">
+        <x:v>Option 6</x:v>
+      </x:c>
+      <x:c r="E16" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F16" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G16" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H16" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="150" customHeight="1">
+      <x:c r="A17" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B17" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C17" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D17" s="93" t="str">
+        <x:v>Option 7</x:v>
+      </x:c>
+      <x:c r="E17" s="93" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="F17" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G17" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H17" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="150" customHeight="1">
+      <x:c r="A18" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B18" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C18" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D18" s="93" t="str">
+        <x:v>Option 8</x:v>
+      </x:c>
+      <x:c r="E18" s="93" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="F18" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G18" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H18" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="150" customHeight="1">
+      <x:c r="A19" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B19" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C19" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D19" s="93" t="str">
+        <x:v>Option 9</x:v>
+      </x:c>
+      <x:c r="E19" s="93" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="F19" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G19" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H19" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="150" customHeight="1">
+      <x:c r="A20" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B20" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C20" s="93" t="str">
+        <x:v>_Per User Settings</x:v>
+      </x:c>
+      <x:c r="D20" s="93" t="str">
+        <x:v>_THISUSER</x:v>
+      </x:c>
+      <x:c r="E20" s="93" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="F20" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G20" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H20" s="93" t="str">
+        <x:v>Key: Yes
+Label: No
+Read-Only: No
+Hidden: Yes
+Virtual?: No
+Initial value: onlyvalue
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="150" customHeight="1">
+      <x:c r="A21" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B21" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C21" s="93" t="str">
+        <x:v>poc_source</x:v>
+      </x:c>
+      <x:c r="D21" s="93" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="E21" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F21" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G21" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H21" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: Yes
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="150" customHeight="1">
+      <x:c r="A22" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B22" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C22" s="93" t="str">
+        <x:v>poc_source</x:v>
+      </x:c>
+      <x:c r="D22" s="93" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E22" s="93" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="F22" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G22" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H22" s="93" t="str">
+        <x:v>Key: Yes
+Label: Yes
+Read-Only: Yes
+Hidden: No
+Virtual?: No
+Initial value: UNIQUEID()
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="150" customHeight="1">
+      <x:c r="A23" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B23" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C23" s="93" t="str">
+        <x:v>poc_source</x:v>
+      </x:c>
+      <x:c r="D23" s="93" t="str">
+        <x:v>input_value</x:v>
+      </x:c>
+      <x:c r="E23" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F23" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G23" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H23" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: No
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="150" customHeight="1">
+      <x:c r="A24" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B24" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C24" s="93" t="str">
+        <x:v>poc_source</x:v>
+      </x:c>
+      <x:c r="D24" s="93" t="str">
+        <x:v>revision</x:v>
+      </x:c>
+      <x:c r="E24" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F24" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G24" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H24" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: No
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="150" customHeight="1">
+      <x:c r="A25" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B25" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C25" s="93" t="str">
+        <x:v>poc_source</x:v>
+      </x:c>
+      <x:c r="D25" s="93" t="str">
+        <x:v>Related poc_events</x:v>
+      </x:c>
+      <x:c r="E25" s="93" t="str">
+        <x:v>List</x:v>
+      </x:c>
+      <x:c r="F25" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G25" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H25" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: Yes
+Hidden: No
+Virtual?: Yes
+App formula: REF_ROWS("poc_events", "source_id")
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="150" customHeight="1">
+      <x:c r="A26" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B26" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C26" s="93" t="str">
+        <x:v>poc_projection</x:v>
+      </x:c>
+      <x:c r="D26" s="93" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="E26" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F26" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G26" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H26" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: Yes
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="150" customHeight="1">
+      <x:c r="A27" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B27" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C27" s="93" t="str">
+        <x:v>poc_projection</x:v>
+      </x:c>
+      <x:c r="D27" s="93" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E27" s="93" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="F27" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G27" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H27" s="93" t="str">
+        <x:v>Key: Yes
+Label: Yes
+Read-Only: No
+Hidden: No
+Virtual?: No
+Initial value: UNIQUEID()
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="150" customHeight="1">
+      <x:c r="A28" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B28" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C28" s="93" t="str">
+        <x:v>poc_projection</x:v>
+      </x:c>
+      <x:c r="D28" s="93" t="str">
+        <x:v>applied_revision</x:v>
+      </x:c>
+      <x:c r="E28" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F28" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G28" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H28" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: No
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="150" customHeight="1">
+      <x:c r="A29" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B29" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C29" s="93" t="str">
+        <x:v>poc_projection</x:v>
+      </x:c>
+      <x:c r="D29" s="93" t="str">
+        <x:v>derived_value</x:v>
+      </x:c>
+      <x:c r="E29" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F29" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G29" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H29" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: No
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="150" customHeight="1">
+      <x:c r="A30" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B30" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C30" s="93" t="str">
+        <x:v>poc_events</x:v>
+      </x:c>
+      <x:c r="D30" s="93" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="E30" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F30" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G30" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H30" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: Yes
+Hidden: Yes
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="150" customHeight="1">
+      <x:c r="A31" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B31" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C31" s="93" t="str">
+        <x:v>poc_events</x:v>
+      </x:c>
+      <x:c r="D31" s="93" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="E31" s="93" t="str">
+        <x:v>Text</x:v>
+      </x:c>
+      <x:c r="F31" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G31" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H31" s="93" t="str">
+        <x:v>Key: Yes
+Label: Yes
+Read-Only: No
+Hidden: No
+Virtual?: No
+Initial value: UNIQUEID()
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="150" customHeight="1">
+      <x:c r="A32" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B32" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C32" s="93" t="str">
+        <x:v>poc_events</x:v>
+      </x:c>
+      <x:c r="D32" s="93" t="str">
+        <x:v>source_id</x:v>
+      </x:c>
+      <x:c r="E32" s="93" t="str">
+        <x:v>Ref</x:v>
+      </x:c>
+      <x:c r="F32" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G32" s="93" t="str">
+        <x:v>Ref -&gt; poc_source[id]; IsAPartOf=false</x:v>
+      </x:c>
+      <x:c r="H32" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: No
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="150" customHeight="1">
+      <x:c r="A33" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B33" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C33" s="93" t="str">
+        <x:v>poc_events</x:v>
+      </x:c>
+      <x:c r="D33" s="93" t="str">
+        <x:v>revision</x:v>
+      </x:c>
+      <x:c r="E33" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F33" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G33" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H33" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: No
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="150" customHeight="1">
+      <x:c r="A34" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B34" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C34" s="93" t="str">
+        <x:v>poc_events</x:v>
+      </x:c>
+      <x:c r="D34" s="93" t="str">
+        <x:v>input_value</x:v>
+      </x:c>
+      <x:c r="E34" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F34" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G34" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H34" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: No
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="150" customHeight="1">
+      <x:c r="A35" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B35" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C35" s="93" t="str">
+        <x:v>poc_events</x:v>
+      </x:c>
+      <x:c r="D35" s="93" t="str">
+        <x:v>derived_value</x:v>
+      </x:c>
+      <x:c r="E35" s="93" t="str">
+        <x:v>Number</x:v>
+      </x:c>
+      <x:c r="F35" s="93" t="str">
+        <x:v>Test only; live appdoc reconciled</x:v>
+      </x:c>
+      <x:c r="G35" s="93" t="str">
+        <x:v>POC only; no OLTP/OLAP consumer</x:v>
+      </x:c>
+      <x:c r="H35" s="93" t="str">
+        <x:v>Key: No
+Label: No
+Read-Only: No
+Hidden: No
+Virtual?: No
+Reset on edit?: No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="150" customHeight="1">
+      <x:c r="A36" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B36" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C36" s="93" t="str">
+        <x:v>poc_source / poc_projection / poc_events</x:v>
+      </x:c>
+      <x:c r="D36" s="93" t="str">
+        <x:v>SQL key types</x:v>
+      </x:c>
+      <x:c r="E36" s="93" t="str">
+        <x:v>varchar</x:v>
+      </x:c>
+      <x:c r="F36" s="93" t="str">
+        <x:v>Test only; DDL and UI verified</x:v>
+      </x:c>
+      <x:c r="G36" s="93" t="str">
+        <x:v>Preserve exact key and Ref text; no uuid casts</x:v>
+      </x:c>
+      <x:c r="H36" s="93" t="str">
+        <x:v>source.id / projection.id / events.source_id: varchar(64)
+events.id: varchar(100)
+projection.id and events.source_id FK -&gt; source.id
+events UNIQUE(source_id, revision)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="150" customHeight="1">
+      <x:c r="A37" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B37" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C37" s="93" t="str">
+        <x:v>poc_source</x:v>
+      </x:c>
+      <x:c r="D37" s="93" t="str">
+        <x:v>AFTER UPDATE trigger</x:v>
+      </x:c>
+      <x:c r="E37" s="93" t="str">
+        <x:v>PL/pgSQL</x:v>
+      </x:c>
+      <x:c r="F37" s="93" t="str">
+        <x:v>Test only; engine + new GUI verified</x:v>
+      </x:c>
+      <x:c r="G37" s="93" t="str">
+        <x:v>One transaction changes source, projection and event</x:v>
+      </x:c>
+      <x:c r="H37" s="93" t="str">
+        <x:v>Unchanged input/revision -&gt; no-op. Otherwise revision=old+1. projection.derived_value=input_value::bigint*2; insert event id=source.id || single hyphen || revision. Negative input deliberately raises after downstream writes, rolling back the transaction. Exact SQL: scripts/cloud-sql-poc-schema.sql.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="150" customHeight="1">
+      <x:c r="A38" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B38" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C38" s="93" t="str">
+        <x:v>App</x:v>
+      </x:c>
+      <x:c r="D38" s="93" t="str">
+        <x:v>Sync settings</x:v>
+      </x:c>
+      <x:c r="E38" s="93" t="str">
+        <x:v>Configuration</x:v>
+      </x:c>
+      <x:c r="F38" s="93" t="str">
+        <x:v>Test only; UI verified before tests</x:v>
+      </x:c>
+      <x:c r="G38" s="93" t="str">
+        <x:v>Full sync required for this acceptance result</x:v>
+      </x:c>
+      <x:c r="H38" s="93" t="str">
+        <x:v>Server cache OFF; delta sync OFF; quick sync OFF; delayed sync OFF; automatic updates ON; sync on start OFF; new desktop design ON.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="150" customHeight="1">
+      <x:c r="A39" s="93" t="str">
+        <x:v>SQL POC</x:v>
+      </x:c>
+      <x:c r="B39" s="93" t="str">
+        <x:v>1.000008</x:v>
+      </x:c>
+      <x:c r="C39" s="93" t="str">
+        <x:v>App</x:v>
+      </x:c>
+      <x:c r="D39" s="93" t="str">
+        <x:v>Validation scope</x:v>
+      </x:c>
+      <x:c r="E39" s="93" t="str">
+        <x:v>Evidence</x:v>
+      </x:c>
+      <x:c r="F39" s="93" t="str">
+        <x:v>Owner acceptance pending</x:v>
+      </x:c>
+      <x:c r="G39" s="93" t="str">
+        <x:v>Results: POC_TEST_REPORT.md and ui-test-evidence.json</x:v>
+      </x:c>
+      <x:c r="H39" s="93" t="str">
+        <x:v>Uppercase and mixed-case updates, trigger propagation, parent Ref navigation and reverse related events passed. Full loan dataset key/Ref reconciliation, concurrency, offline and loan performance are pending.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4299,7 +5503,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40613c357604443c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44948d70ec54414d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14956,7 +16160,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb09b089999644e46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R333cebd994c54469"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15385,7 +16589,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c64ae7a7f954995"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac3ce967758442ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15845,7 +17049,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ba644b5b14846d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20a7c82882aa44a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22819,7 +24023,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb2f9462cb394bf4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb26f1692330943fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27438,7 +28642,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R196b4f6281b84e49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R512ac91e94294119"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27637,7 +28841,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc396ec1e9a8432c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb76306cbb864d41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29290,7 +30494,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref1d43f31d454711"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28fdf7c84b0641a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R16ef4dce4a404f59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R3a3c1dbe9cde4888"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R7d7c6d1b0b9b4855"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rf0274cd7b5cf4361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R795c4633819943b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R6a70cd4520b24fbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rad8890efd2ad4c8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R4f71724f3ba14f40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R99d46dde0e634099"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R3cb019cf2f464b6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R37b3e1a8ef934be5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rc3e951c7837740e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R1c3d80887d6444f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R2a51903f200049b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R4b18e28353fd42f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rf4457ea5ad9e4679"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R0a6b44f9bd1c426a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Ra94b83812d474397"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rec1a96e5461e41e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Racf454f55e914f95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R1e488bf945044610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R2866498f13144e6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R781c18d6bfd24003"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rd6834490d3b34c4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R5daac30fb46d4b51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R7f68816dae59450a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Rcb71592da0d84e82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -99,7 +100,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="25">
+  <x:fills count="29">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -134,6 +135,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -351,7 +372,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="114">
+  <x:cellXfs count="120">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -596,6 +617,20 @@
     <x:xf numFmtId="0" fontId="11" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2503,7 +2538,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R392b43b532d44c18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f8ff738ec7f4404"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5082,6 +5117,779 @@
       </x:c>
       <x:c r="H39" s="93" t="str">
         <x:v>Uppercase and mixed-case updates, trigger propagation, parent Ref navigation and reverse related events passed. Full loan dataset key/Ref reconciliation, concurrency, offline and loan performance are pending.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="119" t="str">
+        <x:v>Experiment</x:v>
+      </x:c>
+      <x:c r="B1" s="119" t="str">
+        <x:v>App version</x:v>
+      </x:c>
+      <x:c r="C1" s="119" t="str">
+        <x:v>Table</x:v>
+      </x:c>
+      <x:c r="D1" s="119" t="str">
+        <x:v>Column / setting</x:v>
+      </x:c>
+      <x:c r="E1" s="119" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="F1" s="119" t="str">
+        <x:v>Scope / status</x:v>
+      </x:c>
+      <x:c r="G1" s="119" t="str">
+        <x:v>Purpose / dependencies</x:v>
+      </x:c>
+      <x:c r="H1" s="119" t="str">
+        <x:v>Exact definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="55" customHeight="1">
+      <x:c r="A2" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B2" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C2" s="93" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D2" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E2" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F2" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G2" s="93" t="str">
+        <x:v>Shared native copy; source rollback 3.000064; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H2" s="93" t="str">
+        <x:v>ID=base/GhFoIWUelX4UMyCCNLda80/tables/Iya7C1Iv_z4ZmO0tyMrMme</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="55" customHeight="1">
+      <x:c r="A3" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B3" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C3" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D3" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E3" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F3" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G3" s="93" t="str">
+        <x:v>Shared native copy; source rollback 3.000064; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H3" s="93" t="str">
+        <x:v>ID=base/GhFoIWUelX4UMyCCNLda80/tables/uhIsbxFaUV4P2yCFRPUWoa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="55" customHeight="1">
+      <x:c r="A4" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B4" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C4" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D4" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E4" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F4" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G4" s="93" t="str">
+        <x:v>Shared native copy; source rollback 3.000064; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H4" s="93" t="str">
+        <x:v>ID=base/GhFoIWUelX4UMyCCNLda80/tables/TA6YmxJirY4Y2DSpa7aR17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="55" customHeight="1">
+      <x:c r="A5" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B5" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C5" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D5" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E5" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F5" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G5" s="93" t="str">
+        <x:v>Shared native copy; source rollback 3.000064; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H5" s="93" t="str">
+        <x:v>ID=base/GhFoIWUelX4UMyCCNLda80/tables/MoJ3e9N4iC4rE7kW9wLSt9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="55" customHeight="1">
+      <x:c r="A6" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B6" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C6" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D6" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E6" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F6" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G6" s="93" t="str">
+        <x:v>Shared native copy; source rollback 3.000064; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H6" s="93" t="str">
+        <x:v>ID=base/GhFoIWUelX4UMyCCNLda80/tables/3EhKRaJBK64SAsNbtGBQU1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="55" customHeight="1">
+      <x:c r="A7" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B7" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C7" s="93" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="D7" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E7" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F7" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G7" s="93" t="str">
+        <x:v>Shared native copy; source rollback 3.000064; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H7" s="93" t="str">
+        <x:v>ID=base/GhFoIWUelX4UMyCCNLda80/tables/cxkDtKcsOZ4vm4kMSHOr66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="55" customHeight="1">
+      <x:c r="A8" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B8" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C8" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D8" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E8" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F8" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G8" s="93" t="str">
+        <x:v>Shared native copy; source rollback 3.000064; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H8" s="93" t="str">
+        <x:v>ID=base/GhFoIWUelX4UMyCCNLda80/tables/MFKNswyWeK4HYkVSIutpvb</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="55" customHeight="1">
+      <x:c r="A9" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B9" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C9" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D9" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E9" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F9" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G9" s="93" t="str">
+        <x:v>Shared native copy; source rollback 3.000064; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H9" s="93" t="str">
+        <x:v>ID=base/GhFoIWUelX4UMyCCNLda80/tables/ULg9Cchxjz4oyzeQgeF-59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="55" customHeight="1">
+      <x:c r="A10" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B10" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C10" s="93" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D10" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E10" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F10" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G10" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H10" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Borrowers; READ_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="55" customHeight="1">
+      <x:c r="A11" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B11" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C11" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D11" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E11" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F11" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G11" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H11" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Loans; READ_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="55" customHeight="1">
+      <x:c r="A12" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B12" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C12" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D12" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E12" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F12" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G12" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H12" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Repayments; READ_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="55" customHeight="1">
+      <x:c r="A13" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B13" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C13" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D13" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E13" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F13" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G13" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H13" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Statistics; ALL_CHANGES</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="55" customHeight="1">
+      <x:c r="A14" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B14" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C14" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D14" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E14" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F14" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G14" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H14" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Charges; READ_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="55" customHeight="1">
+      <x:c r="A15" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B15" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C15" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D15" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E15" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F15" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G15" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H15" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Loan Assessment; ALL_CHANGES</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="55" customHeight="1">
+      <x:c r="A16" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B16" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C16" s="93" t="str">
+        <x:v>Cash Pool Contributions</x:v>
+      </x:c>
+      <x:c r="D16" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E16" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F16" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G16" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H16" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Cash Pool Contributions; ADDS_AND_UPDATES</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="55" customHeight="1">
+      <x:c r="A17" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B17" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C17" s="93" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="D17" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E17" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F17" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G17" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H17" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Partners; ALL_CHANGES</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="55" customHeight="1">
+      <x:c r="A18" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B18" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C18" s="93" t="str">
+        <x:v>Settlements</x:v>
+      </x:c>
+      <x:c r="D18" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E18" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F18" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G18" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H18" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Settlements; ALL_CHANGES</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="55" customHeight="1">
+      <x:c r="A19" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B19" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C19" s="93" t="str">
+        <x:v>Daily Analytics</x:v>
+      </x:c>
+      <x:c r="D19" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E19" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F19" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G19" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H19" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Daily Analytics; ALL_CHANGES</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="55" customHeight="1">
+      <x:c r="A20" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B20" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C20" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D20" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E20" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F20" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G20" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H20" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Payment Allocations; READ_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="55" customHeight="1">
+      <x:c r="A21" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B21" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C21" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D21" s="93" t="str">
+        <x:v>Data source / permissions</x:v>
+      </x:c>
+      <x:c r="E21" s="93" t="str">
+        <x:v>AppSheet database</x:v>
+      </x:c>
+      <x:c r="F21" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G21" s="93" t="str">
+        <x:v>Shared native copy; source rollback 1.100041; clone rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H21" s="93" t="str">
+        <x:v>Database GhFoIWUelX4UMyCCNLda80; qualifier Payments; READ_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="55" customHeight="1">
+      <x:c r="A22" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B22" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C22" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D22" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E22" s="93" t="str">
+        <x:v>Google Sheets</x:v>
+      </x:c>
+      <x:c r="F22" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G22" s="93" t="str">
+        <x:v>Separate source outside shared native database</x:v>
+      </x:c>
+      <x:c r="H22" s="93" t="str">
+        <x:v>Calendar Help Table / Sheet1; READ_ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="55" customHeight="1">
+      <x:c r="A23" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B23" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C23" s="93" t="str">
+        <x:v>Automation</x:v>
+      </x:c>
+      <x:c r="D23" s="93" t="str">
+        <x:v>Notification - New Loan Created</x:v>
+      </x:c>
+      <x:c r="E23" s="93" t="str">
+        <x:v>Bot</x:v>
+      </x:c>
+      <x:c r="F23" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G23" s="93" t="str">
+        <x:v>Prevent notifications or scheduled mutations during migration</x:v>
+      </x:c>
+      <x:c r="H23" s="93" t="str">
+        <x:v>Disabled; production unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="55" customHeight="1">
+      <x:c r="A24" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B24" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C24" s="93" t="str">
+        <x:v>Automation</x:v>
+      </x:c>
+      <x:c r="D24" s="93" t="str">
+        <x:v>Notification - Loan Closed</x:v>
+      </x:c>
+      <x:c r="E24" s="93" t="str">
+        <x:v>Bot</x:v>
+      </x:c>
+      <x:c r="F24" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G24" s="93" t="str">
+        <x:v>Prevent notifications or scheduled mutations during migration</x:v>
+      </x:c>
+      <x:c r="H24" s="93" t="str">
+        <x:v>Disabled; production unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="55" customHeight="1">
+      <x:c r="A25" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B25" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C25" s="93" t="str">
+        <x:v>Automation</x:v>
+      </x:c>
+      <x:c r="D25" s="93" t="str">
+        <x:v>Notification - Charge Received</x:v>
+      </x:c>
+      <x:c r="E25" s="93" t="str">
+        <x:v>Bot</x:v>
+      </x:c>
+      <x:c r="F25" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G25" s="93" t="str">
+        <x:v>Prevent notifications or scheduled mutations during migration</x:v>
+      </x:c>
+      <x:c r="H25" s="93" t="str">
+        <x:v>Disabled; production unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="55" customHeight="1">
+      <x:c r="A26" s="93" t="str">
+        <x:v>OLTP trial</x:v>
+      </x:c>
+      <x:c r="B26" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C26" s="93" t="str">
+        <x:v>Automation</x:v>
+      </x:c>
+      <x:c r="D26" s="93" t="str">
+        <x:v>Generate Daily Charges</x:v>
+      </x:c>
+      <x:c r="E26" s="93" t="str">
+        <x:v>Bot</x:v>
+      </x:c>
+      <x:c r="F26" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G26" s="93" t="str">
+        <x:v>Prevent notifications or scheduled mutations during migration</x:v>
+      </x:c>
+      <x:c r="H26" s="93" t="str">
+        <x:v>Disabled; production unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="55" customHeight="1">
+      <x:c r="A27" s="93" t="str">
+        <x:v>OLAP trial</x:v>
+      </x:c>
+      <x:c r="B27" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C27" s="93" t="str">
+        <x:v>Automation</x:v>
+      </x:c>
+      <x:c r="D27" s="93" t="str">
+        <x:v>Refresh Daily Analytics Daily 2</x:v>
+      </x:c>
+      <x:c r="E27" s="93" t="str">
+        <x:v>Bot</x:v>
+      </x:c>
+      <x:c r="F27" s="93" t="str">
+        <x:v>DELETED by owner request; historical configuration only</x:v>
+      </x:c>
+      <x:c r="G27" s="93" t="str">
+        <x:v>Other two bots already disabled</x:v>
+      </x:c>
+      <x:c r="H27" s="93" t="str">
+        <x:v>All three OLAP bots disabled; production unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="55" customHeight="1">
+      <x:c r="A28" s="93" t="str">
+        <x:v>SQL POC cleanup</x:v>
+      </x:c>
+      <x:c r="B28" s="93" t="str">
+        <x:v>Historical</x:v>
+      </x:c>
+      <x:c r="C28" s="93" t="str">
+        <x:v>All three synthetic POC tables</x:v>
+      </x:c>
+      <x:c r="D28" s="93" t="str">
+        <x:v>Backend deleted</x:v>
+      </x:c>
+      <x:c r="E28" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F28" s="93" t="str">
+        <x:v>DELETED by owner request</x:v>
+      </x:c>
+      <x:c r="G28" s="93" t="str">
+        <x:v>Existing SQL Sync POC app remains; backend unavailable</x:v>
+      </x:c>
+      <x:c r="H28" s="93" t="str">
+        <x:v>appsheet-pg-test-20260914 deletion confirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="55" customHeight="1">
+      <x:c r="A29" s="93" t="str">
+        <x:v>Fresh setup</x:v>
+      </x:c>
+      <x:c r="B29" s="93" t="str">
+        <x:v>Not created</x:v>
+      </x:c>
+      <x:c r="C29" s="93" t="str">
+        <x:v>No tables yet</x:v>
+      </x:c>
+      <x:c r="D29" s="93" t="str">
+        <x:v>Instance draft</x:v>
+      </x:c>
+      <x:c r="E29" s="93" t="str">
+        <x:v>PostgreSQL 18</x:v>
+      </x:c>
+      <x:c r="F29" s="93" t="str">
+        <x:v>UNSUBMITTED; password handoff pending</x:v>
+      </x:c>
+      <x:c r="G29" s="93" t="str">
+        <x:v>Copy original app using documented SQL copy workflow</x:v>
+      </x:c>
+      <x:c r="H29" s="93" t="str">
+        <x:v>appsheet-pg-prod-20260914; db-f1-micro; Singapore; single zone; 10 GB HDD; public IP; SSL-only</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5503,7 +6311,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44948d70ec54414d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaccfb212f8b4af0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16160,7 +16968,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R333cebd994c54469"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R248039cf41224928"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16589,7 +17397,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac3ce967758442ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb21a841f4df4525"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17049,7 +17857,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20a7c82882aa44a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64c3ef939b93434c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24023,7 +24831,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb26f1692330943fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R453477b2163d4927"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28642,7 +29450,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R512ac91e94294119"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fd05bfb46214694"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28841,7 +29649,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb76306cbb864d41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc9f6aa42dff461d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30494,7 +31302,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28fdf7c84b0641a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46d825d5fdc443fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R2a51903f200049b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R4b18e28353fd42f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rf4457ea5ad9e4679"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R0a6b44f9bd1c426a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Ra94b83812d474397"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rec1a96e5461e41e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Racf454f55e914f95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R1e488bf945044610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R2866498f13144e6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R781c18d6bfd24003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rd6834490d3b34c4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R5daac30fb46d4b51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R7f68816dae59450a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Rcb71592da0d84e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R56e4083ab8794a59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R72ea041642594fba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R6019169fab574fc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R4de7abfc3f744cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R52b4144bae784889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R171dc5013b994a9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rcb0e8bfa24fd491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R0c253c55837b4300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rdb3ada79839b4d29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R60d8610f8df043ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R8e3c3f92534b414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R05e2c3a06e924062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R797cd80da9e44298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Rcb8a72f1cfae4857"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -100,7 +100,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="30">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -135,6 +135,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -372,7 +377,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="120">
+  <x:cellXfs count="121">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -631,6 +636,9 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2538,7 +2546,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f8ff738ec7f4404"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R744e30cf91c94f45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5139,28 +5147,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="119" t="str">
+      <x:c r="A1" s="120" t="str">
         <x:v>Experiment</x:v>
       </x:c>
-      <x:c r="B1" s="119" t="str">
+      <x:c r="B1" s="120" t="str">
         <x:v>App version</x:v>
       </x:c>
-      <x:c r="C1" s="119" t="str">
+      <x:c r="C1" s="120" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="D1" s="119" t="str">
+      <x:c r="D1" s="120" t="str">
         <x:v>Column / setting</x:v>
       </x:c>
-      <x:c r="E1" s="119" t="str">
+      <x:c r="E1" s="120" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F1" s="119" t="str">
+      <x:c r="F1" s="120" t="str">
         <x:v>Scope / status</x:v>
       </x:c>
-      <x:c r="G1" s="119" t="str">
+      <x:c r="G1" s="120" t="str">
         <x:v>Purpose / dependencies</x:v>
       </x:c>
-      <x:c r="H1" s="119" t="str">
+      <x:c r="H1" s="120" t="str">
         <x:v>Exact definition</x:v>
       </x:c>
     </x:row>
@@ -5883,13 +5891,377 @@
         <x:v>PostgreSQL 18</x:v>
       </x:c>
       <x:c r="F29" s="93" t="str">
-        <x:v>UNSUBMITTED; password handoff pending</x:v>
+        <x:v>CREATED; official copy transfer blocked</x:v>
       </x:c>
       <x:c r="G29" s="93" t="str">
         <x:v>Copy original app using documented SQL copy workflow</x:v>
       </x:c>
       <x:c r="H29" s="93" t="str">
-        <x:v>appsheet-pg-prod-20260914; db-f1-micro; Singapore; single zone; 10 GB HDD; public IP; SSL-only</x:v>
+        <x:v>34.21.174.215; loan_manager_prod; 13 empty SQL tables; SSL database-2 verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="55" customHeight="1">
+      <x:c r="A30" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B30" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C30" s="93" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D30" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E30" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F30" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G30" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H30" s="93" t="str">
+        <x:v>public."Borrowers"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="55" customHeight="1">
+      <x:c r="A31" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B31" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C31" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D31" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E31" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F31" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G31" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H31" s="93" t="str">
+        <x:v>public."Calendar"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="55" customHeight="1">
+      <x:c r="A32" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B32" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C32" s="93" t="str">
+        <x:v>Cash Pool Contributions</x:v>
+      </x:c>
+      <x:c r="D32" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E32" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F32" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G32" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H32" s="93" t="str">
+        <x:v>public."Cash Pool Contributions"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="55" customHeight="1">
+      <x:c r="A33" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B33" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C33" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D33" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E33" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F33" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G33" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H33" s="93" t="str">
+        <x:v>public."Charges"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="55" customHeight="1">
+      <x:c r="A34" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B34" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C34" s="93" t="str">
+        <x:v>Daily Analytics</x:v>
+      </x:c>
+      <x:c r="D34" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E34" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F34" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G34" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H34" s="93" t="str">
+        <x:v>public."Daily Analytics"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="55" customHeight="1">
+      <x:c r="A35" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B35" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C35" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D35" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E35" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F35" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G35" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H35" s="93" t="str">
+        <x:v>public."Loan Assessment"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="55" customHeight="1">
+      <x:c r="A36" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B36" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C36" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D36" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E36" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F36" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G36" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H36" s="93" t="str">
+        <x:v>public."Loans"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="55" customHeight="1">
+      <x:c r="A37" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B37" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C37" s="93" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="D37" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E37" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F37" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G37" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H37" s="93" t="str">
+        <x:v>public."Partners"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="55" customHeight="1">
+      <x:c r="A38" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B38" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C38" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D38" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E38" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F38" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G38" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H38" s="93" t="str">
+        <x:v>public."Payment Allocations"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="55" customHeight="1">
+      <x:c r="A39" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B39" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C39" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D39" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E39" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F39" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G39" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H39" s="93" t="str">
+        <x:v>public."Payments"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="55" customHeight="1">
+      <x:c r="A40" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B40" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C40" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D40" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E40" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F40" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G40" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H40" s="93" t="str">
+        <x:v>public."Repayments"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="55" customHeight="1">
+      <x:c r="A41" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B41" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C41" s="93" t="str">
+        <x:v>Settlements</x:v>
+      </x:c>
+      <x:c r="D41" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E41" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F41" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G41" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H41" s="93" t="str">
+        <x:v>public."Settlements"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="55" customHeight="1">
+      <x:c r="A42" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B42" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C42" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D42" s="93" t="str">
+        <x:v>SQL transfer status</x:v>
+      </x:c>
+      <x:c r="E42" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F42" s="93" t="str">
+        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+      </x:c>
+      <x:c r="G42" s="93" t="str">
+        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+      </x:c>
+      <x:c r="H42" s="93" t="str">
+        <x:v>public."Statistics"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="55" customHeight="1">
+      <x:c r="A43" s="93" t="str">
+        <x:v>Clean restart</x:v>
+      </x:c>
+      <x:c r="B43" s="93" t="str">
+        <x:v>1.000003</x:v>
+      </x:c>
+      <x:c r="C43" s="93" t="str">
+        <x:v>Automation</x:v>
+      </x:c>
+      <x:c r="D43" s="93" t="str">
+        <x:v>Refresh Daily Analytics Daily 2</x:v>
+      </x:c>
+      <x:c r="E43" s="93" t="str">
+        <x:v>Bot</x:v>
+      </x:c>
+      <x:c r="F43" s="93" t="str">
+        <x:v>DISABLED in copied app</x:v>
+      </x:c>
+      <x:c r="G43" s="93" t="str">
+        <x:v>Prevent scheduled writes to original sources; rollback 1.000002</x:v>
+      </x:c>
+      <x:c r="H43" s="93" t="str">
+        <x:v>Disabled; Refresh Daily Analytics Daily already disabled</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6311,7 +6683,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaccfb212f8b4af0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5c9fe4033dd4b44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16968,7 +17340,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R248039cf41224928"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15cf8c62969a4ebf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17397,7 +17769,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb21a841f4df4525"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67018b76133e4a93"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17857,7 +18229,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64c3ef939b93434c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ca5c585eae54427"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24831,7 +25203,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R453477b2163d4927"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5a6382b59f34226"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29450,7 +29822,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fd05bfb46214694"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16beae1c0aaa4d14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29649,7 +30021,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc9f6aa42dff461d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9493056924574cf1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31302,7 +31674,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46d825d5fdc443fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f64535a51d64121"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R56e4083ab8794a59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R72ea041642594fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R6019169fab574fc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R4de7abfc3f744cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R52b4144bae784889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R171dc5013b994a9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rcb0e8bfa24fd491d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R0c253c55837b4300"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rdb3ada79839b4d29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R60d8610f8df043ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R8e3c3f92534b414e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R05e2c3a06e924062"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R797cd80da9e44298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Rcb8a72f1cfae4857"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Re00d28e4307f4496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rca873092791f4db3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rfd61cd50b99442cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R7f273980703b4f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R669fcf656b4e4bdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R593bbe8299d64d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R461adc2bbb9f4c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Rcbf11a1877f44017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R56dfa8d28a4d4fb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rc97794ccaaba4d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rc7b7f5d5e04e4dc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R63bb829c1f9f4c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R1398610c05a64cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R473eea63780f4761"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -100,7 +100,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="30">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -135,6 +135,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -377,7 +382,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="121">
+  <x:cellXfs count="122">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -639,6 +644,9 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2546,7 +2554,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R744e30cf91c94f45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2708053733d48c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5147,28 +5155,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="120" t="str">
+      <x:c r="A1" s="121" t="str">
         <x:v>Experiment</x:v>
       </x:c>
-      <x:c r="B1" s="120" t="str">
+      <x:c r="B1" s="121" t="str">
         <x:v>App version</x:v>
       </x:c>
-      <x:c r="C1" s="120" t="str">
+      <x:c r="C1" s="121" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="D1" s="120" t="str">
+      <x:c r="D1" s="121" t="str">
         <x:v>Column / setting</x:v>
       </x:c>
-      <x:c r="E1" s="120" t="str">
+      <x:c r="E1" s="121" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F1" s="120" t="str">
+      <x:c r="F1" s="121" t="str">
         <x:v>Scope / status</x:v>
       </x:c>
-      <x:c r="G1" s="120" t="str">
+      <x:c r="G1" s="121" t="str">
         <x:v>Purpose / dependencies</x:v>
       </x:c>
-      <x:c r="H1" s="120" t="str">
+      <x:c r="H1" s="121" t="str">
         <x:v>Exact definition</x:v>
       </x:c>
     </x:row>
@@ -6217,7 +6225,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B42" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000004</x:v>
       </x:c>
       <x:c r="C42" s="93" t="str">
         <x:v>Statistics</x:v>
@@ -6229,13 +6237,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F42" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>MANUAL COPY PASSED; 1 exact row</x:v>
       </x:c>
       <x:c r="G42" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>39 Statistics column configurations preserved; eight dashboard metrics match; other tables still original</x:v>
       </x:c>
       <x:c r="H42" s="93" t="str">
-        <x:v>public."Statistics"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>database-2; Source Path Statistics; Table=public.Statistics__Statistics</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="55" customHeight="1">
@@ -6262,6 +6270,58 @@
       </x:c>
       <x:c r="H43" s="93" t="str">
         <x:v>Disabled; Refresh Daily Analytics Daily already disabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="55" customHeight="1">
+      <x:c r="A44" s="93" t="str">
+        <x:v>Statistics manual</x:v>
+      </x:c>
+      <x:c r="B44" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C44" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D44" s="93" t="str">
+        <x:v>Row ID</x:v>
+      </x:c>
+      <x:c r="E44" s="93" t="str">
+        <x:v>Text / SQL text</x:v>
+      </x:c>
+      <x:c r="F44" s="93" t="str">
+        <x:v>Physical key; exact source key copied</x:v>
+      </x:c>
+      <x:c r="G44" s="93" t="str">
+        <x:v>Not nullable; no SQL default; unchanged app settings</x:v>
+      </x:c>
+      <x:c r="H44" s="93" t="str">
+        <x:v>Key Yes; Initial value UNIQUEID("PackedUUID"); Read-Only Yes; no normalization</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="55" customHeight="1">
+      <x:c r="A45" s="93" t="str">
+        <x:v>Statistics manual</x:v>
+      </x:c>
+      <x:c r="B45" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C45" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D45" s="93" t="str">
+        <x:v>Statistics ID</x:v>
+      </x:c>
+      <x:c r="E45" s="93" t="str">
+        <x:v>Text / SQL text</x:v>
+      </x:c>
+      <x:c r="F45" s="93" t="str">
+        <x:v>Physical label; MAIN copied</x:v>
+      </x:c>
+      <x:c r="G45" s="93" t="str">
+        <x:v>Nullable; no SQL default; unchanged app settings</x:v>
+      </x:c>
+      <x:c r="H45" s="93" t="str">
+        <x:v>Label Yes; Read-Only No; one row</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6683,7 +6743,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5c9fe4033dd4b44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96c3d0ef9da743b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17340,7 +17400,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15cf8c62969a4ebf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8d9f438897c453f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17769,7 +17829,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67018b76133e4a93"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576798a7d0bf4450"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18229,7 +18289,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ca5c585eae54427"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbe18dbd49a74e09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25203,7 +25263,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5a6382b59f34226"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2308807ce4d84f18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29822,7 +29882,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16beae1c0aaa4d14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R829a6bbc7b6b464e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30021,7 +30081,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9493056924574cf1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf459737b2ac45b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31674,7 +31734,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f64535a51d64121"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R126a37544b1b4181"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Re00d28e4307f4496"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rca873092791f4db3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rfd61cd50b99442cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R7f273980703b4f37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R669fcf656b4e4bdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R593bbe8299d64d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R461adc2bbb9f4c13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Rcbf11a1877f44017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R56dfa8d28a4d4fb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rc97794ccaaba4d3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rc7b7f5d5e04e4dc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R63bb829c1f9f4c15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R1398610c05a64cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R473eea63780f4761"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0cf92f2c00ff4e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rf66215da1caf44f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rfbf9b2e2e07243fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rf9557621dbef4d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R1a0b3883428b4bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rf13958d1aff0438f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R3cd6c6a1ef3c4c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R8fa53bf809984729"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Ra3b9441c805d4311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rf16b15d151074b5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rbe2c42ac0bc3428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R84861ec9994d41f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="Rf31c3c015d484f7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Rf8ba14654f974d83"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -100,7 +100,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="31">
+  <x:fills count="32">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -135,6 +135,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -382,7 +387,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="122">
+  <x:cellXfs count="123">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -647,6 +652,9 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2554,7 +2562,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2708053733d48c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55aa89467b404526"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5155,28 +5163,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="121" t="str">
+      <x:c r="A1" s="122" t="str">
         <x:v>Experiment</x:v>
       </x:c>
-      <x:c r="B1" s="121" t="str">
+      <x:c r="B1" s="122" t="str">
         <x:v>App version</x:v>
       </x:c>
-      <x:c r="C1" s="121" t="str">
+      <x:c r="C1" s="122" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="D1" s="121" t="str">
+      <x:c r="D1" s="122" t="str">
         <x:v>Column / setting</x:v>
       </x:c>
-      <x:c r="E1" s="121" t="str">
+      <x:c r="E1" s="122" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F1" s="121" t="str">
+      <x:c r="F1" s="122" t="str">
         <x:v>Scope / status</x:v>
       </x:c>
-      <x:c r="G1" s="121" t="str">
+      <x:c r="G1" s="122" t="str">
         <x:v>Purpose / dependencies</x:v>
       </x:c>
-      <x:c r="H1" s="121" t="str">
+      <x:c r="H1" s="122" t="str">
         <x:v>Exact definition</x:v>
       </x:c>
     </x:row>
@@ -5913,7 +5921,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B30" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C30" s="93" t="str">
         <x:v>Borrowers</x:v>
@@ -5925,13 +5933,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F30" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 29 rows</x:v>
       </x:c>
       <x:c r="G30" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H30" s="93" t="str">
-        <x:v>public."Borrowers"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Borrowers"; 11 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="55" customHeight="1">
@@ -5965,7 +5973,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B32" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C32" s="93" t="str">
         <x:v>Cash Pool Contributions</x:v>
@@ -5977,13 +5985,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F32" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 5 rows</x:v>
       </x:c>
       <x:c r="G32" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H32" s="93" t="str">
-        <x:v>public."Cash Pool Contributions"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Cash Pool Contributions"; 6 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="55" customHeight="1">
@@ -5991,7 +5999,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B33" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C33" s="93" t="str">
         <x:v>Charges</x:v>
@@ -6003,13 +6011,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F33" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 745 rows</x:v>
       </x:c>
       <x:c r="G33" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H33" s="93" t="str">
-        <x:v>public."Charges"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Charges"; 6 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="55" customHeight="1">
@@ -6017,7 +6025,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B34" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C34" s="93" t="str">
         <x:v>Daily Analytics</x:v>
@@ -6029,13 +6037,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F34" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 41 rows</x:v>
       </x:c>
       <x:c r="G34" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H34" s="93" t="str">
-        <x:v>public."Daily Analytics"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Daily Analytics"; 16 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="55" customHeight="1">
@@ -6043,7 +6051,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B35" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C35" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -6055,13 +6063,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F35" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 1 rows</x:v>
       </x:c>
       <x:c r="G35" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H35" s="93" t="str">
-        <x:v>public."Loan Assessment"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Loan Assessment"; 5 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="55" customHeight="1">
@@ -6069,7 +6077,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B36" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C36" s="93" t="str">
         <x:v>Loans</x:v>
@@ -6081,13 +6089,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F36" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 62 rows</x:v>
       </x:c>
       <x:c r="G36" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H36" s="93" t="str">
-        <x:v>public."Loans"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Loans"; 20 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="55" customHeight="1">
@@ -6095,7 +6103,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B37" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C37" s="93" t="str">
         <x:v>Partners</x:v>
@@ -6107,13 +6115,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F37" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 2 rows</x:v>
       </x:c>
       <x:c r="G37" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H37" s="93" t="str">
-        <x:v>public."Partners"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Partners"; 7 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="55" customHeight="1">
@@ -6121,7 +6129,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B38" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C38" s="93" t="str">
         <x:v>Payment Allocations</x:v>
@@ -6133,13 +6141,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F38" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 263 rows</x:v>
       </x:c>
       <x:c r="G38" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H38" s="93" t="str">
-        <x:v>public."Payment Allocations"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Payment Allocations"; 13 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="55" customHeight="1">
@@ -6147,7 +6155,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B39" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C39" s="93" t="str">
         <x:v>Payments</x:v>
@@ -6159,13 +6167,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F39" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 140 rows</x:v>
       </x:c>
       <x:c r="G39" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H39" s="93" t="str">
-        <x:v>public."Payments"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Payments"; 13 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="55" customHeight="1">
@@ -6173,7 +6181,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B40" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C40" s="93" t="str">
         <x:v>Repayments</x:v>
@@ -6185,13 +6193,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F40" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 644 rows</x:v>
       </x:c>
       <x:c r="G40" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H40" s="93" t="str">
-        <x:v>public."Repayments"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Repayments"; 10 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="55" customHeight="1">
@@ -6199,7 +6207,7 @@
         <x:v>Clean restart</x:v>
       </x:c>
       <x:c r="B41" s="93" t="str">
-        <x:v>1.000003</x:v>
+        <x:v>1.000007</x:v>
       </x:c>
       <x:c r="C41" s="93" t="str">
         <x:v>Settlements</x:v>
@@ -6211,13 +6219,13 @@
         <x:v>PostgreSQL table</x:v>
       </x:c>
       <x:c r="F41" s="93" t="str">
-        <x:v>CREATED; 0 rows; not used by copied app</x:v>
+        <x:v>COPIED AND VERIFIED; 2 rows</x:v>
       </x:c>
       <x:c r="G41" s="93" t="str">
-        <x:v>Schema types and data correctness not reconciled; preserve for diagnosis</x:v>
+        <x:v>Trial now reads SQL; all stored fields and related membership verified</x:v>
       </x:c>
       <x:c r="H41" s="93" t="str">
-        <x:v>public."Settlements"; app 494cd013-0d9b-482f-9559-c9d83059de91 still uses original data sources</x:v>
+        <x:v>public."Settlements"; 7 physical columns; exact keys and all fields matched</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="55" customHeight="1">
@@ -6322,6 +6330,344 @@
       </x:c>
       <x:c r="H45" s="93" t="str">
         <x:v>Label Yes; Read-Only No; one row</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="55" customHeight="1">
+      <x:c r="A46" s="93" t="str">
+        <x:v>Master switch</x:v>
+      </x:c>
+      <x:c r="B46" s="93" t="str">
+        <x:v>1.000006</x:v>
+      </x:c>
+      <x:c r="C46" s="93" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D46" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E46" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F46" s="93" t="str">
+        <x:v>READ_ONLY</x:v>
+      </x:c>
+      <x:c r="G46" s="93" t="str">
+        <x:v>Trial only; existing schema, Refs, slices and calculations preserved</x:v>
+      </x:c>
+      <x:c r="H46" s="93" t="str">
+        <x:v>database-2; Source Path Borrowers; Table=public.Borrowers__Borrowers</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="55" customHeight="1">
+      <x:c r="A47" s="93" t="str">
+        <x:v>Master switch</x:v>
+      </x:c>
+      <x:c r="B47" s="93" t="str">
+        <x:v>1.000006</x:v>
+      </x:c>
+      <x:c r="C47" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D47" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E47" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F47" s="93" t="str">
+        <x:v>READ_ONLY</x:v>
+      </x:c>
+      <x:c r="G47" s="93" t="str">
+        <x:v>Trial only; existing schema, Refs, slices and calculations preserved</x:v>
+      </x:c>
+      <x:c r="H47" s="93" t="str">
+        <x:v>database-2; Source Path Loans; Table=public.Loans__Loans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="55" customHeight="1">
+      <x:c r="A48" s="93" t="str">
+        <x:v>Master switch</x:v>
+      </x:c>
+      <x:c r="B48" s="93" t="str">
+        <x:v>1.000006</x:v>
+      </x:c>
+      <x:c r="C48" s="93" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="D48" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E48" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F48" s="93" t="str">
+        <x:v>ALL_CHANGES</x:v>
+      </x:c>
+      <x:c r="G48" s="93" t="str">
+        <x:v>Trial only; existing schema, Refs, slices and calculations preserved</x:v>
+      </x:c>
+      <x:c r="H48" s="93" t="str">
+        <x:v>database-2; Source Path Partners; Table=public.Partners__Partners</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="55" customHeight="1">
+      <x:c r="A49" s="93" t="str">
+        <x:v>Master switch</x:v>
+      </x:c>
+      <x:c r="B49" s="93" t="str">
+        <x:v>1.000005</x:v>
+      </x:c>
+      <x:c r="C49" s="93" t="str">
+        <x:v>Trial app</x:v>
+      </x:c>
+      <x:c r="D49" s="93" t="str">
+        <x:v>Cloud API</x:v>
+      </x:c>
+      <x:c r="E49" s="93" t="str">
+        <x:v>Integration</x:v>
+      </x:c>
+      <x:c r="F49" s="93" t="str">
+        <x:v>ENABLED with explicit owner confirmation</x:v>
+      </x:c>
+      <x:c r="G49" s="93" t="str">
+        <x:v>Extraction script uses Find only; access key itself is not read-only</x:v>
+      </x:c>
+      <x:c r="H49" s="93" t="str">
+        <x:v>Key and raw extracts stored outside Git; original app API settings unchanged</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="55" customHeight="1">
+      <x:c r="A50" s="93" t="str">
+        <x:v>Remaining switch</x:v>
+      </x:c>
+      <x:c r="B50" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C50" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D50" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E50" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F50" s="93" t="str">
+        <x:v>READ_ONLY</x:v>
+      </x:c>
+      <x:c r="G50" s="93" t="str">
+        <x:v>Trial only; schema and formulas unchanged</x:v>
+      </x:c>
+      <x:c r="H50" s="93" t="str">
+        <x:v>database-2; Source Path Repayments; Table=public.Repayments__Repayments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="55" customHeight="1">
+      <x:c r="A51" s="93" t="str">
+        <x:v>Remaining switch</x:v>
+      </x:c>
+      <x:c r="B51" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C51" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D51" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E51" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F51" s="93" t="str">
+        <x:v>READ_ONLY</x:v>
+      </x:c>
+      <x:c r="G51" s="93" t="str">
+        <x:v>Trial only; schema and formulas unchanged</x:v>
+      </x:c>
+      <x:c r="H51" s="93" t="str">
+        <x:v>database-2; Source Path Charges; Table=public.Charges__Charges</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="55" customHeight="1">
+      <x:c r="A52" s="93" t="str">
+        <x:v>Remaining switch</x:v>
+      </x:c>
+      <x:c r="B52" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C52" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D52" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E52" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F52" s="93" t="str">
+        <x:v>ALL_CHANGES</x:v>
+      </x:c>
+      <x:c r="G52" s="93" t="str">
+        <x:v>Trial only; schema and formulas unchanged</x:v>
+      </x:c>
+      <x:c r="H52" s="93" t="str">
+        <x:v>database-2; Source Path Loan Assessment; Table=public.Loan Assessment__Loan Assessment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="55" customHeight="1">
+      <x:c r="A53" s="93" t="str">
+        <x:v>Remaining switch</x:v>
+      </x:c>
+      <x:c r="B53" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C53" s="93" t="str">
+        <x:v>Cash Pool Contributions</x:v>
+      </x:c>
+      <x:c r="D53" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E53" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F53" s="93" t="str">
+        <x:v>ADDS_AND_UPDATES</x:v>
+      </x:c>
+      <x:c r="G53" s="93" t="str">
+        <x:v>Trial only; schema and formulas unchanged</x:v>
+      </x:c>
+      <x:c r="H53" s="93" t="str">
+        <x:v>database-2; Source Path Cash Pool Contributions; Table=public.Cash Pool Contributions__Cash Pool Contributions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="55" customHeight="1">
+      <x:c r="A54" s="93" t="str">
+        <x:v>Remaining switch</x:v>
+      </x:c>
+      <x:c r="B54" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C54" s="93" t="str">
+        <x:v>Settlements</x:v>
+      </x:c>
+      <x:c r="D54" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E54" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F54" s="93" t="str">
+        <x:v>ALL_CHANGES</x:v>
+      </x:c>
+      <x:c r="G54" s="93" t="str">
+        <x:v>Trial only; schema and formulas unchanged</x:v>
+      </x:c>
+      <x:c r="H54" s="93" t="str">
+        <x:v>database-2; Source Path Settlements; Table=public.Settlements__Settlements</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="55" customHeight="1">
+      <x:c r="A55" s="93" t="str">
+        <x:v>Remaining switch</x:v>
+      </x:c>
+      <x:c r="B55" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C55" s="93" t="str">
+        <x:v>Daily Analytics</x:v>
+      </x:c>
+      <x:c r="D55" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E55" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F55" s="93" t="str">
+        <x:v>ALL_CHANGES</x:v>
+      </x:c>
+      <x:c r="G55" s="93" t="str">
+        <x:v>Trial only; schema and formulas unchanged</x:v>
+      </x:c>
+      <x:c r="H55" s="93" t="str">
+        <x:v>database-2; Source Path Daily Analytics; Table=public.Daily Analytics__Daily Analytics</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="55" customHeight="1">
+      <x:c r="A56" s="93" t="str">
+        <x:v>Remaining switch</x:v>
+      </x:c>
+      <x:c r="B56" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C56" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D56" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E56" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F56" s="93" t="str">
+        <x:v>READ_ONLY</x:v>
+      </x:c>
+      <x:c r="G56" s="93" t="str">
+        <x:v>Trial only; schema and formulas unchanged</x:v>
+      </x:c>
+      <x:c r="H56" s="93" t="str">
+        <x:v>database-2; Source Path Payment Allocations; Table=public.Payment Allocations__Payment Allocations</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="55" customHeight="1">
+      <x:c r="A57" s="93" t="str">
+        <x:v>Remaining switch</x:v>
+      </x:c>
+      <x:c r="B57" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C57" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D57" s="93" t="str">
+        <x:v>Source binding</x:v>
+      </x:c>
+      <x:c r="E57" s="93" t="str">
+        <x:v>PostgreSQL table</x:v>
+      </x:c>
+      <x:c r="F57" s="93" t="str">
+        <x:v>READ_ONLY</x:v>
+      </x:c>
+      <x:c r="G57" s="93" t="str">
+        <x:v>Trial only; schema and formulas unchanged</x:v>
+      </x:c>
+      <x:c r="H57" s="93" t="str">
+        <x:v>database-2; Source Path Payments; Table=public.Payments__Payments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="55" customHeight="1">
+      <x:c r="A58" s="93" t="str">
+        <x:v>Remaining switch</x:v>
+      </x:c>
+      <x:c r="B58" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C58" s="93" t="str">
+        <x:v>Charges / Repayments</x:v>
+      </x:c>
+      <x:c r="D58" s="93" t="str">
+        <x:v>Provider row order</x:v>
+      </x:c>
+      <x:c r="E58" s="93" t="str">
+        <x:v>System metadata</x:v>
+      </x:c>
+      <x:c r="F58" s="93" t="str">
+        <x:v>201 Charges and 144 Repayments row numbers changed</x:v>
+      </x:c>
+      <x:c r="G58" s="93" t="str">
+        <x:v>Business values unchanged; 4 related lists reordered with identical membership</x:v>
+      </x:c>
+      <x:c r="H58" s="93" t="str">
+        <x:v>Never treat _RowNumber or unsorted REF_ROWS order as stable; validate write workflows separately</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6743,7 +7089,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96c3d0ef9da743b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06d63c999d584a27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17400,7 +17746,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8d9f438897c453f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree75edcddda04939"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17829,7 +18175,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576798a7d0bf4450"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re25b44cc55da45d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18289,7 +18635,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbe18dbd49a74e09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30fe6472ce884c45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25263,7 +25609,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2308807ce4d84f18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabef0a776c244b82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29882,7 +30228,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R829a6bbc7b6b464e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18aa1fe2329a49a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30081,7 +30427,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf459737b2ac45b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf352d63251904d05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31734,7 +32080,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R126a37544b1b4181"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7097c9961c0d45d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R0cf92f2c00ff4e1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rf66215da1caf44f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rfbf9b2e2e07243fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rf9557621dbef4d0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R1a0b3883428b4bde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rf13958d1aff0438f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R3cd6c6a1ef3c4c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R8fa53bf809984729"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Ra3b9441c805d4311"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rf16b15d151074b5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rbe2c42ac0bc3428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R84861ec9994d41f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="Rf31c3c015d484f7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Rf8ba14654f974d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc8a1b42326d94b1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R330d00b3f1f04219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Ra2d90ba617ba4459"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rb62581c186ff4e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rcafc24c049cd4ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rc3cebf60981b453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R1d6ca97856a84b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R82cabff2644e4d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rfd2096e1cabb4fef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rb53e77ec525b4f3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Red02d9a3a6794ff9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R4292b49d83b24e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R805f2d64b5214280"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Ra3efeb3eb4894156"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -100,7 +100,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="32">
+  <x:fills count="33">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -135,6 +135,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -387,7 +392,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="123">
+  <x:cellXfs count="124">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -655,6 +660,9 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2562,7 +2570,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55aa89467b404526"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d08b96d50c14684"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5163,28 +5171,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="122" t="str">
+      <x:c r="A1" s="123" t="str">
         <x:v>Experiment</x:v>
       </x:c>
-      <x:c r="B1" s="122" t="str">
+      <x:c r="B1" s="123" t="str">
         <x:v>App version</x:v>
       </x:c>
-      <x:c r="C1" s="122" t="str">
+      <x:c r="C1" s="123" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="D1" s="122" t="str">
+      <x:c r="D1" s="123" t="str">
         <x:v>Column / setting</x:v>
       </x:c>
-      <x:c r="E1" s="122" t="str">
+      <x:c r="E1" s="123" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F1" s="122" t="str">
+      <x:c r="F1" s="123" t="str">
         <x:v>Scope / status</x:v>
       </x:c>
-      <x:c r="G1" s="122" t="str">
+      <x:c r="G1" s="123" t="str">
         <x:v>Purpose / dependencies</x:v>
       </x:c>
-      <x:c r="H1" s="122" t="str">
+      <x:c r="H1" s="123" t="str">
         <x:v>Exact definition</x:v>
       </x:c>
     </x:row>
@@ -6668,6 +6676,370 @@
       </x:c>
       <x:c r="H58" s="93" t="str">
         <x:v>Never treat _RowNumber or unsorted REF_ROWS order as stable; validate write workflows separately</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="55" customHeight="1">
+      <x:c r="A59" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B59" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C59" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D59" s="93" t="str">
+        <x:v>Ref Borrowers</x:v>
+      </x:c>
+      <x:c r="E59" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F59" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G59" s="93" t="str">
+        <x:v>Parent Borrowers.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H59" s="93" t="str">
+        <x:v>appsheet_ref_01: REFERENCES public.Borrowers(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="55" customHeight="1">
+      <x:c r="A60" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B60" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C60" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D60" s="93" t="str">
+        <x:v>Ref Loans</x:v>
+      </x:c>
+      <x:c r="E60" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F60" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G60" s="93" t="str">
+        <x:v>Parent Loans.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H60" s="93" t="str">
+        <x:v>appsheet_ref_02: REFERENCES public.Loans(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="55" customHeight="1">
+      <x:c r="A61" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B61" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C61" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D61" s="93" t="str">
+        <x:v>Ref Charges</x:v>
+      </x:c>
+      <x:c r="E61" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F61" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G61" s="93" t="str">
+        <x:v>Parent Charges.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H61" s="93" t="str">
+        <x:v>appsheet_ref_03: REFERENCES public.Charges(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="55" customHeight="1">
+      <x:c r="A62" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B62" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C62" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D62" s="93" t="str">
+        <x:v>Ref Payment</x:v>
+      </x:c>
+      <x:c r="E62" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F62" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G62" s="93" t="str">
+        <x:v>Parent Payments.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H62" s="93" t="str">
+        <x:v>appsheet_ref_04: REFERENCES public.Payments(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="55" customHeight="1">
+      <x:c r="A63" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B63" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C63" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D63" s="93" t="str">
+        <x:v>Ref Payment Allocation</x:v>
+      </x:c>
+      <x:c r="E63" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F63" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G63" s="93" t="str">
+        <x:v>Parent Payment Allocations.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H63" s="93" t="str">
+        <x:v>appsheet_ref_05: REFERENCES public.Payment Allocations(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="55" customHeight="1">
+      <x:c r="A64" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B64" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C64" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D64" s="93" t="str">
+        <x:v>Ref Loans</x:v>
+      </x:c>
+      <x:c r="E64" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F64" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G64" s="93" t="str">
+        <x:v>Parent Loans.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H64" s="93" t="str">
+        <x:v>appsheet_ref_06: REFERENCES public.Loans(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="55" customHeight="1">
+      <x:c r="A65" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B65" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C65" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D65" s="93" t="str">
+        <x:v>Ref Borrower</x:v>
+      </x:c>
+      <x:c r="E65" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F65" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G65" s="93" t="str">
+        <x:v>Parent Borrowers.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H65" s="93" t="str">
+        <x:v>appsheet_ref_07: REFERENCES public.Borrowers(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="55" customHeight="1">
+      <x:c r="A66" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B66" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C66" s="93" t="str">
+        <x:v>Cash Pool Contributions</x:v>
+      </x:c>
+      <x:c r="D66" s="93" t="str">
+        <x:v>Ref Partner</x:v>
+      </x:c>
+      <x:c r="E66" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F66" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G66" s="93" t="str">
+        <x:v>Parent Partners.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H66" s="93" t="str">
+        <x:v>appsheet_ref_08: REFERENCES public.Partners(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="55" customHeight="1">
+      <x:c r="A67" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B67" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C67" s="93" t="str">
+        <x:v>Settlements</x:v>
+      </x:c>
+      <x:c r="D67" s="93" t="str">
+        <x:v>Ref Partner</x:v>
+      </x:c>
+      <x:c r="E67" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F67" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G67" s="93" t="str">
+        <x:v>Parent Partners.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H67" s="93" t="str">
+        <x:v>appsheet_ref_09: REFERENCES public.Partners(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="55" customHeight="1">
+      <x:c r="A68" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B68" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C68" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D68" s="93" t="str">
+        <x:v>Ref Payment</x:v>
+      </x:c>
+      <x:c r="E68" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F68" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G68" s="93" t="str">
+        <x:v>Parent Payments.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H68" s="93" t="str">
+        <x:v>appsheet_ref_10: REFERENCES public.Payments(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="55" customHeight="1">
+      <x:c r="A69" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B69" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C69" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D69" s="93" t="str">
+        <x:v>Ref Charge</x:v>
+      </x:c>
+      <x:c r="E69" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F69" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G69" s="93" t="str">
+        <x:v>Parent Charges.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H69" s="93" t="str">
+        <x:v>appsheet_ref_11: REFERENCES public.Charges(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="55" customHeight="1">
+      <x:c r="A70" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B70" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C70" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D70" s="93" t="str">
+        <x:v>Ref Borrower</x:v>
+      </x:c>
+      <x:c r="E70" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F70" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G70" s="93" t="str">
+        <x:v>Parent Borrowers.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H70" s="93" t="str">
+        <x:v>appsheet_ref_12: REFERENCES public.Borrowers(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="55" customHeight="1">
+      <x:c r="A71" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B71" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C71" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D71" s="93" t="str">
+        <x:v>Ref Target Charge</x:v>
+      </x:c>
+      <x:c r="E71" s="93" t="str">
+        <x:v>Foreign key</x:v>
+      </x:c>
+      <x:c r="F71" s="93" t="str">
+        <x:v>Validated; future production DB</x:v>
+      </x:c>
+      <x:c r="G71" s="93" t="str">
+        <x:v>Parent Charges.Row ID; app Ref unchanged</x:v>
+      </x:c>
+      <x:c r="H71" s="93" t="str">
+        <x:v>appsheet_ref_13: REFERENCES public.Charges(Row ID); UPDATE/DELETE NO ACTION; NOT DEFERRABLE; blank Ref text normalized to NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="55" customHeight="1">
+      <x:c r="A72" s="93" t="str">
+        <x:v>SQL foreign keys</x:v>
+      </x:c>
+      <x:c r="B72" s="93" t="str">
+        <x:v>1.000007</x:v>
+      </x:c>
+      <x:c r="C72" s="93" t="str">
+        <x:v>8 child tables</x:v>
+      </x:c>
+      <x:c r="D72" s="93" t="str">
+        <x:v>appsheet_blank_refs</x:v>
+      </x:c>
+      <x:c r="E72" s="93" t="str">
+        <x:v>BEFORE trigger</x:v>
+      </x:c>
+      <x:c r="F72" s="93" t="str">
+        <x:v>Installed; 1,010 blanks normalized</x:v>
+      </x:c>
+      <x:c r="G72" s="93" t="str">
+        <x:v>Future empty Ref values -&gt; NULL; nonblank values untouched</x:v>
+      </x:c>
+      <x:c r="H72" s="93" t="str">
+        <x:v>public.appsheet_normalize_blank_refs(); BEFORE INSERT OR UPDATE; 13 Ref columns only; no schema columns added</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7089,7 +7461,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06d63c999d584a27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f2faaa92fbc4d3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17746,7 +18118,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree75edcddda04939"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c6dbb03541e44d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18175,7 +18547,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re25b44cc55da45d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R011e64bf89ff4fff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18635,7 +19007,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30fe6472ce884c45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81fa15aad90f4248"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25609,7 +25981,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabef0a776c244b82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01212b8001b34e2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30228,7 +30600,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18aa1fe2329a49a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R792cdcf434a644f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30427,7 +30799,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf352d63251904d05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4ad5836a5b049cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32080,7 +32452,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7097c9961c0d45d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00b32aade3dd4b64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc8a1b42326d94b1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R330d00b3f1f04219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Ra2d90ba617ba4459"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rb62581c186ff4e87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Rcafc24c049cd4ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rc3cebf60981b453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R1d6ca97856a84b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R82cabff2644e4d64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rfd2096e1cabb4fef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="Rb53e77ec525b4f3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Red02d9a3a6794ff9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R4292b49d83b24e9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R805f2d64b5214280"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Ra3efeb3eb4894156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R698351cb75664772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rbc128ea22bc94c34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R136cddf6a8434ef5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R458b9bc5436b42f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R784292437e5f421e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Raedeec4a5b13438e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rb911b941130d40ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Rdb0522a3484249d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rf4edd2e0cd7c476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R6b7b32dda5e64a89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R270b65d5f48b465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R5f3c539ea38047db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="Rcf0798dd5a9449ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R687d05a2fcc94212"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -100,7 +100,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="33">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -135,6 +135,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -392,7 +397,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="124">
+  <x:cellXfs count="125">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -663,6 +668,9 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2570,7 +2578,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d08b96d50c14684"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb617b213d034731"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5171,28 +5179,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="123" t="str">
+      <x:c r="A1" s="124" t="str">
         <x:v>Experiment</x:v>
       </x:c>
-      <x:c r="B1" s="123" t="str">
+      <x:c r="B1" s="124" t="str">
         <x:v>App version</x:v>
       </x:c>
-      <x:c r="C1" s="123" t="str">
+      <x:c r="C1" s="124" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="D1" s="123" t="str">
+      <x:c r="D1" s="124" t="str">
         <x:v>Column / setting</x:v>
       </x:c>
-      <x:c r="E1" s="123" t="str">
+      <x:c r="E1" s="124" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F1" s="123" t="str">
+      <x:c r="F1" s="124" t="str">
         <x:v>Scope / status</x:v>
       </x:c>
-      <x:c r="G1" s="123" t="str">
+      <x:c r="G1" s="124" t="str">
         <x:v>Purpose / dependencies</x:v>
       </x:c>
-      <x:c r="H1" s="123" t="str">
+      <x:c r="H1" s="124" t="str">
         <x:v>Exact definition</x:v>
       </x:c>
     </x:row>
@@ -7040,6 +7048,266 @@
       </x:c>
       <x:c r="H72" s="93" t="str">
         <x:v>public.appsheet_normalize_blank_refs(); BEFORE INSERT OR UPDATE; 13 Ref columns only; no schema columns added</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="55" customHeight="1">
+      <x:c r="A73" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B73" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C73" s="93" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D73" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E73" s="93" t="str">
+        <x:v>SQL binding</x:v>
+      </x:c>
+      <x:c r="F73" s="93" t="str">
+        <x:v>Copied OLTP; testing in progress</x:v>
+      </x:c>
+      <x:c r="G73" s="93" t="str">
+        <x:v>Original OLTP 3.000064 remains on Money</x:v>
+      </x:c>
+      <x:c r="H73" s="93" t="str">
+        <x:v>database-2; Borrowers</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="55" customHeight="1">
+      <x:c r="A74" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B74" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C74" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D74" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E74" s="93" t="str">
+        <x:v>SQL binding</x:v>
+      </x:c>
+      <x:c r="F74" s="93" t="str">
+        <x:v>Copied OLTP; testing in progress</x:v>
+      </x:c>
+      <x:c r="G74" s="93" t="str">
+        <x:v>Original OLTP 3.000064 remains on Money</x:v>
+      </x:c>
+      <x:c r="H74" s="93" t="str">
+        <x:v>database-2; Loans</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="55" customHeight="1">
+      <x:c r="A75" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B75" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C75" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D75" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E75" s="93" t="str">
+        <x:v>SQL binding</x:v>
+      </x:c>
+      <x:c r="F75" s="93" t="str">
+        <x:v>Copied OLTP; testing in progress</x:v>
+      </x:c>
+      <x:c r="G75" s="93" t="str">
+        <x:v>Original OLTP 3.000064 remains on Money</x:v>
+      </x:c>
+      <x:c r="H75" s="93" t="str">
+        <x:v>database-2; Repayments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="55" customHeight="1">
+      <x:c r="A76" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B76" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C76" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D76" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E76" s="93" t="str">
+        <x:v>SQL binding</x:v>
+      </x:c>
+      <x:c r="F76" s="93" t="str">
+        <x:v>Copied OLTP; testing in progress</x:v>
+      </x:c>
+      <x:c r="G76" s="93" t="str">
+        <x:v>Original OLTP 3.000064 remains on Money</x:v>
+      </x:c>
+      <x:c r="H76" s="93" t="str">
+        <x:v>database-2; Statistics</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="55" customHeight="1">
+      <x:c r="A77" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B77" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C77" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D77" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E77" s="93" t="str">
+        <x:v>SQL binding</x:v>
+      </x:c>
+      <x:c r="F77" s="93" t="str">
+        <x:v>Copied OLTP; testing in progress</x:v>
+      </x:c>
+      <x:c r="G77" s="93" t="str">
+        <x:v>Original OLTP 3.000064 remains on Money</x:v>
+      </x:c>
+      <x:c r="H77" s="93" t="str">
+        <x:v>database-2; Charges</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="55" customHeight="1">
+      <x:c r="A78" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B78" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C78" s="93" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="D78" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E78" s="93" t="str">
+        <x:v>SQL binding</x:v>
+      </x:c>
+      <x:c r="F78" s="93" t="str">
+        <x:v>Copied OLTP; testing in progress</x:v>
+      </x:c>
+      <x:c r="G78" s="93" t="str">
+        <x:v>Original OLTP 3.000064 remains on Money</x:v>
+      </x:c>
+      <x:c r="H78" s="93" t="str">
+        <x:v>database-2; Partners</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="55" customHeight="1">
+      <x:c r="A79" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B79" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C79" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D79" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E79" s="93" t="str">
+        <x:v>SQL binding</x:v>
+      </x:c>
+      <x:c r="F79" s="93" t="str">
+        <x:v>Copied OLTP; testing in progress</x:v>
+      </x:c>
+      <x:c r="G79" s="93" t="str">
+        <x:v>Original OLTP 3.000064 remains on Money</x:v>
+      </x:c>
+      <x:c r="H79" s="93" t="str">
+        <x:v>database-2; Payment Allocations</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="55" customHeight="1">
+      <x:c r="A80" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B80" s="93" t="str">
+        <x:v>1.000004</x:v>
+      </x:c>
+      <x:c r="C80" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D80" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E80" s="93" t="str">
+        <x:v>SQL binding</x:v>
+      </x:c>
+      <x:c r="F80" s="93" t="str">
+        <x:v>Copied OLTP; testing in progress</x:v>
+      </x:c>
+      <x:c r="G80" s="93" t="str">
+        <x:v>Original OLTP 3.000064 remains on Money</x:v>
+      </x:c>
+      <x:c r="H80" s="93" t="str">
+        <x:v>database-2; Payments</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="55" customHeight="1">
+      <x:c r="A81" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B81" s="93" t="str">
+        <x:v>OLTP 1.000005; OLAP 1.000007</x:v>
+      </x:c>
+      <x:c r="C81" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D81" s="93" t="str">
+        <x:v>Borrower Name</x:v>
+      </x:c>
+      <x:c r="E81" s="93" t="str">
+        <x:v>SQL lookup triggers</x:v>
+      </x:c>
+      <x:c r="F81" s="93" t="str">
+        <x:v>Installed; insert and rename verified</x:v>
+      </x:c>
+      <x:c r="G81" s="93" t="str">
+        <x:v>Restores native Lookup on Borrowers.Borrower Name for both app consumers</x:v>
+      </x:c>
+      <x:c r="H81" s="93" t="str">
+        <x:v>BEFORE INSERT OR UPDATE Loans: resolve Borrower Name through Ref Borrowers; AFTER Borrower Name update: propagate to Loans. No added columns.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="55" customHeight="1">
+      <x:c r="A82" s="93" t="str">
+        <x:v>OLTP SQL validation</x:v>
+      </x:c>
+      <x:c r="B82" s="93" t="str">
+        <x:v>1.000005</x:v>
+      </x:c>
+      <x:c r="C82" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D82" s="93" t="str">
+        <x:v>Two charge actions</x:v>
+      </x:c>
+      <x:c r="E82" s="93" t="str">
+        <x:v>Display only</x:v>
+      </x:c>
+      <x:c r="F82" s="93" t="str">
+        <x:v>Temporary; restoration pending</x:v>
+      </x:c>
+      <x:c r="G82" s="93" t="str">
+        <x:v>New GUI lifecycle testing</x:v>
+      </x:c>
+      <x:c r="H82" s="93" t="str">
+        <x:v>Generate Today's Charge and New Loan Payment - Create First-Day Charge: Prominent instead of Hide.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7461,7 +7729,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f2faaa92fbc4d3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fcb02f90f3c4150"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18118,7 +18386,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c6dbb03541e44d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f16b6fd4e6649b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18547,7 +18815,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R011e64bf89ff4fff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reea3f36dccbb40a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19007,7 +19275,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81fa15aad90f4248"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0116590085e14856"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25981,7 +26249,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01212b8001b34e2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda2eb747a819434c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30600,7 +30868,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R792cdcf434a644f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3966a8871ace4590"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30799,7 +31067,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4ad5836a5b049cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f1d691b7ad84891"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32452,7 +32720,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00b32aade3dd4b64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R327d8e782f8d4470"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R698351cb75664772"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rbc128ea22bc94c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R136cddf6a8434ef5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R458b9bc5436b42f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R784292437e5f421e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Raedeec4a5b13438e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rb911b941130d40ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Rdb0522a3484249d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rf4edd2e0cd7c476d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R6b7b32dda5e64a89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R270b65d5f48b465e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R5f3c539ea38047db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="Rcf0798dd5a9449ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R687d05a2fcc94212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf35ba5ba504c422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Radc5048076764115"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R093ea272035e4350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R4d4e51304689413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Ra6e2b92f779c401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R8a747f6090bd4b33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rae693b7305794b90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R602678f15f8c47fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rf38d153789174d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R721e6bb7024b4a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R8efe94af0a104724"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rcdf3ffcf3281427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="Rea856778c17542c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Rf2a8ac9f44ee433e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -100,7 +100,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="34">
+  <x:fills count="35">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -135,6 +135,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -397,7 +402,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="125">
+  <x:cellXfs count="126">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -671,6 +676,9 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2578,7 +2586,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb617b213d034731"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e2a617cd844bed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5179,28 +5187,28 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="124" t="str">
+      <x:c r="A1" s="125" t="str">
         <x:v>Experiment</x:v>
       </x:c>
-      <x:c r="B1" s="124" t="str">
+      <x:c r="B1" s="125" t="str">
         <x:v>App version</x:v>
       </x:c>
-      <x:c r="C1" s="124" t="str">
+      <x:c r="C1" s="125" t="str">
         <x:v>Table</x:v>
       </x:c>
-      <x:c r="D1" s="124" t="str">
+      <x:c r="D1" s="125" t="str">
         <x:v>Column / setting</x:v>
       </x:c>
-      <x:c r="E1" s="124" t="str">
+      <x:c r="E1" s="125" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="F1" s="124" t="str">
+      <x:c r="F1" s="125" t="str">
         <x:v>Scope / status</x:v>
       </x:c>
-      <x:c r="G1" s="124" t="str">
+      <x:c r="G1" s="125" t="str">
         <x:v>Purpose / dependencies</x:v>
       </x:c>
-      <x:c r="H1" s="124" t="str">
+      <x:c r="H1" s="125" t="str">
         <x:v>Exact definition</x:v>
       </x:c>
     </x:row>
@@ -7289,7 +7297,7 @@
         <x:v>OLTP SQL validation</x:v>
       </x:c>
       <x:c r="B82" s="93" t="str">
-        <x:v>1.000005</x:v>
+        <x:v>1.000006</x:v>
       </x:c>
       <x:c r="C82" s="93" t="str">
         <x:v>Loans</x:v>
@@ -7301,13 +7309,13 @@
         <x:v>Display only</x:v>
       </x:c>
       <x:c r="F82" s="93" t="str">
-        <x:v>Temporary; restoration pending</x:v>
+        <x:v>Restored to baseline Hide</x:v>
       </x:c>
       <x:c r="G82" s="93" t="str">
-        <x:v>New GUI lifecycle testing</x:v>
+        <x:v>New GUI lifecycle testing complete</x:v>
       </x:c>
       <x:c r="H82" s="93" t="str">
-        <x:v>Generate Today's Charge and New Loan Payment - Create First-Day Charge: Prominent instead of Hide.</x:v>
+        <x:v>Generate Today's Charge and New Loan Payment - Create First-Day Charge: Hide. All 72 actions match copied baseline.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7729,7 +7737,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fcb02f90f3c4150"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac8cbbe7055042a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18386,7 +18394,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f16b6fd4e6649b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R860e73688a58498e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18815,7 +18823,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reea3f36dccbb40a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a94ab0d5d6a4bf3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19275,7 +19283,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0116590085e14856"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6022775a3534717"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26249,7 +26257,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda2eb747a819434c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1a339f52e654366"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30868,7 +30876,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3966a8871ace4590"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf62fd073135f4b50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31067,7 +31075,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f1d691b7ad84891"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf0f3bc89adf4309"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32720,7 +32728,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R327d8e782f8d4470"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf305118bdaf54241"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,20 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf35ba5ba504c422b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Radc5048076764115"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R093ea272035e4350"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R4d4e51304689413f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Ra6e2b92f779c401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R8a747f6090bd4b33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rae693b7305794b90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R602678f15f8c47fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rf38d153789174d3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R721e6bb7024b4a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R8efe94af0a104724"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rcdf3ffcf3281427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="Rea856778c17542c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="Rf2a8ac9f44ee433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R87f961343a4c4162"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Raf890574b7404e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R214a37e456924257"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rf1ef2366d0454831"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R334a6ec9ba484853"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R0d60b2220f0c455b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R0b86f1bd436f43d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R930fa9e07dea4184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Raf32ef7469bc4a46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R78da8a37e92b44cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R1e49f9caa4c74c4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R88dd66015c684121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R8f777c62be1f41b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R5848d795d9294f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Production" sheetId="15" r:id="R65be325a420a4ad3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -100,7 +101,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="35">
+  <x:fills count="36">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -135,6 +136,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -402,7 +408,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="126">
+  <x:cellXfs count="129">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -679,6 +685,11 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2586,7 +2597,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e2a617cd844bed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f0b4debb7964235"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7316,6 +7327,779 @@
       </x:c>
       <x:c r="H82" s="93" t="str">
         <x:v>Generate Today's Charge and New Loan Payment - Create First-Day Charge: Hide. All 72 actions match copied baseline.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="128" t="str">
+        <x:v>Experiment</x:v>
+      </x:c>
+      <x:c r="B1" s="128" t="str">
+        <x:v>App version</x:v>
+      </x:c>
+      <x:c r="C1" s="128" t="str">
+        <x:v>Table</x:v>
+      </x:c>
+      <x:c r="D1" s="128" t="str">
+        <x:v>Column / setting</x:v>
+      </x:c>
+      <x:c r="E1" s="128" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="F1" s="128" t="str">
+        <x:v>Scope / status</x:v>
+      </x:c>
+      <x:c r="G1" s="128" t="str">
+        <x:v>Purpose / dependencies</x:v>
+      </x:c>
+      <x:c r="H1" s="128" t="str">
+        <x:v>Exact definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="70" customHeight="1">
+      <x:c r="A2" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B2" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C2" s="93" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D2" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E2" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F2" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G2" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H2" s="93" t="str">
+        <x:v>database-2; public.Borrowers; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="70" customHeight="1">
+      <x:c r="A3" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B3" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C3" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D3" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E3" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F3" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G3" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H3" s="93" t="str">
+        <x:v>database-2; public.Loans; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="70" customHeight="1">
+      <x:c r="A4" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B4" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C4" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D4" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E4" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F4" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G4" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H4" s="93" t="str">
+        <x:v>database-2; public.Repayments; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="70" customHeight="1">
+      <x:c r="A5" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B5" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C5" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D5" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E5" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F5" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G5" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H5" s="93" t="str">
+        <x:v>database-2; public.Statistics; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="70" customHeight="1">
+      <x:c r="A6" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B6" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C6" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D6" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E6" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F6" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G6" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H6" s="93" t="str">
+        <x:v>database-2; public.Charges; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="70" customHeight="1">
+      <x:c r="A7" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B7" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C7" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D7" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E7" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F7" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G7" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H7" s="93" t="str">
+        <x:v>database-2; public.Loan Assessment; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="70" customHeight="1">
+      <x:c r="A8" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B8" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C8" s="93" t="str">
+        <x:v>Cash Pool Contributions</x:v>
+      </x:c>
+      <x:c r="D8" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E8" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F8" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G8" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H8" s="93" t="str">
+        <x:v>database-2; public.Cash Pool Contributions; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="70" customHeight="1">
+      <x:c r="A9" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B9" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C9" s="93" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="D9" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E9" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F9" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G9" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H9" s="93" t="str">
+        <x:v>database-2; public.Partners; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="70" customHeight="1">
+      <x:c r="A10" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B10" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C10" s="93" t="str">
+        <x:v>Settlements</x:v>
+      </x:c>
+      <x:c r="D10" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E10" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F10" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G10" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H10" s="93" t="str">
+        <x:v>database-2; public.Settlements; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="70" customHeight="1">
+      <x:c r="A11" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B11" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C11" s="93" t="str">
+        <x:v>Daily Analytics</x:v>
+      </x:c>
+      <x:c r="D11" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E11" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F11" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G11" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H11" s="93" t="str">
+        <x:v>database-2; public.Daily Analytics; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="70" customHeight="1">
+      <x:c r="A12" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B12" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C12" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D12" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E12" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F12" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G12" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H12" s="93" t="str">
+        <x:v>database-2; public.Payment Allocations; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="70" customHeight="1">
+      <x:c r="A13" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B13" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C13" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D13" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E13" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F13" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G13" s="93" t="str">
+        <x:v>Reporting and partner management</x:v>
+      </x:c>
+      <x:c r="H13" s="93" t="str">
+        <x:v>database-2; public.Payments; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="70" customHeight="1">
+      <x:c r="A14" s="93" t="str">
+        <x:v>OLTP production</x:v>
+      </x:c>
+      <x:c r="B14" s="93" t="str">
+        <x:v>3.000067</x:v>
+      </x:c>
+      <x:c r="C14" s="93" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D14" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E14" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F14" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G14" s="93" t="str">
+        <x:v>Operational workflow owner</x:v>
+      </x:c>
+      <x:c r="H14" s="93" t="str">
+        <x:v>database-2; public.Borrowers; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="70" customHeight="1">
+      <x:c r="A15" s="93" t="str">
+        <x:v>OLTP production</x:v>
+      </x:c>
+      <x:c r="B15" s="93" t="str">
+        <x:v>3.000067</x:v>
+      </x:c>
+      <x:c r="C15" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D15" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E15" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F15" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G15" s="93" t="str">
+        <x:v>Operational workflow owner</x:v>
+      </x:c>
+      <x:c r="H15" s="93" t="str">
+        <x:v>database-2; public.Loans; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="70" customHeight="1">
+      <x:c r="A16" s="93" t="str">
+        <x:v>OLTP production</x:v>
+      </x:c>
+      <x:c r="B16" s="93" t="str">
+        <x:v>3.000067</x:v>
+      </x:c>
+      <x:c r="C16" s="93" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D16" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E16" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F16" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G16" s="93" t="str">
+        <x:v>Operational workflow owner</x:v>
+      </x:c>
+      <x:c r="H16" s="93" t="str">
+        <x:v>database-2; public.Repayments; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="70" customHeight="1">
+      <x:c r="A17" s="93" t="str">
+        <x:v>OLTP production</x:v>
+      </x:c>
+      <x:c r="B17" s="93" t="str">
+        <x:v>3.000067</x:v>
+      </x:c>
+      <x:c r="C17" s="93" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D17" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E17" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F17" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G17" s="93" t="str">
+        <x:v>Operational workflow owner</x:v>
+      </x:c>
+      <x:c r="H17" s="93" t="str">
+        <x:v>database-2; public.Statistics; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="70" customHeight="1">
+      <x:c r="A18" s="93" t="str">
+        <x:v>OLTP production</x:v>
+      </x:c>
+      <x:c r="B18" s="93" t="str">
+        <x:v>3.000067</x:v>
+      </x:c>
+      <x:c r="C18" s="93" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D18" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E18" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F18" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G18" s="93" t="str">
+        <x:v>Operational workflow owner</x:v>
+      </x:c>
+      <x:c r="H18" s="93" t="str">
+        <x:v>database-2; public.Charges; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="70" customHeight="1">
+      <x:c r="A19" s="93" t="str">
+        <x:v>OLTP production</x:v>
+      </x:c>
+      <x:c r="B19" s="93" t="str">
+        <x:v>3.000067</x:v>
+      </x:c>
+      <x:c r="C19" s="93" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="D19" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E19" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F19" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G19" s="93" t="str">
+        <x:v>Operational workflow owner</x:v>
+      </x:c>
+      <x:c r="H19" s="93" t="str">
+        <x:v>database-2; public.Partners; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="70" customHeight="1">
+      <x:c r="A20" s="93" t="str">
+        <x:v>OLTP production</x:v>
+      </x:c>
+      <x:c r="B20" s="93" t="str">
+        <x:v>3.000067</x:v>
+      </x:c>
+      <x:c r="C20" s="93" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D20" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E20" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F20" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G20" s="93" t="str">
+        <x:v>Operational workflow owner</x:v>
+      </x:c>
+      <x:c r="H20" s="93" t="str">
+        <x:v>database-2; public.Payment Allocations; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="70" customHeight="1">
+      <x:c r="A21" s="93" t="str">
+        <x:v>OLTP production</x:v>
+      </x:c>
+      <x:c r="B21" s="93" t="str">
+        <x:v>3.000067</x:v>
+      </x:c>
+      <x:c r="C21" s="93" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D21" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E21" s="93" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="F21" s="93" t="str">
+        <x:v>Live; verified 15 September 2026</x:v>
+      </x:c>
+      <x:c r="G21" s="93" t="str">
+        <x:v>Operational workflow owner</x:v>
+      </x:c>
+      <x:c r="H21" s="93" t="str">
+        <x:v>database-2; public.Payments; loan_manager_prod</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="70" customHeight="1">
+      <x:c r="A22" s="93" t="str">
+        <x:v>Shared production</x:v>
+      </x:c>
+      <x:c r="B22" s="93" t="str">
+        <x:v>OLAP 1.100044; OLTP 3.000067</x:v>
+      </x:c>
+      <x:c r="C22" s="93" t="str">
+        <x:v>All SQL tables</x:v>
+      </x:c>
+      <x:c r="D22" s="93" t="str">
+        <x:v>Row ID</x:v>
+      </x:c>
+      <x:c r="E22" s="93" t="str">
+        <x:v>Text key</x:v>
+      </x:c>
+      <x:c r="F22" s="93" t="str">
+        <x:v>Exact case and values preserved</x:v>
+      </x:c>
+      <x:c r="G22" s="93" t="str">
+        <x:v>Ref joins and offline identity</x:v>
+      </x:c>
+      <x:c r="H22" s="93" t="str">
+        <x:v>PostgreSQL text primary keys; AppSheet UNIQUEID("PackedUUID") initial preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="70" customHeight="1">
+      <x:c r="A23" s="93" t="str">
+        <x:v>Shared production</x:v>
+      </x:c>
+      <x:c r="B23" s="93" t="str">
+        <x:v>OLAP 1.100044; OLTP 3.000067</x:v>
+      </x:c>
+      <x:c r="C23" s="93" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D23" s="93" t="str">
+        <x:v>Borrower Name</x:v>
+      </x:c>
+      <x:c r="E23" s="93" t="str">
+        <x:v>SQL lookup</x:v>
+      </x:c>
+      <x:c r="F23" s="93" t="str">
+        <x:v>Insert and rename verified in copy</x:v>
+      </x:c>
+      <x:c r="G23" s="93" t="str">
+        <x:v>Both apps consume stored lookup</x:v>
+      </x:c>
+      <x:c r="H23" s="93" t="str">
+        <x:v>Existing SQL lookup and propagation triggers retained. No AppSheet formula change.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="70" customHeight="1">
+      <x:c r="A24" s="93" t="str">
+        <x:v>Shared production</x:v>
+      </x:c>
+      <x:c r="B24" s="93" t="str">
+        <x:v>OLAP 1.100044; OLTP 3.000067</x:v>
+      </x:c>
+      <x:c r="C24" s="93" t="str">
+        <x:v>Shared references</x:v>
+      </x:c>
+      <x:c r="D24" s="93" t="str">
+        <x:v>Foreign keys</x:v>
+      </x:c>
+      <x:c r="E24" s="93" t="str">
+        <x:v>13 constraints</x:v>
+      </x:c>
+      <x:c r="F24" s="93" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="G24" s="93" t="str">
+        <x:v>Protect existing references</x:v>
+      </x:c>
+      <x:c r="H24" s="93" t="str">
+        <x:v>NO ACTION; validated; eight blank-Ref normalization triggers retained.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="70" customHeight="1">
+      <x:c r="A25" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B25" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C25" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D25" s="93" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="E25" s="93" t="str">
+        <x:v>Google Sheets</x:v>
+      </x:c>
+      <x:c r="F25" s="93" t="str">
+        <x:v>Unchanged</x:v>
+      </x:c>
+      <x:c r="G25" s="93" t="str">
+        <x:v>Daily analytics and projections</x:v>
+      </x:c>
+      <x:c r="H25" s="93" t="str">
+        <x:v>Calendar Help Table / Sheet1; source google.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="70" customHeight="1">
+      <x:c r="A26" s="93" t="str">
+        <x:v>OLAP production</x:v>
+      </x:c>
+      <x:c r="B26" s="93" t="str">
+        <x:v>1.100044</x:v>
+      </x:c>
+      <x:c r="C26" s="93" t="str">
+        <x:v>Automation</x:v>
+      </x:c>
+      <x:c r="D26" s="93" t="str">
+        <x:v>Daily analytics schedules</x:v>
+      </x:c>
+      <x:c r="E26" s="93" t="str">
+        <x:v>Bot enablement</x:v>
+      </x:c>
+      <x:c r="F26" s="93" t="str">
+        <x:v>Original state restored</x:v>
+      </x:c>
+      <x:c r="G26" s="93" t="str">
+        <x:v>Reporting snapshots</x:v>
+      </x:c>
+      <x:c r="H26" s="93" t="str">
+        <x:v>Refresh Daily Analytics Daily 2 enabled; Refresh Daily Analytics Daily remains disabled.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="70" customHeight="1">
+      <x:c r="A27" s="93" t="str">
+        <x:v>OLTP production</x:v>
+      </x:c>
+      <x:c r="B27" s="93" t="str">
+        <x:v>3.000067</x:v>
+      </x:c>
+      <x:c r="C27" s="93" t="str">
+        <x:v>Automation</x:v>
+      </x:c>
+      <x:c r="D27" s="93" t="str">
+        <x:v>Generate Daily Charges</x:v>
+      </x:c>
+      <x:c r="E27" s="93" t="str">
+        <x:v>Bot enablement</x:v>
+      </x:c>
+      <x:c r="F27" s="93" t="str">
+        <x:v>Enabled; catch-up verified</x:v>
+      </x:c>
+      <x:c r="G27" s="93" t="str">
+        <x:v>Daily charge workflow</x:v>
+      </x:c>
+      <x:c r="H27" s="93" t="str">
+        <x:v>15 September: 28 eligible daily-interest loans; 28 charges; interest 8040; principal 0; no duplicates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="70" customHeight="1">
+      <x:c r="A28" s="93" t="str">
+        <x:v>Shared production</x:v>
+      </x:c>
+      <x:c r="B28" s="93" t="str">
+        <x:v>OLAP 1.100044; OLTP 3.000067</x:v>
+      </x:c>
+      <x:c r="C28" s="93" t="str">
+        <x:v>All business tables</x:v>
+      </x:c>
+      <x:c r="D28" s="93" t="str">
+        <x:v>Reconciliation</x:v>
+      </x:c>
+      <x:c r="E28" s="93" t="str">
+        <x:v>Readback</x:v>
+      </x:c>
+      <x:c r="F28" s="93" t="str">
+        <x:v>1936 rows before catch-up</x:v>
+      </x:c>
+      <x:c r="G28" s="93" t="str">
+        <x:v>Frozen source versus SQL</x:v>
+      </x:c>
+      <x:c r="H28" s="93" t="str">
+        <x:v>Zero scalar or relationship membership differences. 42 relationship lists had ordering-only changes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="70" customHeight="1">
+      <x:c r="A29" s="93" t="str">
+        <x:v>Rollback</x:v>
+      </x:c>
+      <x:c r="B29" s="93" t="str">
+        <x:v>OLAP 1.100041; OLTP 3.000064</x:v>
+      </x:c>
+      <x:c r="C29" s="93" t="str">
+        <x:v>Money database</x:v>
+      </x:c>
+      <x:c r="D29" s="93" t="str">
+        <x:v>Retained source</x:v>
+      </x:c>
+      <x:c r="E29" s="93" t="str">
+        <x:v>Recovery</x:v>
+      </x:c>
+      <x:c r="F29" s="93" t="str">
+        <x:v>Not receiving production app writes</x:v>
+      </x:c>
+      <x:c r="G29" s="93" t="str">
+        <x:v>Preserve SQL writes before reverting</x:v>
+      </x:c>
+      <x:c r="H29" s="93" t="str">
+        <x:v>Pause writers, reconcile post-cutover SQL rows back to Money, then restore app versions. Version rollback alone is insufficient.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7737,7 +8521,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac8cbbe7055042a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0994f172d94485e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18394,7 +19178,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R860e73688a58498e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3d5328b5ee9454e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18823,7 +19607,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a94ab0d5d6a4bf3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c3ba416a7af4209"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19283,7 +20067,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6022775a3534717"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re15634c62f4b4495"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26257,7 +27041,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1a339f52e654366"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58d5afb30c994d66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30876,7 +31660,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf62fd073135f4b50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re206edd6336e442e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31075,7 +31859,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf0f3bc89adf4309"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra978d656032e42da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32728,7 +33512,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf305118bdaf54241"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32f018daf73d4ca8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R87f961343a4c4162"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Raf890574b7404e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R214a37e456924257"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rf1ef2366d0454831"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R334a6ec9ba484853"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R0d60b2220f0c455b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R0b86f1bd436f43d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R930fa9e07dea4184"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Raf32ef7469bc4a46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R78da8a37e92b44cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R1e49f9caa4c74c4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R88dd66015c684121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R8f777c62be1f41b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R5848d795d9294f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Production" sheetId="15" r:id="R65be325a420a4ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf0ed312a3e6f4b9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rde46409949f642bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rab803b2955cf401b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rc075e7fd93ef4ca1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R683d94cf57a14fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R447093ce53e54b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R3a4039ccda1a4913"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Ree86cf3ec0b34ebc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R7fec76bdb03147be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R53c4f39aea734918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rbc03cfb8c9a54d90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R2e1a80d6ed164700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R2db5f11bbc5247bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R6c46f41c58e04088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Production" sheetId="15" r:id="Reef12395164f47f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2597,7 +2597,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f0b4debb7964235"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ca0b1d095934b11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7379,7 +7379,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B2" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C2" s="93" t="str">
         <x:v>Borrowers</x:v>
@@ -7405,7 +7405,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B3" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C3" s="93" t="str">
         <x:v>Loans</x:v>
@@ -7431,7 +7431,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B4" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C4" s="93" t="str">
         <x:v>Repayments</x:v>
@@ -7457,7 +7457,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B5" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C5" s="93" t="str">
         <x:v>Statistics</x:v>
@@ -7483,7 +7483,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B6" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C6" s="93" t="str">
         <x:v>Charges</x:v>
@@ -7509,7 +7509,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B7" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C7" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -7535,7 +7535,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B8" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C8" s="93" t="str">
         <x:v>Cash Pool Contributions</x:v>
@@ -7561,7 +7561,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B9" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C9" s="93" t="str">
         <x:v>Partners</x:v>
@@ -7587,7 +7587,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B10" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C10" s="93" t="str">
         <x:v>Settlements</x:v>
@@ -7613,7 +7613,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B11" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C11" s="93" t="str">
         <x:v>Daily Analytics</x:v>
@@ -7639,7 +7639,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B12" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C12" s="93" t="str">
         <x:v>Payment Allocations</x:v>
@@ -7665,7 +7665,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B13" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C13" s="93" t="str">
         <x:v>Payments</x:v>
@@ -7691,7 +7691,7 @@
         <x:v>OLTP production</x:v>
       </x:c>
       <x:c r="B14" s="93" t="str">
-        <x:v>3.000067</x:v>
+        <x:v>3.000069</x:v>
       </x:c>
       <x:c r="C14" s="93" t="str">
         <x:v>Borrowers</x:v>
@@ -7717,7 +7717,7 @@
         <x:v>OLTP production</x:v>
       </x:c>
       <x:c r="B15" s="93" t="str">
-        <x:v>3.000067</x:v>
+        <x:v>3.000069</x:v>
       </x:c>
       <x:c r="C15" s="93" t="str">
         <x:v>Loans</x:v>
@@ -7743,7 +7743,7 @@
         <x:v>OLTP production</x:v>
       </x:c>
       <x:c r="B16" s="93" t="str">
-        <x:v>3.000067</x:v>
+        <x:v>3.000069</x:v>
       </x:c>
       <x:c r="C16" s="93" t="str">
         <x:v>Repayments</x:v>
@@ -7769,7 +7769,7 @@
         <x:v>OLTP production</x:v>
       </x:c>
       <x:c r="B17" s="93" t="str">
-        <x:v>3.000067</x:v>
+        <x:v>3.000069</x:v>
       </x:c>
       <x:c r="C17" s="93" t="str">
         <x:v>Statistics</x:v>
@@ -7795,7 +7795,7 @@
         <x:v>OLTP production</x:v>
       </x:c>
       <x:c r="B18" s="93" t="str">
-        <x:v>3.000067</x:v>
+        <x:v>3.000069</x:v>
       </x:c>
       <x:c r="C18" s="93" t="str">
         <x:v>Charges</x:v>
@@ -7821,7 +7821,7 @@
         <x:v>OLTP production</x:v>
       </x:c>
       <x:c r="B19" s="93" t="str">
-        <x:v>3.000067</x:v>
+        <x:v>3.000069</x:v>
       </x:c>
       <x:c r="C19" s="93" t="str">
         <x:v>Partners</x:v>
@@ -7847,7 +7847,7 @@
         <x:v>OLTP production</x:v>
       </x:c>
       <x:c r="B20" s="93" t="str">
-        <x:v>3.000067</x:v>
+        <x:v>3.000069</x:v>
       </x:c>
       <x:c r="C20" s="93" t="str">
         <x:v>Payment Allocations</x:v>
@@ -7873,7 +7873,7 @@
         <x:v>OLTP production</x:v>
       </x:c>
       <x:c r="B21" s="93" t="str">
-        <x:v>3.000067</x:v>
+        <x:v>3.000069</x:v>
       </x:c>
       <x:c r="C21" s="93" t="str">
         <x:v>Payments</x:v>
@@ -7899,7 +7899,7 @@
         <x:v>Shared production</x:v>
       </x:c>
       <x:c r="B22" s="93" t="str">
-        <x:v>OLAP 1.100044; OLTP 3.000067</x:v>
+        <x:v>OLAP 1.100046; OLTP 3.000069</x:v>
       </x:c>
       <x:c r="C22" s="93" t="str">
         <x:v>All SQL tables</x:v>
@@ -7925,7 +7925,7 @@
         <x:v>Shared production</x:v>
       </x:c>
       <x:c r="B23" s="93" t="str">
-        <x:v>OLAP 1.100044; OLTP 3.000067</x:v>
+        <x:v>OLAP 1.100046; OLTP 3.000069</x:v>
       </x:c>
       <x:c r="C23" s="93" t="str">
         <x:v>Loans</x:v>
@@ -7934,16 +7934,16 @@
         <x:v>Borrower Name</x:v>
       </x:c>
       <x:c r="E23" s="93" t="str">
-        <x:v>SQL lookup</x:v>
+        <x:v>VC / Name</x:v>
       </x:c>
       <x:c r="F23" s="93" t="str">
-        <x:v>Insert and rename verified in copy</x:v>
+        <x:v>62/62 names verified</x:v>
       </x:c>
       <x:c r="G23" s="93" t="str">
-        <x:v>Both apps consume stored lookup</x:v>
+        <x:v>Both production apps and both SQL test copies</x:v>
       </x:c>
       <x:c r="H23" s="93" t="str">
-        <x:v>Existing SQL lookup and propagation triggers retained. No AppSheet formula change.</x:v>
+        <x:v>[Ref Borrowers].[Borrower Name]. Stored SQL column and two name triggers/functions removed.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="70" customHeight="1">
@@ -7951,7 +7951,7 @@
         <x:v>Shared production</x:v>
       </x:c>
       <x:c r="B24" s="93" t="str">
-        <x:v>OLAP 1.100044; OLTP 3.000067</x:v>
+        <x:v>OLAP 1.100046; OLTP 3.000069</x:v>
       </x:c>
       <x:c r="C24" s="93" t="str">
         <x:v>Shared references</x:v>
@@ -7977,7 +7977,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B25" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C25" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8003,7 +8003,7 @@
         <x:v>OLAP production</x:v>
       </x:c>
       <x:c r="B26" s="93" t="str">
-        <x:v>1.100044</x:v>
+        <x:v>1.100046</x:v>
       </x:c>
       <x:c r="C26" s="93" t="str">
         <x:v>Automation</x:v>
@@ -8029,7 +8029,7 @@
         <x:v>OLTP production</x:v>
       </x:c>
       <x:c r="B27" s="93" t="str">
-        <x:v>3.000067</x:v>
+        <x:v>3.000069</x:v>
       </x:c>
       <x:c r="C27" s="93" t="str">
         <x:v>Automation</x:v>
@@ -8055,7 +8055,7 @@
         <x:v>Shared production</x:v>
       </x:c>
       <x:c r="B28" s="93" t="str">
-        <x:v>OLAP 1.100044; OLTP 3.000067</x:v>
+        <x:v>OLAP 1.100046; OLTP 3.000069</x:v>
       </x:c>
       <x:c r="C28" s="93" t="str">
         <x:v>All business tables</x:v>
@@ -8312,19 +8312,19 @@
         <x:v>Loans</x:v>
       </x:c>
       <x:c r="B11" s="59" t="str">
-        <x:v>Money database</x:v>
+        <x:v>PostgreSQL loan_manager_prod</x:v>
       </x:c>
       <x:c r="C11" s="57" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
       <x:c r="D11" s="57" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E11" s="57" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E11" s="57" t="n">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="F11" s="57" t="n">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G11" s="59" t="str">
         <x:v>Loan contracts, commercial terms, lifecycle state, balances, daily-installment reporting, and loan-level risk metrics.</x:v>
@@ -8521,7 +8521,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0994f172d94485e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bea91a1e86d4b56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13480,30 +13480,30 @@
         <x:v>Stored source column; initial value: "ยังไม่ปิดยอด"</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="15" customHeight="1">
-      <x:c r="A185" s="57" t="str">
+    <x:row r="185" ht="85" customHeight="1">
+      <x:c r="A185" s="82" t="str">
         <x:v>Loans</x:v>
       </x:c>
-      <x:c r="B185" s="57" t="n">
+      <x:c r="B185" s="82" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C185" s="59" t="str">
+      <x:c r="C185" s="82" t="str">
         <x:v>Borrower Name</x:v>
       </x:c>
-      <x:c r="D185" s="59" t="str">
-        <x:v>Physical / Name</x:v>
-      </x:c>
-      <x:c r="E185" s="57" t="str">
+      <x:c r="D185" s="82" t="str">
+        <x:v>VC / Name</x:v>
+      </x:c>
+      <x:c r="E185" s="82" t="str">
         <x:v>OLTP + OLAP</x:v>
       </x:c>
-      <x:c r="F185" s="57" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="G185" s="59" t="str">
-        <x:v>Stores the authoritative source value for Borrower Name.</x:v>
-      </x:c>
-      <x:c r="H185" s="59" t="str">
-        <x:v>Stored source column</x:v>
+      <x:c r="F185" s="82" t="str">
+        <x:v>Read-only; visible; searchable; display: ชื่อผู้กู้ / Borrower</x:v>
+      </x:c>
+      <x:c r="G185" s="82" t="str">
+        <x:v>Current name from referenced borrower; SQL stored copy and maintenance triggers removed. Verified OLTP 3.000069 / OLAP 1.100046.</x:v>
+      </x:c>
+      <x:c r="H185" s="82" t="str">
+        <x:v>[Ref Borrowers].[Borrower Name]</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="15" customHeight="1">
@@ -19178,7 +19178,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3d5328b5ee9454e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9309fac28842d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19607,7 +19607,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c3ba416a7af4209"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra424ecf4053142ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +20067,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re15634c62f4b4495"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47b05cd0d51b479b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27041,7 +27041,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58d5afb30c994d66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f4cef7ad5234c95"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31660,7 +31660,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re206edd6336e442e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68a4b3d789b5468f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31859,7 +31859,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra978d656032e42da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R121cfdcf720d426f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33512,7 +33512,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32f018daf73d4ca8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re27eaf22dae84519"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,21 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf0ed312a3e6f4b9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rde46409949f642bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rab803b2955cf401b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rc075e7fd93ef4ca1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R683d94cf57a14fcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R447093ce53e54b82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="R3a4039ccda1a4913"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="Ree86cf3ec0b34ebc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R7fec76bdb03147be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R53c4f39aea734918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="Rbc03cfb8c9a54d90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R2e1a80d6ed164700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R2db5f11bbc5247bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R6c46f41c58e04088"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Production" sheetId="15" r:id="Reef12395164f47f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc75993a5ae9741b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R8e1e9dad4c3c4fc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R811906d220094419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rb33b55c9f30e43c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Re59298d9cf21435f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Re38426ef954f449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Re659dca2847d4cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R110eb759a3d54f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rcb9cca1bacd54321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R7e36101782984bea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R983ac1f63b5b4e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R76201da1b8b34104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R51a155331f904249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R5ef0f4c5e673403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Production" sheetId="15" r:id="Rb18515b98bd14dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLAP Assessment SQL" sheetId="16" r:id="Rca4c901941ff47c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -101,7 +102,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="36">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -136,6 +137,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -408,7 +414,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="129">
+  <x:cellXfs count="132">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -690,6 +696,11 @@
     <x:xf numFmtId="0" fontId="11" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2597,7 +2608,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ca0b1d095934b11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf252e8990e2d478d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8100,6 +8111,1585 @@
       </x:c>
       <x:c r="H29" s="93" t="str">
         <x:v>Pause writers, reconcile post-cutover SQL rows back to Money, then restore app versions. Version rollback alone is insufficient.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="23" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="35" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="131" t="str">
+        <x:v>Experiment</x:v>
+      </x:c>
+      <x:c r="B1" s="131" t="str">
+        <x:v>App version</x:v>
+      </x:c>
+      <x:c r="C1" s="131" t="str">
+        <x:v>Table</x:v>
+      </x:c>
+      <x:c r="D1" s="131" t="str">
+        <x:v>Column / setting</x:v>
+      </x:c>
+      <x:c r="E1" s="131" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="F1" s="131" t="str">
+        <x:v>Scope / status</x:v>
+      </x:c>
+      <x:c r="G1" s="131" t="str">
+        <x:v>Purpose / dependencies</x:v>
+      </x:c>
+      <x:c r="H1" s="131" t="str">
+        <x:v>Exact definition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="65" customHeight="1">
+      <x:c r="A2" s="93" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="B2" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C2" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D2" s="93" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="E2" s="93" t="str">
+        <x:v>PostgreSQL view</x:v>
+      </x:c>
+      <x:c r="F2" s="93" t="str">
+        <x:v>Test copy only; review pending</x:v>
+      </x:c>
+      <x:c r="G2" s="93" t="str">
+        <x:v>Own input/result table; reads shared financial data</x:v>
+      </x:c>
+      <x:c r="H2" s="93" t="str">
+        <x:v>public.Loan Assessment SQL Lab View → public.Loan Assessment SQL Lab</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="65" customHeight="1">
+      <x:c r="A3" s="93" t="str">
+        <x:v>Scope</x:v>
+      </x:c>
+      <x:c r="B3" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C3" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D3" s="93" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="E3" s="93" t="str">
+        <x:v>Generated SQL view</x:v>
+      </x:c>
+      <x:c r="F3" s="93" t="str">
+        <x:v>Test copy only; read-only</x:v>
+      </x:c>
+      <x:c r="G3" s="93" t="str">
+        <x:v>153 dates retained for Daily Analytics; 16 assessment VCs removed</x:v>
+      </x:c>
+      <x:c r="H3" s="93" t="str">
+        <x:v>public.OLAP Calendar SQL Lab; 2026-08-01 through 2026-12-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="65" customHeight="1">
+      <x:c r="A4" s="93" t="str">
+        <x:v>Rollback</x:v>
+      </x:c>
+      <x:c r="B4" s="93" t="str">
+        <x:v>1.000013</x:v>
+      </x:c>
+      <x:c r="C4" s="93" t="str">
+        <x:v>OLAP test copy</x:v>
+      </x:c>
+      <x:c r="D4" s="93" t="str">
+        <x:v>Restore app version</x:v>
+      </x:c>
+      <x:c r="E4" s="93" t="str">
+        <x:v>AppSheet version</x:v>
+      </x:c>
+      <x:c r="F4" s="93" t="str">
+        <x:v>Production versions unchanged</x:v>
+      </x:c>
+      <x:c r="G4" s="93" t="str">
+        <x:v>Production OLAP 1.100046; OLTP 3.000069</x:v>
+      </x:c>
+      <x:c r="H4" s="93" t="str">
+        <x:v>Restores original Loan Assessment source and Calendar Help Table / Sheet1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="65" customHeight="1">
+      <x:c r="A5" s="93" t="str">
+        <x:v>Workflow</x:v>
+      </x:c>
+      <x:c r="B5" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C5" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D5" s="93" t="str">
+        <x:v>Refresh Assessment</x:v>
+      </x:c>
+      <x:c r="E5" s="93" t="str">
+        <x:v>Data action</x:v>
+      </x:c>
+      <x:c r="F5" s="93" t="str">
+        <x:v>Test copy only</x:v>
+      </x:c>
+      <x:c r="G5" s="93" t="str">
+        <x:v>Trigger recalculates current row; result timestamp shown</x:v>
+      </x:c>
+      <x:c r="H5" s="93" t="str">
+        <x:v>SQL Refresh Token = UNIQUEID()</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="65" customHeight="1">
+      <x:c r="A6" s="93" t="str">
+        <x:v>Freshness</x:v>
+      </x:c>
+      <x:c r="B6" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C6" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D6" s="93" t="str">
+        <x:v>SQL Source Current</x:v>
+      </x:c>
+      <x:c r="E6" s="93" t="str">
+        <x:v>View calculation</x:v>
+      </x:c>
+      <x:c r="F6" s="93" t="str">
+        <x:v>Checked on sync</x:v>
+      </x:c>
+      <x:c r="G6" s="93" t="str">
+        <x:v>Source fingerprint/date mismatch hides stale outputs; offline changes require sync</x:v>
+      </x:c>
+      <x:c r="H6" s="93" t="str">
+        <x:v>assessment_lab.fingerprint(assessment_lab.inputs(Ref Borrower)); Bangkok as-of date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="65" customHeight="1">
+      <x:c r="A7" s="93" t="str">
+        <x:v>Window</x:v>
+      </x:c>
+      <x:c r="B7" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C7" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D7" s="93" t="str">
+        <x:v>Forecast boundaries</x:v>
+      </x:c>
+      <x:c r="E7" s="93" t="str">
+        <x:v>Explicit dates</x:v>
+      </x:c>
+      <x:c r="F7" s="93" t="str">
+        <x:v>Like-for-like test window</x:v>
+      </x:c>
+      <x:c r="G7" s="93" t="str">
+        <x:v>Rolling horizon and shared/per-user input workflow require review before cutover</x:v>
+      </x:c>
+      <x:c r="H7" s="93" t="str">
+        <x:v>SQL Forecast Start 2026-08-01; SQL Forecast End 2026-12-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="65" customHeight="1">
+      <x:c r="A8" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B8" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C8" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D8" s="93" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="E8" s="93" t="str">
+        <x:v>Physical / Number</x:v>
+      </x:c>
+      <x:c r="F8" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G8" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H8" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="65" customHeight="1">
+      <x:c r="A9" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B9" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C9" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D9" s="93" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="E9" s="93" t="str">
+        <x:v>Physical / Date</x:v>
+      </x:c>
+      <x:c r="F9" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G9" s="93" t="str">
+        <x:v>Key Yes; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H9" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="65" customHeight="1">
+      <x:c r="A10" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B10" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C10" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D10" s="93" t="str">
+        <x:v>Year</x:v>
+      </x:c>
+      <x:c r="E10" s="93" t="str">
+        <x:v>VC / Number</x:v>
+      </x:c>
+      <x:c r="F10" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G10" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H10" s="93" t="str">
+        <x:v>YEAR([Date])</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="65" customHeight="1">
+      <x:c r="A11" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B11" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C11" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D11" s="93" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="E11" s="93" t="str">
+        <x:v>VC / Number</x:v>
+      </x:c>
+      <x:c r="F11" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G11" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H11" s="93" t="str">
+        <x:v>MONTH([Date])</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="65" customHeight="1">
+      <x:c r="A12" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B12" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C12" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D12" s="93" t="str">
+        <x:v>Month Name</x:v>
+      </x:c>
+      <x:c r="E12" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F12" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G12" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H12" s="93" t="str">
+        <x:v>TEXT([Date], "MMMM")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="65" customHeight="1">
+      <x:c r="A13" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B13" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C13" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D13" s="93" t="str">
+        <x:v>Year Month</x:v>
+      </x:c>
+      <x:c r="E13" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F13" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G13" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H13" s="93" t="str">
+        <x:v>TEXT([Date], "YYYY-MM")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="65" customHeight="1">
+      <x:c r="A14" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B14" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C14" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D14" s="93" t="str">
+        <x:v>Week</x:v>
+      </x:c>
+      <x:c r="E14" s="93" t="str">
+        <x:v>VC / Number</x:v>
+      </x:c>
+      <x:c r="F14" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G14" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H14" s="93" t="str">
+        <x:v>WEEKNUM([Date])</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="65" customHeight="1">
+      <x:c r="A15" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B15" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C15" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D15" s="93" t="str">
+        <x:v>Year Week</x:v>
+      </x:c>
+      <x:c r="E15" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F15" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G15" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H15" s="93" t="str">
+        <x:v>CONCATENATE(YEAR([Date]), "-W", RIGHT("0" &amp; WEEKNUM([Date]), 2))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="65" customHeight="1">
+      <x:c r="A16" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B16" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C16" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D16" s="93" t="str">
+        <x:v>Week Start</x:v>
+      </x:c>
+      <x:c r="E16" s="93" t="str">
+        <x:v>VC / Date</x:v>
+      </x:c>
+      <x:c r="F16" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G16" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H16" s="93" t="str">
+        <x:v>[Date] - MOD(WEEKDAY([Date]) + 5, 7)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="65" customHeight="1">
+      <x:c r="A17" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B17" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C17" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D17" s="93" t="str">
+        <x:v>Quarter</x:v>
+      </x:c>
+      <x:c r="E17" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F17" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G17" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H17" s="93" t="str">
+        <x:v>CONCATENATE( "Q", CEILING(MONTH([Date]) / 3) )</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="65" customHeight="1">
+      <x:c r="A18" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B18" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C18" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D18" s="93" t="str">
+        <x:v>Day of Week</x:v>
+      </x:c>
+      <x:c r="E18" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F18" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G18" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H18" s="93" t="str">
+        <x:v>TEXT([Date], "dddd")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="65" customHeight="1">
+      <x:c r="A19" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B19" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C19" s="93" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D19" s="93" t="str">
+        <x:v>Day of Month</x:v>
+      </x:c>
+      <x:c r="E19" s="93" t="str">
+        <x:v>VC / Number</x:v>
+      </x:c>
+      <x:c r="F19" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G19" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H19" s="93" t="str">
+        <x:v>DAY([Date])</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="65" customHeight="1">
+      <x:c r="A20" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B20" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C20" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D20" s="93" t="str">
+        <x:v>_RowNumber</x:v>
+      </x:c>
+      <x:c r="E20" s="93" t="str">
+        <x:v>Physical / Number</x:v>
+      </x:c>
+      <x:c r="F20" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G20" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H20" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="65" customHeight="1">
+      <x:c r="A21" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B21" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C21" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D21" s="93" t="str">
+        <x:v>Row ID</x:v>
+      </x:c>
+      <x:c r="E21" s="93" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="F21" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G21" s="93" t="str">
+        <x:v>Key Yes; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H21" s="93" t="str">
+        <x:v>UNIQUEID("PackedUUID")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="65" customHeight="1">
+      <x:c r="A22" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B22" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C22" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D22" s="93" t="str">
+        <x:v>Assessment ID</x:v>
+      </x:c>
+      <x:c r="E22" s="93" t="str">
+        <x:v>Physical / Text</x:v>
+      </x:c>
+      <x:c r="F22" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G22" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H22" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="65" customHeight="1">
+      <x:c r="A23" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B23" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C23" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D23" s="93" t="str">
+        <x:v>Ref Borrower</x:v>
+      </x:c>
+      <x:c r="E23" s="93" t="str">
+        <x:v>Physical / Ref</x:v>
+      </x:c>
+      <x:c r="F23" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G23" s="93" t="str">
+        <x:v>Key No; read-only No; hidden No</x:v>
+      </x:c>
+      <x:c r="H23" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="65" customHeight="1">
+      <x:c r="A24" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B24" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C24" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D24" s="93" t="str">
+        <x:v>Proposed Loan Amount</x:v>
+      </x:c>
+      <x:c r="E24" s="93" t="str">
+        <x:v>Physical / Price</x:v>
+      </x:c>
+      <x:c r="F24" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G24" s="93" t="str">
+        <x:v>Key No; read-only No; hidden No</x:v>
+      </x:c>
+      <x:c r="H24" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="65" customHeight="1">
+      <x:c r="A25" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B25" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C25" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D25" s="93" t="str">
+        <x:v>Minimum Daily Profit Rate</x:v>
+      </x:c>
+      <x:c r="E25" s="93" t="str">
+        <x:v>Physical / Percent</x:v>
+      </x:c>
+      <x:c r="F25" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G25" s="93" t="str">
+        <x:v>Key No; read-only No; hidden No</x:v>
+      </x:c>
+      <x:c r="H25" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="65" customHeight="1">
+      <x:c r="A26" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B26" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C26" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D26" s="93" t="str">
+        <x:v>SQL Current Principal</x:v>
+      </x:c>
+      <x:c r="E26" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F26" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G26" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H26" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="65" customHeight="1">
+      <x:c r="A27" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B27" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C27" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D27" s="93" t="str">
+        <x:v>SQL Interest Received</x:v>
+      </x:c>
+      <x:c r="E27" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F27" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G27" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H27" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="65" customHeight="1">
+      <x:c r="A28" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B28" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C28" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D28" s="93" t="str">
+        <x:v>SQL Eligible Date</x:v>
+      </x:c>
+      <x:c r="E28" s="93" t="str">
+        <x:v>Physical / Date</x:v>
+      </x:c>
+      <x:c r="F28" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G28" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H28" s="93" t="str">
+        <x:v>TODAY()</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="65" customHeight="1">
+      <x:c r="A29" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B29" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C29" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D29" s="93" t="str">
+        <x:v>SQL Eligible Interest</x:v>
+      </x:c>
+      <x:c r="E29" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F29" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G29" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H29" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="65" customHeight="1">
+      <x:c r="A30" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B30" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C30" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D30" s="93" t="str">
+        <x:v>SQL Eligible Principal</x:v>
+      </x:c>
+      <x:c r="E30" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F30" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G30" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H30" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="65" customHeight="1">
+      <x:c r="A31" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B31" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C31" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D31" s="93" t="str">
+        <x:v>SQL Eligible Profit</x:v>
+      </x:c>
+      <x:c r="E31" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F31" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G31" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H31" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="65" customHeight="1">
+      <x:c r="A32" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B32" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C32" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D32" s="93" t="str">
+        <x:v>SQL Eligible Coverage</x:v>
+      </x:c>
+      <x:c r="E32" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F32" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G32" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H32" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="65" customHeight="1">
+      <x:c r="A33" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B33" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C33" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D33" s="93" t="str">
+        <x:v>SQL Eligible Margin</x:v>
+      </x:c>
+      <x:c r="E33" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F33" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G33" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H33" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="65" customHeight="1">
+      <x:c r="A34" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B34" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C34" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D34" s="93" t="str">
+        <x:v>SQL Current Margin</x:v>
+      </x:c>
+      <x:c r="E34" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F34" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G34" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H34" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="65" customHeight="1">
+      <x:c r="A35" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B35" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C35" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D35" s="93" t="str">
+        <x:v>SQL Calculated At</x:v>
+      </x:c>
+      <x:c r="E35" s="93" t="str">
+        <x:v>Physical / DateTime</x:v>
+      </x:c>
+      <x:c r="F35" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G35" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H35" s="93" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="65" customHeight="1">
+      <x:c r="A36" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B36" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C36" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D36" s="93" t="str">
+        <x:v>SQL As Of</x:v>
+      </x:c>
+      <x:c r="E36" s="93" t="str">
+        <x:v>Physical / Date</x:v>
+      </x:c>
+      <x:c r="F36" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G36" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H36" s="93" t="str">
+        <x:v>TODAY()</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="65" customHeight="1">
+      <x:c r="A37" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B37" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C37" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D37" s="93" t="str">
+        <x:v>SQL Forecast Start</x:v>
+      </x:c>
+      <x:c r="E37" s="93" t="str">
+        <x:v>Physical / Date</x:v>
+      </x:c>
+      <x:c r="F37" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G37" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H37" s="93" t="str">
+        <x:v>TODAY()</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="65" customHeight="1">
+      <x:c r="A38" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B38" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C38" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D38" s="93" t="str">
+        <x:v>SQL Forecast End</x:v>
+      </x:c>
+      <x:c r="E38" s="93" t="str">
+        <x:v>Physical / Date</x:v>
+      </x:c>
+      <x:c r="F38" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G38" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H38" s="93" t="str">
+        <x:v>TODAY()</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="65" customHeight="1">
+      <x:c r="A39" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B39" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C39" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D39" s="93" t="str">
+        <x:v>SQL Refresh Token</x:v>
+      </x:c>
+      <x:c r="E39" s="93" t="str">
+        <x:v>Physical / LongText</x:v>
+      </x:c>
+      <x:c r="F39" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G39" s="93" t="str">
+        <x:v>Key No; read-only No; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H39" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="65" customHeight="1">
+      <x:c r="A40" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B40" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C40" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D40" s="93" t="str">
+        <x:v>SQL Source Fingerprint</x:v>
+      </x:c>
+      <x:c r="E40" s="93" t="str">
+        <x:v>Physical / LongText</x:v>
+      </x:c>
+      <x:c r="F40" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G40" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H40" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="65" customHeight="1">
+      <x:c r="A41" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B41" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C41" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D41" s="93" t="str">
+        <x:v>SQL Input Borrower</x:v>
+      </x:c>
+      <x:c r="E41" s="93" t="str">
+        <x:v>Physical / LongText</x:v>
+      </x:c>
+      <x:c r="F41" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G41" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H41" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="65" customHeight="1">
+      <x:c r="A42" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B42" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C42" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D42" s="93" t="str">
+        <x:v>SQL Input Amount</x:v>
+      </x:c>
+      <x:c r="E42" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F42" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G42" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H42" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="65" customHeight="1">
+      <x:c r="A43" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B43" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C43" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D43" s="93" t="str">
+        <x:v>SQL Input Rate</x:v>
+      </x:c>
+      <x:c r="E43" s="93" t="str">
+        <x:v>Physical / Decimal</x:v>
+      </x:c>
+      <x:c r="F43" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G43" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H43" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="65" customHeight="1">
+      <x:c r="A44" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B44" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C44" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D44" s="93" t="str">
+        <x:v>SQL Source Current</x:v>
+      </x:c>
+      <x:c r="E44" s="93" t="str">
+        <x:v>Physical / Yes/No</x:v>
+      </x:c>
+      <x:c r="F44" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G44" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden Yes</x:v>
+      </x:c>
+      <x:c r="H44" s="93" t="str">
+        <x:v>Stored SQL value / generated date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="100" customHeight="1">
+      <x:c r="A45" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B45" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C45" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D45" s="93" t="str">
+        <x:v>Current Outstanding Principal</x:v>
+      </x:c>
+      <x:c r="E45" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F45" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G45" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H45" s="93" t="str">
+        <x:v>IF(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000)), [SQL Current Principal], "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="100" customHeight="1">
+      <x:c r="A46" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B46" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C46" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D46" s="93" t="str">
+        <x:v>Interest Earned from Active Loans</x:v>
+      </x:c>
+      <x:c r="E46" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F46" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G46" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H46" s="93" t="str">
+        <x:v>IF(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000)), [SQL Interest Received], "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="100" customHeight="1">
+      <x:c r="A47" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B47" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C47" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D47" s="93" t="str">
+        <x:v>Earliest Eligible Date</x:v>
+      </x:c>
+      <x:c r="E47" s="93" t="str">
+        <x:v>VC / Date</x:v>
+      </x:c>
+      <x:c r="F47" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G47" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H47" s="93" t="str">
+        <x:v>IF(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000)), [SQL Eligible Date], "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="65" customHeight="1">
+      <x:c r="A48" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B48" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C48" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D48" s="93" t="str">
+        <x:v>Days Until Eligible</x:v>
+      </x:c>
+      <x:c r="E48" s="93" t="str">
+        <x:v>VC / Number</x:v>
+      </x:c>
+      <x:c r="F48" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G48" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H48" s="93" t="str">
+        <x:v>IF( ISBLANK([Earliest Eligible Date]), "", TOTALHOURS([Earliest Eligible Date] - TODAY()) / 24 )</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="100" customHeight="1">
+      <x:c r="A49" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B49" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C49" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D49" s="93" t="str">
+        <x:v>Projected Interest at Eligible Date</x:v>
+      </x:c>
+      <x:c r="E49" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F49" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G49" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H49" s="93" t="str">
+        <x:v>IF(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000)), [SQL Eligible Interest], "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="100" customHeight="1">
+      <x:c r="A50" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B50" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C50" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D50" s="93" t="str">
+        <x:v>Outstanding Principal at Eligible Date</x:v>
+      </x:c>
+      <x:c r="E50" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F50" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G50" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H50" s="93" t="str">
+        <x:v>IF(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000)), [SQL Eligible Principal], "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="100" customHeight="1">
+      <x:c r="A51" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B51" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C51" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D51" s="93" t="str">
+        <x:v>Minimum Profit at Eligible Date</x:v>
+      </x:c>
+      <x:c r="E51" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F51" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G51" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H51" s="93" t="str">
+        <x:v>IF(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000)), [SQL Eligible Profit], "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="100" customHeight="1">
+      <x:c r="A52" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B52" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C52" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D52" s="93" t="str">
+        <x:v>Required Coverage at Eligible Date</x:v>
+      </x:c>
+      <x:c r="E52" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F52" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G52" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H52" s="93" t="str">
+        <x:v>IF(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000)), [SQL Eligible Coverage], "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="100" customHeight="1">
+      <x:c r="A53" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B53" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C53" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D53" s="93" t="str">
+        <x:v>Safety Margin</x:v>
+      </x:c>
+      <x:c r="E53" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F53" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G53" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H53" s="93" t="str">
+        <x:v>IF(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000)), [SQL Eligible Margin], "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="100" customHeight="1">
+      <x:c r="A54" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B54" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C54" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D54" s="93" t="str">
+        <x:v>Current Coverage Margin</x:v>
+      </x:c>
+      <x:c r="E54" s="93" t="str">
+        <x:v>VC / Price</x:v>
+      </x:c>
+      <x:c r="F54" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G54" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H54" s="93" t="str">
+        <x:v>IF(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000)), [SQL Current Margin], "")</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="65" customHeight="1">
+      <x:c r="A55" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B55" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C55" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D55" s="93" t="str">
+        <x:v>Coverage Ratio at Eligible Date</x:v>
+      </x:c>
+      <x:c r="E55" s="93" t="str">
+        <x:v>VC / Percent</x:v>
+      </x:c>
+      <x:c r="F55" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G55" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H55" s="93" t="str">
+        <x:v>IF( [Required Coverage at Eligible Date] &gt; 0, [Projected Interest at Eligible Date] / [Required Coverage at Eligible Date], 0 )</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="100" customHeight="1">
+      <x:c r="A56" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B56" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C56" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D56" s="93" t="str">
+        <x:v>Recommendation Status</x:v>
+      </x:c>
+      <x:c r="E56" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F56" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G56" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H56" s="93" t="str">
+        <x:v>IF(NOT(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000))), "ต้องคำนวณใหม่ / Refresh required", IFS( ISBLANK([Earliest Eligible Date]), "ยังไม่ผ่านเกณฑ์ - Not Eligible", [Earliest Eligible Date] &lt;= TODAY(), "ปล่อยกู้ได้ตอนนี้ - Eligible Now", TRUE, "ควรรอก่อน - Wait" ))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="180" customHeight="1">
+      <x:c r="A57" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B57" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C57" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D57" s="93" t="str">
+        <x:v>Recommendation</x:v>
+      </x:c>
+      <x:c r="E57" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F57" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G57" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H57" s="93" t="str">
+        <x:v>IF(NOT(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000))), "กรุณาคำนวณใหม่และซิงค์ / Refresh assessment and sync before using this result", CONCATENATE(IFS( ISBLANK([Ref Borrower]), "กรุณาเลือกผู้กู้ / Select a borrower", OR(ISBLANK([Proposed Loan Amount]), [Proposed Loan Amount] &lt;= 0), "กรุณากรอกวงเงินกู้ที่เสนอ / Enter the proposed loan amount", OR(ISBLANK([Minimum Daily Profit Rate]), [Minimum Daily Profit Rate] &lt;= 0), "กรุณากรอกอัตรากำไรขั้นต่ำ / Enter the minimum profit rate", ISBLANK([Earliest Eligible Date]), "ไม่พบวันที่ผ่านเกณฑ์ภายในช่วงเวลาที่ประเมิน / No eligible date found within the forecast period", [Earliest Eligible Date] = TODAY(), "สามารถปล่อยกู้ได้วันนี้ / Eligible to issue the loan today", TRUE, CONCATENATE( "วันที่แนะนำให้ปล่อยกู้ได้เร็วที่สุด / Earliest recommended issue date: ", TEXT([Earliest Eligible Date], "DD/MM/YYYY") ) ), " | คำนวณเมื่อ / Calculated: ", TEXT([SQL Calculated At], "DD/MM/YYYY HH:MM:SS")))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="65" customHeight="1">
+      <x:c r="A58" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B58" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C58" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D58" s="93" t="str">
+        <x:v>Header - Current Position</x:v>
+      </x:c>
+      <x:c r="E58" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F58" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G58" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H58" s="93" t="str">
+        <x:v>"──── สถานะปัจจุบัน / Current Position ────"</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="65" customHeight="1">
+      <x:c r="A59" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B59" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C59" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D59" s="93" t="str">
+        <x:v>Header - Recommendation</x:v>
+      </x:c>
+      <x:c r="E59" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F59" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G59" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H59" s="93" t="str">
+        <x:v>"──── คำแนะนำ / Recommendation ────"</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="65" customHeight="1">
+      <x:c r="A60" s="93" t="str">
+        <x:v>SQL assessment</x:v>
+      </x:c>
+      <x:c r="B60" s="93" t="str">
+        <x:v>1.000022</x:v>
+      </x:c>
+      <x:c r="C60" s="93" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D60" s="93" t="str">
+        <x:v>Header - Calculation</x:v>
+      </x:c>
+      <x:c r="E60" s="93" t="str">
+        <x:v>VC / Text</x:v>
+      </x:c>
+      <x:c r="F60" s="93" t="str">
+        <x:v>Test copy only; production unchanged</x:v>
+      </x:c>
+      <x:c r="G60" s="93" t="str">
+        <x:v>Key No; read-only Yes; hidden No</x:v>
+      </x:c>
+      <x:c r="H60" s="93" t="str">
+        <x:v>"──── รายละเอียดการคำนวณ / Calculation ────"</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8521,7 +10111,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bea91a1e86d4b56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07429ad8f8104e98"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19178,7 +20768,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9309fac28842d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d3dff0a11164357"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19607,7 +21197,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra424ecf4053142ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669e4d0221e5439f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20067,7 +21657,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47b05cd0d51b479b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6d88fa538394de0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27041,7 +28631,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f4cef7ad5234c95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9c980a0a0954b6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31660,7 +33250,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68a4b3d789b5468f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaf3505c63164994"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31859,7 +33449,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R121cfdcf720d426f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1af788574afb429b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33512,7 +35102,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re27eaf22dae84519"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd0432557b1542a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc75993a5ae9741b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R8e1e9dad4c3c4fc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R811906d220094419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rb33b55c9f30e43c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Re59298d9cf21435f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Re38426ef954f449c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Re659dca2847d4cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R110eb759a3d54f14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rcb9cca1bacd54321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R7e36101782984bea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R983ac1f63b5b4e99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R76201da1b8b34104"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R51a155331f904249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R5ef0f4c5e673403b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Production" sheetId="15" r:id="Rb18515b98bd14dcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLAP Assessment SQL" sheetId="16" r:id="Rca4c901941ff47c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R65c5c2b4935747f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rbde9266364574c37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rf298e23b877f4dac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rd56e44aed9fe450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Recd9fd0e796e40f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rccd61c6a98944262"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rd01ac0ffe8b24a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R8e2f6f2d8cb0447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R5822318f31644305"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R76c1f0296e444599"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R2451753417b14c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R8a9930d95e3f4412"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="Rb3240f1e473642c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R50e17d3d49234d10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Production" sheetId="15" r:id="Rdfacc9061291421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLAP Assessment SQL" sheetId="16" r:id="R8642b05e82c94094"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2608,7 +2608,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf252e8990e2d478d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3b96f9a4cc84023"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8163,7 +8163,7 @@
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B2" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C2" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8189,7 +8189,7 @@
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B3" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C3" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8241,25 +8241,25 @@
         <x:v>Workflow</x:v>
       </x:c>
       <x:c r="B5" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C5" s="93" t="str">
         <x:v>Loan Assessment</x:v>
       </x:c>
       <x:c r="D5" s="93" t="str">
-        <x:v>Refresh Assessment</x:v>
+        <x:v>Save inputs</x:v>
       </x:c>
       <x:c r="E5" s="93" t="str">
-        <x:v>Data action</x:v>
+        <x:v>Normal app update</x:v>
       </x:c>
       <x:c r="F5" s="93" t="str">
         <x:v>Test copy only</x:v>
       </x:c>
       <x:c r="G5" s="93" t="str">
-        <x:v>Trigger recalculates current row; result timestamp shown</x:v>
+        <x:v>No separate refresh action. Input save invokes existing database triggers.</x:v>
       </x:c>
       <x:c r="H5" s="93" t="str">
-        <x:v>SQL Refresh Token = UNIQUEID()</x:v>
+        <x:v>Input update → database calculation → automatic sync returns stored results.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="65" customHeight="1">
@@ -8267,7 +8267,7 @@
         <x:v>Freshness</x:v>
       </x:c>
       <x:c r="B6" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C6" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8293,7 +8293,7 @@
         <x:v>Window</x:v>
       </x:c>
       <x:c r="B7" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C7" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8319,7 +8319,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B8" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C8" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8345,7 +8345,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B9" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C9" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8371,7 +8371,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B10" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C10" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8397,7 +8397,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B11" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C11" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8423,7 +8423,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B12" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C12" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8449,7 +8449,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B13" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C13" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8475,7 +8475,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B14" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C14" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8501,7 +8501,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B15" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C15" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8527,7 +8527,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B16" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C16" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8553,7 +8553,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B17" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C17" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8579,7 +8579,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B18" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C18" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8605,7 +8605,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B19" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C19" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8631,7 +8631,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B20" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C20" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8657,7 +8657,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B21" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C21" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8683,7 +8683,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B22" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C22" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8709,7 +8709,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B23" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C23" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8735,7 +8735,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B24" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C24" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8761,7 +8761,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B25" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C25" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8787,7 +8787,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B26" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C26" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8813,7 +8813,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B27" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C27" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8839,7 +8839,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B28" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C28" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8865,7 +8865,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B29" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C29" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8891,7 +8891,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B30" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C30" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8917,7 +8917,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B31" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C31" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8943,7 +8943,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B32" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C32" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8969,7 +8969,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B33" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C33" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8995,7 +8995,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B34" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C34" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9021,7 +9021,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B35" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C35" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9047,7 +9047,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B36" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C36" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9073,7 +9073,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B37" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C37" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9099,7 +9099,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B38" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C38" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9125,7 +9125,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B39" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C39" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9151,7 +9151,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B40" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C40" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9177,7 +9177,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B41" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C41" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9203,7 +9203,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B42" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C42" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9229,7 +9229,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B43" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C43" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9255,7 +9255,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B44" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C44" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9281,7 +9281,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B45" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C45" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9307,7 +9307,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B46" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C46" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9333,7 +9333,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B47" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C47" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9359,7 +9359,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B48" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C48" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9385,7 +9385,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B49" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C49" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9411,7 +9411,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B50" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C50" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9437,7 +9437,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B51" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C51" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9463,7 +9463,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B52" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C52" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9489,7 +9489,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B53" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C53" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9515,7 +9515,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B54" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C54" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9541,7 +9541,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B55" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C55" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9567,7 +9567,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B56" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C56" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9585,15 +9585,15 @@
         <x:v>Key No; read-only Yes; hidden No</x:v>
       </x:c>
       <x:c r="H56" s="93" t="str">
-        <x:v>IF(NOT(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000))), "ต้องคำนวณใหม่ / Refresh required", IFS( ISBLANK([Earliest Eligible Date]), "ยังไม่ผ่านเกณฑ์ - Not Eligible", [Earliest Eligible Date] &lt;= TODAY(), "ปล่อยกู้ได้ตอนนี้ - Eligible Now", TRUE, "ควรรอก่อน - Wait" ))</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="180" customHeight="1">
+        <x:v>IF(NOT(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000))), IF(NOT(AND([Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000))), "กำลังรอผล / Awaiting results", "ผลไม่เป็นปัจจุบัน / Out of date"), IFS( ISBLANK([Earliest Eligible Date]), "ยังไม่ผ่านเกณฑ์ - Not Eligible", [Earliest Eligible Date] &lt;= TODAY(), "ปล่อยกู้ได้ตอนนี้ - Eligible Now", TRUE, "ควรรอก่อน - Wait" ))</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="260" customHeight="1">
       <x:c r="A57" s="93" t="str">
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B57" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C57" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9611,7 +9611,7 @@
         <x:v>Key No; read-only Yes; hidden No</x:v>
       </x:c>
       <x:c r="H57" s="93" t="str">
-        <x:v>IF(NOT(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000))), "กรุณาคำนวณใหม่และซิงค์ / Refresh assessment and sync before using this result", CONCATENATE(IFS( ISBLANK([Ref Borrower]), "กรุณาเลือกผู้กู้ / Select a borrower", OR(ISBLANK([Proposed Loan Amount]), [Proposed Loan Amount] &lt;= 0), "กรุณากรอกวงเงินกู้ที่เสนอ / Enter the proposed loan amount", OR(ISBLANK([Minimum Daily Profit Rate]), [Minimum Daily Profit Rate] &lt;= 0), "กรุณากรอกอัตรากำไรขั้นต่ำ / Enter the minimum profit rate", ISBLANK([Earliest Eligible Date]), "ไม่พบวันที่ผ่านเกณฑ์ภายในช่วงเวลาที่ประเมิน / No eligible date found within the forecast period", [Earliest Eligible Date] = TODAY(), "สามารถปล่อยกู้ได้วันนี้ / Eligible to issue the loan today", TRUE, CONCATENATE( "วันที่แนะนำให้ปล่อยกู้ได้เร็วที่สุด / Earliest recommended issue date: ", TEXT([Earliest Eligible Date], "DD/MM/YYYY") ) ), " | คำนวณเมื่อ / Calculated: ", TEXT([SQL Calculated At], "DD/MM/YYYY HH:MM:SS")))</x:v>
+        <x:v>IF(NOT(AND([SQL Source Current], [SQL As Of] = TODAY(), [Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000))), IF(NOT(AND([Ref Borrower] = [SQL Input Borrower], [Proposed Loan Amount] = [SQL Input Amount], ABS([Minimum Daily Profit Rate] - [SQL Input Rate]) &lt; (1.0 / 10000000))), "กำลังรอผลการคำนวณ ผลจะแสดงหลังบันทึกและซิงค์ / Waiting for calculation results. Results appear after saving and syncing.", "ผลการประเมินไม่เป็นปัจจุบัน กรุณาแก้ไขและบันทึกข้อมูลการประเมิน / Assessment is out of date. Update and save the assessment inputs."), CONCATENATE(IFS( ISBLANK([Ref Borrower]), "กรุณาเลือกผู้กู้ / Select a borrower", OR(ISBLANK([Proposed Loan Amount]), [Proposed Loan Amount] &lt;= 0), "กรุณากรอกวงเงินกู้ที่เสนอ / Enter the proposed loan amount", OR(ISBLANK([Minimum Daily Profit Rate]), [Minimum Daily Profit Rate] &lt;= 0), "กรุณากรอกอัตรากำไรขั้นต่ำ / Enter the minimum profit rate", ISBLANK([Earliest Eligible Date]), "ไม่พบวันที่ผ่านเกณฑ์ภายในช่วงเวลาที่ประเมิน / No eligible date found within the forecast period", [Earliest Eligible Date] = TODAY(), "สามารถปล่อยกู้ได้วันนี้ / Eligible to issue the loan today", TRUE, CONCATENATE( "วันที่แนะนำให้ปล่อยกู้ได้เร็วที่สุด / Earliest recommended issue date: ", TEXT([Earliest Eligible Date], "DD/MM/YYYY") ) ), " | คำนวณเมื่อ / Calculated: ", TEXT([SQL Calculated At], "DD/MM/YYYY HH:MM:SS")))</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="65" customHeight="1">
@@ -9619,7 +9619,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B58" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C58" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9645,7 +9645,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B59" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C59" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9671,7 +9671,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B60" s="93" t="str">
-        <x:v>1.000022</x:v>
+        <x:v>1.000023</x:v>
       </x:c>
       <x:c r="C60" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -10111,7 +10111,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07429ad8f8104e98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc4586c9697c4e1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20768,7 +20768,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d3dff0a11164357"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aa59a5acf934a39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21197,7 +21197,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669e4d0221e5439f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf71ee72aa27343ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21657,7 +21657,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6d88fa538394de0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87f521d7c4d14c3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28631,7 +28631,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9c980a0a0954b6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R333d4218c5024daf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33250,7 +33250,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaf3505c63164994"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4062a1612cd4af7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33449,7 +33449,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1af788574afb429b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3ef8edbc23c4505"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35102,7 +35102,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd0432557b1542a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9eb67ce2c5334b17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Documents/AppSheet_Data_Dictionary.xlsx
+++ b/Documents/AppSheet_Data_Dictionary.xlsx
@@ -2,22 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R65c5c2b4935747f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="Rbde9266364574c37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="Rf298e23b877f4dac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="Rd56e44aed9fe450d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="Recd9fd0e796e40f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="Rccd61c6a98944262"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rd01ac0ffe8b24a15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R8e2f6f2d8cb0447b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="R5822318f31644305"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R76c1f0296e444599"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R2451753417b14c4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="R8a9930d95e3f4412"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="Rb3240f1e473642c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R50e17d3d49234d10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Production" sheetId="15" r:id="Rdfacc9061291421f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLAP Assessment SQL" sheetId="16" r:id="R8642b05e82c94094"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rd0aa167cac724a17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" r:id="R4eec06431cd84f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Columns" sheetId="3" r:id="R8836cc2d5dd14bd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" r:id="R001ba3c11cfe48b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slices" sheetId="5" r:id="R901714bdf58c47ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slice Columns" sheetId="6" r:id="R3ad83d1f279148cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="App Variances" sheetId="7" r:id="Rff6f67367f1b4fbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" r:id="R432740b4fb7f4b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone" sheetId="9" r:id="Rc5609fcfd97149a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payments Clone Slices" sheetId="10" r:id="R1d2d802798b846c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Performance Lab" sheetId="11" r:id="R2e6c5caceac84c9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLTP Combined Test" sheetId="12" r:id="Rf3845f1e480a4ecb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Sync POC" sheetId="13" r:id="R61977f26d118433f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Migration Trial" sheetId="14" r:id="R4036b39eaaaa4440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Production" sheetId="15" r:id="R4129f0347a9e4d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OLAP Assessment SQL" sheetId="16" r:id="Recb23578d60c4130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SQL Development" sheetId="17" r:id="R43199f78449c45ad"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -31,7 +32,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -101,8 +102,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="37">
+  <x:fills count="39">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -137,6 +143,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -414,7 +430,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="132">
+  <x:cellXfs count="137">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
@@ -701,6 +717,21 @@
     <x:xf numFmtId="0" fontId="11" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="12" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2608,7 +2639,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3b96f9a4cc84023"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04853c1de13a408d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8163,7 +8194,7 @@
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B2" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C2" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8178,7 +8209,7 @@
         <x:v>Test copy only; review pending</x:v>
       </x:c>
       <x:c r="G2" s="93" t="str">
-        <x:v>Own input/result table; reads shared financial data</x:v>
+        <x:v>Own input/result table; development financial data on appsheet-pg-dev-20260915</x:v>
       </x:c>
       <x:c r="H2" s="93" t="str">
         <x:v>public.Loan Assessment SQL Lab View → public.Loan Assessment SQL Lab</x:v>
@@ -8189,7 +8220,7 @@
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B3" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C3" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8204,7 +8235,7 @@
         <x:v>Test copy only; read-only</x:v>
       </x:c>
       <x:c r="G3" s="93" t="str">
-        <x:v>153 dates retained for Daily Analytics; 16 assessment VCs removed</x:v>
+        <x:v>Generated date view on appsheet-pg-dev-20260915</x:v>
       </x:c>
       <x:c r="H3" s="93" t="str">
         <x:v>public.OLAP Calendar SQL Lab; 2026-08-01 through 2026-12-31</x:v>
@@ -8241,7 +8272,7 @@
         <x:v>Workflow</x:v>
       </x:c>
       <x:c r="B5" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C5" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8267,7 +8298,7 @@
         <x:v>Freshness</x:v>
       </x:c>
       <x:c r="B6" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C6" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8293,7 +8324,7 @@
         <x:v>Window</x:v>
       </x:c>
       <x:c r="B7" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C7" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8319,7 +8350,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B8" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C8" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8345,7 +8376,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B9" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C9" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8371,7 +8402,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B10" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C10" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8397,7 +8428,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B11" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C11" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8423,7 +8454,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B12" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C12" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8449,7 +8480,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B13" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C13" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8475,7 +8506,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B14" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C14" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8501,7 +8532,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B15" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C15" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8527,7 +8558,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B16" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C16" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8553,7 +8584,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B17" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C17" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8579,7 +8610,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B18" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C18" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8605,7 +8636,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B19" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C19" s="93" t="str">
         <x:v>Calendar</x:v>
@@ -8631,7 +8662,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B20" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C20" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8657,7 +8688,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B21" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C21" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8683,7 +8714,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B22" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C22" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8709,7 +8740,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B23" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C23" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8735,7 +8766,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B24" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C24" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8761,7 +8792,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B25" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C25" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8787,7 +8818,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B26" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C26" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8813,7 +8844,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B27" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C27" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8839,7 +8870,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B28" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C28" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8865,7 +8896,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B29" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C29" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8891,7 +8922,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B30" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C30" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8917,7 +8948,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B31" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C31" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8943,7 +8974,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B32" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C32" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8969,7 +9000,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B33" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C33" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -8995,7 +9026,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B34" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C34" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9021,7 +9052,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B35" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C35" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9047,7 +9078,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B36" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C36" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9073,7 +9104,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B37" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C37" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9099,7 +9130,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B38" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C38" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9125,7 +9156,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B39" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C39" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9151,7 +9182,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B40" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C40" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9177,7 +9208,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B41" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C41" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9203,7 +9234,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B42" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C42" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9229,7 +9260,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B43" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C43" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9255,7 +9286,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B44" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C44" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9281,7 +9312,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B45" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C45" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9307,7 +9338,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B46" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C46" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9333,7 +9364,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B47" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C47" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9359,7 +9390,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B48" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C48" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9385,7 +9416,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B49" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C49" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9411,7 +9442,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B50" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C50" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9437,7 +9468,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B51" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C51" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9463,7 +9494,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B52" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C52" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9489,7 +9520,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B53" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C53" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9515,7 +9546,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B54" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C54" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9541,7 +9572,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B55" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C55" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9567,7 +9598,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B56" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C56" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9593,7 +9624,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B57" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C57" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9619,7 +9650,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B58" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C58" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9645,7 +9676,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B59" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C59" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9671,7 +9702,7 @@
         <x:v>SQL assessment</x:v>
       </x:c>
       <x:c r="B60" s="93" t="str">
-        <x:v>1.000023</x:v>
+        <x:v>1.000025</x:v>
       </x:c>
       <x:c r="C60" s="93" t="str">
         <x:v>Loan Assessment</x:v>
@@ -9690,6 +9721,597 @@
       </x:c>
       <x:c r="H60" s="93" t="str">
         <x:v>"──── รายละเอียดการคำนวณ / Calculation ────"</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="60" customHeight="1">
+      <x:c r="A1" s="136" t="str">
+        <x:v>App</x:v>
+      </x:c>
+      <x:c r="B1" s="136" t="str">
+        <x:v>Version</x:v>
+      </x:c>
+      <x:c r="C1" s="136" t="str">
+        <x:v>Logical table</x:v>
+      </x:c>
+      <x:c r="D1" s="136" t="str">
+        <x:v>Source path</x:v>
+      </x:c>
+      <x:c r="E1" s="136" t="str">
+        <x:v>Data source</x:v>
+      </x:c>
+      <x:c r="F1" s="136" t="str">
+        <x:v>Instance</x:v>
+      </x:c>
+      <x:c r="G1" s="136" t="str">
+        <x:v>Database</x:v>
+      </x:c>
+      <x:c r="H1" s="136" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="60" customHeight="1">
+      <x:c r="A2" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B2" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C2" s="73" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D2" s="73" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="E2" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F2" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G2" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H2" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="60" customHeight="1">
+      <x:c r="A3" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B3" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C3" s="73" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D3" s="73" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="E3" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F3" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G3" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H3" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="60" customHeight="1">
+      <x:c r="A4" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B4" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C4" s="73" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D4" s="73" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="E4" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F4" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G4" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H4" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="60" customHeight="1">
+      <x:c r="A5" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B5" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C5" s="73" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D5" s="73" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="E5" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F5" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G5" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H5" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
+      <x:c r="A6" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B6" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C6" s="73" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D6" s="73" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="E6" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F6" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G6" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H6" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="60" customHeight="1">
+      <x:c r="A7" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B7" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C7" s="73" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="D7" s="73" t="str">
+        <x:v>OLAP Calendar SQL Lab</x:v>
+      </x:c>
+      <x:c r="E7" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F7" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G7" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H7" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="60" customHeight="1">
+      <x:c r="A8" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B8" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C8" s="73" t="str">
+        <x:v>Loan Assessment</x:v>
+      </x:c>
+      <x:c r="D8" s="73" t="str">
+        <x:v>Loan Assessment SQL Lab View</x:v>
+      </x:c>
+      <x:c r="E8" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F8" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G8" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H8" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="60" customHeight="1">
+      <x:c r="A9" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B9" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C9" s="73" t="str">
+        <x:v>Cash Pool Contributions</x:v>
+      </x:c>
+      <x:c r="D9" s="73" t="str">
+        <x:v>Cash Pool Contributions</x:v>
+      </x:c>
+      <x:c r="E9" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F9" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G9" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H9" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="60" customHeight="1">
+      <x:c r="A10" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B10" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C10" s="73" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="D10" s="73" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="E10" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F10" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G10" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H10" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="60" customHeight="1">
+      <x:c r="A11" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B11" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C11" s="73" t="str">
+        <x:v>Settlements</x:v>
+      </x:c>
+      <x:c r="D11" s="73" t="str">
+        <x:v>Settlements</x:v>
+      </x:c>
+      <x:c r="E11" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F11" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G11" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H11" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="60" customHeight="1">
+      <x:c r="A12" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B12" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C12" s="73" t="str">
+        <x:v>Daily Analytics</x:v>
+      </x:c>
+      <x:c r="D12" s="73" t="str">
+        <x:v>Daily Analytics</x:v>
+      </x:c>
+      <x:c r="E12" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F12" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G12" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H12" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="60" customHeight="1">
+      <x:c r="A13" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B13" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C13" s="73" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D13" s="73" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="E13" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F13" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G13" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H13" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="60" customHeight="1">
+      <x:c r="A14" s="73" t="str">
+        <x:v>LoanInsights PG Trial 20260914</x:v>
+      </x:c>
+      <x:c r="B14" s="73" t="str">
+        <x:v>1.000025</x:v>
+      </x:c>
+      <x:c r="C14" s="73" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D14" s="73" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="E14" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F14" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G14" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H14" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="60" customHeight="1">
+      <x:c r="A15" s="73" t="str">
+        <x:v>LoanMgr PG Test 20260914</x:v>
+      </x:c>
+      <x:c r="B15" s="73" t="str">
+        <x:v>1.000011</x:v>
+      </x:c>
+      <x:c r="C15" s="73" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="D15" s="73" t="str">
+        <x:v>Borrowers</x:v>
+      </x:c>
+      <x:c r="E15" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F15" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G15" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H15" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="60" customHeight="1">
+      <x:c r="A16" s="73" t="str">
+        <x:v>LoanMgr PG Test 20260914</x:v>
+      </x:c>
+      <x:c r="B16" s="73" t="str">
+        <x:v>1.000011</x:v>
+      </x:c>
+      <x:c r="C16" s="73" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="D16" s="73" t="str">
+        <x:v>Loans</x:v>
+      </x:c>
+      <x:c r="E16" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F16" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G16" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H16" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="60" customHeight="1">
+      <x:c r="A17" s="73" t="str">
+        <x:v>LoanMgr PG Test 20260914</x:v>
+      </x:c>
+      <x:c r="B17" s="73" t="str">
+        <x:v>1.000011</x:v>
+      </x:c>
+      <x:c r="C17" s="73" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="D17" s="73" t="str">
+        <x:v>Repayments</x:v>
+      </x:c>
+      <x:c r="E17" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F17" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G17" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H17" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="60" customHeight="1">
+      <x:c r="A18" s="73" t="str">
+        <x:v>LoanMgr PG Test 20260914</x:v>
+      </x:c>
+      <x:c r="B18" s="73" t="str">
+        <x:v>1.000011</x:v>
+      </x:c>
+      <x:c r="C18" s="73" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="D18" s="73" t="str">
+        <x:v>Statistics</x:v>
+      </x:c>
+      <x:c r="E18" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F18" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G18" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H18" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="60" customHeight="1">
+      <x:c r="A19" s="73" t="str">
+        <x:v>LoanMgr PG Test 20260914</x:v>
+      </x:c>
+      <x:c r="B19" s="73" t="str">
+        <x:v>1.000011</x:v>
+      </x:c>
+      <x:c r="C19" s="73" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="D19" s="73" t="str">
+        <x:v>Charges</x:v>
+      </x:c>
+      <x:c r="E19" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F19" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G19" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H19" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="60" customHeight="1">
+      <x:c r="A20" s="73" t="str">
+        <x:v>LoanMgr PG Test 20260914</x:v>
+      </x:c>
+      <x:c r="B20" s="73" t="str">
+        <x:v>1.000011</x:v>
+      </x:c>
+      <x:c r="C20" s="73" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="D20" s="73" t="str">
+        <x:v>Partners</x:v>
+      </x:c>
+      <x:c r="E20" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F20" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G20" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H20" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="60" customHeight="1">
+      <x:c r="A21" s="73" t="str">
+        <x:v>LoanMgr PG Test 20260914</x:v>
+      </x:c>
+      <x:c r="B21" s="73" t="str">
+        <x:v>1.000011</x:v>
+      </x:c>
+      <x:c r="C21" s="73" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="D21" s="73" t="str">
+        <x:v>Payment Allocations</x:v>
+      </x:c>
+      <x:c r="E21" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F21" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G21" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H21" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="60" customHeight="1">
+      <x:c r="A22" s="73" t="str">
+        <x:v>LoanMgr PG Test 20260914</x:v>
+      </x:c>
+      <x:c r="B22" s="73" t="str">
+        <x:v>1.000011</x:v>
+      </x:c>
+      <x:c r="C22" s="73" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="D22" s="73" t="str">
+        <x:v>Payments</x:v>
+      </x:c>
+      <x:c r="E22" s="73" t="str">
+        <x:v>database-3</x:v>
+      </x:c>
+      <x:c r="F22" s="73" t="str">
+        <x:v>appsheet-pg-dev-20260915</x:v>
+      </x:c>
+      <x:c r="G22" s="73" t="str">
+        <x:v>loan_manager_prod</x:v>
+      </x:c>
+      <x:c r="H22" s="73" t="str">
+        <x:v>Development only; source binding verified</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10111,7 +10733,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc4586c9697c4e1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d5a760a9c9f4300"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20768,7 +21390,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aa59a5acf934a39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e6138cd4fac48bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21197,7 +21819,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf71ee72aa27343ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0029ef6058d24aeb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21657,7 +22279,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87f521d7c4d14c3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5199fd1f26984dba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28631,7 +29253,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R333d4218c5024daf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9acf103a4164e71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33250,7 +33872,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4062a1612cd4af7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a86648460894460"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33449,7 +34071,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3ef8edbc23c4505"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe91c8096f154c9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35102,7 +35724,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9eb67ce2c5334b17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83d2ac6408584b89"/>
   </x:tableParts>
 </x:worksheet>
 </file>